--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>100.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>139.2%</t>
+          <t>134.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-614.1%</t>
+          <t>-617.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-106.4%</t>
+          <t>-112.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.1%</t>
+          <t>-322.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-83.7%</t>
+          <t>-87.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>115.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.7%</t>
+          <t>104.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>82.5%</t>
         </is>
       </c>
     </row>
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>2.834009020654386</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.258687543445998</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3729573637146681</v>
+        <v>0.3301775789622385</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.1780292819166325</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769971236256836</v>
+        <v>2.727191451504407</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>2.825295034400908</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.205718021192009</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3854311863627853</v>
+        <v>0.3426514016103557</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.1250597596626437</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793038963355751</v>
+        <v>2.750259178603322</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>2.818334422305814</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.039929825231718</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4447858526518087</v>
+        <v>0.4020060678993791</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.1250597596626437</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786078351260658</v>
+        <v>2.743298566508229</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>2.832796776686958</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.00656661875295</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4725934896244595</v>
+        <v>0.4298137048720299</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.1250597596626437</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800540705641801</v>
+        <v>2.757760920889372</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>2.827328897146153</v>
       </c>
       <c r="D1914" t="n">
         <v>-5.898307481630428</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5104292649326632</v>
+        <v>0.4676494801802336</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.1250597596626437</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795072826100996</v>
+        <v>2.752293041348567</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>2.824826991156729</v>
       </c>
       <c r="D1915" t="n">
         <v>-5.775016346813297</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5572438128700923</v>
+        <v>0.5144640281176627</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.001768624845513156</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866545601001851</v>
+        <v>2.823765816249422</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>2.832527969394055</v>
       </c>
       <c r="D1916" t="n">
         <v>-5.722319479682006</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5860235379599339</v>
+        <v>0.5432437532075043</v>
       </c>
       <c r="F1916" t="n">
         <v>0.05092824228577802</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.905864699517951</v>
+        <v>2.863084914765522</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>2.828308677741105</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.478554037698562</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6793104231003624</v>
+        <v>0.6365306383479328</v>
       </c>
       <c r="F1917" t="n">
         <v>0.05092824228577802</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.901645407865002</v>
+        <v>2.858865623112572</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>2.830432991661121</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.388778365322089</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7173450059709672</v>
+        <v>0.6745652212185376</v>
       </c>
       <c r="F1918" t="n">
         <v>0.112527687200088</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.940729388733604</v>
+        <v>2.897949603981175</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>2.823175066644823</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.138927971373015</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8100272385342993</v>
+        <v>0.7672474537818696</v>
       </c>
       <c r="F1919" t="n">
         <v>0.112527687200088</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.933471463717306</v>
+        <v>2.890691678964877</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>2.826774190165472</v>
       </c>
       <c r="D1920" t="n">
         <v>-4.963035878905583</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8839831990419207</v>
+        <v>0.8412034142894911</v>
       </c>
       <c r="F1920" t="n">
         <v>0.112527687200088</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.937070587237955</v>
+        <v>2.894290802485525</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>2.840101696220026</v>
       </c>
       <c r="D1921" t="n">
         <v>-4.791589415883119</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9658892903054599</v>
+        <v>0.9231095055530303</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2839741502225512</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053265971105986</v>
+        <v>3.010486186353557</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>2.839122173836323</v>
       </c>
       <c r="D1922" t="n">
         <v>-4.711567128773998</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9969186827654051</v>
+        <v>0.9541388980129755</v>
       </c>
       <c r="F1922" t="n">
         <v>0.3639964373316721</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100299820987756</v>
+        <v>3.057520036235327</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>2.84381697489064</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.647931386540064</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.027067780713296</v>
+        <v>0.9842879959608666</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4276321795656067</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.143176067382434</v>
+        <v>3.100396282630004</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>2.825011233674436</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.554234068323669</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.04574096678365</v>
+        <v>1.00296118203122</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4276321795656067</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124370326166229</v>
+        <v>3.0815905414138</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>2.826754310299313</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.564736691388958</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.043282994182412</v>
+        <v>1.000503209429982</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4171295565003178</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119811828951934</v>
+        <v>3.077032044199504</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>2.830683624134133</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.452250430720083</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.092206812284782</v>
+        <v>1.049427027532352</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4171295565003178</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123741142786754</v>
+        <v>3.080961358034324</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>2.831362208051473</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.434536743842218</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.099970870953268</v>
+        <v>1.057191086200838</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4203108853972346</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126328524042244</v>
+        <v>3.083548739289814</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>2.828360279271467</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.311062472529199</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.146358650698469</v>
+        <v>1.103578865946039</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4203108853972346</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123326595262237</v>
+        <v>3.080546810509808</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>2.829939316282081</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.091041674492189</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.235946006923887</v>
+        <v>1.193166222171457</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5615307304652148</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.20963753931364</v>
+        <v>3.16685775456121</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>2.845833499083904</v>
       </c>
       <c r="D1930" t="n">
         <v>-3.958173985428911</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.304987265351021</v>
+        <v>1.262207480598592</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5615307304652148</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225531722115463</v>
+        <v>3.182751937363034</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>2.846979343524206</v>
       </c>
       <c r="D1931" t="n">
         <v>-3.838000902064412</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.354202343137123</v>
+        <v>1.311422558384693</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6817038138297138</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298781416574464</v>
+        <v>3.256001631822035</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>2.857067446085646</v>
       </c>
       <c r="D1932" t="n">
         <v>-3.702747540734435</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.418391790230554</v>
+        <v>1.375612005478124</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8169571751596909</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.390021535933891</v>
+        <v>3.347241751181461</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>2.843104937487072</v>
       </c>
       <c r="D1933" t="n">
         <v>-3.762622368092127</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.380479350688903</v>
+        <v>1.337699565936473</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7570823478019988</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.340134130920701</v>
+        <v>3.297354346168271</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>2.85839410672128</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.64280213718129</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.443696612287446</v>
+        <v>1.400916827535017</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7570823478019988</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355423300154909</v>
+        <v>3.31264351540248</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>2.766038306043722</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.645271843643096</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.350352929025165</v>
+        <v>1.307573144272736</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7546126413401926</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261585675600267</v>
+        <v>3.218805890847838</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>2.685300167529023</v>
       </c>
       <c r="D1936" t="n">
         <v>-3.713642029967105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.242266715980863</v>
+        <v>1.199486931228433</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7638883403764075</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186412956507298</v>
+        <v>3.143633171754868</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.675736876160915</v>
       </c>
       <c r="D1937" t="n">
         <v>-3.825514309593256</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.187954512762294</v>
+        <v>1.145174728009864</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7638883403764075</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176849665139189</v>
+        <v>3.134069880386759</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.855547497605547</v>
+        <v>2.812767712853117</v>
       </c>
       <c r="D1938" t="n">
         <v>-3.881034385485846</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.30277731909746</v>
+        <v>1.259997534345031</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7638883403764075</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313880501831391</v>
+        <v>3.271100717078962</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.860114729597334</v>
+        <v>2.817334944844905</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.705560125693376</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.377534255006236</v>
+        <v>1.334754470253806</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7638883403764075</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.318447733823179</v>
+        <v>3.275667949070749</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.835856758358541</v>
+        <v>2.793076973606112</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.697635751108462</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.356446033601409</v>
+        <v>1.313666248848979</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7638883403764075</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.294189762584386</v>
+        <v>3.251409977831957</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.764395071759991</v>
+        <v>2.721615287007562</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.691357548538613</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.287495628030798</v>
+        <v>1.244715843278368</v>
       </c>
       <c r="F1941" t="n">
         <v>0.7701665429462565</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.226494997527745</v>
+        <v>3.183715212775316</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.774567458192124</v>
+        <v>2.731787673439694</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.63150492933489</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.32160906214442</v>
+        <v>1.27882927739199</v>
       </c>
       <c r="F1942" t="n">
         <v>0.7701665429462565</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.236667383959878</v>
+        <v>3.193887599207448</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.769513728765984</v>
+        <v>2.726733944013554</v>
       </c>
       <c r="D1943" t="n">
         <v>-3.545261466308513</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.351052717928831</v>
+        <v>1.308272933176401</v>
       </c>
       <c r="F1943" t="n">
         <v>0.7701665429462565</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.231613654533738</v>
+        <v>3.188833869781309</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.761289504210509</v>
+        <v>2.71850971945808</v>
       </c>
       <c r="D1944" t="n">
         <v>-3.590568285707493</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.324705765613764</v>
+        <v>1.281925980861335</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7293563799370257</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.198903332172725</v>
+        <v>3.156123547420296</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.761841377243611</v>
+        <v>2.719061592491181</v>
       </c>
       <c r="D1945" t="n">
         <v>-3.619601390409794</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.313644396765945</v>
+        <v>1.270864612013516</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7293563799370257</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.199455205205827</v>
+        <v>3.156675420453397</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.691114069134977</v>
+        <v>2.648334284382547</v>
       </c>
       <c r="D1946" t="n">
         <v>-3.526790908958935</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.280041281237655</v>
+        <v>1.237261496485225</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8221668613878851</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.184414185967708</v>
+        <v>3.141634401215279</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.692987545059577</v>
+        <v>2.650207760307148</v>
       </c>
       <c r="D1947" t="n">
         <v>-3.571180378288362</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.264158969430484</v>
+        <v>1.221379184678055</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7777773920584574</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159653980294652</v>
+        <v>3.116874195542223</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.6880632535713</v>
+        <v>2.645283468818871</v>
       </c>
       <c r="D1948" t="n">
         <v>-3.550676684402865</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.267436155496406</v>
+        <v>1.224656370743977</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7982810859439547</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.167031905137673</v>
+        <v>3.124252120385244</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.693554549401968</v>
+        <v>2.650774764649538</v>
       </c>
       <c r="D1949" t="n">
         <v>-3.590600778985437</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.256957813494045</v>
+        <v>1.214178028741615</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.172523200968341</v>
+        <v>3.129743416215911</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.705051751170507</v>
+        <v>2.662271966418077</v>
       </c>
       <c r="D1950" t="n">
         <v>-3.61838117688679</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.257342856102043</v>
+        <v>1.214563071349613</v>
       </c>
       <c r="F1950" t="n">
         <v>0.7705006880426017</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.167352163996068</v>
+        <v>3.124572379243638</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.54340747117116</v>
+        <v>2.50062768641873</v>
       </c>
       <c r="D1951" t="n">
         <v>-3.736761849616929</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.04834630701064</v>
+        <v>1.005566522258211</v>
       </c>
       <c r="F1951" t="n">
         <v>0.7032828358916255</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.965377172706136</v>
+        <v>2.922597387953706</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.663557131890366</v>
+        <v>2.620777347137936</v>
       </c>
       <c r="D1952" t="n">
         <v>-3.84537592806026</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.125050336352514</v>
+        <v>1.082270551600084</v>
       </c>
       <c r="F1952" t="n">
         <v>0.7032828358916255</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.085526833425341</v>
+        <v>3.042747048672912</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.678070157992689</v>
+        <v>2.635290373240259</v>
       </c>
       <c r="D1953" t="n">
         <v>-3.809966889812117</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.153726977754094</v>
+        <v>1.110947193001664</v>
       </c>
       <c r="F1953" t="n">
         <v>0.7032828358916255</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.100039859527664</v>
+        <v>3.057260074775235</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.675489599335057</v>
+        <v>2.632709814582628</v>
       </c>
       <c r="D1954" t="n">
         <v>-3.771583227253966</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.166499884119723</v>
+        <v>1.123720099367293</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7416664984497767</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.120489498404924</v>
+        <v>3.077709713652494</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.672218628180359</v>
+        <v>2.62943884342793</v>
       </c>
       <c r="D1955" t="n">
         <v>-3.5944668972188</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.234075444979091</v>
+        <v>1.191295660226662</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7416664984497767</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.117218527250226</v>
+        <v>3.074438742497796</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.672902019942272</v>
+        <v>2.630122235189843</v>
       </c>
       <c r="D1956" t="n">
         <v>-3.639559142052345</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.216721938807586</v>
+        <v>1.173942154055157</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6797704552803869</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.080764293110505</v>
+        <v>3.037984508358075</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.666688995248687</v>
+        <v>2.623909210496257</v>
       </c>
       <c r="D1957" t="n">
         <v>-3.460183720813578</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.282259082609508</v>
+        <v>1.239479297857078</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8365472134511056</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.16861732331935</v>
+        <v>3.125837538566921</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.647496450580276</v>
+        <v>2.604716665827847</v>
       </c>
       <c r="D1958" t="n">
         <v>-3.505197934334184</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.245060852532855</v>
+        <v>1.202281067780425</v>
       </c>
       <c r="F1958" t="n">
         <v>0.806198318136501</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.131215441462177</v>
+        <v>3.088435656709748</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.653188012919222</v>
+        <v>2.610408228166793</v>
       </c>
       <c r="D1959" t="n">
         <v>-3.772202444606619</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.143950610762827</v>
+        <v>1.101170826010397</v>
       </c>
       <c r="F1959" t="n">
         <v>0.6118352800935525</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.020289180975354</v>
+        <v>2.977509396222924</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.652391934815724</v>
+        <v>2.609612150063294</v>
       </c>
       <c r="D1960" t="n">
         <v>-3.873400226043792</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.102675420084459</v>
+        <v>1.059895635332029</v>
       </c>
       <c r="F1960" t="n">
         <v>0.5434264665482333</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.978447814744664</v>
+        <v>2.935668029992234</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.64999189637004</v>
+        <v>2.607212111617611</v>
       </c>
       <c r="D1961" t="n">
         <v>-3.866889259429479</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.102879768284501</v>
+        <v>1.060099983532071</v>
       </c>
       <c r="F1961" t="n">
         <v>0.5434264665482333</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.976047776298981</v>
+        <v>2.933267991546551</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.646516615578285</v>
+        <v>2.603736830825856</v>
       </c>
       <c r="D1962" t="n">
         <v>-3.847851131722182</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.107019738575665</v>
+        <v>1.064239953823235</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4852428552170388</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.937662328708509</v>
+        <v>2.894882543956079</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.765811017212476</v>
+        <v>2.723031232460046</v>
       </c>
       <c r="D1963" t="n">
         <v>-3.900366933997002</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.205307819299927</v>
+        <v>1.162528034547497</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4852428552170388</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.056956730342699</v>
+        <v>3.01417694559027</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.766644346198609</v>
+        <v>2.72386456144618</v>
       </c>
       <c r="D1964" t="n">
         <v>-3.903775245431582</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.204777823712229</v>
+        <v>1.161998038959799</v>
       </c>
       <c r="F1964" t="n">
         <v>0.5177594242264162</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.077300000734459</v>
+        <v>3.03452021598203</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.772652876595535</v>
+        <v>2.729873091843106</v>
       </c>
       <c r="D1965" t="n">
         <v>-3.884419109537735</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.218528808466693</v>
+        <v>1.175749023714264</v>
       </c>
       <c r="F1965" t="n">
         <v>0.5177594242264162</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.083308531131385</v>
+        <v>3.040528746378956</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.670603097872735</v>
+        <v>2.627823313120305</v>
       </c>
       <c r="D1966" t="n">
         <v>-3.736676139302733</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.175576217837894</v>
+        <v>1.132796433085464</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6855667814612993</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.081943166749515</v>
+        <v>3.039163381997085</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.673396719404216</v>
+        <v>2.630616934651786</v>
       </c>
       <c r="D1967" t="n">
         <v>-3.820497360577431</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.144841350859495</v>
+        <v>1.102061566107066</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6855667814612993</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.084736788280996</v>
+        <v>3.041957003528566</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.674059067795874</v>
+        <v>2.631279283043444</v>
       </c>
       <c r="D1968" t="n">
         <v>-3.814344654524646</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.147964781672268</v>
+        <v>1.105184996919838</v>
       </c>
       <c r="F1968" t="n">
         <v>0.6917194875140836</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.089090760304325</v>
+        <v>3.046310975551895</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.673139544535984</v>
+        <v>2.630359759783555</v>
       </c>
       <c r="D1969" t="n">
         <v>-3.831153952675148</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.140321539152177</v>
+        <v>1.097541754399748</v>
       </c>
       <c r="F1969" t="n">
         <v>0.674910189363582</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.078085658154134</v>
+        <v>3.035305873401704</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.739475098332805</v>
+        <v>2.696695313580376</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.768855953899026</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.231576292459447</v>
+        <v>1.188796507707017</v>
       </c>
       <c r="F1970" t="n">
         <v>0.7202044536380241</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.17159777051562</v>
+        <v>3.12881798576319</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.541767100046932</v>
+        <v>2.498987315294503</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.567065756233868</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.114584373239637</v>
+        <v>1.071804588487207</v>
       </c>
       <c r="F1971" t="n">
         <v>0.9182226458071785</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.09270068753124</v>
+        <v>3.04992090277881</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.612057332369107</v>
+        <v>2.569277547616678</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.617952468920063</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.164519920487334</v>
+        <v>1.121740135734905</v>
       </c>
       <c r="F1972" t="n">
         <v>0.867335933120984</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.132458892241698</v>
+        <v>3.089679107489268</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.626685068485151</v>
+        <v>2.583905283732721</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.531341726270255</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.213791953663301</v>
+        <v>1.171012168910871</v>
       </c>
       <c r="F1973" t="n">
         <v>0.9459616643261423</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.194262067080837</v>
+        <v>3.151482282328407</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.625221049309823</v>
+        <v>2.582441264557393</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.59155102427554</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.188244215285859</v>
+        <v>1.145464430533429</v>
       </c>
       <c r="F1974" t="n">
         <v>0.8857523663208577</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.156672469102338</v>
+        <v>3.113892684349908</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.623712667349751</v>
+        <v>2.580932882597322</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.542364375591188</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.206410492799528</v>
+        <v>1.163630708047098</v>
       </c>
       <c r="F1975" t="n">
         <v>0.8857523663208577</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.155164087142266</v>
+        <v>3.112384302389836</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.623575534785187</v>
+        <v>2.580795750032758</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.49799124395262</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.224022612890391</v>
+        <v>1.181242828137962</v>
       </c>
       <c r="F1976" t="n">
         <v>0.9301254979594263</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.181650833560844</v>
+        <v>3.138871048808414</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.617969328923778</v>
+        <v>2.575189544171348</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.520471594811505</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.209424266685428</v>
+        <v>1.166644481932999</v>
       </c>
       <c r="F1977" t="n">
         <v>0.9301254979594263</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.176044627699434</v>
+        <v>3.133264842947004</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.624351085951583</v>
+        <v>2.581571301199153</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.472815864250449</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.234868315937655</v>
+        <v>1.192088531185226</v>
       </c>
       <c r="F1978" t="n">
         <v>0.977781228520482</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.211019823063872</v>
+        <v>3.168240038311442</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.629243459326307</v>
+        <v>2.586463674573878</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.372297705751694</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.279967952711882</v>
+        <v>1.237188167959452</v>
       </c>
       <c r="F1979" t="n">
         <v>1.078299387019237</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.27622309153785</v>
+        <v>3.23344330678542</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61599813180218</v>
+        <v>2.57321834704975</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.356392376319342</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.273084756960695</v>
+        <v>1.230304972208266</v>
       </c>
       <c r="F1980" t="n">
         <v>0.9991867263099976</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.215510167588179</v>
+        <v>3.172730382835749</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.620095834412808</v>
+        <v>2.577316049660379</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.311553974710943</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.295117820214683</v>
+        <v>1.252338035462253</v>
       </c>
       <c r="F1981" t="n">
         <v>1.003730159254867</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.222333929965729</v>
+        <v>3.179554145213299</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.624256774043886</v>
+        <v>2.581476989291457</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.331052430952952</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.291479377348958</v>
+        <v>1.248699592596528</v>
       </c>
       <c r="F1982" t="n">
         <v>0.9556455179749628</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.197644084828864</v>
+        <v>3.154864300076435</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.630136376571723</v>
+        <v>2.587356591819294</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.286849593867051</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.315040114711155</v>
+        <v>1.272260329958725</v>
       </c>
       <c r="F1983" t="n">
         <v>0.9998483550608632</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.230045389608242</v>
+        <v>3.187265604855812</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.628546377040971</v>
+        <v>2.585766592288541</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.294409259704098</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.310426248845584</v>
+        <v>1.267646464093154</v>
       </c>
       <c r="F1984" t="n">
         <v>1.054651759070683</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.261337432483381</v>
+        <v>3.218557647730951</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.679794142224011</v>
+        <v>2.637014357471581</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.136117842164826</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.424990581044332</v>
+        <v>1.382210796291903</v>
       </c>
       <c r="F1985" t="n">
         <v>1.054651759070683</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.31258519766642</v>
+        <v>3.269805412913991</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.678234846818264</v>
+        <v>2.635455062065834</v>
       </c>
       <c r="D1986" t="n">
         <v>-2.92847583853035</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.506488087092376</v>
+        <v>1.463708302339946</v>
       </c>
       <c r="F1986" t="n">
         <v>1.262293762705159</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.435611104441359</v>
+        <v>3.39283131968893</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.673183075056534</v>
+        <v>2.630403290304104</v>
       </c>
       <c r="D1987" t="n">
         <v>-2.877443745807822</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.521849152419657</v>
+        <v>1.479069367667228</v>
       </c>
       <c r="F1987" t="n">
         <v>1.313325855427687</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.461178588313146</v>
+        <v>3.418398803560716</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.690370479149239</v>
+        <v>2.647590694396809</v>
       </c>
       <c r="D1988" t="n">
         <v>-2.812219564680616</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.565126228963244</v>
+        <v>1.522346444210815</v>
       </c>
       <c r="F1988" t="n">
         <v>1.378550036554892</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.517500501082174</v>
+        <v>3.474720716329745</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.686331451448519</v>
+        <v>2.643551666696089</v>
       </c>
       <c r="D1989" t="n">
         <v>-2.774792544609482</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.576058009290978</v>
+        <v>1.533278224538549</v>
       </c>
       <c r="F1989" t="n">
         <v>1.383801574584074</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.516612396198964</v>
+        <v>3.473832611446534</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.687588243779759</v>
+        <v>2.64480845902733</v>
       </c>
       <c r="D1990" t="n">
         <v>-2.79490420064419</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.569270139208335</v>
+        <v>1.526490354455906</v>
       </c>
       <c r="F1990" t="n">
         <v>1.394828919581493</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.524485595528656</v>
+        <v>3.481705810776226</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.84814601480097</v>
+        <v>2.80536623004854</v>
       </c>
       <c r="D1991" t="n">
         <v>-2.766490937544307</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.741193215469499</v>
+        <v>1.69841343071707</v>
       </c>
       <c r="F1991" t="n">
         <v>1.335853356835065</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.649658028902009</v>
+        <v>3.60687824414958</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.968258924018787</v>
+        <v>2.925479139266358</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.691708676519294</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.891219029097322</v>
+        <v>1.848439244344892</v>
       </c>
       <c r="F1992" t="n">
         <v>1.410635617860077</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.814640294734834</v>
+        <v>3.771860509982404</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.959966900032646</v>
+        <v>2.917187115280217</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.665624592255486</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.893360638816704</v>
+        <v>1.850580854064274</v>
       </c>
       <c r="F1993" t="n">
         <v>1.410635617860077</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.806348270748693</v>
+        <v>3.763568485996263</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.958160095616426</v>
+        <v>2.915380310863996</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.577746679146366</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.926704999644132</v>
+        <v>1.883925214891702</v>
       </c>
       <c r="F1994" t="n">
         <v>1.526561260283428</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.874096851786483</v>
+        <v>3.831317067034053</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.975714501343217</v>
+        <v>2.932934716590788</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.568854217753082</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.947816389928236</v>
+        <v>1.905036605175807</v>
       </c>
       <c r="F1995" t="n">
         <v>1.526561260283428</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.891651257513274</v>
+        <v>3.848871472760845</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.967569548747801</v>
+        <v>2.924789763995371</v>
       </c>
       <c r="D1996" t="n">
         <v>-2.73733033472296</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.872280990544869</v>
+        <v>1.82950120579244</v>
       </c>
       <c r="F1996" t="n">
         <v>1.498613424566847</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.86673760348791</v>
+        <v>3.82395781873548</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.948839245935663</v>
+        <v>2.906059461183233</v>
       </c>
       <c r="D1997" t="n">
         <v>-2.29107414209352</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.032053164784507</v>
+        <v>1.989273380032077</v>
       </c>
       <c r="F1997" t="n">
         <v>1.403894754897215</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.791176098873992</v>
+        <v>3.748396314121562</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.939503268432567</v>
+        <v>2.896723483680138</v>
       </c>
       <c r="D1998" t="n">
         <v>-2.268353038410368</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.031805628754673</v>
+        <v>1.989025844002243</v>
       </c>
       <c r="F1998" t="n">
         <v>1.403894754897215</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.781840121370896</v>
+        <v>3.739060336618467</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.098409394283737</v>
+        <v>3.055629609531307</v>
       </c>
       <c r="D1999" t="n">
         <v>-2.39755485170441</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.139031029288224</v>
+        <v>2.096251244535795</v>
       </c>
       <c r="F1999" t="n">
         <v>1.274692941603172</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.86322515924564</v>
+        <v>3.820445374493211</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.135487216777383</v>
+        <v>3.092707432024953</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.423429250178436</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.165759092392261</v>
+        <v>2.122979307639831</v>
       </c>
       <c r="F2000" t="n">
         <v>1.319604550314914</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.927249946966332</v>
+        <v>3.884470162213902</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.132162572766928</v>
+        <v>3.089382788014499</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.416374559963262</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.165256324467876</v>
+        <v>2.122476539715446</v>
       </c>
       <c r="F2001" t="n">
         <v>1.326659240530087</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.928158117084981</v>
+        <v>3.885378332332551</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.14216872641167</v>
+        <v>3.09938894165924</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.389423335636774</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.186042967843212</v>
+        <v>2.143263183090783</v>
       </c>
       <c r="F2002" t="n">
         <v>1.341539586557807</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.947092478346354</v>
+        <v>3.904312693593925</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32627185855663</v>
+        <v>3.2834920738042</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.410967563467561</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.361528408855857</v>
+        <v>2.318748624103427</v>
       </c>
       <c r="F2003" t="n">
         <v>1.341539586557807</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.131195610491313</v>
+        <v>4.088415825738884</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.318388553459623</v>
+        <v>3.275608768707193</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.433375681272433</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.344681856636901</v>
+        <v>2.301902071884472</v>
       </c>
       <c r="F2004" t="n">
         <v>1.341539586557807</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.123312305394307</v>
+        <v>4.080532520641877</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.32044255300926</v>
+        <v>3.27766276825683</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.461599916850034</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.335446161955498</v>
+        <v>2.292666377203069</v>
       </c>
       <c r="F2005" t="n">
         <v>1.359516339009115</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.13615235641473</v>
+        <v>4.0933725716623</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.376696270731107</v>
+        <v>3.333916485978678</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.471040842738564</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.387923509321934</v>
+        <v>2.345143724569504</v>
       </c>
       <c r="F2006" t="n">
         <v>1.481943456552507</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.265862344662612</v>
+        <v>4.223082559910182</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.379587365276408</v>
+        <v>3.336807580523979</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.559917473907038</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.355263951399845</v>
+        <v>2.312484166647415</v>
       </c>
       <c r="F2007" t="n">
         <v>1.393066825384033</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.215427460506828</v>
+        <v>4.172647675754399</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.377699178170183</v>
+        <v>3.334919393417754</v>
       </c>
       <c r="D2008" t="n">
         <v>-2.636247451507943</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.322843773253258</v>
+        <v>2.280063988500828</v>
       </c>
       <c r="F2008" t="n">
         <v>1.393066825384033</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.213539273400603</v>
+        <v>4.170759488648174</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.372519407773046</v>
+        <v>3.329739623020616</v>
       </c>
       <c r="D2009" t="n">
         <v>-2.729911396185485</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.280198424985104</v>
+        <v>2.237418640232674</v>
       </c>
       <c r="F2009" t="n">
         <v>1.299402880706491</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.15216113619694</v>
+        <v>4.109381351444511</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.370953417983198</v>
+        <v>3.328173633230768</v>
       </c>
       <c r="D2010" t="n">
         <v>-2.89147982171274</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.214005064984354</v>
+        <v>2.171225280231925</v>
       </c>
       <c r="F2010" t="n">
         <v>1.172619956908612</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.074525392128366</v>
+        <v>4.031745607375936</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.384026824849117</v>
+        <v>3.341247040096687</v>
       </c>
       <c r="D2011" t="n">
         <v>-2.999780483582859</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.183758207102225</v>
+        <v>2.140978422349795</v>
       </c>
       <c r="F2011" t="n">
         <v>1.172619956908612</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.087598798994284</v>
+        <v>4.044819014241854</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.376032021632057</v>
+        <v>3.333252236879627</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.017584455303604</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.168641815196867</v>
+        <v>2.125862030444438</v>
       </c>
       <c r="F2012" t="n">
         <v>1.102085334003411</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.037283222034104</v>
+        <v>3.994503437281674</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.374556062759059</v>
+        <v>3.331776278006629</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.045485242413076</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.15600554148008</v>
+        <v>2.11322575672765</v>
       </c>
       <c r="F2013" t="n">
         <v>1.067488409860476</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.015049108675345</v>
+        <v>3.972269323922915</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.371320506736257</v>
+        <v>3.328540721983828</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.16801134511597</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.103759544376121</v>
+        <v>2.060979759623692</v>
       </c>
       <c r="F2014" t="n">
         <v>0.9449623071575823</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.938297891030807</v>
+        <v>3.895518106278377</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.438026466326761</v>
+        <v>3.395246681574331</v>
       </c>
       <c r="D2015" t="n">
         <v>-3.398525841301559</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.078259705492389</v>
+        <v>2.035479920739959</v>
       </c>
       <c r="F2015" t="n">
         <v>0.7144478109719936</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.866695152909958</v>
+        <v>3.823915368157528</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.578338185328608</v>
+        <v>3.535558400576178</v>
       </c>
       <c r="D2016" t="n">
         <v>-3.747270926526003</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.079073390404459</v>
+        <v>2.03629360565203</v>
       </c>
       <c r="F2016" t="n">
         <v>0.6056998570530958</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.941758099560466</v>
+        <v>3.898978314808036</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.647318454474248</v>
+        <v>3.604538669721818</v>
       </c>
       <c r="D2017" t="n">
         <v>-3.901257344302143</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.086459092439642</v>
+        <v>2.043679307687213</v>
       </c>
       <c r="F2017" t="n">
         <v>0.6056998570530958</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.010738368706106</v>
+        <v>3.967958583953676</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.633369656594369</v>
+        <v>3.590589871841939</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.105856779165152</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.99067052061456</v>
+        <v>1.94789073586213</v>
       </c>
       <c r="F2018" t="n">
         <v>0.6056998570530958</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.996789570826227</v>
+        <v>3.954009786073797</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.645240145649783</v>
+        <v>3.602460360897353</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.358331933172876</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.901550948066884</v>
+        <v>1.858771163314455</v>
       </c>
       <c r="F2019" t="n">
         <v>0.6056998570530958</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.008660059881641</v>
+        <v>3.965880275129211</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.646450680168726</v>
+        <v>3.603670895416297</v>
       </c>
       <c r="D2020" t="n">
         <v>-4.651227689652289</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.785603179994063</v>
+        <v>1.742823395241633</v>
       </c>
       <c r="F2020" t="n">
         <v>0.6056998570530958</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.009870594400584</v>
+        <v>3.967090809648155</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.650572422396048</v>
+        <v>3.607792637643618</v>
       </c>
       <c r="D2021" t="n">
         <v>-4.837891817787097</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715059270967461</v>
+        <v>1.672279486215032</v>
       </c>
       <c r="F2021" t="n">
         <v>0.5789608862285359</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.99794895413317</v>
+        <v>3.95516916938074</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.645650275132237</v>
+        <v>3.602870490379808</v>
       </c>
       <c r="D2022" t="n">
         <v>-4.983912504701059</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.651728848938066</v>
+        <v>1.608949064185636</v>
       </c>
       <c r="F2022" t="n">
         <v>0.5698777944346789</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.987576951793045</v>
+        <v>3.944797167040615</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.807854331831281</v>
+        <v>3.765074547078852</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.075626513810644</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777247301993276</v>
+        <v>1.734467517240847</v>
       </c>
       <c r="F2023" t="n">
         <v>0.5698777944346789</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.149781008492089</v>
+        <v>4.107001223739659</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.802700969795096</v>
+        <v>3.759921185042666</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.107278172870613</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.759433276333102</v>
+        <v>1.716653491580673</v>
       </c>
       <c r="F2024" t="n">
         <v>0.5647093371902387</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.141526572109239</v>
+        <v>4.098746787356809</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.812930387363587</v>
+        <v>3.770150602611157</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.189212991139496</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.73688876659404</v>
+        <v>1.694108981841611</v>
       </c>
       <c r="F2025" t="n">
         <v>0.5547745916031586</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.145795142325482</v>
+        <v>4.103015357573052</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.821856025819489</v>
+        <v>3.77907624106706</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.291189113387904</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.70502395615058</v>
+        <v>1.66224417139815</v>
       </c>
       <c r="F2026" t="n">
         <v>0.452798469354751</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.09353510743234</v>
+        <v>4.05075532267991</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.814008913063665</v>
+        <v>3.771229128311235</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.181182829910682</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741179356785644</v>
+        <v>1.698399572033214</v>
       </c>
       <c r="F2027" t="n">
         <v>0.4760030412720262</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.099610737826881</v>
+        <v>4.056830953074451</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.818258923785639</v>
+        <v>3.775479139033209</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.038123254169756</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.802653197803989</v>
+        <v>1.759873413051559</v>
       </c>
       <c r="F2028" t="n">
         <v>0.4840164678620055</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.108668804502843</v>
+        <v>4.065889019750413</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.782740021915745</v>
       </c>
       <c r="D2029" t="n">
         <v>-4.736676528697918</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.93049277087526</v>
+        <v>1.88771298612283</v>
       </c>
       <c r="F2029" t="n">
         <v>0.7854631933338427</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.29679772266848</v>
+        <v>4.254017937916051</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.783711199668456</v>
       </c>
       <c r="D2030" t="n">
         <v>-4.761266772933102</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.921627850933897</v>
+        <v>1.878848066181467</v>
       </c>
       <c r="F2030" t="n">
         <v>0.7854631933338427</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.297768900421191</v>
+        <v>4.254989115668762</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.784554104048211</v>
       </c>
       <c r="D2031" t="n">
         <v>-4.710228396926582</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.94288610571626</v>
+        <v>1.90010632096383</v>
       </c>
       <c r="F2031" t="n">
         <v>0.7854631933338427</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.298611804800947</v>
+        <v>4.255832020048517</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.803592202922357</v>
       </c>
       <c r="D2032" t="n">
         <v>-4.669089102059951</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.978379922537058</v>
+        <v>1.935600137784628</v>
       </c>
       <c r="F2032" t="n">
         <v>0.8266024882004736</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.34233348059507</v>
+        <v>4.299553695842641</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.619776199046291</v>
       </c>
       <c r="D2033" t="n">
         <v>-4.572454190041311</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833217883468448</v>
+        <v>1.790438098716019</v>
       </c>
       <c r="F2033" t="n">
         <v>0.9232374002191135</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.216498423930189</v>
+        <v>4.17371863917776</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.623278243120255</v>
       </c>
       <c r="D2034" t="n">
         <v>-4.703034924572154</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.784487633730076</v>
+        <v>1.741707848977646</v>
       </c>
       <c r="F2034" t="n">
         <v>0.792656665688271</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.141652027285648</v>
+        <v>4.098872242533218</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.607705062196338</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.538538590381192</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.834712986482543</v>
+        <v>1.791933201730113</v>
       </c>
       <c r="F2035" t="n">
         <v>0.9571529998792329</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.224776646876307</v>
+        <v>4.181996862123878</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.606892772632768</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.461439988839319</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.864740137535722</v>
+        <v>1.821960352783292</v>
       </c>
       <c r="F2036" t="n">
         <v>0.9571529998792329</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.223964357312737</v>
+        <v>4.181184572560308</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.61676155175784</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.471825183729209</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.870454838704838</v>
+        <v>1.827675053952409</v>
       </c>
       <c r="F2037" t="n">
         <v>0.9467678049893435</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.227602019503876</v>
+        <v>4.184822234751446</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.687598557534265</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.490413342451434</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.933856580992374</v>
+        <v>1.891076796239944</v>
       </c>
       <c r="F2038" t="n">
         <v>0.9281796462671181</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.287286130046966</v>
+        <v>4.244506345294536</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.684467568352564</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.49071188914747</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.930606173132258</v>
+        <v>1.887826388379828</v>
       </c>
       <c r="F2039" t="n">
         <v>0.9278810995710822</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.283976012847643</v>
+        <v>4.241196228095213</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.688998463291955</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.389888755457042</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.97546632154782</v>
+        <v>1.932686536795391</v>
       </c>
       <c r="F2040" t="n">
         <v>0.9403453150554361</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.295985437077647</v>
+        <v>4.253205652325217</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.689127716770499</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.199107394704635</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.051908119327326</v>
+        <v>2.009128334574897</v>
       </c>
       <c r="F2041" t="n">
         <v>1.131126675807844</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.410583507007635</v>
+        <v>4.367803722255205</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.668964562508095</v>
       </c>
       <c r="D2042" t="n">
         <v>-4.092144036855213</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.074530308204691</v>
+        <v>2.031750523452262</v>
       </c>
       <c r="F2042" t="n">
         <v>1.189591283767645</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.425499117521112</v>
+        <v>4.382719332768683</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.703931499120154</v>
       </c>
       <c r="D2043" t="n">
         <v>-4.036813448953451</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.131629479977455</v>
+        <v>2.088849695225025</v>
       </c>
       <c r="F2043" t="n">
         <v>1.244921871669407</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.493664406874228</v>
+        <v>4.450884622121798</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.697618067021591</v>
       </c>
       <c r="D2044" t="n">
         <v>-4.024759322040488</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.130137698644078</v>
+        <v>2.087357913891648</v>
       </c>
       <c r="F2044" t="n">
         <v>1.25697599858237</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.494583450923443</v>
+        <v>4.451803666171013</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.699498697205727</v>
       </c>
       <c r="D2045" t="n">
         <v>-4.065914441608709</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.115556281000925</v>
+        <v>2.072776496248496</v>
       </c>
       <c r="F2045" t="n">
         <v>1.215820879014149</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.471771009366647</v>
+        <v>4.428991224614217</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.71234972308361</v>
       </c>
       <c r="D2046" t="n">
         <v>-3.997865878917179</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.15562673195542</v>
+        <v>2.11284694720299</v>
       </c>
       <c r="F2046" t="n">
         <v>1.283869441705679</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.525451172859447</v>
+        <v>4.482671388107017</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.732552393257204</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.22946627208668</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.083189244861213</v>
+        <v>2.040409460108784</v>
       </c>
       <c r="F2047" t="n">
         <v>1.283869441705679</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.545653843033041</v>
+        <v>4.502874058280612</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.758938414076515</v>
+        <v>3.716158629324086</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.279517817615899</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.046774862716408</v>
+        <v>2.003995077963978</v>
       </c>
       <c r="F2048" t="n">
         <v>1.283869441705679</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.529260079099923</v>
+        <v>4.486480294347493</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.719190327669982</v>
+        <v>3.676410542917552</v>
       </c>
       <c r="D2049" t="n">
         <v>-4.454624650192343</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.936984043279296</v>
+        <v>1.894204258526867</v>
       </c>
       <c r="F2049" t="n">
         <v>1.283869441705679</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.48951199269339</v>
+        <v>4.44673220794096</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.726212946666922</v>
+        <v>3.683433161914492</v>
       </c>
       <c r="D2050" t="n">
         <v>-4.258524496761821</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.022446723648446</v>
+        <v>1.979666938896016</v>
       </c>
       <c r="F2050" t="n">
         <v>1.479969595136202</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.614194703748644</v>
+        <v>4.571414918996214</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.825383946239826</v>
+        <v>3.782604161487397</v>
       </c>
       <c r="D2051" t="n">
         <v>-4.105499104648536</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.182827880066664</v>
+        <v>2.140048095314234</v>
       </c>
       <c r="F2051" t="n">
         <v>1.632994987249486</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.805180938589518</v>
+        <v>4.762401153837089</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.012850171148119</v>
+        <v>3.970070386395689</v>
       </c>
       <c r="D2052" t="n">
         <v>-4.133806418521806</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.358971179425648</v>
+        <v>2.316191394673219</v>
       </c>
       <c r="F2052" t="n">
         <v>1.632994987249486</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.992647163497811</v>
+        <v>4.949867378745381</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.982253122502201</v>
+        <v>3.939473337749772</v>
       </c>
       <c r="D2053" t="n">
         <v>-4.300399643635329</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.261736840734322</v>
+        <v>2.218957055981893</v>
       </c>
       <c r="F2053" t="n">
         <v>1.466401762135963</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.86209417978378</v>
+        <v>4.81931439503135</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.985929525163919</v>
+        <v>3.943149740411489</v>
       </c>
       <c r="D2054" t="n">
         <v>-4.277363850273763</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.274627560740666</v>
+        <v>2.231847775988236</v>
       </c>
       <c r="F2054" t="n">
         <v>1.466401762135963</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.865770582445498</v>
+        <v>4.822990797693068</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.983547580287414</v>
+        <v>3.940767795534985</v>
       </c>
       <c r="D2055" t="n">
         <v>-4.248117869818066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.28394400804644</v>
+        <v>2.24116422329401</v>
       </c>
       <c r="F2055" t="n">
         <v>1.466401762135963</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.863388637568993</v>
+        <v>4.820608852816563</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.980840819445049</v>
+        <v>3.93806103469262</v>
       </c>
       <c r="D2056" t="n">
         <v>-4.355043417695917</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.238467028052934</v>
+        <v>2.195687243300505</v>
       </c>
       <c r="F2056" t="n">
         <v>1.359476214258112</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.796526547999917</v>
+        <v>4.753746763247487</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.982269621588284</v>
+        <v>3.939489836835854</v>
       </c>
       <c r="D2057" t="n">
         <v>-4.500061976203166</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.181888406793269</v>
+        <v>2.13910862204084</v>
       </c>
       <c r="F2057" t="n">
         <v>1.214457655750864</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.710944215038802</v>
+        <v>4.668164430286373</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.082200860846037</v>
+        <v>4.039421076093607</v>
       </c>
       <c r="D2058" t="n">
         <v>-4.618403741987883</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.234482939737135</v>
+        <v>2.191703154984705</v>
       </c>
       <c r="F2058" t="n">
         <v>1.225143694313754</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.817287077434289</v>
+        <v>4.774507292681859</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.079986557971975</v>
+        <v>4.037206773219546</v>
       </c>
       <c r="D2059" t="n">
         <v>-4.669814164308591</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.211704467934791</v>
+        <v>2.168924683182361</v>
       </c>
       <c r="F2059" t="n">
         <v>1.225143694313754</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.815072774560227</v>
+        <v>4.772292989807798</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.079889686046265</v>
+        <v>4.037109901293835</v>
       </c>
       <c r="D2060" t="n">
         <v>-4.749233615516343</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.179839815525979</v>
+        <v>2.13706003077355</v>
       </c>
       <c r="F2060" t="n">
         <v>1.225143694313754</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.814975902634517</v>
+        <v>4.772196117882087</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.7368049522984</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.079883579604308</v>
+        <v>4.037103794851879</v>
       </c>
       <c r="D2061" t="n">
         <v>-4.844696613433561</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.141648509917136</v>
+        <v>2.098868725164706</v>
       </c>
       <c r="F2061" t="n">
         <v>1.225143694313754</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.81496979619256</v>
+        <v>4.772190011440131</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.077979976166919</v>
+        <v>4.035200191414489</v>
       </c>
       <c r="D2062" t="n">
         <v>-4.780320702582846</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.165495270820033</v>
+        <v>2.122715486067603</v>
       </c>
       <c r="F2062" t="n">
         <v>1.289519605164469</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.8516917392656</v>
+        <v>4.808911954513171</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.083713793914646</v>
+        <v>4.040934009162216</v>
       </c>
       <c r="D2063" t="n">
         <v>-4.835689864715039</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.149081423714882</v>
+        <v>2.106301638962452</v>
       </c>
       <c r="F2063" t="n">
         <v>1.289519605164469</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.857425557013327</v>
+        <v>4.814645772260898</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.083252157257578</v>
+        <v>4.040472372505148</v>
       </c>
       <c r="D2064" t="n">
         <v>-4.881127644545867</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.130444675125483</v>
+        <v>2.087664890373053</v>
       </c>
       <c r="F2064" t="n">
         <v>1.246674614486309</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.831256925949363</v>
+        <v>4.788477141196934</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113691</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.103126550107897</v>
+        <v>4.060346765355467</v>
       </c>
       <c r="D2065" t="n">
         <v>-4.792920810398289</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.185601801634833</v>
+        <v>2.142822016882404</v>
       </c>
       <c r="F2065" t="n">
         <v>1.246674614486309</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.851131318799682</v>
+        <v>4.808351534047253</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.086827250632624</v>
+        <v>4.044047465880195</v>
       </c>
       <c r="D2066" t="n">
         <v>-4.686885815192979</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.211716500241685</v>
+        <v>2.168936715489255</v>
       </c>
       <c r="F2066" t="n">
         <v>1.246674614486309</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.83483201932441</v>
+        <v>4.79205223457198</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.08925820009667</v>
+        <v>4.04647841534424</v>
       </c>
       <c r="D2067" t="n">
         <v>-4.503674152059884</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.287432114958968</v>
+        <v>2.244652330206539</v>
       </c>
       <c r="F2067" t="n">
         <v>1.246674614486309</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.837262968788456</v>
+        <v>4.794483184036026</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>4.01226960119213</v>
       </c>
       <c r="D2068" t="n">
         <v>-4.431952705046033</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.281911879612398</v>
+        <v>2.239132094859968</v>
       </c>
       <c r="F2068" t="n">
         <v>1.31839606150016</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.846087022844656</v>
+        <v>4.803307238092226</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.959185347113301</v>
       </c>
       <c r="D2069" t="n">
         <v>-4.409579679438327</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.237776835776653</v>
+        <v>2.194997051024223</v>
       </c>
       <c r="F2069" t="n">
         <v>1.329651812613061</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.799756219433569</v>
+        <v>4.756976434681139</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>4.144383551998657</v>
       </c>
       <c r="D2070" t="n">
         <v>-4.442595975349072</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.40976852229771</v>
+        <v>2.36698873754528</v>
       </c>
       <c r="F2070" t="n">
         <v>1.26021443594631</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.943291998318872</v>
+        <v>4.900512213566443</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883679</v>
+        <v>3.713762536883678</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>4.136304777826906</v>
       </c>
       <c r="D2071" t="n">
         <v>-4.431068339699463</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.406300802385802</v>
+        <v>2.363521017633373</v>
       </c>
       <c r="F2071" t="n">
         <v>1.319215094147672</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.970613619067939</v>
+        <v>4.92783383431551</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236299</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>4.139972890348695</v>
       </c>
       <c r="D2072" t="n">
         <v>-4.528409841041832</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.371032314370644</v>
+        <v>2.328252529618214</v>
       </c>
       <c r="F2072" t="n">
         <v>1.274794911982184</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.947629622290435</v>
+        <v>4.904849837538006</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427687</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>4.141223972541533</v>
       </c>
       <c r="D2073" t="n">
         <v>-4.614265870381798</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.337940984827495</v>
+        <v>2.295161200075065</v>
       </c>
       <c r="F2073" t="n">
         <v>1.232418842756049</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.923455062947592</v>
+        <v>4.880675278195162</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610378</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>4.123643174362035</v>
       </c>
       <c r="D2074" t="n">
         <v>-4.623102667797918</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.316825467681549</v>
+        <v>2.27404568292912</v>
       </c>
       <c r="F2074" t="n">
         <v>1.224976670114698</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.901408961183283</v>
+        <v>4.858629176430854</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176587470159514</v>
+        <v>4.133807685407084</v>
       </c>
       <c r="D2075" t="n">
         <v>-4.714485230363376</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.290436953700415</v>
+        <v>2.247657168947986</v>
       </c>
       <c r="F2075" t="n">
         <v>1.188411785395354</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.889634541396726</v>
+        <v>4.846854756644296</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889194</v>
+        <v>3.673978374889193</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.278715727983782</v>
+        <v>4.235935943231352</v>
       </c>
       <c r="D2076" t="n">
         <v>-4.70277851237637</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.397247898719486</v>
+        <v>2.354468113967056</v>
       </c>
       <c r="F2076" t="n">
         <v>1.20011850338236</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.998786830013198</v>
+        <v>4.956007045260768</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940957</v>
+        <v>3.682476099409568</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.281748066715187</v>
+        <v>4.238968281962757</v>
       </c>
       <c r="D2077" t="n">
         <v>-4.603115008292708</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.440145639084355</v>
+        <v>2.397365854331926</v>
       </c>
       <c r="F2077" t="n">
         <v>1.263305586586047</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.039731418666815</v>
+        <v>4.996951633914385</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.494652899993245</v>
+        <v>4.451873115240815</v>
       </c>
       <c r="D2078" t="n">
         <v>-4.61343110645906</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.648924033095873</v>
+        <v>2.606144248343443</v>
       </c>
       <c r="F2078" t="n">
         <v>1.263305586586047</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.252636251944873</v>
+        <v>5.209856467192443</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762289</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.493831566905334</v>
+        <v>4.451051782152905</v>
       </c>
       <c r="D2079" t="n">
         <v>-4.613337138441687</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.648140287214912</v>
+        <v>2.605360502462482</v>
       </c>
       <c r="F2079" t="n">
         <v>1.263675447933365</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.252036835665353</v>
+        <v>5.209257050912924</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988022</v>
+        <v>3.63321346798802</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.488063552849688</v>
+        <v>4.445283768097259</v>
       </c>
       <c r="D2080" t="n">
         <v>-4.620555962641531</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.639484743479327</v>
+        <v>2.596704958726898</v>
       </c>
       <c r="F2080" t="n">
         <v>1.263675447933365</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.246268821609707</v>
+        <v>5.203489036857277</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.488063552849688</v>
+        <v>4.445283768097259</v>
       </c>
       <c r="D2081" t="n">
         <v>-4.619607539523493</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.639864112726543</v>
+        <v>2.597084327974113</v>
       </c>
       <c r="F2081" t="n">
         <v>1.263675447933365</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.246268821609707</v>
+        <v>5.203489036857277</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.50079116083078</v>
+        <v>4.458011376078351</v>
       </c>
       <c r="D2082" t="n">
         <v>-4.776675997779117</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.589764337405385</v>
+        <v>2.546984552652956</v>
       </c>
       <c r="F2082" t="n">
         <v>1.263675447933365</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.258996429590799</v>
+        <v>5.21621664483837</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.502737159255168</v>
+        <v>4.459957374502738</v>
       </c>
       <c r="D2083" t="n">
         <v>-4.770683750990306</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.594107234545298</v>
+        <v>2.551327449792868</v>
       </c>
       <c r="F2083" t="n">
         <v>1.263675447933365</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.260942428015187</v>
+        <v>5.218162643262757</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.496391295272937</v>
+        <v>4.453611510520507</v>
       </c>
       <c r="D2084" t="n">
         <v>-4.682125789859538</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.623184555015373</v>
+        <v>2.580404770262944</v>
       </c>
       <c r="F2084" t="n">
         <v>1.263675447933365</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.254596564032956</v>
+        <v>5.211816779280526</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383087</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.495699972711932</v>
+        <v>4.452920187959503</v>
       </c>
       <c r="D2085" t="n">
         <v>-4.664366712356464</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.629596863455599</v>
+        <v>2.586817078703169</v>
       </c>
       <c r="F2085" t="n">
         <v>1.263675447933365</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.253905241471951</v>
+        <v>5.211125456719522</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.908079222633912</v>
+        <v>3.821530237458278</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.508482158620519</v>
+        <v>4.46570237386809</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.524864358148359</v>
+        <v>-4.561641191183691</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.698179991047428</v>
+        <v>2.640689473080865</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.403177802141469</v>
+        <v>1.366400969106137</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.350388839905401</v>
+        <v>5.285542955331772</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.5%</t>
+          <t>102.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>134.9%</t>
+          <t>139.2%</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-617.7%</t>
+          <t>-619.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-112.2%</t>
+          <t>-108.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.9%</t>
+          <t>-325.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-87.4%</t>
+          <t>-82.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.0%</t>
+          <t>118.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>104.9%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>89.9%</t>
         </is>
       </c>
     </row>
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.834009020654386</v>
+        <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.258687543445998</v>
+        <v>-6.305213594169796</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3301775789622385</v>
+        <v>0.3543469434251487</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1780292819166325</v>
+        <v>-0.1596374461646781</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.727191451504407</v>
+        <v>2.781006337708009</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.825295034400908</v>
+        <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.205718021192009</v>
+        <v>-6.252244071915808</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3426514016103557</v>
+        <v>0.3668207660732659</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1066679239106892</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.750259178603322</v>
+        <v>2.804074064806924</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.818334422305814</v>
+        <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.039929825231718</v>
+        <v>-6.086455875955517</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4020060678993791</v>
+        <v>0.4261754323622893</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1066679239106892</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.743298566508229</v>
+        <v>2.797113452711831</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.832796776686958</v>
+        <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.00656661875295</v>
+        <v>-6.053092669476748</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4298137048720299</v>
+        <v>0.4539830693349396</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1066679239106892</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.757760920889372</v>
+        <v>2.811575807092974</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.827328897146153</v>
+        <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.898307481630428</v>
+        <v>-5.944833532354227</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4676494801802336</v>
+        <v>0.4918188446431437</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1066679239106892</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.752293041348567</v>
+        <v>2.806107927552169</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.824826991156729</v>
+        <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.775016346813297</v>
+        <v>-5.821542397537096</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5144640281176627</v>
+        <v>0.5386333925805729</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.001768624845513156</v>
+        <v>0.01662321090644131</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.823765816249422</v>
+        <v>2.877580702453024</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.832527969394055</v>
+        <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.722319479682006</v>
+        <v>-5.768845530405804</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5432437532075043</v>
+        <v>0.5674131176704145</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.06932007803773249</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.863084914765522</v>
+        <v>2.916899800969124</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.828308677741105</v>
+        <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.478554037698562</v>
+        <v>-5.52508008842236</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6365306383479328</v>
+        <v>0.660700002810843</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.06932007803773249</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.858865623112572</v>
+        <v>2.912680509316175</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.830432991661121</v>
+        <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.388778365322089</v>
+        <v>-5.435304416045888</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6745652212185376</v>
+        <v>0.6987345856814478</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1309195229520425</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.897949603981175</v>
+        <v>2.951764490184777</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.823175066644823</v>
+        <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.138927971373015</v>
+        <v>-5.185454022096813</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7672474537818696</v>
+        <v>0.7914168182447798</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1309195229520425</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.890691678964877</v>
+        <v>2.944506565168479</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.826774190165472</v>
+        <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.963035878905583</v>
+        <v>-5.009561929629381</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8412034142894911</v>
+        <v>0.8653727787524015</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1309195229520425</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.894290802485525</v>
+        <v>2.948105688689127</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.840101696220026</v>
+        <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.791589415883119</v>
+        <v>-4.838115466606918</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9231095055530303</v>
+        <v>0.9472788700159405</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2839741502225512</v>
+        <v>0.3023659859745056</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.010486186353557</v>
+        <v>3.064301072557159</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.839122173836323</v>
+        <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.711567128773998</v>
+        <v>-4.758093179497797</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9541388980129755</v>
+        <v>0.9783082624758856</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3639964373316721</v>
+        <v>0.3823882730836266</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.057520036235327</v>
+        <v>3.111334922438929</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.84381697489064</v>
+        <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.647931386540064</v>
+        <v>-4.694457437263862</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9842879959608666</v>
+        <v>1.008457360423777</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4460240153175611</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.100396282630004</v>
+        <v>3.154211168833607</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.825011233674436</v>
+        <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.554234068323669</v>
+        <v>-4.600760119047467</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.00296118203122</v>
+        <v>1.02713054649413</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4460240153175611</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.0815905414138</v>
+        <v>3.135405427617402</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.826754310299313</v>
+        <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.564736691388958</v>
+        <v>-4.611262742112756</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.000503209429982</v>
+        <v>1.024672573892892</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.4355213922522723</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.077032044199504</v>
+        <v>3.130846930403107</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.830683624134133</v>
+        <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.452250430720083</v>
+        <v>-4.498776481443882</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.049427027532352</v>
+        <v>1.073596391995262</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.4355213922522723</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.080961358034324</v>
+        <v>3.134776244237926</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.831362208051473</v>
+        <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.434536743842218</v>
+        <v>-4.481062794566016</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.057191086200838</v>
+        <v>1.081360450663748</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4387027211491891</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.083548739289814</v>
+        <v>3.137363625493417</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.828360279271467</v>
+        <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.311062472529199</v>
+        <v>-4.357588523252998</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.103578865946039</v>
+        <v>1.127748230408949</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4387027211491891</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.080546810509808</v>
+        <v>3.13436169671341</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.829939316282081</v>
+        <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.091041674492189</v>
+        <v>-4.137567725215987</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.193166222171457</v>
+        <v>1.217335586634368</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5799225662171693</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.16685775456121</v>
+        <v>3.220672640764812</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.845833499083904</v>
+        <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.958173985428911</v>
+        <v>-4.004700036152709</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.262207480598592</v>
+        <v>1.286376845061502</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5799225662171693</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.182751937363034</v>
+        <v>3.236566823566636</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.846979343524206</v>
+        <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.838000902064412</v>
+        <v>-3.88452695278821</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.311422558384693</v>
+        <v>1.335591922847604</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6817038138297138</v>
+        <v>0.7000956495816683</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.256001631822035</v>
+        <v>3.309816518025637</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.857067446085646</v>
+        <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.702747540734435</v>
+        <v>-3.749273591458233</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.375612005478124</v>
+        <v>1.399781369941034</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8169571751596909</v>
+        <v>0.8353490109116454</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.347241751181461</v>
+        <v>3.401056637385063</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.843104937487072</v>
+        <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.762622368092127</v>
+        <v>-3.809148418815925</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.337699565936473</v>
+        <v>1.361868930399383</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7754741835539533</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.297354346168271</v>
+        <v>3.351169232371874</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.85839410672128</v>
+        <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.64280213718129</v>
+        <v>-3.689328187905088</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.400916827535017</v>
+        <v>1.425086191997927</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7754741835539533</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.31264351540248</v>
+        <v>3.366458401606082</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.766038306043722</v>
+        <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.645271843643096</v>
+        <v>-3.691797894366894</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.307573144272736</v>
+        <v>1.331742508735646</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7546126413401926</v>
+        <v>0.7730044770921471</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.218805890847838</v>
+        <v>3.27262077705144</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.685300167529023</v>
+        <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.713642029967105</v>
+        <v>-3.760168080690903</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.199486931228433</v>
+        <v>1.223656295691343</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7822801761283621</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.143633171754868</v>
+        <v>3.197448057958471</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.675736876160915</v>
+        <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.825514309593256</v>
+        <v>-3.872040360317054</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.145174728009864</v>
+        <v>1.169344092472774</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7822801761283621</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.134069880386759</v>
+        <v>3.187884766590362</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.812767712853117</v>
+        <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.881034385485846</v>
+        <v>-3.927560436209644</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.259997534345031</v>
+        <v>1.284166898807941</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7822801761283621</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.271100717078962</v>
+        <v>3.324915603282564</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.817334944844905</v>
+        <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.705560125693376</v>
+        <v>-3.752086176417174</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.334754470253806</v>
+        <v>1.358923834716717</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7822801761283621</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.275667949070749</v>
+        <v>3.329482835274352</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.793076973606112</v>
+        <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.697635751108462</v>
+        <v>-3.74416180183226</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.313666248848979</v>
+        <v>1.337835613311889</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7822801761283621</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.251409977831957</v>
+        <v>3.305224864035559</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.721615287007562</v>
+        <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.691357548538613</v>
+        <v>-3.737883599262411</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.244715843278368</v>
+        <v>1.268885207741278</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7885583786982111</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.183715212775316</v>
+        <v>3.237530098978918</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.731787673439694</v>
+        <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.63150492933489</v>
+        <v>-3.678030980058688</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.27882927739199</v>
+        <v>1.3029986418549</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7885583786982111</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.193887599207448</v>
+        <v>3.24770248541105</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.726733944013554</v>
+        <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.545261466308513</v>
+        <v>-3.591787517032311</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.308272933176401</v>
+        <v>1.332442297639311</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7885583786982111</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.188833869781309</v>
+        <v>3.242648755984911</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.71850971945808</v>
+        <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.590568285707493</v>
+        <v>-3.637094336431291</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.281925980861335</v>
+        <v>1.306095345324245</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7477482156889803</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.156123547420296</v>
+        <v>3.209938433623898</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.719061592491181</v>
+        <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.619601390409794</v>
+        <v>-3.666127441133592</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.270864612013516</v>
+        <v>1.295033976476426</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7477482156889803</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.156675420453397</v>
+        <v>3.210490306656999</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.648334284382547</v>
+        <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.526790908958935</v>
+        <v>-3.573316959682733</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.237261496485225</v>
+        <v>1.261430860948135</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8221668613878851</v>
+        <v>0.8405586971398397</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.141634401215279</v>
+        <v>3.195449287418881</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.650207760307148</v>
+        <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.571180378288362</v>
+        <v>-3.617706429012161</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.221379184678055</v>
+        <v>1.245548549140965</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7777773920584574</v>
+        <v>0.796169227810412</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.116874195542223</v>
+        <v>3.170689081745825</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.645283468818871</v>
+        <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.550676684402865</v>
+        <v>-3.597202735126663</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.224656370743977</v>
+        <v>1.248825735206887</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.8166729216959093</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.124252120385244</v>
+        <v>3.178067006588846</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.650774764649538</v>
+        <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.590600778985437</v>
+        <v>-3.637126829709235</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.214178028741615</v>
+        <v>1.238347393204525</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.8166729216959093</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.129743416215911</v>
+        <v>3.183558302419514</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.662271966418077</v>
+        <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.61838117688679</v>
+        <v>-3.664907227610589</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.214563071349613</v>
+        <v>1.238732435812523</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7705006880426017</v>
+        <v>0.7888925237945563</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.124572379243638</v>
+        <v>3.178387265447241</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.50062768641873</v>
+        <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.736761849616929</v>
+        <v>-3.783287900340727</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.005566522258211</v>
+        <v>1.029735886721121</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7216746716435801</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.922597387953706</v>
+        <v>2.976412274157308</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.620777347137936</v>
+        <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.84537592806026</v>
+        <v>-3.891901978784058</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.082270551600084</v>
+        <v>1.106439916062994</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7216746716435801</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.042747048672912</v>
+        <v>3.096561934876514</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.635290373240259</v>
+        <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.809966889812117</v>
+        <v>-3.856492940535915</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.110947193001664</v>
+        <v>1.135116557464575</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7216746716435801</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.057260074775235</v>
+        <v>3.111074960978837</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.632709814582628</v>
+        <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.771583227253966</v>
+        <v>-3.818109277977764</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.123720099367293</v>
+        <v>1.147889463830204</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7600583342017313</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.077709713652494</v>
+        <v>3.131524599856097</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.62943884342793</v>
+        <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.5944668972188</v>
+        <v>-3.640992947942598</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.191295660226662</v>
+        <v>1.215465024689572</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7600583342017313</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.074438742497796</v>
+        <v>3.128253628701398</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.630122235189843</v>
+        <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.639559142052345</v>
+        <v>-3.686085192776143</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.173942154055157</v>
+        <v>1.198111518518067</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6797704552803869</v>
+        <v>0.6981622910323415</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.037984508358075</v>
+        <v>3.091799394561678</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.623909210496257</v>
+        <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.460183720813578</v>
+        <v>-3.506709771537376</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.239479297857078</v>
+        <v>1.263648662319988</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8365472134511056</v>
+        <v>0.8549390492030602</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.125837538566921</v>
+        <v>3.179652424770523</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.604716665827847</v>
+        <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.505197934334184</v>
+        <v>-3.551723985057982</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.202281067780425</v>
+        <v>1.226450432243336</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.806198318136501</v>
+        <v>0.8245901538884556</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.088435656709748</v>
+        <v>3.14225054291335</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.610408228166793</v>
+        <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.772202444606619</v>
+        <v>-3.818728495330417</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.101170826010397</v>
+        <v>1.125340190473307</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6118352800935525</v>
+        <v>0.6302271158455071</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.977509396222924</v>
+        <v>3.031324282426527</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.609612150063294</v>
+        <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.873400226043792</v>
+        <v>-3.91992627676759</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.059895635332029</v>
+        <v>1.084064999794939</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5618183023001879</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.935668029992234</v>
+        <v>2.989482916195837</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.607212111617611</v>
+        <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.866889259429479</v>
+        <v>-3.913415310153277</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.060099983532071</v>
+        <v>1.084269347994981</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5618183023001879</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.933267991546551</v>
+        <v>2.987082877750153</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.603736830825856</v>
+        <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.847851131722182</v>
+        <v>-3.89437718244598</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.064239953823235</v>
+        <v>1.088409318286145</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.5036346909689934</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.894882543956079</v>
+        <v>2.948697430159682</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.723031232460046</v>
+        <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.900366933997002</v>
+        <v>-3.9468929847208</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.162528034547497</v>
+        <v>1.186697399010407</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.5036346909689934</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.01417694559027</v>
+        <v>3.067991831793872</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.72386456144618</v>
+        <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.903775245431582</v>
+        <v>-3.95030129615538</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.161998038959799</v>
+        <v>1.186167403422709</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5361512599783708</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.03452021598203</v>
+        <v>3.088335102185632</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.729873091843106</v>
+        <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.884419109537735</v>
+        <v>-3.930945160261533</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.175749023714264</v>
+        <v>1.199918388177174</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5361512599783708</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.040528746378956</v>
+        <v>3.094343632582558</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.627823313120305</v>
+        <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.736676139302733</v>
+        <v>-3.783202190026531</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.132796433085464</v>
+        <v>1.156965797548374</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.7039586172132539</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.039163381997085</v>
+        <v>3.092978268200687</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.630616934651786</v>
+        <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.820497360577431</v>
+        <v>-3.867023411301229</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.102061566107066</v>
+        <v>1.126230930569976</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.7039586172132539</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.041957003528566</v>
+        <v>3.095771889732168</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.631279283043444</v>
+        <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.814344654524646</v>
+        <v>-3.860870705248444</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.105184996919838</v>
+        <v>1.129354361382748</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6917194875140836</v>
+        <v>0.7101113232660382</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.046310975551895</v>
+        <v>3.100125861755497</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.630359759783555</v>
+        <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.831153952675148</v>
+        <v>-3.877680003398946</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.097541754399748</v>
+        <v>1.121711118862658</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.674910189363582</v>
+        <v>0.6933020251155366</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.035305873401704</v>
+        <v>3.089120759605307</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.696695313580376</v>
+        <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.768855953899026</v>
+        <v>-3.815382004622824</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.188796507707017</v>
+        <v>1.212965872169927</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7202044536380241</v>
+        <v>0.7385962893899787</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.12881798576319</v>
+        <v>3.182632871966792</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.498987315294503</v>
+        <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.567065756233868</v>
+        <v>-3.613591806957666</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.071804588487207</v>
+        <v>1.095973952950118</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9182226458071785</v>
+        <v>0.9366144815591331</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.04992090277881</v>
+        <v>3.103735788982412</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.569277547616678</v>
+        <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.617952468920063</v>
+        <v>-3.664478519643861</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.121740135734905</v>
+        <v>1.145909500197815</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.867335933120984</v>
+        <v>0.8857277688729386</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.089679107489268</v>
+        <v>3.143493993692871</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.583905283732721</v>
+        <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.531341726270255</v>
+        <v>-3.577867776994053</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.171012168910871</v>
+        <v>1.195181533373781</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9459616643261423</v>
+        <v>0.9643535000780968</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.151482282328407</v>
+        <v>3.20529716853201</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.582441264557393</v>
+        <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.59155102427554</v>
+        <v>-3.638077074999338</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.145464430533429</v>
+        <v>1.169633794996339</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.9041442020728123</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.113892684349908</v>
+        <v>3.16770757055351</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.580932882597322</v>
+        <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.542364375591188</v>
+        <v>-3.588890426314987</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.163630708047098</v>
+        <v>1.187800072510008</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.9041442020728123</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.112384302389836</v>
+        <v>3.166199188593439</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.580795750032758</v>
+        <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.49799124395262</v>
+        <v>-3.544517294676418</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.181242828137962</v>
+        <v>1.205412192600872</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9301254979594263</v>
+        <v>0.9485173337113809</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.138871048808414</v>
+        <v>3.192685935012016</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.575189544171348</v>
+        <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.520471594811505</v>
+        <v>-3.566997645535303</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.166644481932999</v>
+        <v>1.190813846395909</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9301254979594263</v>
+        <v>0.9485173337113809</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.133264842947004</v>
+        <v>3.187079729150607</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.581571301199153</v>
+        <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.472815864250449</v>
+        <v>-3.519341914974247</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.192088531185226</v>
+        <v>1.216257895648136</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.977781228520482</v>
+        <v>0.9961730642724365</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.168240038311442</v>
+        <v>3.222054924515045</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.586463674573878</v>
+        <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.372297705751694</v>
+        <v>-3.418823756475492</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.237188167959452</v>
+        <v>1.261357532422362</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.078299387019237</v>
+        <v>1.096691222771191</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.23344330678542</v>
+        <v>3.287258192989023</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.57321834704975</v>
+        <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.356392376319342</v>
+        <v>-3.40291842704314</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.230304972208266</v>
+        <v>1.254474336671176</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9991867263099976</v>
+        <v>1.017578562061952</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.172730382835749</v>
+        <v>3.226545269039351</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.577316049660379</v>
+        <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.311553974710943</v>
+        <v>-3.358080025434742</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.252338035462253</v>
+        <v>1.276507399925163</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.003730159254867</v>
+        <v>1.022121995006822</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.179554145213299</v>
+        <v>3.233369031416902</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.581476989291457</v>
+        <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.331052430952952</v>
+        <v>-3.37757848167675</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.248699592596528</v>
+        <v>1.272868957059438</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9556455179749628</v>
+        <v>0.9740373537269174</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.154864300076435</v>
+        <v>3.208679186280037</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.587356591819294</v>
+        <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.286849593867051</v>
+        <v>-3.333375644590849</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.272260329958725</v>
+        <v>1.296429694421636</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9998483550608632</v>
+        <v>1.018240190812818</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.187265604855812</v>
+        <v>3.241080491059414</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.585766592288541</v>
+        <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.294409259704098</v>
+        <v>-3.340935310427896</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.267646464093154</v>
+        <v>1.291815828556064</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.054651759070683</v>
+        <v>1.073043594822637</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.218557647730951</v>
+        <v>3.272372533934553</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.637014357471581</v>
+        <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.136117842164826</v>
+        <v>-3.182643892888624</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.382210796291903</v>
+        <v>1.406380160754813</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.054651759070683</v>
+        <v>1.073043594822637</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.269805412913991</v>
+        <v>3.323620299117593</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.635455062065834</v>
+        <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.92847583853035</v>
+        <v>-2.975001889254148</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.463708302339946</v>
+        <v>1.487877666802856</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.262293762705159</v>
+        <v>1.280685598457113</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.39283131968893</v>
+        <v>3.446646205892532</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.630403290304104</v>
+        <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.877443745807822</v>
+        <v>-2.92396979653162</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.479069367667228</v>
+        <v>1.503238732130138</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.313325855427687</v>
+        <v>1.331717691179641</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.418398803560716</v>
+        <v>3.472213689764319</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.647590694396809</v>
+        <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.812219564680616</v>
+        <v>-2.858745615404414</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.522346444210815</v>
+        <v>1.546515808673725</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.378550036554892</v>
+        <v>1.396941872306847</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.474720716329745</v>
+        <v>3.528535602533347</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.643551666696089</v>
+        <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.774792544609482</v>
+        <v>-2.82131859533328</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.533278224538549</v>
+        <v>1.557447589001459</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.383801574584074</v>
+        <v>1.402193410336029</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.473832611446534</v>
+        <v>3.527647497650137</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.64480845902733</v>
+        <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.79490420064419</v>
+        <v>-2.841430251367989</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.526490354455906</v>
+        <v>1.550659718918816</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.394828919581493</v>
+        <v>1.413220755333448</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.481705810776226</v>
+        <v>3.535520696979829</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.80536623004854</v>
+        <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.766490937544307</v>
+        <v>-2.813016988268105</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.69841343071707</v>
+        <v>1.72258279517998</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.335853356835065</v>
+        <v>1.354245192587019</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.60687824414958</v>
+        <v>3.660693130353182</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.925479139266358</v>
+        <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.691708676519294</v>
+        <v>-2.738234727243092</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.848439244344892</v>
+        <v>1.872608608807802</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.410635617860077</v>
+        <v>1.429027453612032</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.771860509982404</v>
+        <v>3.825675396186007</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.917187115280217</v>
+        <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.665624592255486</v>
+        <v>-2.712150642979284</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.850580854064274</v>
+        <v>1.874750218527184</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.410635617860077</v>
+        <v>1.429027453612032</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.763568485996263</v>
+        <v>3.817383372199866</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.915380310863996</v>
+        <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.577746679146366</v>
+        <v>-2.624272729870164</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.883925214891702</v>
+        <v>1.908094579354612</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.526561260283428</v>
+        <v>1.544953096035383</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.831317067034053</v>
+        <v>3.885131953237656</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.932934716590788</v>
+        <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.568854217753082</v>
+        <v>-2.61538026847688</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.905036605175807</v>
+        <v>1.929205969638717</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.526561260283428</v>
+        <v>1.544953096035383</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.848871472760845</v>
+        <v>3.902686358964447</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.924789763995371</v>
+        <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.73733033472296</v>
+        <v>-2.783856385446758</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.82950120579244</v>
+        <v>1.85367057025535</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.498613424566847</v>
+        <v>1.517005260318802</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.82395781873548</v>
+        <v>3.877772704939082</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.906059461183233</v>
+        <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.29107414209352</v>
+        <v>-2.337600192817318</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.989273380032077</v>
+        <v>2.013442744494987</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.403894754897215</v>
+        <v>1.422286590649169</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.748396314121562</v>
+        <v>3.802211200325165</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632637</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.896723483680138</v>
+        <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.268353038410368</v>
+        <v>-2.314879089134166</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.989025844002243</v>
+        <v>2.013195208465153</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.403894754897215</v>
+        <v>1.422286590649169</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.739060336618467</v>
+        <v>3.792875222822069</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777674</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.055629609531307</v>
+        <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.39755485170441</v>
+        <v>-2.444080902428208</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.096251244535795</v>
+        <v>2.120420608998705</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.274692941603172</v>
+        <v>1.293084777355127</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.820445374493211</v>
+        <v>3.874260260696813</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.092707432024953</v>
+        <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.423429250178436</v>
+        <v>-2.469955300902234</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.122979307639831</v>
+        <v>2.147148672102742</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.319604550314914</v>
+        <v>1.337996386066868</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.884470162213902</v>
+        <v>3.938285048417504</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.089382788014499</v>
+        <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.416374559963262</v>
+        <v>-2.46290061068706</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.122476539715446</v>
+        <v>2.146645904178356</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.326659240530087</v>
+        <v>1.345051076282042</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.885378332332551</v>
+        <v>3.939193218536154</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.09938894165924</v>
+        <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.389423335636774</v>
+        <v>-2.435949386360572</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.143263183090783</v>
+        <v>2.167432547553693</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.341539586557807</v>
+        <v>1.359931422309761</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.904312693593925</v>
+        <v>3.958127579797527</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.2834920738042</v>
+        <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.410967563467561</v>
+        <v>-2.457493614191359</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.318748624103427</v>
+        <v>2.342917988566338</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.341539586557807</v>
+        <v>1.359931422309761</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.088415825738884</v>
+        <v>4.142230711942487</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.275608768707193</v>
+        <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.433375681272433</v>
+        <v>-2.479901731996232</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.301902071884472</v>
+        <v>2.326071436347382</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.341539586557807</v>
+        <v>1.359931422309761</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.080532520641877</v>
+        <v>4.13434740684548</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.27766276825683</v>
+        <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.461599916850034</v>
+        <v>-2.508125967573832</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.292666377203069</v>
+        <v>2.316835741665979</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.359516339009115</v>
+        <v>1.37790817476107</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.0933725716623</v>
+        <v>4.147187457865902</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.333916485978678</v>
+        <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.471040842738564</v>
+        <v>-2.517566893462362</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.345143724569504</v>
+        <v>2.369313089032414</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.481943456552507</v>
+        <v>1.500335292304461</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.223082559910182</v>
+        <v>4.276897446113784</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.336807580523979</v>
+        <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.559917473907038</v>
+        <v>-2.606443524630836</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.312484166647415</v>
+        <v>2.336653531110326</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.393066825384033</v>
+        <v>1.411458661135987</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.172647675754399</v>
+        <v>4.226462561958001</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.334919393417754</v>
+        <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.636247451507943</v>
+        <v>-2.682773502231742</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.280063988500828</v>
+        <v>2.304233352963738</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.393066825384033</v>
+        <v>1.411458661135987</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.170759488648174</v>
+        <v>4.224574374851776</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.329739623020616</v>
+        <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.729911396185485</v>
+        <v>-2.776437446909283</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.237418640232674</v>
+        <v>2.261588004695584</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.299402880706491</v>
+        <v>1.317794716458446</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.109381351444511</v>
+        <v>4.163196237648114</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.328173633230768</v>
+        <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.89147982171274</v>
+        <v>-2.938005872436538</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.171225280231925</v>
+        <v>2.195394644694835</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.172619956908612</v>
+        <v>1.191011792660567</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.031745607375936</v>
+        <v>4.085560493579538</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.341247040096687</v>
+        <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.999780483582859</v>
+        <v>-3.046306534306658</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.140978422349795</v>
+        <v>2.165147786812705</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.172619956908612</v>
+        <v>1.191011792660567</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.044819014241854</v>
+        <v>4.098633900445456</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.333252236879627</v>
+        <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.017584455303604</v>
+        <v>-3.064110506027402</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.125862030444438</v>
+        <v>2.150031394907348</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.102085334003411</v>
+        <v>1.120477169755365</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.994503437281674</v>
+        <v>4.048318323485276</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.331776278006629</v>
+        <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.045485242413076</v>
+        <v>-3.092011293136875</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.11322575672765</v>
+        <v>2.13739512119056</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.067488409860476</v>
+        <v>1.085880245612431</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.972269323922915</v>
+        <v>4.026084210126517</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.328540721983828</v>
+        <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.16801134511597</v>
+        <v>-3.214537395839768</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.060979759623692</v>
+        <v>2.085149124086602</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9449623071575823</v>
+        <v>0.9633541429095369</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.895518106278377</v>
+        <v>3.949332992481979</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.395246681574331</v>
+        <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.398525841301559</v>
+        <v>-3.445051892025357</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.035479920739959</v>
+        <v>2.05964928520287</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7144478109719936</v>
+        <v>0.7328396467239482</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.823915368157528</v>
+        <v>3.87773025436113</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.535558400576178</v>
+        <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.747270926526003</v>
+        <v>-3.793796977249801</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.03629360565203</v>
+        <v>2.06046297011494</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6240916928050504</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.898978314808036</v>
+        <v>3.952793201011638</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.604538669721818</v>
+        <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.901257344302143</v>
+        <v>-3.947783395025942</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.043679307687213</v>
+        <v>2.067848672150123</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6240916928050504</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.967958583953676</v>
+        <v>4.021773470157278</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.590589871841939</v>
+        <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.105856779165152</v>
+        <v>-4.15238282988895</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.94789073586213</v>
+        <v>1.972060100325041</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6240916928050504</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.954009786073797</v>
+        <v>4.007824672277399</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.602460360897353</v>
+        <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.358331933172876</v>
+        <v>-4.404857983896674</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.858771163314455</v>
+        <v>1.882940527777365</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6240916928050504</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.965880275129211</v>
+        <v>4.019695161332813</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.603670895416297</v>
+        <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.651227689652289</v>
+        <v>-4.697753740376086</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.742823395241633</v>
+        <v>1.766992759704544</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6240916928050504</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.967090809648155</v>
+        <v>4.020905695851757</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.607792637643618</v>
+        <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.837891817787097</v>
+        <v>-4.884417868510894</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.672279486215032</v>
+        <v>1.696448850677942</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5789608862285359</v>
+        <v>0.5973527219804905</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.95516916938074</v>
+        <v>4.008984055584342</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.602870490379808</v>
+        <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.983912504701059</v>
+        <v>-5.030438555424857</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.608949064185636</v>
+        <v>1.633118428648547</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5698777944346789</v>
+        <v>0.5882696301866335</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.944797167040615</v>
+        <v>3.998612053244218</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.765074547078852</v>
+        <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.075626513810644</v>
+        <v>-5.122152564534441</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.734467517240847</v>
+        <v>1.758636881703757</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5698777944346789</v>
+        <v>0.5882696301866335</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.107001223739659</v>
+        <v>4.160816109943262</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.759921185042666</v>
+        <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.107278172870613</v>
+        <v>-5.153804223594411</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.716653491580673</v>
+        <v>1.740822856043583</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5647093371902387</v>
+        <v>0.5831011729421933</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.098746787356809</v>
+        <v>4.152561673560411</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.770150602611157</v>
+        <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.189212991139496</v>
+        <v>-5.235739041863294</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.694108981841611</v>
+        <v>1.718278346304521</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5547745916031586</v>
+        <v>0.5731664273551131</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.103015357573052</v>
+        <v>4.156830243776655</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.77907624106706</v>
+        <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.291189113387904</v>
+        <v>-5.337715164111701</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.66224417139815</v>
+        <v>1.68641353586106</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.452798469354751</v>
+        <v>0.4711903051067056</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.05075532267991</v>
+        <v>4.104570208883513</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.771229128311235</v>
+        <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.181182829910682</v>
+        <v>-5.22770888063448</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.698399572033214</v>
+        <v>1.722568936496124</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4760030412720262</v>
+        <v>0.4943948770239808</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.056830953074451</v>
+        <v>4.110645839278053</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.775479139033209</v>
+        <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.038123254169756</v>
+        <v>-5.084649304893554</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.759873413051559</v>
+        <v>1.784042777514469</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4840164678620055</v>
+        <v>0.50240830361396</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.065889019750413</v>
+        <v>4.119703905954015</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.782740021915745</v>
+        <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.736676528697918</v>
+        <v>-4.783202579421716</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.88771298612283</v>
+        <v>1.91188235058574</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8038550290857973</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.254017937916051</v>
+        <v>4.307832824119654</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.783711199668456</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.761266772933102</v>
+        <v>-4.8077928236569</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.878848066181467</v>
+        <v>1.903017430644377</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8038550290857973</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.254989115668762</v>
+        <v>4.308804001872364</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.784554104048211</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.710228396926582</v>
+        <v>-4.75675444765038</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.90010632096383</v>
+        <v>1.924275685426741</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8038550290857973</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.255832020048517</v>
+        <v>4.309646906252119</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.803592202922357</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.669089102059951</v>
+        <v>-4.715615152783749</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.935600137784628</v>
+        <v>1.959769502247538</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8266024882004736</v>
+        <v>0.8449943239524281</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.299553695842641</v>
+        <v>4.353368582046244</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.619776199046291</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.572454190041311</v>
+        <v>-4.618980240765109</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.790438098716019</v>
+        <v>1.814607463178929</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9232374002191135</v>
+        <v>0.9416292359710681</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.17371863917776</v>
+        <v>4.227533525381362</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.623278243120255</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.703034924572154</v>
+        <v>-4.749560975295951</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.741707848977646</v>
+        <v>1.765877213440556</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.792656665688271</v>
+        <v>0.8110485014402256</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.098872242533218</v>
+        <v>4.152687128736821</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.607705062196338</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.538538590381192</v>
+        <v>-4.58506464110499</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.791933201730113</v>
+        <v>1.816102566193023</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9571529998792329</v>
+        <v>0.9755448356311874</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.181996862123878</v>
+        <v>4.23581174832748</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.606892772632768</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.461439988839319</v>
+        <v>-4.507966039563117</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.821960352783292</v>
+        <v>1.846129717246202</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9571529998792329</v>
+        <v>0.9755448356311874</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.181184572560308</v>
+        <v>4.23499945876391</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.61676155175784</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.471825183729209</v>
+        <v>-4.518351234453006</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.827675053952409</v>
+        <v>1.851844418415319</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9467678049893435</v>
+        <v>0.9651596407412981</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.184822234751446</v>
+        <v>4.238637120955049</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.687598557534265</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.490413342451434</v>
+        <v>-4.536939393175231</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.891076796239944</v>
+        <v>1.915246160702854</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9281796462671181</v>
+        <v>0.9465714820190727</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.244506345294536</v>
+        <v>4.298321231498138</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.684467568352564</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.49071188914747</v>
+        <v>-4.537237939871267</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.887826388379828</v>
+        <v>1.911995752842738</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9278810995710822</v>
+        <v>0.9462729353230368</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.241196228095213</v>
+        <v>4.295011114298815</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.688998463291955</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.389888755457042</v>
+        <v>-4.436414806180839</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.932686536795391</v>
+        <v>1.956855901258301</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9403453150554361</v>
+        <v>0.9587371508073906</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.253205652325217</v>
+        <v>4.307020538528819</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.689127716770499</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.199107394704635</v>
+        <v>-4.245633445428433</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.009128334574897</v>
+        <v>2.033297699037807</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.131126675807844</v>
+        <v>1.149518511559798</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.367803722255205</v>
+        <v>4.421618608458807</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.668964562508095</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.092144036855213</v>
+        <v>-4.138670087579011</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.031750523452262</v>
+        <v>2.055919887915172</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.189591283767645</v>
+        <v>1.2079831195196</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.382719332768683</v>
+        <v>4.436534218972285</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.703931499120154</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.036813448953451</v>
+        <v>-4.083339499677249</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.088849695225025</v>
+        <v>2.113019059687935</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.244921871669407</v>
+        <v>1.263313707421362</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.450884622121798</v>
+        <v>4.5046995083254</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.697618067021591</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.024759322040488</v>
+        <v>-4.071285372764286</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.087357913891648</v>
+        <v>2.111527278354558</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.25697599858237</v>
+        <v>1.275367834334324</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.451803666171013</v>
+        <v>4.505618552374616</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.699498697205727</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.065914441608709</v>
+        <v>-4.112440492332507</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.072776496248496</v>
+        <v>2.096945860711406</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.215820879014149</v>
+        <v>1.234212714766104</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.428991224614217</v>
+        <v>4.482806110817819</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.71234972308361</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.997865878917179</v>
+        <v>-4.044391929640977</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.11284694720299</v>
+        <v>2.1370163116659</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.283869441705679</v>
+        <v>1.302261277457633</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.482671388107017</v>
+        <v>4.53648627431062</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.732552393257204</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.22946627208668</v>
+        <v>-4.275992322810477</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.040409460108784</v>
+        <v>2.064578824571694</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.283869441705679</v>
+        <v>1.302261277457633</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.502874058280612</v>
+        <v>4.556688944484214</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.716158629324086</v>
+        <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.279517817615899</v>
+        <v>-4.326043868339696</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.003995077963978</v>
+        <v>2.028164442426888</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.283869441705679</v>
+        <v>1.302261277457633</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.486480294347493</v>
+        <v>4.540295180551095</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.676410542917552</v>
+        <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.454624650192343</v>
+        <v>-4.501150700916141</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.894204258526867</v>
+        <v>1.918373622989777</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.283869441705679</v>
+        <v>1.302261277457633</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.44673220794096</v>
+        <v>4.500547094144562</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.683433161914492</v>
+        <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.258524496761821</v>
+        <v>-4.305050547485618</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.979666938896016</v>
+        <v>2.003836303358926</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.479969595136202</v>
+        <v>1.498361430888156</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.571414918996214</v>
+        <v>4.625229805199816</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.782604161487397</v>
+        <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.105499104648536</v>
+        <v>-4.152025155372334</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.140048095314234</v>
+        <v>2.164217459777145</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.632994987249486</v>
+        <v>1.65138682300144</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.762401153837089</v>
+        <v>4.816216040040691</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.970070386395689</v>
+        <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.133806418521806</v>
+        <v>-4.180332469245604</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.316191394673219</v>
+        <v>2.340360759136129</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.632994987249486</v>
+        <v>1.65138682300144</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.949867378745381</v>
+        <v>5.003682264948983</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.939473337749772</v>
+        <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.300399643635329</v>
+        <v>-4.346925694359126</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.218957055981893</v>
+        <v>2.243126420444803</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.466401762135963</v>
+        <v>1.484793597887918</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.81931439503135</v>
+        <v>4.873129281234952</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.943149740411489</v>
+        <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.277363850273763</v>
+        <v>-4.32388990099756</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.231847775988236</v>
+        <v>2.256017140451147</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.466401762135963</v>
+        <v>1.484793597887918</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.822990797693068</v>
+        <v>4.87680568389667</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.940767795534985</v>
+        <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.248117869818066</v>
+        <v>-4.294643920541864</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.24116422329401</v>
+        <v>2.265333587756921</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.466401762135963</v>
+        <v>1.484793597887918</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.820608852816563</v>
+        <v>4.874423739020165</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.93806103469262</v>
+        <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.355043417695917</v>
+        <v>-4.401569468419715</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.195687243300505</v>
+        <v>2.219856607763415</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.359476214258112</v>
+        <v>1.377868050010067</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.753746763247487</v>
+        <v>4.80756164945109</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.939489836835854</v>
+        <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.500061976203166</v>
+        <v>-4.546588026926964</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.13910862204084</v>
+        <v>2.16327798650375</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.214457655750864</v>
+        <v>1.232849491502818</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.668164430286373</v>
+        <v>4.721979316489975</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.039421076093607</v>
+        <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.618403741987883</v>
+        <v>-4.664929792711681</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.191703154984705</v>
+        <v>2.215872519447616</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.225143694313754</v>
+        <v>1.243535530065708</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.774507292681859</v>
+        <v>4.828322178885462</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.037206773219546</v>
+        <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.669814164308591</v>
+        <v>-4.716340215032389</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.168924683182361</v>
+        <v>2.193094047645271</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.225143694313754</v>
+        <v>1.243535530065708</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.772292989807798</v>
+        <v>4.826107876011401</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.037109901293835</v>
+        <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.749233615516343</v>
+        <v>-4.795759666240141</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.13706003077355</v>
+        <v>2.16122939523646</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.225143694313754</v>
+        <v>1.243535530065708</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.772196117882087</v>
+        <v>4.82601100408569</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.7368049522984</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.037103794851879</v>
+        <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.844696613433561</v>
+        <v>-4.891222664157358</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.098868725164706</v>
+        <v>2.123038089627617</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.225143694313754</v>
+        <v>1.243535530065708</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.772190011440131</v>
+        <v>4.826004897643734</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.035200191414489</v>
+        <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.780320702582846</v>
+        <v>-4.826846753306643</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.122715486067603</v>
+        <v>2.146884850530513</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.289519605164469</v>
+        <v>1.307911440916423</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.808911954513171</v>
+        <v>4.862726840716773</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.040934009162216</v>
+        <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.835689864715039</v>
+        <v>-4.882215915438837</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.106301638962452</v>
+        <v>2.130471003425362</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.289519605164469</v>
+        <v>1.307911440916423</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.814645772260898</v>
+        <v>4.8684606584645</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.040472372505148</v>
+        <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.881127644545867</v>
+        <v>-4.927653695269664</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.087664890373053</v>
+        <v>2.111834254835963</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.246674614486309</v>
+        <v>1.265066450238264</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.788477141196934</v>
+        <v>4.842292027400536</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113691</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.060346765355467</v>
+        <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.792920810398289</v>
+        <v>-4.839446861122086</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.142822016882404</v>
+        <v>2.166991381345314</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.246674614486309</v>
+        <v>1.265066450238264</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.808351534047253</v>
+        <v>4.862166420250855</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.044047465880195</v>
+        <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.686885815192979</v>
+        <v>-4.733411865916777</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.168936715489255</v>
+        <v>2.193106079952165</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.246674614486309</v>
+        <v>1.265066450238264</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.79205223457198</v>
+        <v>4.845867120775583</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.04647841534424</v>
+        <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.503674152059884</v>
+        <v>-4.550200202783682</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.244652330206539</v>
+        <v>2.268821694669449</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.246674614486309</v>
+        <v>1.265066450238264</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.794483184036026</v>
+        <v>4.848298070239628</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.01226960119213</v>
+        <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.431952705046033</v>
+        <v>-4.478478755769831</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.239132094859968</v>
+        <v>2.263301459322879</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.31839606150016</v>
+        <v>1.336787897252115</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.803307238092226</v>
+        <v>4.857122124295828</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394113</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.959185347113301</v>
+        <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.409579679438327</v>
+        <v>-4.456105730162125</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.194997051024223</v>
+        <v>2.219166415487133</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.329651812613061</v>
+        <v>1.348043648365016</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.756976434681139</v>
+        <v>4.810791320884741</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.144383551998657</v>
+        <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.442595975349072</v>
+        <v>-4.489122026072869</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.36698873754528</v>
+        <v>2.39115810200819</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.26021443594631</v>
+        <v>1.278606271698264</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.900512213566443</v>
+        <v>4.954327099770046</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883678</v>
+        <v>3.713762536883679</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.136304777826906</v>
+        <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.431068339699463</v>
+        <v>-4.477594390423261</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.363521017633373</v>
+        <v>2.387690382096283</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.319215094147672</v>
+        <v>1.337606929899627</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.92783383431551</v>
+        <v>4.981648720519112</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236299</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.139972890348695</v>
+        <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.528409841041832</v>
+        <v>-4.574935891765629</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.328252529618214</v>
+        <v>2.352421894081124</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.274794911982184</v>
+        <v>1.293186747734139</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.904849837538006</v>
+        <v>4.958664723741608</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427686</v>
+        <v>3.705201079427687</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.141223972541533</v>
+        <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.614265870381798</v>
+        <v>-4.660791921105596</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.295161200075065</v>
+        <v>2.319330564537975</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.232418842756049</v>
+        <v>1.250810678508004</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.880675278195162</v>
+        <v>4.934490164398765</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610378</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.123643174362035</v>
+        <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.623102667797918</v>
+        <v>-4.669628718521715</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.27404568292912</v>
+        <v>2.29821504739203</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.224976670114698</v>
+        <v>1.243368505866653</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.858629176430854</v>
+        <v>4.912444062634457</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667456</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.133807685407084</v>
+        <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.714485230363376</v>
+        <v>-4.761011281087174</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.247657168947986</v>
+        <v>2.271826533410896</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.188411785395354</v>
+        <v>1.206803621147308</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.846854756644296</v>
+        <v>4.900669642847899</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889193</v>
+        <v>3.673978374889194</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.235935943231352</v>
+        <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.70277851237637</v>
+        <v>-4.749304563100168</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.354468113967056</v>
+        <v>2.378637478429966</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.20011850338236</v>
+        <v>1.218510339134315</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.956007045260768</v>
+        <v>5.009821931464371</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409568</v>
+        <v>3.68247609940957</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.238968281962757</v>
+        <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.603115008292708</v>
+        <v>-4.649641059016505</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.397365854331926</v>
+        <v>2.421535218794836</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.263305586586047</v>
+        <v>1.281697422338001</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.996951633914385</v>
+        <v>5.050766520117987</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.451873115240815</v>
+        <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.61343110645906</v>
+        <v>-4.659957157182857</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.606144248343443</v>
+        <v>2.630313612806353</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.263305586586047</v>
+        <v>1.281697422338001</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.209856467192443</v>
+        <v>5.263671353396045</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762289</v>
+        <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.451051782152905</v>
+        <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.613337138441687</v>
+        <v>-4.659863189165485</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.605360502462482</v>
+        <v>2.629529866925392</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.263675447933365</v>
+        <v>1.282067283685319</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.209257050912924</v>
+        <v>5.263071937116526</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.63321346798802</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.445283768097259</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.620555962641531</v>
+        <v>-4.667082013365329</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.596704958726898</v>
+        <v>2.620874323189808</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.263675447933365</v>
+        <v>1.282067283685319</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.203489036857277</v>
+        <v>5.25730392306088</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740919</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.445283768097259</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.619607539523493</v>
+        <v>-4.66613359024729</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.597084327974113</v>
+        <v>2.621253692437024</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.263675447933365</v>
+        <v>1.282067283685319</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.203489036857277</v>
+        <v>5.25730392306088</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.458011376078351</v>
+        <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.776675997779117</v>
+        <v>-4.823202048502915</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.546984552652956</v>
+        <v>2.571153917115866</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.263675447933365</v>
+        <v>1.282067283685319</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.21621664483837</v>
+        <v>5.270031531041972</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.459957374502738</v>
+        <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.770683750990306</v>
+        <v>-4.817209801714103</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.551327449792868</v>
+        <v>2.575496814255779</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.263675447933365</v>
+        <v>1.282067283685319</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.218162643262757</v>
+        <v>5.271977529466359</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.453611510520507</v>
+        <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.682125789859538</v>
+        <v>-4.728651840583336</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.580404770262944</v>
+        <v>2.604574134725854</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.263675447933365</v>
+        <v>1.282067283685319</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.211816779280526</v>
+        <v>5.265631665484128</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383087</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.452920187959503</v>
+        <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.664366712356464</v>
+        <v>-4.710892763080262</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.586817078703169</v>
+        <v>2.610986443166079</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.263675447933365</v>
+        <v>1.282067283685319</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.211125456719522</v>
+        <v>5.264940342923124</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.821530237458278</v>
+        <v>3.822637488317762</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.46570237386809</v>
+        <v>4.508482158620519</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.561641191183691</v>
+        <v>-4.57471438664145</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.640689473080865</v>
+        <v>2.678239979650191</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.366400969106137</v>
+        <v>1.418245660124131</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.285542955331772</v>
+        <v>5.359429554694998</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-619.0%</t>
+          <t>-610.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-108.4%</t>
+          <t>-104.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-325.5%</t>
+          <t>-322.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-82.2%</t>
+          <t>-84.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>88.8%</t>
         </is>
       </c>
     </row>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.766317079436229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388731</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626477</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.305213594169796</v>
+        <v>-6.258687543445998</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3543469434251487</v>
+        <v>0.3729573637146681</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1596374461646781</v>
+        <v>-0.1780292819166325</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.781006337708009</v>
+        <v>2.769971236256836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.252244071915808</v>
+        <v>-6.205718021192009</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3668207660732659</v>
+        <v>0.3854311863627853</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1066679239106892</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.804074064806924</v>
+        <v>2.793038963355751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.086455875955517</v>
+        <v>-6.039929825231718</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4261754323622893</v>
+        <v>0.4447858526518087</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1066679239106892</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.797113452711831</v>
+        <v>2.786078351260658</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.053092669476748</v>
+        <v>-6.00656661875295</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4539830693349396</v>
+        <v>0.4725934896244595</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1066679239106892</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.811575807092974</v>
+        <v>2.800540705641801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.944833532354227</v>
+        <v>-5.898307481630428</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4918188446431437</v>
+        <v>0.5104292649326632</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1066679239106892</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.806107927552169</v>
+        <v>2.795072826100996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.821542397537096</v>
+        <v>-5.775016346813297</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5386333925805729</v>
+        <v>0.5572438128700923</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.01662321090644131</v>
+        <v>-0.001768624845513156</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.877580702453024</v>
+        <v>2.866545601001851</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.768845530405804</v>
+        <v>-5.722319479682006</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5674131176704145</v>
+        <v>0.5860235379599339</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.06932007803773249</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.916899800969124</v>
+        <v>2.905864699517951</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.52508008842236</v>
+        <v>-5.478554037698562</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.660700002810843</v>
+        <v>0.6793104231003624</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.06932007803773249</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.912680509316175</v>
+        <v>2.901645407865002</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.435304416045888</v>
+        <v>-5.388778365322089</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6987345856814478</v>
+        <v>0.7173450059709672</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1309195229520425</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.951764490184777</v>
+        <v>2.940729388733604</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.185454022096813</v>
+        <v>-5.138927971373015</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7914168182447798</v>
+        <v>0.8100272385342993</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1309195229520425</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.944506565168479</v>
+        <v>2.933471463717306</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.009561929629381</v>
+        <v>-4.963035878905583</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8653727787524015</v>
+        <v>0.8839831990419207</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1309195229520425</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.948105688689127</v>
+        <v>2.937070587237955</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.838115466606918</v>
+        <v>-4.791589415883119</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9472788700159405</v>
+        <v>0.9658892903054599</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3023659859745056</v>
+        <v>0.2839741502225512</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.064301072557159</v>
+        <v>3.053265971105986</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.758093179497797</v>
+        <v>-4.711567128773998</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9783082624758856</v>
+        <v>0.9969186827654051</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3823882730836266</v>
+        <v>0.3639964373316721</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.111334922438929</v>
+        <v>3.100299820987756</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.694457437263862</v>
+        <v>-4.647931386540064</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.008457360423777</v>
+        <v>1.027067780713296</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4460240153175611</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.154211168833607</v>
+        <v>3.143176067382434</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.600760119047467</v>
+        <v>-4.554234068323669</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.02713054649413</v>
+        <v>1.04574096678365</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4460240153175611</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.135405427617402</v>
+        <v>3.124370326166229</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.611262742112756</v>
+        <v>-4.564736691388958</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.024672573892892</v>
+        <v>1.043282994182412</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4355213922522723</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.130846930403107</v>
+        <v>3.119811828951934</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.498776481443882</v>
+        <v>-4.452250430720083</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.073596391995262</v>
+        <v>1.092206812284782</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4355213922522723</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.134776244237926</v>
+        <v>3.123741142786754</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.481062794566016</v>
+        <v>-4.434536743842218</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.081360450663748</v>
+        <v>1.099970870953268</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4387027211491891</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.137363625493417</v>
+        <v>3.126328524042244</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.357588523252998</v>
+        <v>-4.311062472529199</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.127748230408949</v>
+        <v>1.146358650698469</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4387027211491891</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.13436169671341</v>
+        <v>3.123326595262237</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.137567725215987</v>
+        <v>-4.091041674492189</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.217335586634368</v>
+        <v>1.235946006923887</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5799225662171693</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.220672640764812</v>
+        <v>3.20963753931364</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.004700036152709</v>
+        <v>-3.958173985428911</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.286376845061502</v>
+        <v>1.304987265351021</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5799225662171693</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.236566823566636</v>
+        <v>3.225531722115463</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.88452695278821</v>
+        <v>-3.838000902064412</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.335591922847604</v>
+        <v>1.354202343137123</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7000956495816683</v>
+        <v>0.6817038138297138</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.309816518025637</v>
+        <v>3.298781416574464</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.749273591458233</v>
+        <v>-3.702747540734435</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.399781369941034</v>
+        <v>1.418391790230554</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8353490109116454</v>
+        <v>0.8169571751596909</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.401056637385063</v>
+        <v>3.390021535933891</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.809148418815925</v>
+        <v>-3.762622368092127</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.361868930399383</v>
+        <v>1.380479350688903</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7754741835539533</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.351169232371874</v>
+        <v>3.340134130920701</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.689328187905088</v>
+        <v>-3.64280213718129</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.425086191997927</v>
+        <v>1.443696612287446</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7754741835539533</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.366458401606082</v>
+        <v>3.355423300154909</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.691797894366894</v>
+        <v>-3.645271843643096</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.331742508735646</v>
+        <v>1.350352929025165</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7730044770921471</v>
+        <v>0.7546126413401926</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.27262077705144</v>
+        <v>3.261585675600267</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.760168080690903</v>
+        <v>-3.713642029967105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.223656295691343</v>
+        <v>1.242266715980863</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7822801761283621</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.197448057958471</v>
+        <v>3.186412956507298</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.872040360317054</v>
+        <v>-3.785495712198642</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.169344092472774</v>
+        <v>1.203961951720139</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7822801761283621</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.187884766590362</v>
+        <v>3.176849665139189</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.927560436209644</v>
+        <v>-3.841015788091231</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.284166898807941</v>
+        <v>1.318784758055306</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7822801761283621</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.324915603282564</v>
+        <v>3.313880501831391</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.752086176417174</v>
+        <v>-3.665541528298762</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.358923834716717</v>
+        <v>1.393541693964081</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7822801761283621</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.329482835274352</v>
+        <v>3.318447733823179</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.74416180183226</v>
+        <v>-3.657617153713848</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.337835613311889</v>
+        <v>1.372453472559254</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7822801761283621</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.305224864035559</v>
+        <v>3.294189762584386</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.737883599262411</v>
+        <v>-3.651338951143999</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.268885207741278</v>
+        <v>1.303503066988644</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7885583786982111</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.237530098978918</v>
+        <v>3.226494997527745</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.678030980058688</v>
+        <v>-3.591486331940276</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.3029986418549</v>
+        <v>1.337616501102265</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7885583786982111</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.24770248541105</v>
+        <v>3.236667383959878</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.591787517032311</v>
+        <v>-3.505242868913898</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.332442297639311</v>
+        <v>1.367060156886677</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7885583786982111</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.242648755984911</v>
+        <v>3.231613654533738</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.637094336431291</v>
+        <v>-3.550549688312878</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.306095345324245</v>
+        <v>1.34071320457161</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7477482156889803</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.209938433623898</v>
+        <v>3.198903332172725</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.666127441133592</v>
+        <v>-3.57958279301518</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.295033976476426</v>
+        <v>1.329651835723791</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7477482156889803</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.210490306656999</v>
+        <v>3.199455205205827</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.573316959682733</v>
+        <v>-3.48677231156432</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.261430860948135</v>
+        <v>1.2960487201955</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8405586971398397</v>
+        <v>0.8221668613878851</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.195449287418881</v>
+        <v>3.184414185967708</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.617706429012161</v>
+        <v>-3.531161780893748</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.245548549140965</v>
+        <v>1.28016640838833</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.796169227810412</v>
+        <v>0.7777773920584574</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.170689081745825</v>
+        <v>3.159653980294652</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.597202735126663</v>
+        <v>-3.510658087008251</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.248825735206887</v>
+        <v>1.283443594454252</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.8166729216959093</v>
+        <v>0.7982810859439547</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.178067006588846</v>
+        <v>3.167031905137673</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.637126829709235</v>
+        <v>-3.550582181590823</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.238347393204525</v>
+        <v>1.272965252451891</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.8166729216959093</v>
+        <v>0.7982810859439547</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.183558302419514</v>
+        <v>3.172523200968341</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.664907227610589</v>
+        <v>-3.578362579492176</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.238732435812523</v>
+        <v>1.273350295059889</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7888925237945563</v>
+        <v>0.7705006880426017</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.178387265447241</v>
+        <v>3.167352163996068</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.783287900340727</v>
+        <v>-3.696743252222314</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.029735886721121</v>
+        <v>1.064353745968486</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7216746716435801</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.976412274157308</v>
+        <v>2.965377172706136</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.891901978784058</v>
+        <v>-3.805357330665645</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.106439916062994</v>
+        <v>1.141057775310359</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7216746716435801</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.096561934876514</v>
+        <v>3.085526833425341</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.856492940535915</v>
+        <v>-3.769948292417503</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.135116557464575</v>
+        <v>1.16973441671194</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7216746716435801</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.111074960978837</v>
+        <v>3.100039859527664</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.818109277977764</v>
+        <v>-3.731564629859351</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.147889463830204</v>
+        <v>1.182507323077569</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7600583342017313</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.131524599856097</v>
+        <v>3.120489498404924</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.640992947942598</v>
+        <v>-3.554448299824185</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.215465024689572</v>
+        <v>1.250082883936937</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7600583342017313</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.128253628701398</v>
+        <v>3.117218527250226</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.686085192776143</v>
+        <v>-3.599540544657731</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.198111518518067</v>
+        <v>1.232729377765432</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6981622910323415</v>
+        <v>0.6797704552803869</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.091799394561678</v>
+        <v>3.080764293110505</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.506709771537376</v>
+        <v>-3.420165123418963</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.263648662319988</v>
+        <v>1.298266521567354</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8549390492030602</v>
+        <v>0.8365472134511056</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.179652424770523</v>
+        <v>3.16861732331935</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982222</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.551723985057982</v>
+        <v>-3.465179336939569</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.226450432243336</v>
+        <v>1.261068291490701</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8245901538884556</v>
+        <v>0.806198318136501</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.14225054291335</v>
+        <v>3.131215441462177</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.818728495330417</v>
+        <v>-3.732183847212005</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.125340190473307</v>
+        <v>1.159958049720673</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6302271158455071</v>
+        <v>0.6118352800935525</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.031324282426527</v>
+        <v>3.020289180975354</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.91992627676759</v>
+        <v>-3.833381628649177</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.084064999794939</v>
+        <v>1.118682859042305</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5618183023001879</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.989482916195837</v>
+        <v>2.978447814744664</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.913415310153277</v>
+        <v>-3.826870662034865</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.084269347994981</v>
+        <v>1.118887207242347</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5618183023001879</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.987082877750153</v>
+        <v>2.976047776298981</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.89437718244598</v>
+        <v>-3.807832534327567</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.088409318286145</v>
+        <v>1.12302717753351</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.5036346909689934</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.948697430159682</v>
+        <v>2.937662328708509</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131244</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.9468929847208</v>
+        <v>-3.860348336602387</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.186697399010407</v>
+        <v>1.221315258257773</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.5036346909689934</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.067991831793872</v>
+        <v>3.056956730342699</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.72244736206786</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.95030129615538</v>
+        <v>-3.863756648036967</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.186167403422709</v>
+        <v>1.220785262670074</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5361512599783708</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.088335102185632</v>
+        <v>3.077300000734459</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.930945160261533</v>
+        <v>-3.84440051214312</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.199918388177174</v>
+        <v>1.234536247424539</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5361512599783708</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.094343632582558</v>
+        <v>3.083308531131385</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.783202190026531</v>
+        <v>-3.696657541908118</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.156965797548374</v>
+        <v>1.191583656795739</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.7039586172132539</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.092978268200687</v>
+        <v>3.081943166749515</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181163</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.867023411301229</v>
+        <v>-3.780478763182816</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.126230930569976</v>
+        <v>1.160848789817341</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.7039586172132539</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.095771889732168</v>
+        <v>3.084736788280996</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.860870705248444</v>
+        <v>-3.774326057130032</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.129354361382748</v>
+        <v>1.163972220630113</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.7101113232660382</v>
+        <v>0.6917194875140836</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.100125861755497</v>
+        <v>3.089090760304325</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890606</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.877680003398946</v>
+        <v>-3.791135355280533</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.121711118862658</v>
+        <v>1.156328978110023</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6933020251155366</v>
+        <v>0.674910189363582</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.089120759605307</v>
+        <v>3.078085658154134</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798421</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.815382004622824</v>
+        <v>-3.728837356504411</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.212965872169927</v>
+        <v>1.247583731417293</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7385962893899787</v>
+        <v>0.7202044536380241</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.182632871966792</v>
+        <v>3.17159777051562</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.613591806957666</v>
+        <v>-3.527047158839253</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.095973952950118</v>
+        <v>1.130591812197483</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9366144815591331</v>
+        <v>0.9182226458071785</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.103735788982412</v>
+        <v>3.09270068753124</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852418</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.664478519643861</v>
+        <v>-3.577933871525448</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.145909500197815</v>
+        <v>1.18052735944518</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8857277688729386</v>
+        <v>0.867335933120984</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.143493993692871</v>
+        <v>3.132458892241698</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319537</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.577867776994053</v>
+        <v>-3.491323128875641</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.195181533373781</v>
+        <v>1.229799392621147</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9643535000780968</v>
+        <v>0.9459616643261423</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.20529716853201</v>
+        <v>3.194262067080837</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489377</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.638077074999338</v>
+        <v>-3.551532426880925</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.169633794996339</v>
+        <v>1.204251654243705</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.9041442020728123</v>
+        <v>0.8857523663208577</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.16770757055351</v>
+        <v>3.156672469102338</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397786</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.588890426314987</v>
+        <v>-3.502345778196574</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.187800072510008</v>
+        <v>1.222417931757374</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.9041442020728123</v>
+        <v>0.8857523663208577</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.166199188593439</v>
+        <v>3.155164087142266</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316241</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.544517294676418</v>
+        <v>-3.457972646558005</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.205412192600872</v>
+        <v>1.240030051848237</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9485173337113809</v>
+        <v>0.9301254979594263</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.192685935012016</v>
+        <v>3.181650833560844</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.82156211710596</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.566997645535303</v>
+        <v>-3.48045299741689</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.190813846395909</v>
+        <v>1.225431705643274</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9485173337113809</v>
+        <v>0.9301254979594263</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.187079729150607</v>
+        <v>3.176044627699434</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190318</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.519341914974247</v>
+        <v>-3.432797266855834</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.216257895648136</v>
+        <v>1.250875754895501</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9961730642724365</v>
+        <v>0.977781228520482</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.222054924515045</v>
+        <v>3.211019823063872</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.82267821056961</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.418823756475492</v>
+        <v>-3.33227910835708</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.261357532422362</v>
+        <v>1.295975391669728</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.096691222771191</v>
+        <v>1.078299387019237</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.287258192989023</v>
+        <v>3.27622309153785</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.40291842704314</v>
+        <v>-3.316373778924727</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.254474336671176</v>
+        <v>1.289092195918541</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.017578562061952</v>
+        <v>0.9991867263099976</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.226545269039351</v>
+        <v>3.215510167588179</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932762</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.358080025434742</v>
+        <v>-3.271535377316329</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.276507399925163</v>
+        <v>1.311125259172529</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.022121995006822</v>
+        <v>1.003730159254867</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.233369031416902</v>
+        <v>3.222333929965729</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917044</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.37757848167675</v>
+        <v>-3.291033833558337</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.272868957059438</v>
+        <v>1.307486816306803</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9740373537269174</v>
+        <v>0.9556455179749628</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.208679186280037</v>
+        <v>3.197644084828864</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.333375644590849</v>
+        <v>-3.246830996472437</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.296429694421636</v>
+        <v>1.331047553669001</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.018240190812818</v>
+        <v>0.9998483550608632</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.241080491059414</v>
+        <v>3.230045389608242</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.340935310427896</v>
+        <v>-3.254390662309484</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.291815828556064</v>
+        <v>1.32643368780343</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.073043594822637</v>
+        <v>1.054651759070683</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.272372533934553</v>
+        <v>3.261337432483381</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.182643892888624</v>
+        <v>-3.096099244770211</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.406380160754813</v>
+        <v>1.440998020002178</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.073043594822637</v>
+        <v>1.054651759070683</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.323620299117593</v>
+        <v>3.31258519766642</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.975001889254148</v>
+        <v>-2.888457241135735</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.487877666802856</v>
+        <v>1.522495526050222</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.280685598457113</v>
+        <v>1.262293762705159</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.446646205892532</v>
+        <v>3.435611104441359</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.92396979653162</v>
+        <v>-2.837425148413207</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.503238732130138</v>
+        <v>1.537856591377503</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.331717691179641</v>
+        <v>1.313325855427687</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.472213689764319</v>
+        <v>3.461178588313146</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.858745615404414</v>
+        <v>-2.772200967286001</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.546515808673725</v>
+        <v>1.58113366792109</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.396941872306847</v>
+        <v>1.378550036554892</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.528535602533347</v>
+        <v>3.517500501082174</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.84006118688255</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.82131859533328</v>
+        <v>-2.734773947214868</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.557447589001459</v>
+        <v>1.592065448248824</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.402193410336029</v>
+        <v>1.383801574584074</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.527647497650137</v>
+        <v>3.516612396198964</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992653</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.841430251367989</v>
+        <v>-2.754885603249576</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.550659718918816</v>
+        <v>1.585277578166181</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.413220755333448</v>
+        <v>1.394828919581493</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.535520696979829</v>
+        <v>3.524485595528656</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636279</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.813016988268105</v>
+        <v>-2.726472340149692</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.72258279517998</v>
+        <v>1.757200654427345</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.354245192587019</v>
+        <v>1.335853356835065</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.660693130353182</v>
+        <v>3.649658028902009</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957618</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.738234727243092</v>
+        <v>-2.65169007912468</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.872608608807802</v>
+        <v>1.907226468055168</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.429027453612032</v>
+        <v>1.410635617860077</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.825675396186007</v>
+        <v>3.814640294734834</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998749</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.712150642979284</v>
+        <v>-2.625605994860872</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.874750218527184</v>
+        <v>1.90936807777455</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.429027453612032</v>
+        <v>1.410635617860077</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.817383372199866</v>
+        <v>3.806348270748693</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.624272729870164</v>
+        <v>-2.537728081751751</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.908094579354612</v>
+        <v>1.942712438601977</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.544953096035383</v>
+        <v>1.526561260283428</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.885131953237656</v>
+        <v>3.874096851786483</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.61538026847688</v>
+        <v>-2.528835620358468</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.929205969638717</v>
+        <v>1.963823828886082</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.544953096035383</v>
+        <v>1.526561260283428</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.902686358964447</v>
+        <v>3.891651257513274</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.783856385446758</v>
+        <v>-2.697311737328346</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.85367057025535</v>
+        <v>1.888288429502715</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.517005260318802</v>
+        <v>1.498613424566847</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.877772704939082</v>
+        <v>3.86673760348791</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.337600192817318</v>
+        <v>-2.251055544698906</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.013442744494987</v>
+        <v>2.048060603742353</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.422286590649169</v>
+        <v>1.403894754897215</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.802211200325165</v>
+        <v>3.791176098873992</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632637</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.314879089134166</v>
+        <v>-2.228334441015753</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.013195208465153</v>
+        <v>2.047813067712518</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.422286590649169</v>
+        <v>1.403894754897215</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.792875222822069</v>
+        <v>3.781840121370896</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777674</v>
+        <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.444080902428208</v>
+        <v>-2.357536254309796</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.120420608998705</v>
+        <v>2.155038468246071</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.293084777355127</v>
+        <v>1.274692941603172</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.874260260696813</v>
+        <v>3.86322515924564</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.469955300902234</v>
+        <v>-2.383410652783821</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.147148672102742</v>
+        <v>2.181766531350107</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.337996386066868</v>
+        <v>1.319604550314914</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.938285048417504</v>
+        <v>3.927249946966332</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.46290061068706</v>
+        <v>-2.376355962568648</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.146645904178356</v>
+        <v>2.181263763425721</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.345051076282042</v>
+        <v>1.326659240530087</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.939193218536154</v>
+        <v>3.928158117084981</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.435949386360572</v>
+        <v>-2.34940473824216</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.167432547553693</v>
+        <v>2.202050406801058</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.359931422309761</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.958127579797527</v>
+        <v>3.947092478346354</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.457493614191359</v>
+        <v>-2.370948966072947</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.342917988566338</v>
+        <v>2.377535847813703</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.359931422309761</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.142230711942487</v>
+        <v>4.131195610491313</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.479901731996232</v>
+        <v>-2.393357083877819</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.326071436347382</v>
+        <v>2.360689295594747</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.359931422309761</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.13434740684548</v>
+        <v>4.123312305394307</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.508125967573832</v>
+        <v>-2.421581319455419</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.316835741665979</v>
+        <v>2.351453600913344</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.37790817476107</v>
+        <v>1.359516339009115</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.147187457865902</v>
+        <v>4.13615235641473</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.72945228516197</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.517566893462362</v>
+        <v>-2.431022245343949</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.369313089032414</v>
+        <v>2.403930948279779</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.500335292304461</v>
+        <v>1.481943456552507</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.276897446113784</v>
+        <v>4.265862344662612</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321627</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.606443524630836</v>
+        <v>-2.519898876512423</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.336653531110326</v>
+        <v>2.371271390357691</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.411458661135987</v>
+        <v>1.393066825384033</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.226462561958001</v>
+        <v>4.215427460506828</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.682773502231742</v>
+        <v>-2.596228854113329</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304233352963738</v>
+        <v>2.338851212211104</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.411458661135987</v>
+        <v>1.393066825384033</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.224574374851776</v>
+        <v>4.213539273400603</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887741</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.776437446909283</v>
+        <v>-2.68989279879087</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.261588004695584</v>
+        <v>2.29620586394295</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.317794716458446</v>
+        <v>1.299402880706491</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.163196237648114</v>
+        <v>4.15216113619694</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343059</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.938005872436538</v>
+        <v>-2.851461224318125</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.195394644694835</v>
+        <v>2.2300125039422</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.191011792660567</v>
+        <v>1.172619956908612</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.085560493579538</v>
+        <v>4.074525392128366</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389342</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.046306534306658</v>
+        <v>-2.959761886188245</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.165147786812705</v>
+        <v>2.199765646060071</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.191011792660567</v>
+        <v>1.172619956908612</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.098633900445456</v>
+        <v>4.087598798994284</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378385</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.064110506027402</v>
+        <v>-2.977565857908989</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.150031394907348</v>
+        <v>2.184649254154713</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.120477169755365</v>
+        <v>1.102085334003411</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.048318323485276</v>
+        <v>4.037283222034104</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006969</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.092011293136875</v>
+        <v>-3.005466645018462</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.13739512119056</v>
+        <v>2.172012980437926</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.085880245612431</v>
+        <v>1.067488409860476</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.026084210126517</v>
+        <v>4.015049108675345</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787382</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.214537395839768</v>
+        <v>-3.127992747721356</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.085149124086602</v>
+        <v>2.119766983333967</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9633541429095369</v>
+        <v>0.9449623071575823</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.949332992481979</v>
+        <v>3.938297891030807</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585931</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.445051892025357</v>
+        <v>-3.358507243906945</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.05964928520287</v>
+        <v>2.094267144450235</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7328396467239482</v>
+        <v>0.7144478109719936</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.87773025436113</v>
+        <v>3.866695152909958</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.64075008781466</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.793796977249801</v>
+        <v>-3.707252329131388</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.06046297011494</v>
+        <v>2.095080829362304</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6240916928050504</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.952793201011638</v>
+        <v>3.941758099560466</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.66828900423709</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.947783395025942</v>
+        <v>-3.861238746907529</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.067848672150123</v>
+        <v>2.102466531397488</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6240916928050504</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.021773470157278</v>
+        <v>4.010738368706106</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.15238282988895</v>
+        <v>-4.065838181770538</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.972060100325041</v>
+        <v>2.006677959572406</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6240916928050504</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.007824672277399</v>
+        <v>3.996789570826227</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.404857983896674</v>
+        <v>-4.318313335778262</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.882940527777365</v>
+        <v>1.91755838702473</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6240916928050504</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.019695161332813</v>
+        <v>4.008660059881641</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973152</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.697753740376086</v>
+        <v>-4.611209092257674</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.766992759704544</v>
+        <v>1.801610618951909</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6240916928050504</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.020905695851757</v>
+        <v>4.009870594400584</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.66350945725194</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.884417868510894</v>
+        <v>-4.797873220392482</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.696448850677942</v>
+        <v>1.731066709925307</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5973527219804905</v>
+        <v>0.5789608862285359</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.008984055584342</v>
+        <v>3.99794895413317</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916195</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.030438555424857</v>
+        <v>-4.943893907306444</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.633118428648547</v>
+        <v>1.667736287895912</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5882696301866335</v>
+        <v>0.5698777944346789</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.998612053244218</v>
+        <v>3.987576951793045</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830331</v>
+        <v>3.667962306830321</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.122152564534441</v>
+        <v>-5.03560791641603</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.758636881703757</v>
+        <v>1.793254740951121</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5882696301866335</v>
+        <v>0.5698777944346789</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.160816109943262</v>
+        <v>4.149781008492089</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071544</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.153804223594411</v>
+        <v>-5.067259575475999</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.740822856043583</v>
+        <v>1.775440715290948</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5831011729421933</v>
+        <v>0.5647093371902387</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.152561673560411</v>
+        <v>4.141526572109239</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868138</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.235739041863294</v>
+        <v>-5.149194393744883</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.718278346304521</v>
+        <v>1.752896205551886</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5731664273551131</v>
+        <v>0.5547745916031586</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.156830243776655</v>
+        <v>4.145795142325482</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332683</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.337715164111701</v>
+        <v>-5.25117051599329</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.68641353586106</v>
+        <v>1.721031395108425</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4711903051067056</v>
+        <v>0.452798469354751</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.104570208883513</v>
+        <v>4.09353510743234</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231799</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.22770888063448</v>
+        <v>-5.141164232516068</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.722568936496124</v>
+        <v>1.757186795743489</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4943948770239808</v>
+        <v>0.4760030412720262</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.110645839278053</v>
+        <v>4.099610737826881</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818514</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.084649304893554</v>
+        <v>-4.998104656775142</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.784042777514469</v>
+        <v>1.818660636761834</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.50240830361396</v>
+        <v>0.4840164678620055</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.119703905954015</v>
+        <v>4.108668804502843</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051781</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.783202579421716</v>
+        <v>-4.696657931303305</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.91188235058574</v>
+        <v>1.946500209833105</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8038550290857973</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.307832824119654</v>
+        <v>4.29679772266848</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679618</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.8077928236569</v>
+        <v>-4.721248175538489</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.903017430644377</v>
+        <v>1.937635289891742</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8038550290857973</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.308804001872364</v>
+        <v>4.297768900421191</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.75675444765038</v>
+        <v>-4.670209799531968</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.924275685426741</v>
+        <v>1.958893544674106</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8038550290857973</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.309646906252119</v>
+        <v>4.298611804800947</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969536</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.715615152783749</v>
+        <v>-4.629070504665338</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.959769502247538</v>
+        <v>1.994387361494903</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8449943239524281</v>
+        <v>0.8266024882004736</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.353368582046244</v>
+        <v>4.34233348059507</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.82575293270047</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.618980240765109</v>
+        <v>-4.532435592646697</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.814607463178929</v>
+        <v>1.849225322426294</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9416292359710681</v>
+        <v>0.9232374002191135</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.227533525381362</v>
+        <v>4.216498423930189</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077632</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.749560975295951</v>
+        <v>-4.66301632717754</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.765877213440556</v>
+        <v>1.800495072687921</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8110485014402256</v>
+        <v>0.792656665688271</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.152687128736821</v>
+        <v>4.141652027285648</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.77502886083345</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.58506464110499</v>
+        <v>-4.498519992986578</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.816102566193023</v>
+        <v>1.850720425440388</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9755448356311874</v>
+        <v>0.9571529998792329</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.23581174832748</v>
+        <v>4.224776646876307</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077621</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.507966039563117</v>
+        <v>-4.421421391444706</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.846129717246202</v>
+        <v>1.880747576493567</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9755448356311874</v>
+        <v>0.9571529998792329</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.23499945876391</v>
+        <v>4.223964357312737</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.518351234453006</v>
+        <v>-4.431806586334595</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.851844418415319</v>
+        <v>1.886462277662684</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9651596407412981</v>
+        <v>0.9467678049893435</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.238637120955049</v>
+        <v>4.227602019503876</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735273</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.536939393175231</v>
+        <v>-4.45039474505682</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.915246160702854</v>
+        <v>1.949864019950219</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9465714820190727</v>
+        <v>0.9281796462671181</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.298321231498138</v>
+        <v>4.287286130046966</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.537237939871267</v>
+        <v>-4.450693291752856</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.911995752842738</v>
+        <v>1.946613612090103</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9462729353230368</v>
+        <v>0.9278810995710822</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.295011114298815</v>
+        <v>4.283976012847643</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108848</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.436414806180839</v>
+        <v>-4.349870158062428</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.956855901258301</v>
+        <v>1.991473760505666</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9587371508073906</v>
+        <v>0.9403453150554361</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.307020538528819</v>
+        <v>4.295985437077647</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121458</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.245633445428433</v>
+        <v>-4.159088797310021</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.033297699037807</v>
+        <v>2.067915558285172</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.149518511559798</v>
+        <v>1.131126675807844</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.421618608458807</v>
+        <v>4.410583507007635</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906071</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.138670087579011</v>
+        <v>-4.0521254394606</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.055919887915172</v>
+        <v>2.090537747162537</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.2079831195196</v>
+        <v>1.189591283767645</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.436534218972285</v>
+        <v>4.425499117521112</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912976</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.083339499677249</v>
+        <v>-3.996794851558838</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.113019059687935</v>
+        <v>2.1476369189353</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.263313707421362</v>
+        <v>1.244921871669407</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.5046995083254</v>
+        <v>4.493664406874228</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539886</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.071285372764286</v>
+        <v>-3.984740724645875</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.111527278354558</v>
+        <v>2.146145137601923</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.275367834334324</v>
+        <v>1.25697599858237</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.505618552374616</v>
+        <v>4.494583450923443</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.112440492332507</v>
+        <v>-4.025895844214096</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.096945860711406</v>
+        <v>2.13156371995877</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.234212714766104</v>
+        <v>1.215820879014149</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.482806110817819</v>
+        <v>4.471771009366647</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382911</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.044391929640977</v>
+        <v>-3.957847281522566</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.1370163116659</v>
+        <v>2.171634170913265</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.302261277457633</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.53648627431062</v>
+        <v>4.525451172859447</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001343</v>
+        <v>3.645256780013418</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.275992322810477</v>
+        <v>-4.189447674692067</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.064578824571694</v>
+        <v>2.099196683819058</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.302261277457633</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.556688944484214</v>
+        <v>4.545653843033041</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498963</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.326043868339696</v>
+        <v>-4.239499220221287</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.028164442426888</v>
+        <v>2.062782301674253</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.302261277457633</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.540295180551095</v>
+        <v>4.529260079099923</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800092</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.501150700916141</v>
+        <v>-4.414606052797732</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.918373622989777</v>
+        <v>1.952991482237142</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.302261277457633</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.500547094144562</v>
+        <v>4.48951199269339</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660845</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.305050547485618</v>
+        <v>-4.218505899367209</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.003836303358926</v>
+        <v>2.038454162606291</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.498361430888156</v>
+        <v>1.479969595136202</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.625229805199816</v>
+        <v>4.614194703748644</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395082</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.152025155372334</v>
+        <v>-4.065480507253924</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.164217459777145</v>
+        <v>2.198835319024509</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.65138682300144</v>
+        <v>1.632994987249486</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.816216040040691</v>
+        <v>4.805180938589518</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.741278332791143</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.180332469245604</v>
+        <v>-4.093787821127195</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.340360759136129</v>
+        <v>2.374978618383493</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.65138682300144</v>
+        <v>1.632994987249486</v>
       </c>
       <c r="G2052" t="n">
-        <v>5.003682264948983</v>
+        <v>4.992647163497811</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620429</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.346925694359126</v>
+        <v>-4.260381046240717</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.243126420444803</v>
+        <v>2.277744279692167</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.484793597887918</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.873129281234952</v>
+        <v>4.86209417978378</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285643</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.32388990099756</v>
+        <v>-4.237345252879151</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.256017140451147</v>
+        <v>2.29063499969851</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.484793597887918</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.87680568389667</v>
+        <v>4.865770582445498</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399464</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.294643920541864</v>
+        <v>-4.208099272423454</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.265333587756921</v>
+        <v>2.299951447004284</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.484793597887918</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.874423739020165</v>
+        <v>4.863388637568993</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256366</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.401569468419715</v>
+        <v>-4.315024820301305</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.219856607763415</v>
+        <v>2.254474467010779</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.377868050010067</v>
+        <v>1.359476214258112</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.80756164945109</v>
+        <v>4.796526547999917</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600700995</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.546588026926964</v>
+        <v>-4.460043378808554</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.16327798650375</v>
+        <v>2.197895845751114</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.232849491502818</v>
+        <v>1.214457655750864</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.721979316489975</v>
+        <v>4.710944215038802</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687006</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.664929792711681</v>
+        <v>-4.578385144593272</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.215872519447616</v>
+        <v>2.25049037869498</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.243535530065708</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.828322178885462</v>
+        <v>4.817287077434289</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790805</v>
+        <v>3.714879051790796</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.716340215032389</v>
+        <v>-4.629795566913979</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.193094047645271</v>
+        <v>2.227711906892635</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.243535530065708</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.826107876011401</v>
+        <v>4.815072774560227</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.704757949437324</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.795759666240141</v>
+        <v>-4.709215018121731</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.16122939523646</v>
+        <v>2.195847254483824</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.243535530065708</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.82601100408569</v>
+        <v>4.814975902634517</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.7368049522984</v>
+        <v>3.736804952298391</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.891222664157358</v>
+        <v>-4.804678016038949</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.123038089627617</v>
+        <v>2.15765594887498</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.243535530065708</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.826004897643734</v>
+        <v>4.81496979619256</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218003</v>
+        <v>3.715372960217993</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.826846753306643</v>
+        <v>-4.740302105188234</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.146884850530513</v>
+        <v>2.181502709777877</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.307911440916423</v>
+        <v>1.289519605164469</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.862726840716773</v>
+        <v>4.8516917392656</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353539</v>
+        <v>3.736089413353528</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.882215915438837</v>
+        <v>-4.795671267320428</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.130471003425362</v>
+        <v>2.165088862672726</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.307911440916423</v>
+        <v>1.289519605164469</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.8684606584645</v>
+        <v>4.857425557013327</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113282</v>
+        <v>3.736822870113271</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.927653695269664</v>
+        <v>-4.841109047151255</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.111834254835963</v>
+        <v>2.146452114083328</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.265066450238264</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.842292027400536</v>
+        <v>4.831256925949363</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113691</v>
+        <v>3.79027250011368</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.839446861122086</v>
+        <v>-4.752902213003677</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.166991381345314</v>
+        <v>2.201609240592678</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.265066450238264</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.862166420250855</v>
+        <v>4.851131318799682</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016434</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.733411865916777</v>
+        <v>-4.646867217798367</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.193106079952165</v>
+        <v>2.22772393919953</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.265066450238264</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.845867120775583</v>
+        <v>4.83483201932441</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307665</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.550200202783682</v>
+        <v>-4.463655554665272</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.268821694669449</v>
+        <v>2.303439553916813</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.265066450238264</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.848298070239628</v>
+        <v>4.837262968788456</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863546</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.478478755769831</v>
+        <v>-4.391934107651421</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.263301459322879</v>
+        <v>2.297919318570243</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.336787897252115</v>
+        <v>1.31839606150016</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.857122124295828</v>
+        <v>4.846087022844656</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394107</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.456105730162125</v>
+        <v>-4.369561082043715</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.219166415487133</v>
+        <v>2.253784274734497</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.348043648365016</v>
+        <v>1.329651812613061</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.810791320884741</v>
+        <v>4.799756219433569</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456723</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.489122026072869</v>
+        <v>-4.40257737795446</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.39115810200819</v>
+        <v>2.425775961255555</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.278606271698264</v>
+        <v>1.26021443594631</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.954327099770046</v>
+        <v>4.943291998318872</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883679</v>
+        <v>3.713762536883669</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.477594390423261</v>
+        <v>-4.391049742304851</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.387690382096283</v>
+        <v>2.422308241343647</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.337606929899627</v>
+        <v>1.319215094147672</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.981648720519112</v>
+        <v>4.970613619067939</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236289</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.574935891765629</v>
+        <v>-4.48839124364722</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.352421894081124</v>
+        <v>2.387039753328488</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.293186747734139</v>
+        <v>1.274794911982184</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.958664723741608</v>
+        <v>4.947629622290435</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427687</v>
+        <v>3.705201079427676</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.660791921105596</v>
+        <v>-4.574247272987186</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.319330564537975</v>
+        <v>2.35394842378534</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.250810678508004</v>
+        <v>1.232418842756049</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.934490164398765</v>
+        <v>4.923455062947592</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610375</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.669628718521715</v>
+        <v>-4.583084070403306</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.29821504739203</v>
+        <v>2.332832906639394</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.243368505866653</v>
+        <v>1.224976670114698</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.912444062634457</v>
+        <v>4.901408961183283</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.715544411667447</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.761011281087174</v>
+        <v>-4.674466632968764</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.271826533410896</v>
+        <v>2.30644439265826</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.206803621147308</v>
+        <v>1.188411785395354</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.900669642847899</v>
+        <v>4.889634541396726</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889194</v>
+        <v>3.673978374889183</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.749304563100168</v>
+        <v>-4.662759914981758</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.378637478429966</v>
+        <v>2.41325533767733</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.218510339134315</v>
+        <v>1.20011850338236</v>
       </c>
       <c r="G2076" t="n">
-        <v>5.009821931464371</v>
+        <v>4.998786830013198</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940957</v>
+        <v>3.682476099409559</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.649641059016505</v>
+        <v>-4.563096410898096</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.421535218794836</v>
+        <v>2.4561530780422</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.281697422338001</v>
+        <v>1.263305586586047</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.050766520117987</v>
+        <v>5.039731418666815</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452566</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.659957157182857</v>
+        <v>-4.573412509064448</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.630313612806353</v>
+        <v>2.664931472053718</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.281697422338001</v>
+        <v>1.263305586586047</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.263671353396045</v>
+        <v>5.252636251944873</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762279</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.659863189165485</v>
+        <v>-4.573318541047075</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.629529866925392</v>
+        <v>2.664147726172756</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.282067283685319</v>
+        <v>1.263675447933365</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.263071937116526</v>
+        <v>5.252036835665353</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988022</v>
+        <v>3.63321346798801</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.667082013365329</v>
+        <v>-4.580537365246919</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.620874323189808</v>
+        <v>2.655492182437173</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.282067283685319</v>
+        <v>1.263675447933365</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.25730392306088</v>
+        <v>5.246268821609707</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740916</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.66613359024729</v>
+        <v>-4.579588942128881</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.621253692437024</v>
+        <v>2.655871551684388</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.282067283685319</v>
+        <v>1.263675447933365</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.25730392306088</v>
+        <v>5.246268821609707</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.88106536666362</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.823202048502915</v>
+        <v>-4.736657400384505</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.571153917115866</v>
+        <v>2.60577177636323</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.282067283685319</v>
+        <v>1.263675447933365</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.270031531041972</v>
+        <v>5.258996429590799</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424764</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.817209801714103</v>
+        <v>-4.730665153595694</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.575496814255779</v>
+        <v>2.610114673503142</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.282067283685319</v>
+        <v>1.263675447933365</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.271977529466359</v>
+        <v>5.260942428015187</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149212</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.728651840583336</v>
+        <v>-4.642107192464926</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.604574134725854</v>
+        <v>2.639191993973219</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.282067283685319</v>
+        <v>1.263675447933365</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.265631665484128</v>
+        <v>5.254596564032956</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383085</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.710892763080262</v>
+        <v>-4.624348114961852</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.610986443166079</v>
+        <v>2.645604302413444</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.282067283685319</v>
+        <v>1.263675447933365</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.264940342923124</v>
+        <v>5.253905241471951</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.822637488317762</v>
+        <v>3.823325522419355</v>
       </c>
       <c r="C2086" t="n">
         <v>4.508482158620519</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.57471438664145</v>
+        <v>-4.48816973852304</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.678239979650191</v>
+        <v>2.712857838897555</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.418245660124131</v>
+        <v>1.399853824372176</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.359429554694998</v>
+        <v>5.348394453243825</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.3%</t>
+          <t>102.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>139.2%</t>
+          <t>140.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.4%</t>
+          <t>-630.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-104.9%</t>
+          <t>-117.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.7%</t>
+          <t>-326.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-84.0%</t>
+          <t>-95.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2024-09-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>107.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>5.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2086"/>
+  <dimension ref="A1:G2087"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>2.834009020654386</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.258687543445998</v>
+        <v>-6.307371425769619</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3729573637146681</v>
+        <v>0.3107040260327905</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1780292819166325</v>
+        <v>-0.1591699220614363</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769971236256836</v>
+        <v>2.738507067417524</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>2.825295034400908</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.205718021192009</v>
+        <v>-6.25440190351563</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3854311863627853</v>
+        <v>0.3231778486809076</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1062003998074474</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793038963355751</v>
+        <v>2.761574794516439</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>2.818334422305814</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.039929825231718</v>
+        <v>-6.088613707555339</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4447858526518087</v>
+        <v>0.3825325149699306</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1062003998074474</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786078351260658</v>
+        <v>2.754614182421346</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>2.832796776686958</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.00656661875295</v>
+        <v>-6.05525050107657</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4725934896244595</v>
+        <v>0.4103401519425813</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1062003998074474</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800540705641801</v>
+        <v>2.769076536802489</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>2.827328897146153</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.898307481630428</v>
+        <v>-5.946991363954049</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5104292649326632</v>
+        <v>0.448175927250785</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1062003998074474</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795072826100996</v>
+        <v>2.763608657261684</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>2.824826991156729</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.775016346813297</v>
+        <v>-5.823700229136918</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5572438128700923</v>
+        <v>0.4949904751882142</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.001768624845513156</v>
+        <v>0.01709073500968311</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866545601001851</v>
+        <v>2.83508143216254</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>2.832527969394055</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.722319479682006</v>
+        <v>-5.771003362005627</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5860235379599339</v>
+        <v>0.5237702002780558</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.06978760214097429</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.905864699517951</v>
+        <v>2.874400530678639</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>2.828308677741105</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.478554037698562</v>
+        <v>-5.527237920022182</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6793104231003624</v>
+        <v>0.6170570854184843</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.06978760214097429</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.901645407865002</v>
+        <v>2.87018123902569</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>2.830432991661121</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.388778365322089</v>
+        <v>-5.43746224764571</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7173450059709672</v>
+        <v>0.655091668289089</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1313870470552843</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.940729388733604</v>
+        <v>2.909265219894292</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>2.823175066644823</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.138927971373015</v>
+        <v>-5.187611853696636</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8100272385342993</v>
+        <v>0.7477739008524211</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1313870470552843</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.933471463717306</v>
+        <v>2.902007294877994</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>2.826774190165472</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.963035878905583</v>
+        <v>-5.011719761229203</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8839831990419207</v>
+        <v>0.8217298613600428</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1313870470552843</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.937070587237955</v>
+        <v>2.905606418398643</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>2.840101696220026</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.791589415883119</v>
+        <v>-4.84027329820674</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9658892903054599</v>
+        <v>0.9036359526235818</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2839741502225512</v>
+        <v>0.3028335100777474</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053265971105986</v>
+        <v>3.021801802266674</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>2.839122173836323</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.711567128773998</v>
+        <v>-4.760251011097619</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9969186827654051</v>
+        <v>0.9346653450835272</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3639964373316721</v>
+        <v>0.3828557971868684</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100299820987756</v>
+        <v>3.068835652148444</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>2.84381697489064</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.647931386540064</v>
+        <v>-4.696615268863685</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.027067780713296</v>
+        <v>0.9648144430314183</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4464915394208029</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.143176067382434</v>
+        <v>3.111711898543122</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>2.825011233674436</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.554234068323669</v>
+        <v>-4.602917950647289</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.04574096678365</v>
+        <v>0.983487629101772</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4464915394208029</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124370326166229</v>
+        <v>3.092906157326918</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>2.826754310299313</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.564736691388958</v>
+        <v>-4.613420573712578</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.043282994182412</v>
+        <v>0.9810296565005339</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.4359889163555141</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119811828951934</v>
+        <v>3.088347660112622</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>2.830683624134133</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.452250430720083</v>
+        <v>-4.500934313043704</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.092206812284782</v>
+        <v>1.029953474602904</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.4359889163555141</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123741142786754</v>
+        <v>3.092276973947442</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>2.831362208051473</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.434536743842218</v>
+        <v>-4.483220626165838</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.099970870953268</v>
+        <v>1.03771753327139</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4391702452524309</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126328524042244</v>
+        <v>3.094864355202932</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>2.828360279271467</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.311062472529199</v>
+        <v>-4.35974635485282</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.146358650698469</v>
+        <v>1.084105313016591</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4391702452524309</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123326595262237</v>
+        <v>3.091862426422926</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>2.829939316282081</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.091041674492189</v>
+        <v>-4.13972555681581</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.235946006923887</v>
+        <v>1.173692669242009</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5803900903204111</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.20963753931364</v>
+        <v>3.178173370474328</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>2.845833499083904</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.958173985428911</v>
+        <v>-4.006857867752531</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.304987265351021</v>
+        <v>1.242733927669144</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5803900903204111</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225531722115463</v>
+        <v>3.194067553276151</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>2.846979343524206</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.838000902064412</v>
+        <v>-3.886684784388032</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.354202343137123</v>
+        <v>1.291949005455245</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6817038138297138</v>
+        <v>0.7005631736849101</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298781416574464</v>
+        <v>3.267317247735153</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>2.857067446085646</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.702747540734435</v>
+        <v>-3.751431423058055</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.418391790230554</v>
+        <v>1.356138452548676</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8169571751596909</v>
+        <v>0.8358165350148872</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.390021535933891</v>
+        <v>3.358557367094579</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>2.843104937487072</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.762622368092127</v>
+        <v>-3.811306250415747</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.380479350688903</v>
+        <v>1.318226013007025</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7759417076571951</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.340134130920701</v>
+        <v>3.308669962081389</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>2.85839410672128</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.64280213718129</v>
+        <v>-3.69148601950491</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.443696612287446</v>
+        <v>1.381443274605568</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7759417076571951</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355423300154909</v>
+        <v>3.323959131315598</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>2.766038306043722</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.645271843643096</v>
+        <v>-3.693955725966716</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.350352929025165</v>
+        <v>1.288099591343287</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7546126413401926</v>
+        <v>0.7734720011953888</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261585675600267</v>
+        <v>3.230121506760955</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>2.685300167529023</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.713642029967105</v>
+        <v>-3.762325912290726</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.242266715980863</v>
+        <v>1.180013378298985</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7827477002316038</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186412956507298</v>
+        <v>3.154948787667986</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.675736876160915</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.785495712198642</v>
+        <v>-3.840702314217968</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.203961951720139</v>
+        <v>1.139099526159979</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.79224708834082</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176849665139189</v>
+        <v>3.151085129165407</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.855547497605547</v>
+        <v>2.812767712853117</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.841015788091231</v>
+        <v>-3.896222390110557</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.318784758055306</v>
+        <v>1.253922332495146</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.79224708834082</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313880501831391</v>
+        <v>3.288115965857609</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.860114729597334</v>
+        <v>2.817334944844905</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.665541528298762</v>
+        <v>-3.720748130318088</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.393541693964081</v>
+        <v>1.328679268403921</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.79224708834082</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.318447733823179</v>
+        <v>3.292683197849397</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.835856758358541</v>
+        <v>2.793076973606112</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.657617153713848</v>
+        <v>-3.712823755733174</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.372453472559254</v>
+        <v>1.307591046999094</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.79224708834082</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.294189762584386</v>
+        <v>3.268425226610604</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.764395071759991</v>
+        <v>2.721615287007562</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.651338951143999</v>
+        <v>-3.706545553163325</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.303503066988644</v>
+        <v>1.238640641428483</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.798525290910669</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.226494997527745</v>
+        <v>3.200730461553963</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.774567458192124</v>
+        <v>2.731787673439694</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.591486331940276</v>
+        <v>-3.646692933959602</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.337616501102265</v>
+        <v>1.272754075542105</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.798525290910669</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.236667383959878</v>
+        <v>3.210902847986095</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.769513728765984</v>
+        <v>2.726733944013554</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.505242868913898</v>
+        <v>-3.560449470933225</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.367060156886677</v>
+        <v>1.302197731326516</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.798525290910669</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.231613654533738</v>
+        <v>3.205849118559956</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.761289504210509</v>
+        <v>2.71850971945808</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.550549688312878</v>
+        <v>-3.605756290332204</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.34071320457161</v>
+        <v>1.27585077901145</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7577151279014382</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.198903332172725</v>
+        <v>3.173138796198943</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.761841377243611</v>
+        <v>2.719061592491181</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.57958279301518</v>
+        <v>-3.634789395034506</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.329651835723791</v>
+        <v>1.264789410163631</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7577151279014382</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.199455205205827</v>
+        <v>3.173690669232045</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.691114069134977</v>
+        <v>2.648334284382547</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.48677231156432</v>
+        <v>-3.541978913583647</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.2960487201955</v>
+        <v>1.23118629463534</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8221668613878851</v>
+        <v>0.8505256093522976</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.184414185967708</v>
+        <v>3.158649649993926</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.692987545059577</v>
+        <v>2.650207760307148</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.531161780893748</v>
+        <v>-3.586368382913074</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.28016640838833</v>
+        <v>1.21530398282817</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7777773920584574</v>
+        <v>0.8061361400228699</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159653980294652</v>
+        <v>3.13388944432087</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.6880632535713</v>
+        <v>2.645283468818871</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.510658087008251</v>
+        <v>-3.565864689027577</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.283443594454252</v>
+        <v>1.218581168894092</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.8266398339083673</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.167031905137673</v>
+        <v>3.141267369163891</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.693554549401968</v>
+        <v>2.650774764649538</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.550582181590823</v>
+        <v>-3.605788783610149</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.272965252451891</v>
+        <v>1.20810282689173</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.8266398339083673</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.172523200968341</v>
+        <v>3.146758664994559</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.705051751170507</v>
+        <v>2.662271966418077</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.578362579492176</v>
+        <v>-3.633569181511502</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.273350295059889</v>
+        <v>1.208487869499728</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7705006880426017</v>
+        <v>0.7988594360070143</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.167352163996068</v>
+        <v>3.141587628022286</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.54340747117116</v>
+        <v>2.50062768641873</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.696743252222314</v>
+        <v>-3.751949854241641</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.064353745968486</v>
+        <v>0.999491320408326</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7316415838560381</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.965377172706136</v>
+        <v>2.939612636732353</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.663557131890366</v>
+        <v>2.620777347137936</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.805357330665645</v>
+        <v>-3.860563932684972</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.141057775310359</v>
+        <v>1.076195349750199</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7316415838560381</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.085526833425341</v>
+        <v>3.059762297451559</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.678070157992689</v>
+        <v>2.635290373240259</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.769948292417503</v>
+        <v>-3.825154894436829</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.16973441671194</v>
+        <v>1.104871991151779</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7316415838560381</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.100039859527664</v>
+        <v>3.074275323553882</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.675489599335057</v>
+        <v>2.632709814582628</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.731564629859351</v>
+        <v>-3.786771231878678</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.182507323077569</v>
+        <v>1.117644897517408</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7700252464141892</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.120489498404924</v>
+        <v>3.094724962431142</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.672218628180359</v>
+        <v>2.62943884342793</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.554448299824185</v>
+        <v>-3.609654901843512</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.250082883936937</v>
+        <v>1.185220458376777</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7700252464141892</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.117218527250226</v>
+        <v>3.091453991276444</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.672902019942272</v>
+        <v>2.630122235189843</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.599540544657731</v>
+        <v>-3.654747146677057</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.232729377765432</v>
+        <v>1.167866952205272</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6797704552803869</v>
+        <v>0.7081292032447994</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.080764293110505</v>
+        <v>3.054999757136723</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.666688995248687</v>
+        <v>2.623909210496257</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.420165123418963</v>
+        <v>-3.475371725438289</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.298266521567354</v>
+        <v>1.233404096007193</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8365472134511056</v>
+        <v>0.8649059614155181</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.16861732331935</v>
+        <v>3.142852787345568</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982222</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.647496450580276</v>
+        <v>2.604716665827847</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.465179336939569</v>
+        <v>-3.520385938958896</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.261068291490701</v>
+        <v>1.196205865930541</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.806198318136501</v>
+        <v>0.8345570661009135</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.131215441462177</v>
+        <v>3.105450905488395</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.653188012919222</v>
+        <v>2.610408228166793</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.732183847212005</v>
+        <v>-3.787390449231331</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.159958049720673</v>
+        <v>1.095095624160512</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6118352800935525</v>
+        <v>0.640194028057965</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.020289180975354</v>
+        <v>2.994524645001572</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760807</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.652391934815724</v>
+        <v>2.609612150063294</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.833381628649177</v>
+        <v>-3.888588230668504</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.118682859042305</v>
+        <v>1.053820433482144</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5717852145126459</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.978447814744664</v>
+        <v>2.952683278770882</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.64999189637004</v>
+        <v>2.607212111617611</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.826870662034865</v>
+        <v>-3.882077264054191</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.118887207242347</v>
+        <v>1.054024781682186</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5717852145126459</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.976047776298981</v>
+        <v>2.950283240325199</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.646516615578285</v>
+        <v>2.603736830825856</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.807832534327567</v>
+        <v>-3.863039136346894</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.12302717753351</v>
+        <v>1.05816475197335</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.5136016031814513</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.937662328708509</v>
+        <v>2.911897792734727</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131244</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.765811017212476</v>
+        <v>2.723031232460046</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.860348336602387</v>
+        <v>-3.915554938621714</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.221315258257773</v>
+        <v>1.156452832697612</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.5136016031814513</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.056956730342699</v>
+        <v>3.031192194368917</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.72244736206786</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.766644346198609</v>
+        <v>2.72386456144618</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.863756648036967</v>
+        <v>-3.918963250056294</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.220785262670074</v>
+        <v>1.155922837109914</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5461181721908287</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.077300000734459</v>
+        <v>3.051535464760677</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.772652876595535</v>
+        <v>2.729873091843106</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.84440051214312</v>
+        <v>-3.899607114162447</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.234536247424539</v>
+        <v>1.169673821864379</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5461181721908287</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.083308531131385</v>
+        <v>3.057543995157603</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519904</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.670603097872735</v>
+        <v>2.627823313120305</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.696657541908118</v>
+        <v>-3.751864143927444</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.191583656795739</v>
+        <v>1.126721231235579</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.7139255294257119</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.081943166749515</v>
+        <v>3.056178630775733</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181163</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.673396719404216</v>
+        <v>2.630616934651786</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.780478763182816</v>
+        <v>-3.835685365202143</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.160848789817341</v>
+        <v>1.095986364257181</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.7139255294257119</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.084736788280996</v>
+        <v>3.058972252307214</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394723</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.674059067795874</v>
+        <v>2.631279283043444</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.774326057130032</v>
+        <v>-3.829532659149358</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.163972220630113</v>
+        <v>1.099109795069953</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6917194875140836</v>
+        <v>0.7200782354784961</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.089090760304325</v>
+        <v>3.063326224330542</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890606</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.673139544535984</v>
+        <v>2.630359759783555</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.791135355280533</v>
+        <v>-3.84634195729986</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.156328978110023</v>
+        <v>1.091466552549863</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.674910189363582</v>
+        <v>0.7032689373279946</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.078085658154134</v>
+        <v>3.052321122180352</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798421</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.739475098332805</v>
+        <v>2.696695313580376</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.728837356504411</v>
+        <v>-3.784043958523738</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.247583731417293</v>
+        <v>1.182721305857132</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7202044536380241</v>
+        <v>0.7485632016024366</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.17159777051562</v>
+        <v>3.145833234541838</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.541767100046932</v>
+        <v>2.498987315294503</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.527047158839253</v>
+        <v>-3.58225376085858</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.130591812197483</v>
+        <v>1.065729386637323</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9182226458071785</v>
+        <v>0.946581393771591</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.09270068753124</v>
+        <v>3.066936151557457</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852418</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.612057332369107</v>
+        <v>2.569277547616678</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.577933871525448</v>
+        <v>-3.633140473544775</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.18052735944518</v>
+        <v>1.11566493388502</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.867335933120984</v>
+        <v>0.8956946810853965</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.132458892241698</v>
+        <v>3.106694356267916</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319537</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.626685068485151</v>
+        <v>2.583905283732721</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.491323128875641</v>
+        <v>-3.546529730894967</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.229799392621147</v>
+        <v>1.164936967060986</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9459616643261423</v>
+        <v>0.9743204122905548</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.194262067080837</v>
+        <v>3.168497531107055</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489377</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.625221049309823</v>
+        <v>2.582441264557393</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.551532426880925</v>
+        <v>-3.606739028900252</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.204251654243705</v>
+        <v>1.139389228683544</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.9141111142852703</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.156672469102338</v>
+        <v>3.130907933128555</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397786</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.623712667349751</v>
+        <v>2.580932882597322</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.502345778196574</v>
+        <v>-3.5575523802159</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.222417931757374</v>
+        <v>1.157555506197213</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.9141111142852703</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.155164087142266</v>
+        <v>3.129399551168484</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316241</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.623575534785187</v>
+        <v>2.580795750032758</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.457972646558005</v>
+        <v>-3.513179248577332</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.240030051848237</v>
+        <v>1.175167626288077</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9301254979594263</v>
+        <v>0.9584842459238389</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.181650833560844</v>
+        <v>3.155886297587061</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.82156211710596</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.617969328923778</v>
+        <v>2.575189544171348</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.48045299741689</v>
+        <v>-3.535659599436217</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.225431705643274</v>
+        <v>1.160569280083114</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9301254979594263</v>
+        <v>0.9584842459238389</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.176044627699434</v>
+        <v>3.150280091725652</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190318</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.624351085951583</v>
+        <v>2.581571301199153</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.432797266855834</v>
+        <v>-3.488003868875161</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.250875754895501</v>
+        <v>1.186013329335341</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.977781228520482</v>
+        <v>1.006139976484894</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.211019823063872</v>
+        <v>3.18525528709009</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.82267821056961</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.629243459326307</v>
+        <v>2.586463674573878</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.33227910835708</v>
+        <v>-3.387485710376406</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.295975391669728</v>
+        <v>1.231112966109567</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.078299387019237</v>
+        <v>1.106658134983649</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.27622309153785</v>
+        <v>3.250458555564068</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.61599813180218</v>
+        <v>2.57321834704975</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.316373778924727</v>
+        <v>-3.371580380944053</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.289092195918541</v>
+        <v>1.22422977035838</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9991867263099976</v>
+        <v>1.02754547427441</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.215510167588179</v>
+        <v>3.189745631614397</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932762</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.620095834412808</v>
+        <v>2.577316049660379</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.271535377316329</v>
+        <v>-3.326741979335655</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.311125259172529</v>
+        <v>1.246262833612368</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.003730159254867</v>
+        <v>1.03208890721928</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.222333929965729</v>
+        <v>3.196569393991947</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917044</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.624256774043886</v>
+        <v>2.581476989291457</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.291033833558337</v>
+        <v>-3.346240435577664</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.307486816306803</v>
+        <v>1.242624390746643</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9556455179749628</v>
+        <v>0.9840042659393753</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.197644084828864</v>
+        <v>3.171879548855082</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.630136376571723</v>
+        <v>2.587356591819294</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.246830996472437</v>
+        <v>-3.302037598491763</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.331047553669001</v>
+        <v>1.26618512810884</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9998483550608632</v>
+        <v>1.028207103025276</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.230045389608242</v>
+        <v>3.204280853634459</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.628546377040971</v>
+        <v>2.585766592288541</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.254390662309484</v>
+        <v>-3.30959726432881</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.32643368780343</v>
+        <v>1.261571262243269</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.054651759070683</v>
+        <v>1.083010507035095</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.261337432483381</v>
+        <v>3.235572896509598</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.679794142224011</v>
+        <v>2.637014357471581</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.096099244770211</v>
+        <v>-3.151305846789538</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.440998020002178</v>
+        <v>1.376135594442018</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.054651759070683</v>
+        <v>1.083010507035095</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.31258519766642</v>
+        <v>3.286820661692638</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.678234846818264</v>
+        <v>2.635455062065834</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.888457241135735</v>
+        <v>-2.943663843155062</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.522495526050222</v>
+        <v>1.457633100490061</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.262293762705159</v>
+        <v>1.290652510669571</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.435611104441359</v>
+        <v>3.409846568467577</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.673183075056534</v>
+        <v>2.630403290304104</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.837425148413207</v>
+        <v>-2.892631750432534</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.537856591377503</v>
+        <v>1.472994165817343</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.313325855427687</v>
+        <v>1.341684603392099</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.461178588313146</v>
+        <v>3.435414052339364</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.690370479149239</v>
+        <v>2.647590694396809</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.772200967286001</v>
+        <v>-2.827407569305328</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.58113366792109</v>
+        <v>1.51627124236093</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.378550036554892</v>
+        <v>1.406908784519305</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.517500501082174</v>
+        <v>3.491735965108392</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.84006118688255</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.686331451448519</v>
+        <v>2.643551666696089</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.734773947214868</v>
+        <v>-2.789980549234194</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.592065448248824</v>
+        <v>1.527203022688664</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.383801574584074</v>
+        <v>1.412160322548487</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.516612396198964</v>
+        <v>3.490847860225182</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992653</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.687588243779759</v>
+        <v>2.64480845902733</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.754885603249576</v>
+        <v>-2.810092205268902</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.585277578166181</v>
+        <v>1.520415152606021</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.394828919581493</v>
+        <v>1.423187667545906</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.524485595528656</v>
+        <v>3.498721059554874</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636279</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.84814601480097</v>
+        <v>2.80536623004854</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.726472340149692</v>
+        <v>-2.781678942169019</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.757200654427345</v>
+        <v>1.692338228867185</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.335853356835065</v>
+        <v>1.364212104799477</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.649658028902009</v>
+        <v>3.623893492928227</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957618</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.968258924018787</v>
+        <v>2.925479139266358</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.65169007912468</v>
+        <v>-2.706896681144006</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.907226468055168</v>
+        <v>1.842364042495007</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.410635617860077</v>
+        <v>1.43899436582449</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.814640294734834</v>
+        <v>3.788875758761052</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998749</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.959966900032646</v>
+        <v>2.917187115280217</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.625605994860872</v>
+        <v>-2.680812596880198</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.90936807777455</v>
+        <v>1.844505652214389</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.410635617860077</v>
+        <v>1.43899436582449</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.806348270748693</v>
+        <v>3.780583734774911</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.958160095616426</v>
+        <v>2.915380310863996</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.537728081751751</v>
+        <v>-2.592934683771078</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.942712438601977</v>
+        <v>1.877850013041817</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.526561260283428</v>
+        <v>1.554920008247841</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.874096851786483</v>
+        <v>3.848332315812701</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.975714501343217</v>
+        <v>2.932934716590788</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.528835620358468</v>
+        <v>-2.584042222377794</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.963823828886082</v>
+        <v>1.898961403325922</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.526561260283428</v>
+        <v>1.554920008247841</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.891651257513274</v>
+        <v>3.865886721539492</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.967569548747801</v>
+        <v>2.924789763995371</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.697311737328346</v>
+        <v>-2.752518339347672</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.888288429502715</v>
+        <v>1.823426003942554</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.498613424566847</v>
+        <v>1.52697217253126</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.86673760348791</v>
+        <v>3.840973067514128</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.948839245935663</v>
+        <v>2.906059461183233</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.251055544698906</v>
+        <v>-2.306262146718232</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.048060603742353</v>
+        <v>1.983198178182192</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.403894754897215</v>
+        <v>1.432253502861627</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.791176098873992</v>
+        <v>3.76541156290021</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.939503268432567</v>
+        <v>2.896723483680138</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.228334441015753</v>
+        <v>-2.28354104303508</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.047813067712518</v>
+        <v>1.982950642152358</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.403894754897215</v>
+        <v>1.432253502861627</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.781840121370896</v>
+        <v>3.756075585397114</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.098409394283737</v>
+        <v>3.055629609531307</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.357536254309796</v>
+        <v>-2.412742856329122</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.155038468246071</v>
+        <v>2.09017604268591</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.274692941603172</v>
+        <v>1.303051689567585</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.86322515924564</v>
+        <v>3.837460623271858</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.135487216777383</v>
+        <v>3.092707432024953</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.383410652783821</v>
+        <v>-2.438617254803148</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.181766531350107</v>
+        <v>2.116904105789946</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.319604550314914</v>
+        <v>1.347963298279326</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.927249946966332</v>
+        <v>3.901485410992549</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.132162572766928</v>
+        <v>3.089382788014499</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.376355962568648</v>
+        <v>-2.431562564587974</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.181263763425721</v>
+        <v>2.116401337865561</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.326659240530087</v>
+        <v>1.3550179884945</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.928158117084981</v>
+        <v>3.902393581111199</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.14216872641167</v>
+        <v>3.09938894165924</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.34940473824216</v>
+        <v>-2.404611340261486</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.202050406801058</v>
+        <v>2.137187981240897</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.341539586557807</v>
+        <v>1.369898334522219</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.947092478346354</v>
+        <v>3.921327942372572</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.32627185855663</v>
+        <v>3.2834920738042</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.370948966072947</v>
+        <v>-2.426155568092273</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.377535847813703</v>
+        <v>2.312673422253543</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.341539586557807</v>
+        <v>1.369898334522219</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.131195610491313</v>
+        <v>4.105431074517532</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.318388553459623</v>
+        <v>3.275608768707193</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.393357083877819</v>
+        <v>-2.448563685897145</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.360689295594747</v>
+        <v>2.295826870034587</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.341539586557807</v>
+        <v>1.369898334522219</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.123312305394307</v>
+        <v>4.097547769420525</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.32044255300926</v>
+        <v>3.27766276825683</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.421581319455419</v>
+        <v>-2.476787921474746</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.351453600913344</v>
+        <v>2.286591175353184</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.359516339009115</v>
+        <v>1.387875086973528</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.13615235641473</v>
+        <v>4.110387820440947</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.72945228516197</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.376696270731107</v>
+        <v>3.333916485978678</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.431022245343949</v>
+        <v>-2.486228847363276</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.403930948279779</v>
+        <v>2.339068522719619</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.481943456552507</v>
+        <v>1.510302204516919</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.265862344662612</v>
+        <v>4.240097808688829</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321627</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.379587365276408</v>
+        <v>3.336807580523979</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.519898876512423</v>
+        <v>-2.57510547853175</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.371271390357691</v>
+        <v>2.306408964797531</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.393066825384033</v>
+        <v>1.421425573348445</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.215427460506828</v>
+        <v>4.189662924533046</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.377699178170183</v>
+        <v>3.334919393417754</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.596228854113329</v>
+        <v>-2.651435456132655</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.338851212211104</v>
+        <v>2.273988786650944</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.393066825384033</v>
+        <v>1.421425573348445</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.213539273400603</v>
+        <v>4.187774737426821</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887741</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.372519407773046</v>
+        <v>3.329739623020616</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.68989279879087</v>
+        <v>-2.745099400810197</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.29620586394295</v>
+        <v>2.231343438382789</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.299402880706491</v>
+        <v>1.327761628670904</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.15216113619694</v>
+        <v>4.126396600223159</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343059</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.370953417983198</v>
+        <v>3.328173633230768</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.851461224318125</v>
+        <v>-2.906667826337452</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.2300125039422</v>
+        <v>2.165150078382039</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.172619956908612</v>
+        <v>1.200978704873024</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.074525392128366</v>
+        <v>4.048760856154583</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389342</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.384026824849117</v>
+        <v>3.341247040096687</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.959761886188245</v>
+        <v>-3.014968488207571</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.199765646060071</v>
+        <v>2.13490322049991</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.172619956908612</v>
+        <v>1.200978704873024</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.087598798994284</v>
+        <v>4.061834263020502</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378385</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.376032021632057</v>
+        <v>3.333252236879627</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.977565857908989</v>
+        <v>-3.032772459928315</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.184649254154713</v>
+        <v>2.119786828594552</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.102085334003411</v>
+        <v>1.130444081967823</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.037283222034104</v>
+        <v>4.011518686060321</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006969</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.374556062759059</v>
+        <v>3.331776278006629</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.005466645018462</v>
+        <v>-3.060673247037788</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.172012980437926</v>
+        <v>2.107150554877765</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.067488409860476</v>
+        <v>1.095847157824889</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.015049108675345</v>
+        <v>3.989284572701562</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787382</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.371320506736257</v>
+        <v>3.328540721983828</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.127992747721356</v>
+        <v>-3.183199349740682</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.119766983333967</v>
+        <v>2.054904557773806</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9449623071575823</v>
+        <v>0.9733210551219948</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.938297891030807</v>
+        <v>3.912533355057024</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585931</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.438026466326761</v>
+        <v>3.395246681574331</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.358507243906945</v>
+        <v>-3.413713845926271</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.094267144450235</v>
+        <v>2.029404718890075</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7144478109719936</v>
+        <v>0.7428065589364061</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.866695152909958</v>
+        <v>3.840930616936175</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.64075008781466</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.578338185328608</v>
+        <v>3.535558400576178</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.707252329131388</v>
+        <v>-3.762458931150715</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.095080829362304</v>
+        <v>2.030218403802144</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6340586050175083</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.941758099560466</v>
+        <v>3.915993563586683</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.66828900423709</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.647318454474248</v>
+        <v>3.604538669721818</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.861238746907529</v>
+        <v>-3.916445348926855</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.102466531397488</v>
+        <v>2.037604105837328</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6340586050175083</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.010738368706106</v>
+        <v>3.984973832732323</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.633369656594369</v>
+        <v>3.590589871841939</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.065838181770538</v>
+        <v>-4.121044783789864</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.006677959572406</v>
+        <v>1.941815534012245</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6340586050175083</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.996789570826227</v>
+        <v>3.971025034852445</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.645240145649783</v>
+        <v>3.602460360897353</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.318313335778262</v>
+        <v>-4.373519937797589</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.91755838702473</v>
+        <v>1.852695961464569</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6340586050175083</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.008660059881641</v>
+        <v>3.982895523907859</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973152</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.646450680168726</v>
+        <v>3.603670895416297</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.611209092257674</v>
+        <v>-4.666415694277001</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.801610618951909</v>
+        <v>1.736748193391748</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6340586050175083</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.009870594400584</v>
+        <v>3.984106058426802</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.66350945725194</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.650572422396048</v>
+        <v>3.607792637643618</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.797873220392482</v>
+        <v>-4.853079822411809</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.731066709925307</v>
+        <v>1.666204284365147</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5789608862285359</v>
+        <v>0.6073196341929484</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.99794895413317</v>
+        <v>3.972184418159387</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916195</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.645650275132237</v>
+        <v>3.602870490379808</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.943893907306444</v>
+        <v>-4.999100509325771</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.667736287895912</v>
+        <v>1.602873862335751</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5698777944346789</v>
+        <v>0.5982365423990914</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.987576951793045</v>
+        <v>3.961812415819263</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830321</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.807854331831281</v>
+        <v>3.765074547078852</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.03560791641603</v>
+        <v>-5.090814518435357</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.793254740951121</v>
+        <v>1.728392315390961</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5698777944346789</v>
+        <v>0.5982365423990914</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.149781008492089</v>
+        <v>4.124016472518307</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071544</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.802700969795096</v>
+        <v>3.759921185042666</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.067259575475999</v>
+        <v>-5.122466177495326</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.775440715290948</v>
+        <v>1.710578289730787</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5647093371902387</v>
+        <v>0.5930680851546513</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.141526572109239</v>
+        <v>4.115762036135457</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868138</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.812930387363587</v>
+        <v>3.770150602611157</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.149194393744883</v>
+        <v>-5.204400995764209</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.752896205551886</v>
+        <v>1.688033779991725</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5547745916031586</v>
+        <v>0.5831333395675711</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.145795142325482</v>
+        <v>4.1200306063517</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332683</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.821856025819489</v>
+        <v>3.77907624106706</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.25117051599329</v>
+        <v>-5.306377118012617</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.721031395108425</v>
+        <v>1.656168969548265</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.452798469354751</v>
+        <v>0.4811572173191635</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.09353510743234</v>
+        <v>4.067770571458558</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231799</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.814008913063665</v>
+        <v>3.771229128311235</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.141164232516068</v>
+        <v>-5.196370834535395</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.757186795743489</v>
+        <v>1.692324370183329</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4760030412720262</v>
+        <v>0.5043617892364387</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.099610737826881</v>
+        <v>4.073846201853098</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818514</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.818258923785639</v>
+        <v>3.775479139033209</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.998104656775142</v>
+        <v>-5.053311258794469</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.818660636761834</v>
+        <v>1.753798211201674</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4840164678620055</v>
+        <v>0.512375215826418</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.108668804502843</v>
+        <v>4.08290426852906</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051781</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.782740021915745</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.696657931303305</v>
+        <v>-4.751864533322632</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.946500209833105</v>
+        <v>1.881637784272945</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8138219412982552</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.29679772266848</v>
+        <v>4.271033186694699</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679618</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.783711199668456</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.721248175538489</v>
+        <v>-4.776454777557816</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.937635289891742</v>
+        <v>1.872772864331582</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8138219412982552</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.297768900421191</v>
+        <v>4.272004364447409</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.784554104048211</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.670209799531968</v>
+        <v>-4.725416401551295</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.958893544674106</v>
+        <v>1.894031119113945</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8138219412982552</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.298611804800947</v>
+        <v>4.272847268827165</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969536</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.803592202922357</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.629070504665338</v>
+        <v>-4.684277106684664</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.994387361494903</v>
+        <v>1.929524935934743</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8266024882004736</v>
+        <v>0.8549612361648861</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.34233348059507</v>
+        <v>4.316568944621289</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.82575293270047</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.619776199046291</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.532435592646697</v>
+        <v>-4.587642194666024</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.849225322426294</v>
+        <v>1.784362896866134</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9232374002191135</v>
+        <v>0.951596148183526</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.216498423930189</v>
+        <v>4.190733887956407</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077632</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.623278243120255</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.66301632717754</v>
+        <v>-4.718222929196867</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.800495072687921</v>
+        <v>1.735632647127761</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.792656665688271</v>
+        <v>0.8210154136526835</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.141652027285648</v>
+        <v>4.115887491311866</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.77502886083345</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.607705062196338</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.498519992986578</v>
+        <v>-4.553726595005905</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.850720425440388</v>
+        <v>1.785857999880228</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9571529998792329</v>
+        <v>0.9855117478436454</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.224776646876307</v>
+        <v>4.199012110902525</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077621</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.606892772632768</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.421421391444706</v>
+        <v>-4.476627993464033</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.880747576493567</v>
+        <v>1.815885150933407</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9571529998792329</v>
+        <v>0.9855117478436454</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.223964357312737</v>
+        <v>4.198199821338955</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.61676155175784</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.431806586334595</v>
+        <v>-4.487013188353922</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.886462277662684</v>
+        <v>1.821599852102523</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9467678049893435</v>
+        <v>0.9751265529537561</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.227602019503876</v>
+        <v>4.201837483530094</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735273</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.687598557534265</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.45039474505682</v>
+        <v>-4.505601347076147</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.949864019950219</v>
+        <v>1.885001594390059</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9281796462671181</v>
+        <v>0.9565383942315306</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.287286130046966</v>
+        <v>4.261521594073184</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.684467568352564</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.450693291752856</v>
+        <v>-4.505899893772183</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.946613612090103</v>
+        <v>1.881751186529943</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9278810995710822</v>
+        <v>0.9562398475354947</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.283976012847643</v>
+        <v>4.258211476873861</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108848</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.688998463291955</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.349870158062428</v>
+        <v>-4.405076760081755</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.991473760505666</v>
+        <v>1.926611334945505</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9403453150554361</v>
+        <v>0.9687040630198486</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.295985437077647</v>
+        <v>4.270220901103865</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121458</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.689127716770499</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.159088797310021</v>
+        <v>-4.214295399329348</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.067915558285172</v>
+        <v>2.003053132725011</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.131126675807844</v>
+        <v>1.159485423772256</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.410583507007635</v>
+        <v>4.384818971033853</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906071</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.668964562508095</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.0521254394606</v>
+        <v>-4.107332041479927</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.090537747162537</v>
+        <v>2.025675321602376</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.189591283767645</v>
+        <v>1.217950031732058</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.425499117521112</v>
+        <v>4.39973458154733</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912976</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.703931499120154</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.996794851558838</v>
+        <v>-4.052001453578164</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.1476369189353</v>
+        <v>2.08277449337514</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.244921871669407</v>
+        <v>1.27328061963382</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.493664406874228</v>
+        <v>4.467899870900445</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539886</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.697618067021591</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.984740724645875</v>
+        <v>-4.039947326665201</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.146145137601923</v>
+        <v>2.081282712041763</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.25697599858237</v>
+        <v>1.285334746546782</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.494583450923443</v>
+        <v>4.468818914949661</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.699498697205727</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.025895844214096</v>
+        <v>-4.081102446233422</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.13156371995877</v>
+        <v>2.066701294398611</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.215820879014149</v>
+        <v>1.244179626978561</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.471771009366647</v>
+        <v>4.446006473392864</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382911</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.71234972308361</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.957847281522566</v>
+        <v>-4.013053883541892</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.171634170913265</v>
+        <v>2.106771745353105</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.283869441705679</v>
+        <v>1.312228189670091</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.525451172859447</v>
+        <v>4.499686636885665</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013418</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.732552393257204</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.189447674692067</v>
+        <v>-4.244654276711393</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.099196683819058</v>
+        <v>2.034334258258899</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.283869441705679</v>
+        <v>1.312228189670091</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.545653843033041</v>
+        <v>4.519889307059259</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498963</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.758938414076515</v>
+        <v>3.716158629324086</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.239499220221287</v>
+        <v>-4.294705822240612</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.062782301674253</v>
+        <v>1.997919876114093</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.283869441705679</v>
+        <v>1.312228189670091</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.529260079099923</v>
+        <v>4.503495543126141</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800092</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.719190327669982</v>
+        <v>3.676410542917552</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.414606052797732</v>
+        <v>-4.469812654817057</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.952991482237142</v>
+        <v>1.888129056676982</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.283869441705679</v>
+        <v>1.312228189670091</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.48951199269339</v>
+        <v>4.463747456719608</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660845</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.726212946666922</v>
+        <v>3.683433161914492</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.218505899367209</v>
+        <v>-4.273712501386534</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.038454162606291</v>
+        <v>1.973591737046131</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.479969595136202</v>
+        <v>1.508328343100614</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.614194703748644</v>
+        <v>4.588430167774861</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395082</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.825383946239826</v>
+        <v>3.782604161487397</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.065480507253924</v>
+        <v>-4.120687109273249</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.198835319024509</v>
+        <v>2.133972893464349</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.632994987249486</v>
+        <v>1.661353735213898</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.805180938589518</v>
+        <v>4.779416402615736</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791143</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.012850171148119</v>
+        <v>3.970070386395689</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.093787821127195</v>
+        <v>-4.14899442314652</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.374978618383493</v>
+        <v>2.310116192823334</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.632994987249486</v>
+        <v>1.661353735213898</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.992647163497811</v>
+        <v>4.966882627524028</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620429</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.982253122502201</v>
+        <v>3.939473337749772</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.260381046240717</v>
+        <v>-4.315587648260042</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.277744279692167</v>
+        <v>2.212881854132007</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.466401762135963</v>
+        <v>1.494760510100376</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.86209417978378</v>
+        <v>4.836329643809997</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285643</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.985929525163919</v>
+        <v>3.943149740411489</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.237345252879151</v>
+        <v>-4.292551854898476</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.29063499969851</v>
+        <v>2.225772574138351</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.466401762135963</v>
+        <v>1.494760510100376</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.865770582445498</v>
+        <v>4.840006046471715</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399464</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.983547580287414</v>
+        <v>3.940767795534985</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.208099272423454</v>
+        <v>-4.263305874442779</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.299951447004284</v>
+        <v>2.235089021444125</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.466401762135963</v>
+        <v>1.494760510100376</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.863388637568993</v>
+        <v>4.83762410159521</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699404642256366</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.980840819445049</v>
+        <v>3.93806103469262</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.315024820301305</v>
+        <v>-4.37023142232063</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.254474467010779</v>
+        <v>2.189612041450619</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.359476214258112</v>
+        <v>1.387834962222525</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.796526547999917</v>
+        <v>4.770762012026134</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600700995</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.982269621588284</v>
+        <v>3.939489836835854</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.460043378808554</v>
+        <v>-4.515249980827879</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.197895845751114</v>
+        <v>2.133033420190954</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.214457655750864</v>
+        <v>1.242816403715276</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.710944215038802</v>
+        <v>4.68517967906502</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687006</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.082200860846037</v>
+        <v>4.039421076093607</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.578385144593272</v>
+        <v>-4.633591746612597</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.25049037869498</v>
+        <v>2.18562795313482</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.225143694313754</v>
+        <v>1.253502442278166</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.817287077434289</v>
+        <v>4.791522541460507</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790796</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.079986557971975</v>
+        <v>4.037206773219546</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.629795566913979</v>
+        <v>-4.685002168933305</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.227711906892635</v>
+        <v>2.162849481332476</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.225143694313754</v>
+        <v>1.253502442278166</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.815072774560227</v>
+        <v>4.789308238586446</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437324</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.079889686046265</v>
+        <v>4.037109901293835</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.709215018121731</v>
+        <v>-4.764421620141056</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.195847254483824</v>
+        <v>2.130984828923665</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.225143694313754</v>
+        <v>1.253502442278166</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.814975902634517</v>
+        <v>4.789211366660735</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298391</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.079883579604308</v>
+        <v>4.037103794851879</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.804678016038949</v>
+        <v>-4.859884618058274</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.15765594887498</v>
+        <v>2.092793523314821</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.225143694313754</v>
+        <v>1.253502442278166</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.81496979619256</v>
+        <v>4.789205260218779</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960217993</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.077979976166919</v>
+        <v>4.035200191414489</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.740302105188234</v>
+        <v>-4.795508707207559</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.181502709777877</v>
+        <v>2.116640284217718</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.289519605164469</v>
+        <v>1.317878353128881</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.8516917392656</v>
+        <v>4.825927203291818</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353528</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.083713793914646</v>
+        <v>4.040934009162216</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.795671267320428</v>
+        <v>-4.850877869339753</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.165088862672726</v>
+        <v>2.100226437112567</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.289519605164469</v>
+        <v>1.317878353128881</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.857425557013327</v>
+        <v>4.831661021039545</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113271</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.083252157257578</v>
+        <v>4.040472372505148</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.841109047151255</v>
+        <v>-4.89631564917058</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.146452114083328</v>
+        <v>2.081589688523168</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.246674614486309</v>
+        <v>1.275033362450722</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.831256925949363</v>
+        <v>4.805492389975581</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.79027250011368</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.103126550107897</v>
+        <v>4.060346765355467</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.752902213003677</v>
+        <v>-4.808108815023002</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.201609240592678</v>
+        <v>2.136746815032518</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.246674614486309</v>
+        <v>1.275033362450722</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.851131318799682</v>
+        <v>4.8253667828259</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016434</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.086827250632624</v>
+        <v>4.044047465880195</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.646867217798367</v>
+        <v>-4.702073819817692</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.22772393919953</v>
+        <v>2.16286151363937</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.246674614486309</v>
+        <v>1.275033362450722</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.83483201932441</v>
+        <v>4.809067483350628</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794705093307665</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.08925820009667</v>
+        <v>4.04647841534424</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.463655554665272</v>
+        <v>-4.518862156684597</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.303439553916813</v>
+        <v>2.238577128356654</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.246674614486309</v>
+        <v>1.275033362450722</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.837262968788456</v>
+        <v>4.811498432814673</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863546</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>4.01226960119213</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.391934107651421</v>
+        <v>-4.447140709670746</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.297919318570243</v>
+        <v>2.233056893010083</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.31839606150016</v>
+        <v>1.346754809464572</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.846087022844656</v>
+        <v>4.820322486870873</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394107</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.959185347113301</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.369561082043715</v>
+        <v>-4.42476768406304</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.253784274734497</v>
+        <v>2.188921849174338</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.329651812613061</v>
+        <v>1.358010560577474</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.799756219433569</v>
+        <v>4.773991683459786</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456723</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>4.144383551998657</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.40257737795446</v>
+        <v>-4.457783979973785</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.425775961255555</v>
+        <v>2.360913535695395</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.26021443594631</v>
+        <v>1.288573183910722</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.943291998318872</v>
+        <v>4.917527462345091</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883669</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>4.136304777826906</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.391049742304851</v>
+        <v>-4.446256344324176</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.422308241343647</v>
+        <v>2.357445815783487</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.319215094147672</v>
+        <v>1.347573842112085</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.970613619067939</v>
+        <v>4.944849083094157</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236289</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>4.139972890348695</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.48839124364722</v>
+        <v>-4.543597845666545</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.387039753328488</v>
+        <v>2.322177327768329</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.274794911982184</v>
+        <v>1.303153659946596</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.947629622290435</v>
+        <v>4.921865086316653</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427676</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>4.141223972541533</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.574247272987186</v>
+        <v>-4.629453875006512</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.35394842378534</v>
+        <v>2.28908599822518</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.232418842756049</v>
+        <v>1.260777590720461</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.923455062947592</v>
+        <v>4.89769052697381</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610375</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>4.123643174362035</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.583084070403306</v>
+        <v>-4.638290672422631</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.332832906639394</v>
+        <v>2.267970481079234</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.224976670114698</v>
+        <v>1.253335418079111</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.901408961183283</v>
+        <v>4.875644425209501</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667447</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176587470159514</v>
+        <v>4.133807685407084</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.674466632968764</v>
+        <v>-4.729673234988089</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.30644439265826</v>
+        <v>2.2415819670981</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.188411785395354</v>
+        <v>1.216770533359766</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.889634541396726</v>
+        <v>4.863870005422944</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889183</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.278715727983782</v>
+        <v>4.235935943231352</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.662759914981758</v>
+        <v>-4.717966517001083</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.41325533767733</v>
+        <v>2.348392912117171</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.20011850338236</v>
+        <v>1.228477251346773</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.998786830013198</v>
+        <v>4.973022294039416</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409559</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.281748066715187</v>
+        <v>4.238968281962757</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.563096410898096</v>
+        <v>-4.618303012917421</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.4561530780422</v>
+        <v>2.391290652482041</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.263305586586047</v>
+        <v>1.291664334550459</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.039731418666815</v>
+        <v>5.013966882693032</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452566</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.494652899993245</v>
+        <v>4.451873115240815</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.573412509064448</v>
+        <v>-4.628619111083773</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.664931472053718</v>
+        <v>2.600069046493558</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.263305586586047</v>
+        <v>1.291664334550459</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.252636251944873</v>
+        <v>5.22687171597109</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762279</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.493831566905334</v>
+        <v>4.451051782152905</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.573318541047075</v>
+        <v>-4.6285251430664</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.664147726172756</v>
+        <v>2.599285300612597</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.263675447933365</v>
+        <v>1.292034195897777</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.252036835665353</v>
+        <v>5.226272299691571</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.63321346798801</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.488063552849688</v>
+        <v>4.445283768097259</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.580537365246919</v>
+        <v>-4.635743967266245</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.655492182437173</v>
+        <v>2.590629756877012</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.263675447933365</v>
+        <v>1.292034195897777</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.246268821609707</v>
+        <v>5.220504285635925</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740916</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.488063552849688</v>
+        <v>4.445283768097259</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.579588942128881</v>
+        <v>-4.634795544148206</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.655871551684388</v>
+        <v>2.591009126124228</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.263675447933365</v>
+        <v>1.292034195897777</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.246268821609707</v>
+        <v>5.220504285635925</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.88106536666362</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.50079116083078</v>
+        <v>4.458011376078351</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.736657400384505</v>
+        <v>-4.79186400240383</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.60577177636323</v>
+        <v>2.54090935080307</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.263675447933365</v>
+        <v>1.292034195897777</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.258996429590799</v>
+        <v>5.233231893617017</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424764</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.502737159255168</v>
+        <v>4.459957374502738</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.730665153595694</v>
+        <v>-4.785871755615019</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.610114673503142</v>
+        <v>2.545252247942983</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.263675447933365</v>
+        <v>1.292034195897777</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.260942428015187</v>
+        <v>5.235177892041404</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149212</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.496391295272937</v>
+        <v>4.453611510520507</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.642107192464926</v>
+        <v>-4.697313794484251</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.639191993973219</v>
+        <v>2.574329568413058</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.263675447933365</v>
+        <v>1.292034195897777</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.254596564032956</v>
+        <v>5.228832028059173</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383085</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.495699972711932</v>
+        <v>4.452920187959503</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.624348114961852</v>
+        <v>-4.679554716981177</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.645604302413444</v>
+        <v>2.580741876853284</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.263675447933365</v>
+        <v>1.292034195897777</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.253905241471951</v>
+        <v>5.228140705498169</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,45 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.823325522419355</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.508482158620519</v>
+        <v>4.46570237386809</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.48816973852304</v>
+        <v>-4.689456412594282</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.712857838897555</v>
+        <v>2.589563384516629</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.399853824372176</v>
+        <v>1.282132500284672</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.348394453243825</v>
+        <v>5.234981874038893</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="2" t="n">
+        <v>45549</v>
+      </c>
+      <c r="B2087" t="n">
+        <v>3.821469290221052</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>4.524645482255539</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>-4.689456412594282</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>2.589563384516629</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>1.282132500284672</v>
+      </c>
+      <c r="G2087" t="n">
+        <v>4.517709279241907</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>19.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.5%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,11 +815,11 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>140.8%</t>
+          <t>129.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>420.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.5%</t>
+          <t>-632.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-117.3%</t>
+          <t>-127.4%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-326.5%</t>
+          <t>-324.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-95.8%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,42 +1471,42 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>-6.1%</t>
         </is>
       </c>
     </row>
@@ -45478,19 +45478,19 @@
         <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.834009020654386</v>
+        <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.307371425769619</v>
+        <v>-6.258687543445998</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3107040260327905</v>
+        <v>0.3729573637146681</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1591699220614363</v>
+        <v>-0.1780292819166325</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.738507067417524</v>
+        <v>2.769971236256836</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.825295034400908</v>
+        <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.25440190351563</v>
+        <v>-6.205718021192009</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3231778486809076</v>
+        <v>0.3854311863627853</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1062003998074474</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.761574794516439</v>
+        <v>2.793038963355751</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.818334422305814</v>
+        <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.088613707555339</v>
+        <v>-6.039929825231718</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3825325149699306</v>
+        <v>0.4447858526518087</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1062003998074474</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.754614182421346</v>
+        <v>2.786078351260658</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.832796776686958</v>
+        <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.05525050107657</v>
+        <v>-6.00656661875295</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4103401519425813</v>
+        <v>0.4725934896244595</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1062003998074474</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.769076536802489</v>
+        <v>2.800540705641801</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.827328897146153</v>
+        <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.946991363954049</v>
+        <v>-5.898307481630428</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.448175927250785</v>
+        <v>0.5104292649326632</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1062003998074474</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.763608657261684</v>
+        <v>2.795072826100996</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.824826991156729</v>
+        <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.823700229136918</v>
+        <v>-5.775016346813297</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4949904751882142</v>
+        <v>0.5572438128700923</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.01709073500968311</v>
+        <v>-0.001768624845513156</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.83508143216254</v>
+        <v>2.866545601001851</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919905</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.832527969394055</v>
+        <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.771003362005627</v>
+        <v>-5.722319479682006</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5237702002780558</v>
+        <v>0.5860235379599339</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.06978760214097429</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.874400530678639</v>
+        <v>2.905864699517951</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.828308677741105</v>
+        <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.527237920022182</v>
+        <v>-5.478554037698562</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6170570854184843</v>
+        <v>0.6793104231003624</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.06978760214097429</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.87018123902569</v>
+        <v>2.901645407865002</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.830432991661121</v>
+        <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.43746224764571</v>
+        <v>-5.388778365322089</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.655091668289089</v>
+        <v>0.7173450059709672</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1313870470552843</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.909265219894292</v>
+        <v>2.940729388733604</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.823175066644823</v>
+        <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.187611853696636</v>
+        <v>-5.138927971373015</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7477739008524211</v>
+        <v>0.8100272385342993</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1313870470552843</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.902007294877994</v>
+        <v>2.933471463717306</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.826774190165472</v>
+        <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.011719761229203</v>
+        <v>-4.963035878905583</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8217298613600428</v>
+        <v>0.8839831990419207</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1313870470552843</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.905606418398643</v>
+        <v>2.937070587237955</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.840101696220026</v>
+        <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.84027329820674</v>
+        <v>-4.791589415883119</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9036359526235818</v>
+        <v>0.9658892903054599</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.3028335100777474</v>
+        <v>0.2839741502225512</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.021801802266674</v>
+        <v>3.053265971105986</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.839122173836323</v>
+        <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.760251011097619</v>
+        <v>-4.711567128773998</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9346653450835272</v>
+        <v>0.9969186827654051</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3828557971868684</v>
+        <v>0.3639964373316721</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.068835652148444</v>
+        <v>3.100299820987756</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.84381697489064</v>
+        <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.696615268863685</v>
+        <v>-4.647931386540064</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9648144430314183</v>
+        <v>1.027067780713296</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4464915394208029</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.111711898543122</v>
+        <v>3.143176067382434</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.79881477107478</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.825011233674436</v>
+        <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602917950647289</v>
+        <v>-4.554234068323669</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.983487629101772</v>
+        <v>1.04574096678365</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4464915394208029</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.092906157326918</v>
+        <v>3.124370326166229</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.826754310299313</v>
+        <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.613420573712578</v>
+        <v>-4.564736691388958</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9810296565005339</v>
+        <v>1.043282994182412</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4359889163555141</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.088347660112622</v>
+        <v>3.119811828951934</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.830683624134133</v>
+        <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.500934313043704</v>
+        <v>-4.452250430720083</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.029953474602904</v>
+        <v>1.092206812284782</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4359889163555141</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.092276973947442</v>
+        <v>3.123741142786754</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.831362208051473</v>
+        <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.483220626165838</v>
+        <v>-4.434536743842218</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.03771753327139</v>
+        <v>1.099970870953268</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4391702452524309</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.094864355202932</v>
+        <v>3.126328524042244</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.828360279271467</v>
+        <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.35974635485282</v>
+        <v>-4.311062472529199</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.084105313016591</v>
+        <v>1.146358650698469</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4391702452524309</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.091862426422926</v>
+        <v>3.123326595262237</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.829939316282081</v>
+        <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.13972555681581</v>
+        <v>-4.091041674492189</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.173692669242009</v>
+        <v>1.235946006923887</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5803900903204111</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.178173370474328</v>
+        <v>3.20963753931364</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.845833499083904</v>
+        <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.006857867752531</v>
+        <v>-3.958173985428911</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.242733927669144</v>
+        <v>1.304987265351021</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5803900903204111</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.194067553276151</v>
+        <v>3.225531722115463</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.846979343524206</v>
+        <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.886684784388032</v>
+        <v>-3.838000902064412</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.291949005455245</v>
+        <v>1.354202343137123</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.7005631736849101</v>
+        <v>0.6817038138297138</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.267317247735153</v>
+        <v>3.298781416574464</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.857067446085646</v>
+        <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.751431423058055</v>
+        <v>-3.702747540734435</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.356138452548676</v>
+        <v>1.418391790230554</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8358165350148872</v>
+        <v>0.8169571751596909</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.358557367094579</v>
+        <v>3.390021535933891</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.843104937487072</v>
+        <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.811306250415747</v>
+        <v>-3.762622368092127</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.318226013007025</v>
+        <v>1.380479350688903</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7759417076571951</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.308669962081389</v>
+        <v>3.340134130920701</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.85839410672128</v>
+        <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.69148601950491</v>
+        <v>-3.64280213718129</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.381443274605568</v>
+        <v>1.443696612287446</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7759417076571951</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.323959131315598</v>
+        <v>3.355423300154909</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.766038306043722</v>
+        <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.693955725966716</v>
+        <v>-3.645271843643096</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.288099591343287</v>
+        <v>1.350352929025165</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7734720011953888</v>
+        <v>0.7546126413401926</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.230121506760955</v>
+        <v>3.261585675600267</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.685300167529023</v>
+        <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.762325912290726</v>
+        <v>-3.713642029967105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.180013378298985</v>
+        <v>1.242266715980863</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7827477002316038</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.154948787667986</v>
+        <v>3.186412956507298</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.675736876160915</v>
+        <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.840702314217968</v>
+        <v>-3.825514309593256</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.139099526159979</v>
+        <v>1.187954512762294</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.79224708834082</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.151085129165407</v>
+        <v>3.176849665139189</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.812767712853117</v>
+        <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.896222390110557</v>
+        <v>-3.881034385485846</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.253922332495146</v>
+        <v>1.30277731909746</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.79224708834082</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.288115965857609</v>
+        <v>3.313880501831391</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.817334944844905</v>
+        <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.720748130318088</v>
+        <v>-3.705560125693376</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.328679268403921</v>
+        <v>1.377534255006236</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.79224708834082</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.292683197849397</v>
+        <v>3.318447733823179</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.793076973606112</v>
+        <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.712823755733174</v>
+        <v>-3.697635751108462</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.307591046999094</v>
+        <v>1.356446033601409</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.79224708834082</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.268425226610604</v>
+        <v>3.294189762584386</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.721615287007562</v>
+        <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.706545553163325</v>
+        <v>-3.691357548538613</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.238640641428483</v>
+        <v>1.287495628030798</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.798525290910669</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.200730461553963</v>
+        <v>3.226494997527745</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.731787673439694</v>
+        <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.646692933959602</v>
+        <v>-3.63150492933489</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.272754075542105</v>
+        <v>1.32160906214442</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.798525290910669</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.210902847986095</v>
+        <v>3.236667383959878</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.726733944013554</v>
+        <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.560449470933225</v>
+        <v>-3.545261466308513</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.302197731326516</v>
+        <v>1.351052717928831</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.798525290910669</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.205849118559956</v>
+        <v>3.231613654533738</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.71850971945808</v>
+        <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.605756290332204</v>
+        <v>-3.590568285707493</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.27585077901145</v>
+        <v>1.324705765613764</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7577151279014382</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.173138796198943</v>
+        <v>3.198903332172725</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.719061592491181</v>
+        <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.634789395034506</v>
+        <v>-3.619601390409794</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.264789410163631</v>
+        <v>1.313644396765945</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7577151279014382</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.173690669232045</v>
+        <v>3.199455205205827</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.648334284382547</v>
+        <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.541978913583647</v>
+        <v>-3.526790908958935</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.23118629463534</v>
+        <v>1.280041281237655</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8505256093522976</v>
+        <v>0.8221668613878851</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.158649649993926</v>
+        <v>3.184414185967708</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.650207760307148</v>
+        <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.586368382913074</v>
+        <v>-3.571180378288362</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.21530398282817</v>
+        <v>1.264158969430484</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.8061361400228699</v>
+        <v>0.7777773920584574</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.13388944432087</v>
+        <v>3.159653980294652</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.645283468818871</v>
+        <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.565864689027577</v>
+        <v>-3.550676684402865</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.218581168894092</v>
+        <v>1.267436155496406</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.8266398339083673</v>
+        <v>0.7982810859439547</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.141267369163891</v>
+        <v>3.167031905137673</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.650774764649538</v>
+        <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.605788783610149</v>
+        <v>-3.590600778985437</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.20810282689173</v>
+        <v>1.256957813494045</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.8266398339083673</v>
+        <v>0.7982810859439547</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.146758664994559</v>
+        <v>3.172523200968341</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.662271966418077</v>
+        <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.633569181511502</v>
+        <v>-3.61838117688679</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.208487869499728</v>
+        <v>1.257342856102043</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7988594360070143</v>
+        <v>0.7705006880426017</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.141587628022286</v>
+        <v>3.167352163996068</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.50062768641873</v>
+        <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.751949854241641</v>
+        <v>-3.736761849616929</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.999491320408326</v>
+        <v>1.04834630701064</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7316415838560381</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.939612636732353</v>
+        <v>2.965377172706136</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.620777347137936</v>
+        <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.860563932684972</v>
+        <v>-3.84537592806026</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.076195349750199</v>
+        <v>1.125050336352514</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7316415838560381</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.059762297451559</v>
+        <v>3.085526833425341</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.635290373240259</v>
+        <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.825154894436829</v>
+        <v>-3.809966889812117</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.104871991151779</v>
+        <v>1.153726977754094</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7316415838560381</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.074275323553882</v>
+        <v>3.100039859527664</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.632709814582628</v>
+        <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.786771231878678</v>
+        <v>-3.771583227253966</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.117644897517408</v>
+        <v>1.166499884119723</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7700252464141892</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.094724962431142</v>
+        <v>3.120489498404924</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.62943884342793</v>
+        <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.609654901843512</v>
+        <v>-3.5944668972188</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.185220458376777</v>
+        <v>1.234075444979091</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7700252464141892</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.091453991276444</v>
+        <v>3.117218527250226</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.630122235189843</v>
+        <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.654747146677057</v>
+        <v>-3.639559142052345</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.167866952205272</v>
+        <v>1.216721938807586</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.7081292032447994</v>
+        <v>0.6797704552803869</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.054999757136723</v>
+        <v>3.080764293110505</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.623909210496257</v>
+        <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.475371725438289</v>
+        <v>-3.460183720813578</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.233404096007193</v>
+        <v>1.282259082609508</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8649059614155181</v>
+        <v>0.8365472134511056</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.142852787345568</v>
+        <v>3.16861732331935</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982222</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.604716665827847</v>
+        <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.520385938958896</v>
+        <v>-3.505197934334184</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.196205865930541</v>
+        <v>1.245060852532855</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8345570661009135</v>
+        <v>0.806198318136501</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.105450905488395</v>
+        <v>3.131215441462177</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509531</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.610408228166793</v>
+        <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.787390449231331</v>
+        <v>-3.772202444606619</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.095095624160512</v>
+        <v>1.143950610762827</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.640194028057965</v>
+        <v>0.6118352800935525</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.994524645001572</v>
+        <v>3.020289180975354</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760807</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.609612150063294</v>
+        <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.888588230668504</v>
+        <v>-3.873400226043792</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.053820433482144</v>
+        <v>1.102675420084459</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5717852145126459</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.952683278770882</v>
+        <v>2.978447814744664</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.607212111617611</v>
+        <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.882077264054191</v>
+        <v>-3.866889259429479</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.054024781682186</v>
+        <v>1.102879768284501</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5717852145126459</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.950283240325199</v>
+        <v>2.976047776298981</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.603736830825856</v>
+        <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.863039136346894</v>
+        <v>-3.847851131722182</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.05816475197335</v>
+        <v>1.107019738575665</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.5136016031814513</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.911897792734727</v>
+        <v>2.937662328708509</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131244</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.723031232460046</v>
+        <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.915554938621714</v>
+        <v>-3.900366933997002</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.156452832697612</v>
+        <v>1.205307819299927</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.5136016031814513</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.031192194368917</v>
+        <v>3.056956730342699</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.72244736206786</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.72386456144618</v>
+        <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.918963250056294</v>
+        <v>-3.903775245431582</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.155922837109914</v>
+        <v>1.204777823712229</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5461181721908287</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.051535464760677</v>
+        <v>3.077300000734459</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.729873091843106</v>
+        <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.899607114162447</v>
+        <v>-3.884419109537735</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.169673821864379</v>
+        <v>1.218528808466693</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5461181721908287</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.057543995157603</v>
+        <v>3.083308531131385</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519904</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.627823313120305</v>
+        <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.751864143927444</v>
+        <v>-3.736676139302733</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.126721231235579</v>
+        <v>1.175576217837894</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.7139255294257119</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.056178630775733</v>
+        <v>3.081943166749515</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181163</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.630616934651786</v>
+        <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.835685365202143</v>
+        <v>-3.820497360577431</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.095986364257181</v>
+        <v>1.144841350859495</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.7139255294257119</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.058972252307214</v>
+        <v>3.084736788280996</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394723</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.631279283043444</v>
+        <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.829532659149358</v>
+        <v>-3.814344654524646</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.099109795069953</v>
+        <v>1.147964781672268</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.7200782354784961</v>
+        <v>0.6917194875140836</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.063326224330542</v>
+        <v>3.089090760304325</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890606</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.630359759783555</v>
+        <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.84634195729986</v>
+        <v>-3.831153952675148</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.091466552549863</v>
+        <v>1.140321539152177</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.7032689373279946</v>
+        <v>0.674910189363582</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.052321122180352</v>
+        <v>3.078085658154134</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798421</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.696695313580376</v>
+        <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.784043958523738</v>
+        <v>-3.768855953899026</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.182721305857132</v>
+        <v>1.231576292459447</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7485632016024366</v>
+        <v>0.7202044536380241</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.145833234541838</v>
+        <v>3.17159777051562</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.498987315294503</v>
+        <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.58225376085858</v>
+        <v>-3.750576425446168</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.065729386637323</v>
+        <v>1.041180105554717</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.946581393771591</v>
+        <v>0.7907694160234544</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.066936151557457</v>
+        <v>3.016228749661005</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852418</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.569277547616678</v>
+        <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.633140473544775</v>
+        <v>-3.801463138132362</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.11566493388502</v>
+        <v>1.091115652802414</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8956946810853965</v>
+        <v>0.7398827033372599</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.106694356267916</v>
+        <v>3.055986954371464</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319537</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.583905283732721</v>
+        <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.546529730894967</v>
+        <v>-3.714852395482555</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.164936967060986</v>
+        <v>1.140387685978381</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9743204122905548</v>
+        <v>0.8185084345424182</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.168497531107055</v>
+        <v>3.117790129210602</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489377</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.582441264557393</v>
+        <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.606739028900252</v>
+        <v>-3.77506169348784</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.139389228683544</v>
+        <v>1.114839947600939</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.9141111142852703</v>
+        <v>0.7582991365371337</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.130907933128555</v>
+        <v>3.080200531232103</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397786</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.580932882597322</v>
+        <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.5575523802159</v>
+        <v>-3.725875044803488</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.157555506197213</v>
+        <v>1.133006225114608</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.9141111142852703</v>
+        <v>0.7582991365371337</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.129399551168484</v>
+        <v>3.078692149272032</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316241</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.580795750032758</v>
+        <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.513179248577332</v>
+        <v>-3.68150191316492</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.175167626288077</v>
+        <v>1.150618345205472</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9584842459238389</v>
+        <v>0.8026722681757023</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.155886297587061</v>
+        <v>3.105178895690609</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.82156211710596</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.575189544171348</v>
+        <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.535659599436217</v>
+        <v>-3.703982264023804</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.160569280083114</v>
+        <v>1.136019999000508</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9584842459238389</v>
+        <v>0.8026722681757023</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.150280091725652</v>
+        <v>3.0995726898292</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190318</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.581571301199153</v>
+        <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.488003868875161</v>
+        <v>-3.656326533462749</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.186013329335341</v>
+        <v>1.161464048252735</v>
       </c>
       <c r="F1978" t="n">
-        <v>1.006139976484894</v>
+        <v>0.8503279987367579</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.18525528709009</v>
+        <v>3.134547885193637</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.82267821056961</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.586463674573878</v>
+        <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.387485710376406</v>
+        <v>-3.555808374963994</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.231112966109567</v>
+        <v>1.206563685026962</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.106658134983649</v>
+        <v>0.9508461572355125</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.250458555564068</v>
+        <v>3.199751153667615</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.57321834704975</v>
+        <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.371580380944053</v>
+        <v>-3.539903045531641</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.22422977035838</v>
+        <v>1.199680489275775</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.02754547427441</v>
+        <v>0.8717334965262735</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.189745631614397</v>
+        <v>3.139038229717944</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932762</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.577316049660379</v>
+        <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.326741979335655</v>
+        <v>-3.495064643923243</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.246262833612368</v>
+        <v>1.221713552529763</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.03208890721928</v>
+        <v>0.876276929471143</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.196569393991947</v>
+        <v>3.145861992095494</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917044</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.581476989291457</v>
+        <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.346240435577664</v>
+        <v>-3.514563100165252</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.242624390746643</v>
+        <v>1.218075109664038</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9840042659393753</v>
+        <v>0.8281922881912387</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.171879548855082</v>
+        <v>3.12117214695863</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.587356591819294</v>
+        <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.302037598491763</v>
+        <v>-3.470360263079351</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.26618512810884</v>
+        <v>1.241635847026235</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.028207103025276</v>
+        <v>0.8723951252771391</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.204280853634459</v>
+        <v>3.153573451738007</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.585766592288541</v>
+        <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.30959726432881</v>
+        <v>-3.477919928916398</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.261571262243269</v>
+        <v>1.237021981160664</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.083010507035095</v>
+        <v>0.9271985292869585</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.235572896509598</v>
+        <v>3.184865494613146</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.637014357471581</v>
+        <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.151305846789538</v>
+        <v>-3.319628511377126</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.376135594442018</v>
+        <v>1.351586313359412</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.083010507035095</v>
+        <v>0.9271985292869585</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.286820661692638</v>
+        <v>3.236113259796186</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.635455062065834</v>
+        <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.943663843155062</v>
+        <v>-3.11198650774265</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.457633100490061</v>
+        <v>1.433083819407456</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.290652510669571</v>
+        <v>1.134840532921435</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.409846568467577</v>
+        <v>3.359139166571125</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.630403290304104</v>
+        <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.892631750432534</v>
+        <v>-3.060954415020122</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.472994165817343</v>
+        <v>1.448444884734737</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.341684603392099</v>
+        <v>1.185872625643963</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.435414052339364</v>
+        <v>3.384706650442912</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.647590694396809</v>
+        <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.827407569305328</v>
+        <v>-2.995730233892916</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.51627124236093</v>
+        <v>1.491721961278324</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.406908784519305</v>
+        <v>1.251096806771168</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.491735965108392</v>
+        <v>3.44102856321194</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.84006118688255</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.643551666696089</v>
+        <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.789980549234194</v>
+        <v>-2.958303213821782</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.527203022688664</v>
+        <v>1.502653741606058</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.412160322548487</v>
+        <v>1.25634834480035</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.490847860225182</v>
+        <v>3.440140458328729</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992653</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.64480845902733</v>
+        <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.810092205268902</v>
+        <v>-2.97841486985649</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.520415152606021</v>
+        <v>1.495865871523415</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.423187667545906</v>
+        <v>1.267375689797769</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.498721059554874</v>
+        <v>3.448013657658421</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636279</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.80536623004854</v>
+        <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.781678942169019</v>
+        <v>-2.950001606756607</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.692338228867185</v>
+        <v>1.66778894778458</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.364212104799477</v>
+        <v>1.20840012705134</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.623893492928227</v>
+        <v>3.573186091031775</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957618</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.925479139266358</v>
+        <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.706896681144006</v>
+        <v>-2.875219345731594</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.842364042495007</v>
+        <v>1.817814761412402</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.43899436582449</v>
+        <v>1.283182388076353</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.788875758761052</v>
+        <v>3.7381683568646</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998749</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.917187115280217</v>
+        <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.680812596880198</v>
+        <v>-2.849135261467786</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.844505652214389</v>
+        <v>1.819956371131784</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.43899436582449</v>
+        <v>1.283182388076353</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.780583734774911</v>
+        <v>3.729876332878459</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.915380310863996</v>
+        <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.592934683771078</v>
+        <v>-2.761257348358666</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.877850013041817</v>
+        <v>1.853300731959212</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.554920008247841</v>
+        <v>1.399108030499704</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.848332315812701</v>
+        <v>3.797624913916248</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959853</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.932934716590788</v>
+        <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.584042222377794</v>
+        <v>-2.752364886965382</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.898961403325922</v>
+        <v>1.874412122243316</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.554920008247841</v>
+        <v>1.399108030499704</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.865886721539492</v>
+        <v>3.81517931964304</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945362</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.924789763995371</v>
+        <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.752518339347672</v>
+        <v>-2.92084100393526</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.823426003942554</v>
+        <v>1.798876722859949</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.52697217253126</v>
+        <v>1.371160194783123</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.840973067514128</v>
+        <v>3.790265665617675</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.906059461183233</v>
+        <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.306262146718232</v>
+        <v>-2.47458481130582</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.983198178182192</v>
+        <v>1.958648897099587</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.432253502861627</v>
+        <v>1.276441525113491</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.76541156290021</v>
+        <v>3.714704161003758</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.896723483680138</v>
+        <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.28354104303508</v>
+        <v>-2.451863707622667</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.982950642152358</v>
+        <v>1.958401361069753</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.432253502861627</v>
+        <v>1.276441525113491</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.756075585397114</v>
+        <v>3.705368183500662</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.055629609531307</v>
+        <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.412742856329122</v>
+        <v>-2.58106552091671</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.09017604268591</v>
+        <v>2.065626761603305</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.303051689567585</v>
+        <v>1.147239711819448</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.837460623271858</v>
+        <v>3.786753221375406</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.092707432024953</v>
+        <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.438617254803148</v>
+        <v>-2.606939919390736</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.116904105789946</v>
+        <v>2.092354824707341</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.347963298279326</v>
+        <v>1.19215132053119</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.901485410992549</v>
+        <v>3.850778009096097</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.089382788014499</v>
+        <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.431562564587974</v>
+        <v>-2.599885229175562</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.116401337865561</v>
+        <v>2.091852056782955</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.3550179884945</v>
+        <v>1.199206010746363</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.902393581111199</v>
+        <v>3.851686179214747</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.09938894165924</v>
+        <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.404611340261486</v>
+        <v>-2.572934004849074</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.137187981240897</v>
+        <v>2.112638700158292</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.369898334522219</v>
+        <v>1.214086356774082</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.921327942372572</v>
+        <v>3.87062054047612</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784103</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.2834920738042</v>
+        <v>3.191495693610232</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.426155568092273</v>
+        <v>-2.594478232679861</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.312673422253543</v>
+        <v>2.15334797622454</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.369898334522219</v>
+        <v>1.214086356774082</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.105431074517532</v>
+        <v>3.919947507674681</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.275608768707193</v>
+        <v>3.183612388513225</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.448563685897145</v>
+        <v>-2.616886350484733</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.295826870034587</v>
+        <v>2.136501424005584</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.369898334522219</v>
+        <v>1.214086356774082</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.097547769420525</v>
+        <v>3.912064202577675</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.27766276825683</v>
+        <v>3.185666388062863</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.476787921474746</v>
+        <v>-2.645110586062334</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.286591175353184</v>
+        <v>2.127265729324181</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.387875086973528</v>
+        <v>1.232063109225391</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.110387820440947</v>
+        <v>3.924904253598098</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.72945228516197</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.333916485978678</v>
+        <v>3.24192010578471</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.486228847363276</v>
+        <v>-2.654551511950864</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.339068522719619</v>
+        <v>2.179743076690617</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.510302204516919</v>
+        <v>1.354490226768783</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.240097808688829</v>
+        <v>4.05461424184598</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321627</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.336807580523979</v>
+        <v>3.244811200330011</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.57510547853175</v>
+        <v>-2.743428143119337</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.306408964797531</v>
+        <v>2.147083518768528</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.421425573348445</v>
+        <v>1.265613595600309</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.189662924533046</v>
+        <v>4.004179357690196</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.334919393417754</v>
+        <v>3.242923013223786</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.651435456132655</v>
+        <v>-2.819758120720243</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.273988786650944</v>
+        <v>2.114663340621941</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.421425573348445</v>
+        <v>1.265613595600309</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.187774737426821</v>
+        <v>4.002291170583971</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887741</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.329739623020616</v>
+        <v>3.237743242826648</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.745099400810197</v>
+        <v>-2.913422065397785</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.231343438382789</v>
+        <v>2.072017992353786</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.327761628670904</v>
+        <v>1.171949650922767</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.126396600223159</v>
+        <v>3.940913033380308</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343059</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.328173633230768</v>
+        <v>3.2361772530368</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.906667826337452</v>
+        <v>-3.07499049092504</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.165150078382039</v>
+        <v>2.005824632353037</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.200978704873024</v>
+        <v>1.045166727124888</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.048760856154583</v>
+        <v>3.863277289311733</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389342</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.341247040096687</v>
+        <v>3.249250659902719</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.014968488207571</v>
+        <v>-3.183291152795159</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.13490322049991</v>
+        <v>1.975577774470907</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.200978704873024</v>
+        <v>1.045166727124888</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.061834263020502</v>
+        <v>3.876350696177652</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378385</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.333252236879627</v>
+        <v>3.241255856685659</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.032772459928315</v>
+        <v>-3.201095124515903</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.119786828594552</v>
+        <v>1.960461382565549</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.130444081967823</v>
+        <v>0.9746321042196868</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.011518686060321</v>
+        <v>3.826035119217472</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006969</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.331776278006629</v>
+        <v>3.239779897812661</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.060673247037788</v>
+        <v>-3.228995911625376</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.107150554877765</v>
+        <v>1.947825108848763</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.095847157824889</v>
+        <v>0.940035180076752</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.989284572701562</v>
+        <v>3.803801005858713</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787382</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.328540721983828</v>
+        <v>3.23654434178986</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.183199349740682</v>
+        <v>-3.35152201432827</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.054904557773806</v>
+        <v>1.895579111744804</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9733210551219948</v>
+        <v>0.8175090773738581</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.912533355057024</v>
+        <v>3.727049788214175</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585931</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.395246681574331</v>
+        <v>3.303250301380364</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.413713845926271</v>
+        <v>-3.582036510513859</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.029404718890075</v>
+        <v>1.870079272861072</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7428065589364061</v>
+        <v>0.5869945811882694</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.840930616936175</v>
+        <v>3.655447050093326</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.64075008781466</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.535558400576178</v>
+        <v>3.443562020382211</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.762458931150715</v>
+        <v>-3.930781595738303</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.030218403802144</v>
+        <v>1.870892957773141</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6340586050175083</v>
+        <v>0.4782466272693716</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.915993563586683</v>
+        <v>3.730509996743834</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.66828900423709</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.604538669721818</v>
+        <v>3.51254228952785</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.916445348926855</v>
+        <v>-4.084768013514443</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.037604105837328</v>
+        <v>1.878278659808325</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6340586050175083</v>
+        <v>0.4782466272693716</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.984973832732323</v>
+        <v>3.799490265889474</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423383</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.590589871841939</v>
+        <v>3.498593491647971</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.121044783789864</v>
+        <v>-4.289367448377452</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.941815534012245</v>
+        <v>1.782490087983243</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6340586050175083</v>
+        <v>0.4782466272693716</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.971025034852445</v>
+        <v>3.785541468009594</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609749</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.602460360897353</v>
+        <v>3.510463980703385</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.373519937797589</v>
+        <v>-4.541842602385176</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.852695961464569</v>
+        <v>1.693370515435567</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6340586050175083</v>
+        <v>0.4782466272693716</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.982895523907859</v>
+        <v>3.797411957065008</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973152</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.603670895416297</v>
+        <v>3.511674515222329</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.666415694277001</v>
+        <v>-4.834738358864588</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.736748193391748</v>
+        <v>1.577422747362746</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6340586050175083</v>
+        <v>0.4782466272693716</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.984106058426802</v>
+        <v>3.798622491583952</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.66350945725194</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.607792637643618</v>
+        <v>3.51579625744965</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.853079822411809</v>
+        <v>-5.021402486999397</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.666204284365147</v>
+        <v>1.506878838336144</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6073196341929484</v>
+        <v>0.4515076564448117</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.972184418159387</v>
+        <v>3.786700851316538</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916195</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.602870490379808</v>
+        <v>3.51087411018584</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.999100509325771</v>
+        <v>-5.167423173913359</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.602873862335751</v>
+        <v>1.443548416306748</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5982365423990914</v>
+        <v>0.4424245646509548</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.961812415819263</v>
+        <v>3.776328848976413</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830321</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.765074547078852</v>
+        <v>3.673078166884884</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.090814518435357</v>
+        <v>-5.259137183022943</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.728392315390961</v>
+        <v>1.569066869361959</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5982365423990914</v>
+        <v>0.4424245646509548</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.124016472518307</v>
+        <v>3.938532905675457</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071544</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.759921185042666</v>
+        <v>3.667924804848698</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.122466177495326</v>
+        <v>-5.290788842082913</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.710578289730787</v>
+        <v>1.551252843701785</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5930680851546513</v>
+        <v>0.4372561074065145</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.115762036135457</v>
+        <v>3.930278469292607</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868138</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.770150602611157</v>
+        <v>3.678154222417189</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.204400995764209</v>
+        <v>-5.372723660351796</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.688033779991725</v>
+        <v>1.528708333962723</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5831333395675711</v>
+        <v>0.4273213618194344</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.1200306063517</v>
+        <v>3.93454703950885</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332683</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.77907624106706</v>
+        <v>3.687079860873092</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.306377118012617</v>
+        <v>-5.474699782600204</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.656168969548265</v>
+        <v>1.496843523519262</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4811572173191635</v>
+        <v>0.3253452395710268</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.067770571458558</v>
+        <v>3.882287004615708</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231799</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.771229128311235</v>
+        <v>3.679232748117267</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.196370834535395</v>
+        <v>-5.364693499122982</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.692324370183329</v>
+        <v>1.532998924154326</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5043617892364387</v>
+        <v>0.348549811488302</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.073846201853098</v>
+        <v>3.888362635010249</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818514</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.775479139033209</v>
+        <v>3.683482758839241</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.053311258794469</v>
+        <v>-5.221633923382056</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.753798211201674</v>
+        <v>1.594472765172671</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.512375215826418</v>
+        <v>0.3565632380782813</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.08290426852906</v>
+        <v>3.89742070168621</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051781</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.782740021915745</v>
+        <v>3.690743641721777</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.751864533322632</v>
+        <v>-4.920187197910218</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.881637784272945</v>
+        <v>1.722312338243942</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8138219412982552</v>
+        <v>0.6580099635501185</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.271033186694699</v>
+        <v>4.085549619851848</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679618</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.783711199668456</v>
+        <v>3.691714819474488</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.776454777557816</v>
+        <v>-4.944777442145402</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.872772864331582</v>
+        <v>1.713447418302579</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8138219412982552</v>
+        <v>0.6580099635501185</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.272004364447409</v>
+        <v>4.086520797604559</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474154</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.784554104048211</v>
+        <v>3.692557723854244</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.725416401551295</v>
+        <v>-4.893739066138882</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.894031119113945</v>
+        <v>1.734705673084943</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8138219412982552</v>
+        <v>0.6580099635501185</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.272847268827165</v>
+        <v>4.087363701984315</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969536</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.803592202922357</v>
+        <v>3.711595822728389</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.684277106684664</v>
+        <v>-4.852599771272251</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.929524935934743</v>
+        <v>1.77019948990574</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8549612361648861</v>
+        <v>0.6991492584167494</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.316568944621289</v>
+        <v>4.131085377778438</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.82575293270047</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.619776199046291</v>
+        <v>3.527779818852324</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.587642194666024</v>
+        <v>-4.755964859253611</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.784362896866134</v>
+        <v>1.625037450837131</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.951596148183526</v>
+        <v>0.7957841704353893</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.190733887956407</v>
+        <v>4.005250321113557</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077632</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.623278243120255</v>
+        <v>3.531281862926288</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.718222929196867</v>
+        <v>-4.886545593784454</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.735632647127761</v>
+        <v>1.576307201098758</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8210154136526835</v>
+        <v>0.6652034359045468</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.115887491311866</v>
+        <v>3.930403924469016</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.77502886083345</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.607705062196338</v>
+        <v>3.51570868200237</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.553726595005905</v>
+        <v>-4.722049259593492</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.785857999880228</v>
+        <v>1.626532553851225</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9855117478436454</v>
+        <v>0.8296997700955087</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.199012110902525</v>
+        <v>4.013528544059676</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077621</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.606892772632768</v>
+        <v>3.5148963924388</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.476627993464033</v>
+        <v>-4.644950658051619</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.815885150933407</v>
+        <v>1.656559704904404</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9855117478436454</v>
+        <v>0.8296997700955087</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.198199821338955</v>
+        <v>4.012716254496105</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.61676155175784</v>
+        <v>3.524765171563872</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.487013188353922</v>
+        <v>-4.655335852941509</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.821599852102523</v>
+        <v>1.662274406073521</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9751265529537561</v>
+        <v>0.8193145752056193</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.201837483530094</v>
+        <v>4.016353916687244</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735273</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.687598557534265</v>
+        <v>3.595602177340298</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.505601347076147</v>
+        <v>-4.673924011663734</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.885001594390059</v>
+        <v>1.725676148361056</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9565383942315306</v>
+        <v>0.800726416483394</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.261521594073184</v>
+        <v>4.076038027230334</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496548</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.684467568352564</v>
+        <v>3.592471188158596</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.505899893772183</v>
+        <v>-4.674222558359769</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.881751186529943</v>
+        <v>1.72242574050094</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9562398475354947</v>
+        <v>0.8004278697873581</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.258211476873861</v>
+        <v>4.072727910031011</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108848</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.688998463291955</v>
+        <v>3.597002083097987</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.405076760081755</v>
+        <v>-4.573399424669342</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.926611334945505</v>
+        <v>1.767285888916503</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9687040630198486</v>
+        <v>0.812892085271712</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.270220901103865</v>
+        <v>4.084737334261015</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121458</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.689127716770499</v>
+        <v>3.597131336576531</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.214295399329348</v>
+        <v>-4.382618063916935</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.003053132725011</v>
+        <v>1.843727686696009</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.159485423772256</v>
+        <v>1.003673446024119</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.384818971033853</v>
+        <v>4.199335404191003</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906071</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.668964562508095</v>
+        <v>3.576968182314127</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.107332041479927</v>
+        <v>-4.275654706067513</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.025675321602376</v>
+        <v>1.866349875573374</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.217950031732058</v>
+        <v>1.062138053983921</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.39973458154733</v>
+        <v>4.21425101470448</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912976</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.703931499120154</v>
+        <v>3.611935118926186</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.052001453578164</v>
+        <v>-4.220324118165751</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.08277449337514</v>
+        <v>1.923449047346137</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.27328061963382</v>
+        <v>1.117468641885683</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.467899870900445</v>
+        <v>4.282416304057596</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539886</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.697618067021591</v>
+        <v>3.605621686827623</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.039947326665201</v>
+        <v>-4.208269991252788</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.081282712041763</v>
+        <v>1.92195726601276</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.285334746546782</v>
+        <v>1.129522768798646</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.468818914949661</v>
+        <v>4.283335348106811</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.699498697205727</v>
+        <v>3.607502317011759</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.081102446233422</v>
+        <v>-4.249425110821009</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.066701294398611</v>
+        <v>1.907375848369608</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.244179626978561</v>
+        <v>1.088367649230425</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.446006473392864</v>
+        <v>4.260522906550015</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382911</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.71234972308361</v>
+        <v>3.620353342889642</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.013053883541892</v>
+        <v>-4.181376548129479</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.106771745353105</v>
+        <v>1.947446299324102</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.312228189670091</v>
+        <v>1.156416211921955</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.499686636885665</v>
+        <v>4.314203070042815</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013418</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.732552393257204</v>
+        <v>3.640556013063236</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.244654276711393</v>
+        <v>-4.41297694129898</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.034334258258899</v>
+        <v>1.875008812229896</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.312228189670091</v>
+        <v>1.156416211921955</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.519889307059259</v>
+        <v>4.334405740216409</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498963</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.716158629324086</v>
+        <v>3.624162249130118</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.294705822240612</v>
+        <v>-4.463028486828199</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.997919876114093</v>
+        <v>1.83859443008509</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.312228189670091</v>
+        <v>1.156416211921955</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.503495543126141</v>
+        <v>4.318011976283291</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800092</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.676410542917552</v>
+        <v>3.584414162723585</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.469812654817057</v>
+        <v>-4.638135319404643</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.888129056676982</v>
+        <v>1.728803610647979</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.312228189670091</v>
+        <v>1.156416211921955</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.463747456719608</v>
+        <v>4.278263889876758</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660845</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.683433161914492</v>
+        <v>3.591436781720525</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.273712501386534</v>
+        <v>-4.44203516597412</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.973591737046131</v>
+        <v>1.814266291017129</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.508328343100614</v>
+        <v>1.352516365352478</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.588430167774861</v>
+        <v>4.402946600932012</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395082</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.782604161487397</v>
+        <v>3.690607781293429</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.120687109273249</v>
+        <v>-4.289009773860836</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.133972893464349</v>
+        <v>1.974647447435347</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.661353735213898</v>
+        <v>1.505541757465762</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.779416402615736</v>
+        <v>4.593932835772886</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791143</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.970070386395689</v>
+        <v>3.878074006201722</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.14899442314652</v>
+        <v>-4.317317087734106</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.310116192823334</v>
+        <v>2.150790746794331</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.661353735213898</v>
+        <v>1.505541757465762</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.966882627524028</v>
+        <v>4.781399060681179</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620429</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.939473337749772</v>
+        <v>3.847476957555804</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.315587648260042</v>
+        <v>-4.483910312847629</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.212881854132007</v>
+        <v>2.053556408103005</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.494760510100376</v>
+        <v>1.338948532352239</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.836329643809997</v>
+        <v>4.650846076967148</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285643</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.943149740411489</v>
+        <v>3.851153360217522</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.292551854898476</v>
+        <v>-4.460874519486063</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.225772574138351</v>
+        <v>2.066447128109349</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.494760510100376</v>
+        <v>1.338948532352239</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.840006046471715</v>
+        <v>4.654522479628866</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399464</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.940767795534985</v>
+        <v>3.848771415341017</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.263305874442779</v>
+        <v>-4.431628539030366</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.235089021444125</v>
+        <v>2.075763575415123</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.494760510100376</v>
+        <v>1.338948532352239</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.83762410159521</v>
+        <v>4.652140534752361</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699404642256366</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.93806103469262</v>
+        <v>3.846064654498652</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.37023142232063</v>
+        <v>-4.538554086908217</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.189612041450619</v>
+        <v>2.030286595421618</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.387834962222525</v>
+        <v>1.232022984474388</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.770762012026134</v>
+        <v>4.585278445183286</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600700995</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.939489836835854</v>
+        <v>3.847493456641887</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.515249980827879</v>
+        <v>-4.683572645415466</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.133033420190954</v>
+        <v>1.973707974161952</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.242816403715276</v>
+        <v>1.087004425967139</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.68517967906502</v>
+        <v>4.49969611222217</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687006</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.039421076093607</v>
+        <v>3.947424695899639</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.633591746612597</v>
+        <v>-4.801914411200183</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.18562795313482</v>
+        <v>2.026302507105818</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.253502442278166</v>
+        <v>1.09769046453003</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.791522541460507</v>
+        <v>4.606038974617658</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790796</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.037206773219546</v>
+        <v>3.945210393025578</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.685002168933305</v>
+        <v>-4.853324833520891</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.162849481332476</v>
+        <v>2.003524035303474</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.253502442278166</v>
+        <v>1.09769046453003</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.789308238586446</v>
+        <v>4.603824671743595</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437324</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.037109901293835</v>
+        <v>3.945113521099867</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.764421620141056</v>
+        <v>-4.932744284728643</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.130984828923665</v>
+        <v>1.971659382894662</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.253502442278166</v>
+        <v>1.09769046453003</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.789211366660735</v>
+        <v>4.603727799817886</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298391</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.037103794851879</v>
+        <v>3.945107414657911</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.859884618058274</v>
+        <v>-5.028207282645861</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.092793523314821</v>
+        <v>1.933468077285819</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.253502442278166</v>
+        <v>1.09769046453003</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.789205260218779</v>
+        <v>4.603721693375929</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960217993</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.035200191414489</v>
+        <v>3.943203811220521</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.795508707207559</v>
+        <v>-4.963831371795146</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.116640284217718</v>
+        <v>1.957314838188715</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.317878353128881</v>
+        <v>1.162066375380745</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.825927203291818</v>
+        <v>4.640443636448969</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353528</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.040934009162216</v>
+        <v>3.948937628968248</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.850877869339753</v>
+        <v>-5.019200533927339</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.100226437112567</v>
+        <v>1.940900991083564</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.317878353128881</v>
+        <v>1.162066375380745</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.831661021039545</v>
+        <v>4.646177454196695</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113271</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.040472372505148</v>
+        <v>3.948475992311181</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.89631564917058</v>
+        <v>-5.064638313758167</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.081589688523168</v>
+        <v>1.922264242494166</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.275033362450722</v>
+        <v>1.119221384702585</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.805492389975581</v>
+        <v>4.620008823132732</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.79027250011368</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.060346765355467</v>
+        <v>3.9683503851615</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.808108815023002</v>
+        <v>-4.976431479610588</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.136746815032518</v>
+        <v>1.977421369003517</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.275033362450722</v>
+        <v>1.119221384702585</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.8253667828259</v>
+        <v>4.639883215983051</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016434</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.044047465880195</v>
+        <v>3.952051085686228</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.702073819817692</v>
+        <v>-4.870396484405279</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.16286151363937</v>
+        <v>2.003536067610368</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.275033362450722</v>
+        <v>1.119221384702585</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.809067483350628</v>
+        <v>4.623583916507779</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794705093307665</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.04647841534424</v>
+        <v>3.954482035150273</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.518862156684597</v>
+        <v>-4.687184821272184</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.238577128356654</v>
+        <v>2.079251682327652</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.275033362450722</v>
+        <v>1.119221384702585</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.811498432814673</v>
+        <v>4.626014865971825</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863546</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.01226960119213</v>
+        <v>3.920273220998163</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.447140709670746</v>
+        <v>-4.615463374258333</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.233056893010083</v>
+        <v>2.073731446981082</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.346754809464572</v>
+        <v>1.190942831716436</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.820322486870873</v>
+        <v>4.634838920028025</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394107</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.959185347113301</v>
+        <v>3.867188966919334</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.42476768406304</v>
+        <v>-4.593090348650627</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.188921849174338</v>
+        <v>2.029596403145336</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.358010560577474</v>
+        <v>1.202198582829337</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.773991683459786</v>
+        <v>4.588508116616937</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456723</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.144383551998657</v>
+        <v>4.05238717180469</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.457783979973785</v>
+        <v>-4.626106644561371</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.360913535695395</v>
+        <v>2.201588089666394</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.288573183910722</v>
+        <v>1.132761206162586</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.917527462345091</v>
+        <v>4.732043895502242</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883669</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.136304777826906</v>
+        <v>4.044308397632939</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.446256344324176</v>
+        <v>-4.614579008911763</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.357445815783487</v>
+        <v>2.198120369754486</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.347573842112085</v>
+        <v>1.191761864363948</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.944849083094157</v>
+        <v>4.759365516251308</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236289</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.139972890348695</v>
+        <v>4.047976510154728</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.543597845666545</v>
+        <v>-4.711920510254132</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.322177327768329</v>
+        <v>2.162851881739327</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.303153659946596</v>
+        <v>1.14734168219846</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.921865086316653</v>
+        <v>4.736381519473804</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427676</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.141223972541533</v>
+        <v>4.049227592347566</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.629453875006512</v>
+        <v>-4.797776539594098</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.28908599822518</v>
+        <v>2.129760552196179</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.260777590720461</v>
+        <v>1.104965612972325</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.89769052697381</v>
+        <v>4.712206960130961</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610375</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.123643174362035</v>
+        <v>4.031646794168068</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.638290672422631</v>
+        <v>-4.806613337010218</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.267970481079234</v>
+        <v>2.108645035050233</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.253335418079111</v>
+        <v>1.097523440330974</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.875644425209501</v>
+        <v>4.690160858366652</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667447</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.133807685407084</v>
+        <v>4.041811305213117</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.729673234988089</v>
+        <v>-4.897995899575676</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.2415819670981</v>
+        <v>2.082256521069099</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.216770533359766</v>
+        <v>1.060958555611629</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.863870005422944</v>
+        <v>4.678386438580095</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889183</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.235935943231352</v>
+        <v>4.143939563037385</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.717966517001083</v>
+        <v>-4.88628918158867</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.348392912117171</v>
+        <v>2.189067466088169</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.228477251346773</v>
+        <v>1.072665273598636</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.973022294039416</v>
+        <v>4.787538727196567</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409559</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.238968281962757</v>
+        <v>4.14697190176879</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.618303012917421</v>
+        <v>-4.786625677505008</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.391290652482041</v>
+        <v>2.231965206453039</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.291664334550459</v>
+        <v>1.135852356802322</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.013966882693032</v>
+        <v>4.828483315850184</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452566</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.451873115240815</v>
+        <v>4.359876735046848</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.628619111083773</v>
+        <v>-4.796941775671359</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.600069046493558</v>
+        <v>2.440743600464557</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.291664334550459</v>
+        <v>1.135852356802322</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.22687171597109</v>
+        <v>5.041388149128242</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762279</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.451051782152905</v>
+        <v>4.359055401958938</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.6285251430664</v>
+        <v>-4.796847807653987</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.599285300612597</v>
+        <v>2.439959854583595</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.292034195897777</v>
+        <v>1.13622221814964</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.226272299691571</v>
+        <v>5.040788732848722</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.63321346798801</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.445283768097259</v>
+        <v>4.353287387903292</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.635743967266245</v>
+        <v>-4.804066631853831</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.590629756877012</v>
+        <v>2.431304310848011</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.292034195897777</v>
+        <v>1.13622221814964</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.220504285635925</v>
+        <v>5.035020718793076</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740916</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.445283768097259</v>
+        <v>4.353287387903292</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.634795544148206</v>
+        <v>-4.803118208735793</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.591009126124228</v>
+        <v>2.431683680095227</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.292034195897777</v>
+        <v>1.13622221814964</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.220504285635925</v>
+        <v>5.035020718793076</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.88106536666362</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.458011376078351</v>
+        <v>4.366014995884384</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.79186400240383</v>
+        <v>-4.960186666991417</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.54090935080307</v>
+        <v>2.381583904774069</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.292034195897777</v>
+        <v>1.13622221814964</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.233231893617017</v>
+        <v>5.047748326774168</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424764</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.459957374502738</v>
+        <v>4.367960994308771</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.785871755615019</v>
+        <v>-4.954194420202605</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.545252247942983</v>
+        <v>2.385926801913981</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.292034195897777</v>
+        <v>1.13622221814964</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.235177892041404</v>
+        <v>5.049694325198556</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149212</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.453611510520507</v>
+        <v>4.36161513032654</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.697313794484251</v>
+        <v>-4.865636459071838</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.574329568413058</v>
+        <v>2.415004122384057</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.292034195897777</v>
+        <v>1.13622221814964</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.228832028059173</v>
+        <v>5.043348461216325</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383085</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.452920187959503</v>
+        <v>4.360923807765536</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.679554716981177</v>
+        <v>-4.847877381568764</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.580741876853284</v>
+        <v>2.421416430824283</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.292034195897777</v>
+        <v>1.13622221814964</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.228140705498169</v>
+        <v>5.04265713865532</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720996</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.46570237386809</v>
+        <v>4.373705993674123</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.689456412594282</v>
+        <v>-4.711699005129952</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.589563384516629</v>
+        <v>2.488669967308394</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.282132500284672</v>
+        <v>1.272400594588452</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.234981874038893</v>
+        <v>5.137146350427194</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.821469290221052</v>
+        <v>3.471484921079516</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.524645482255539</v>
+        <v>4.406306053828998</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.689456412594282</v>
+        <v>-4.711699005129952</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.589563384516629</v>
+        <v>2.488669967308394</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.282132500284672</v>
+        <v>1.272400594588452</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.517709279241907</v>
+        <v>4.399369850815366</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>106.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>129.0%</t>
+          <t>151.1%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-76.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>122.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.2%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-632.7%</t>
+          <t>-626.1%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-127.4%</t>
+          <t>-111.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-324.7%</t>
+          <t>-324.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.8%</t>
+          <t>-85.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,52 +1461,52 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
     </row>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.685717243089963</v>
+        <v>-8.66165290190634</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2921262127167896</v>
+        <v>-0.2825004762433405</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.447973044473831</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.307950273995118</v>
+        <v>2.313733282148645</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.613584067802082</v>
+        <v>-8.589519726618459</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2575392383630009</v>
+        <v>-0.2479135018895517</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.447973044473831</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.313683978233754</v>
+        <v>2.319466986387281</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.542217675192434</v>
+        <v>-8.518153334008812</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.238729943713007</v>
+        <v>-0.2291042072395579</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.376606651864184</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.346766551405678</v>
+        <v>2.352549559559205</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232413</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.44875864120721</v>
+        <v>-8.424694300023587</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2112298114318247</v>
+        <v>-0.2016040749583756</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.376606651864184</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.33688307009277</v>
+        <v>2.342666078246297</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436229</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.438105459653778</v>
+        <v>-8.414041118470156</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2088030993098262</v>
+        <v>-0.1991773628363771</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.376606651864184</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.335048509593396</v>
+        <v>2.340831517746924</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.340198420977288</v>
+        <v>-8.316134079793665</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1699405988126905</v>
+        <v>-0.1603148623392414</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.318259248926172</v>
+        <v>-1.308620902003627</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37553964453627</v>
+        <v>2.381322652689796</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.31624488000133</v>
+        <v>-8.292180538817707</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.159690676276814</v>
+        <v>-0.1500649398033649</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.294305707950215</v>
+        <v>-1.28466736102767</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.390580275267338</v>
+        <v>2.396363283420865</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.052184941678533</v>
+        <v>-8.02812060049491</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.06732701710944733</v>
+        <v>-0.05770128063599822</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.020607422704873</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.535755922099263</v>
+        <v>2.54153893025279</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.345105318173695</v>
+        <v>-7.321040976990072</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2127177986321871</v>
+        <v>0.2223435351056362</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.020607422704873</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.532968888438962</v>
+        <v>2.53875189659249</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.304921019807504</v>
+        <v>-7.280856678623882</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2291351418665046</v>
+        <v>0.2387608783399537</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9900614712612278</v>
+        <v>-0.9804231243386826</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.557423091346518</v>
+        <v>2.563206099500045</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.141521148868142</v>
+        <v>-7.117456807684519</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2938619114630066</v>
+        <v>0.3034876479364557</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8266616003218653</v>
+        <v>-0.8170232533993201</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.654829835130893</v>
+        <v>2.66061284328442</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.908039926638543</v>
+        <v>-6.88397558545492</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3951788291926985</v>
+        <v>0.4048045656661476</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5931803780922668</v>
+        <v>-0.5835420311697216</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.802842997306504</v>
+        <v>2.808626005460031</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.758373535631028</v>
+        <v>-6.734309194447405</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4521531752827452</v>
+        <v>0.4617789117561943</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5002768868497308</v>
+        <v>-0.4906385399271856</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855692881739067</v>
+        <v>2.861475889892593</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.626098062000142</v>
+        <v>-6.602033720816519</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4063241507422544</v>
+        <v>0.4159498872157035</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3680014132188442</v>
+        <v>-0.358363066296299</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.836318951924753</v>
+        <v>2.84210196007828</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.454236846435239</v>
+        <v>-6.430172505251616</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4778836976558525</v>
+        <v>0.4875094341293016</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1961401976539413</v>
+        <v>-0.1865018507313961</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.942250741951332</v>
+        <v>2.948033750104859</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.36927217970592</v>
+        <v>-6.345207838522297</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5247759055712389</v>
+        <v>0.534401642044688</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1111755309246217</v>
+        <v>-0.1015371840020766</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.006135883212582</v>
+        <v>3.011918891366109</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.474862169479024</v>
+        <v>-6.450797828295402</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3545639800627782</v>
+        <v>0.3641897165362273</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2167655206977261</v>
+        <v>-0.2071271737751809</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.814805959749501</v>
+        <v>2.820588967903028</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.406627584853597</v>
+        <v>-6.382563243669974</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4304021557900355</v>
+        <v>0.4400278922634846</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1983501978251901</v>
+        <v>-0.1887118509026449</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.874399495350109</v>
+        <v>2.880182503503636</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.258687543445998</v>
+        <v>-6.234623202262375</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3729573637146681</v>
+        <v>0.3825831001881173</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1780292819166325</v>
+        <v>-0.1683909349940874</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769971236256836</v>
+        <v>2.775754244410363</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.205718021192009</v>
+        <v>-6.181653680008386</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3854311863627853</v>
+        <v>0.3950569228362344</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1154214127400985</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793038963355751</v>
+        <v>2.798821971509278</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.039929825231718</v>
+        <v>-6.015865484048096</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4447858526518087</v>
+        <v>0.4544115891252578</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1154214127400985</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786078351260658</v>
+        <v>2.791861359414185</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.00656661875295</v>
+        <v>-5.982502277569327</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4725934896244595</v>
+        <v>0.4822192260979086</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1154214127400985</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800540705641801</v>
+        <v>2.806323713795328</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.898307481630428</v>
+        <v>-5.874243140446805</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5104292649326632</v>
+        <v>0.5200550014061123</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1154214127400985</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795072826100996</v>
+        <v>2.800855834254523</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.775016346813297</v>
+        <v>-5.750952005629674</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5572438128700923</v>
+        <v>0.5668695493435414</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.001768624845513156</v>
+        <v>0.007869722077032015</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866545601001851</v>
+        <v>2.872328609155379</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.722319479682006</v>
+        <v>-5.698255138498383</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5860235379599339</v>
+        <v>0.595649274433383</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.0605665892083232</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.905864699517951</v>
+        <v>2.911647707671478</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.478554037698562</v>
+        <v>-5.454489696514939</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6793104231003624</v>
+        <v>0.6889361595738115</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.0605665892083232</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.901645407865002</v>
+        <v>2.907428416018529</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.388778365322089</v>
+        <v>-5.364714024138467</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7173450059709672</v>
+        <v>0.7269707424444163</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1221660341226332</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.940729388733604</v>
+        <v>2.946512396887131</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.138927971373015</v>
+        <v>-5.114863630189392</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8100272385342993</v>
+        <v>0.8196529750077484</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1221660341226332</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.933471463717306</v>
+        <v>2.939254471870833</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.963035878905583</v>
+        <v>-4.93897153772196</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8839831990419207</v>
+        <v>0.8936089355153698</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1221660341226332</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.937070587237955</v>
+        <v>2.942853595391482</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.791589415883119</v>
+        <v>-4.767525074699496</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9658892903054599</v>
+        <v>0.975515026778909</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2839741502225512</v>
+        <v>0.2936124971450964</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053265971105986</v>
+        <v>3.059048979259514</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.711567128773998</v>
+        <v>-4.687502787590375</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9969186827654051</v>
+        <v>1.006544419238854</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3639964373316721</v>
+        <v>0.3736347842542173</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100299820987756</v>
+        <v>3.106082829141283</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.647931386540064</v>
+        <v>-4.623867045356441</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.027067780713296</v>
+        <v>1.036693517186745</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4372705264881518</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.143176067382434</v>
+        <v>3.148959075535961</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.79881477107478</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.554234068323669</v>
+        <v>-4.530169727140046</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.04574096678365</v>
+        <v>1.055366703257099</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4372705264881518</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124370326166229</v>
+        <v>3.130153334319757</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.564736691388958</v>
+        <v>-4.540672350205335</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.043282994182412</v>
+        <v>1.052908730655861</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.426767903422863</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119811828951934</v>
+        <v>3.125594837105461</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.452250430720083</v>
+        <v>-4.42818608953646</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.092206812284782</v>
+        <v>1.101832548758231</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.426767903422863</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123741142786754</v>
+        <v>3.129524150940281</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.434536743842218</v>
+        <v>-4.410472402658595</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.099970870953268</v>
+        <v>1.109596607426717</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4299492323197798</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126328524042244</v>
+        <v>3.132111532195771</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.311062472529199</v>
+        <v>-4.286998131345577</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.146358650698469</v>
+        <v>1.155984387171918</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.4299492323197798</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123326595262237</v>
+        <v>3.129109603415765</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.091041674492189</v>
+        <v>-4.066977333308566</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.235946006923887</v>
+        <v>1.245571743397336</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.57116907738776</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.20963753931364</v>
+        <v>3.215420547467167</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.958173985428911</v>
+        <v>-3.934109644245288</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.304987265351021</v>
+        <v>1.314613001824471</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.57116907738776</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225531722115463</v>
+        <v>3.23131473026899</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.838000902064412</v>
+        <v>-3.813936560880789</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.354202343137123</v>
+        <v>1.363828079610572</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6817038138297138</v>
+        <v>0.691342160752259</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298781416574464</v>
+        <v>3.304564424727992</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.702747540734435</v>
+        <v>-3.678683199550812</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.418391790230554</v>
+        <v>1.428017526704003</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8169571751596909</v>
+        <v>0.8265955220822361</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.390021535933891</v>
+        <v>3.395804544087417</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.762622368092127</v>
+        <v>-3.738558026908504</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.380479350688903</v>
+        <v>1.390105087162352</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.766720694724544</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.340134130920701</v>
+        <v>3.345917139074228</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.64280213718129</v>
+        <v>-3.618737795997667</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.443696612287446</v>
+        <v>1.453322348760895</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.766720694724544</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355423300154909</v>
+        <v>3.361206308308437</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.645271843643096</v>
+        <v>-3.621207502459473</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.350352929025165</v>
+        <v>1.359978665498614</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7546126413401926</v>
+        <v>0.7642509882627377</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261585675600267</v>
+        <v>3.267368683753794</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.713642029967105</v>
+        <v>-3.689577688783483</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.242266715980863</v>
+        <v>1.251892452454312</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7735266872989527</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186412956507298</v>
+        <v>3.192195964660825</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.825514309593256</v>
+        <v>-3.801449968409633</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.187954512762294</v>
+        <v>1.197580249235743</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7735266872989527</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176849665139189</v>
+        <v>3.182632673292716</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.881034385485846</v>
+        <v>-3.856970044302223</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.30277731909746</v>
+        <v>1.312403055570909</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7735266872989527</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313880501831391</v>
+        <v>3.319663509984919</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.705560125693376</v>
+        <v>-3.681495784509754</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.377534255006236</v>
+        <v>1.387159991479685</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7735266872989527</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.318447733823179</v>
+        <v>3.324230741976706</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.697635751108462</v>
+        <v>-3.673571409924839</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.356446033601409</v>
+        <v>1.366071770074858</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7735266872989527</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.294189762584386</v>
+        <v>3.299972770737913</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.691357548538613</v>
+        <v>-3.66729320735499</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.287495628030798</v>
+        <v>1.297121364504247</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7798048898688017</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.226494997527745</v>
+        <v>3.232278005681272</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.63150492933489</v>
+        <v>-3.607440588151267</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.32160906214442</v>
+        <v>1.331234798617869</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7798048898688017</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.236667383959878</v>
+        <v>3.242450392113405</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.545261466308513</v>
+        <v>-3.52119712512489</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.351052717928831</v>
+        <v>1.36067845440228</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7798048898688017</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.231613654533738</v>
+        <v>3.237396662687265</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.590568285707493</v>
+        <v>-3.56650394452387</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.324705765613764</v>
+        <v>1.334331502087214</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7389947268595709</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.198903332172725</v>
+        <v>3.204686340326252</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.619601390409794</v>
+        <v>-3.595537049226171</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.313644396765945</v>
+        <v>1.323270133239395</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7389947268595709</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.199455205205827</v>
+        <v>3.205238213359354</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.526790908958935</v>
+        <v>-3.502726567775312</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.280041281237655</v>
+        <v>1.289667017711104</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8221668613878851</v>
+        <v>0.8318052083104303</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.184414185967708</v>
+        <v>3.190197194121235</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.571180378288362</v>
+        <v>-3.54711603710474</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.264158969430484</v>
+        <v>1.273784705903934</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7777773920584574</v>
+        <v>0.7874157389810026</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159653980294652</v>
+        <v>3.165436988448179</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.550676684402865</v>
+        <v>-3.526612343219242</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.267436155496406</v>
+        <v>1.277061891969856</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.8079194328664999</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.167031905137673</v>
+        <v>3.172814913291201</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.590600778985437</v>
+        <v>-3.566536437801815</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.256957813494045</v>
+        <v>1.266583549967494</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.8079194328664999</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.172523200968341</v>
+        <v>3.178306209121868</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.61838117688679</v>
+        <v>-3.594316835703168</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.257342856102043</v>
+        <v>1.266968592575492</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7705006880426017</v>
+        <v>0.7801390349651469</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.167352163996068</v>
+        <v>3.173135172149595</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.736761849616929</v>
+        <v>-3.712697508433306</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.04834630701064</v>
+        <v>1.05797204348409</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7129211828141707</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.965377172706136</v>
+        <v>2.971160180859663</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.84537592806026</v>
+        <v>-3.821311586876637</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.125050336352514</v>
+        <v>1.134676072825963</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7129211828141707</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.085526833425341</v>
+        <v>3.091309841578868</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.809966889812117</v>
+        <v>-3.836083859358026</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.153726977754094</v>
+        <v>1.14328018993573</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7129211828141707</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.100039859527664</v>
+        <v>3.105822867681191</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.771583227253966</v>
+        <v>-3.797700196799875</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.166499884119723</v>
+        <v>1.156053096301359</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7513048453723219</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.120489498404924</v>
+        <v>3.126272506558451</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.5944668972188</v>
+        <v>-3.620583866764709</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.234075444979091</v>
+        <v>1.223628657160728</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7513048453723219</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.117218527250226</v>
+        <v>3.123001535403753</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.639559142052345</v>
+        <v>-3.665676111598255</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.216721938807586</v>
+        <v>1.206275150989223</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6797704552803869</v>
+        <v>0.6894088022029321</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.080764293110505</v>
+        <v>3.086547301264032</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.460183720813578</v>
+        <v>-3.486300690359487</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.282259082609508</v>
+        <v>1.271812294791144</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8365472134511056</v>
+        <v>0.8461855603736508</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.16861732331935</v>
+        <v>3.174400331472877</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982222</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.505197934334184</v>
+        <v>-3.531314903880093</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.245060852532855</v>
+        <v>1.234614064714491</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.806198318136501</v>
+        <v>0.8158366650590462</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.131215441462177</v>
+        <v>3.136998449615704</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509531</v>
+        <v>3.737026608509541</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.772202444606619</v>
+        <v>-3.798319414152528</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.143950610762827</v>
+        <v>1.133503822944463</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6118352800935525</v>
+        <v>0.6214736270160977</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.020289180975354</v>
+        <v>3.026072189128881</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760807</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.873400226043792</v>
+        <v>-3.899517195589701</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.102675420084459</v>
+        <v>1.092228632266095</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5530648134707785</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.978447814744664</v>
+        <v>2.984230822898191</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.866889259429479</v>
+        <v>-3.893006228975389</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.102879768284501</v>
+        <v>1.092432980466137</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5530648134707785</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.976047776298981</v>
+        <v>2.981830784452508</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.847851131722182</v>
+        <v>-3.873968101268091</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.107019738575665</v>
+        <v>1.096572950757301</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.494881202139584</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.937662328708509</v>
+        <v>2.943445336862036</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131244</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.900366933997002</v>
+        <v>-3.926483903542911</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.205307819299927</v>
+        <v>1.194861031481563</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.494881202139584</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.056956730342699</v>
+        <v>3.062739738496226</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.72244736206786</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.903775245431582</v>
+        <v>-3.929892214977491</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.204777823712229</v>
+        <v>1.194331035893865</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5273977711489614</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.077300000734459</v>
+        <v>3.083083008887986</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.884419109537735</v>
+        <v>-3.910536079083644</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.218528808466693</v>
+        <v>1.20808202064833</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5273977711489614</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.083308531131385</v>
+        <v>3.089091539284912</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.736676139302733</v>
+        <v>-3.762793108848642</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.175576217837894</v>
+        <v>1.16512943001953</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.6952051283838445</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.081943166749515</v>
+        <v>3.087726174903042</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181163</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.820497360577431</v>
+        <v>-3.84661433012334</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.144841350859495</v>
+        <v>1.134394563041132</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.6952051283838445</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.084736788280996</v>
+        <v>3.090519796434523</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394723</v>
+        <v>3.805608985394734</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.814344654524646</v>
+        <v>-3.840461624070556</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.147964781672268</v>
+        <v>1.137517993853904</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6917194875140836</v>
+        <v>0.7013578344366288</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.089090760304325</v>
+        <v>3.094873768457851</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890606</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.831153952675148</v>
+        <v>-3.857270922221057</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.140321539152177</v>
+        <v>1.129874751333813</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.674910189363582</v>
+        <v>0.6845485362861272</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.078085658154134</v>
+        <v>3.083868666307661</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798421</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.768855953899026</v>
+        <v>-3.794972923444935</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.231576292459447</v>
+        <v>1.221129504641083</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7202044536380241</v>
+        <v>0.7298428005605693</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.17159777051562</v>
+        <v>3.177380778669147</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.750576425446168</v>
+        <v>-3.593182725779777</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.041180105554717</v>
+        <v>1.104137585421273</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7907694160234544</v>
+        <v>0.9278609927297237</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.016228749661005</v>
+        <v>3.098483695684767</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852418</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.801463138132362</v>
+        <v>-3.644069438465972</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.091115652802414</v>
+        <v>1.154073132668971</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7398827033372599</v>
+        <v>0.8769742800435292</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.055986954371464</v>
+        <v>3.138241900395225</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319537</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.714852395482555</v>
+        <v>-3.557458695816165</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.140387685978381</v>
+        <v>1.203345165844937</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8185084345424182</v>
+        <v>0.9556000112486874</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.117790129210602</v>
+        <v>3.200045075234364</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489377</v>
+        <v>3.831819032489388</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.77506169348784</v>
+        <v>-3.617667993821449</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.114839947600939</v>
+        <v>1.177797427467495</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7582991365371337</v>
+        <v>0.8953907132434029</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.080200531232103</v>
+        <v>3.162455477255865</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397786</v>
+        <v>3.836411672397798</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.725875044803488</v>
+        <v>-3.568481345137098</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.133006225114608</v>
+        <v>1.195963704981164</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7582991365371337</v>
+        <v>0.8953907132434029</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.078692149272032</v>
+        <v>3.160947095295793</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316241</v>
+        <v>3.833513460316253</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.68150191316492</v>
+        <v>-3.524108213498529</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.150618345205472</v>
+        <v>1.213575825072028</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8026722681757023</v>
+        <v>0.9397638448819715</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.105178895690609</v>
+        <v>3.187433841714371</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.82156211710596</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.703982264023804</v>
+        <v>-3.546588564357414</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.136019999000508</v>
+        <v>1.198977478867064</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8026722681757023</v>
+        <v>0.9397638448819715</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.0995726898292</v>
+        <v>3.181827635852961</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190318</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.656326533462749</v>
+        <v>-3.498932833796358</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.161464048252735</v>
+        <v>1.224421528119291</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8503279987367579</v>
+        <v>0.9874195754430272</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.134547885193637</v>
+        <v>3.216802831217399</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056961</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.555808374963994</v>
+        <v>-3.398414675297603</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.206563685026962</v>
+        <v>1.269521164893518</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9508461572355125</v>
+        <v>1.087937733941782</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.199751153667615</v>
+        <v>3.282006099691377</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557288</v>
+        <v>3.828808877557295</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.539903045531641</v>
+        <v>-3.382509345865251</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.199680489275775</v>
+        <v>1.262637969142331</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8717334965262735</v>
+        <v>1.008825073232543</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.139038229717944</v>
+        <v>3.221293175741706</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932762</v>
+        <v>3.816837033932769</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.495064643923243</v>
+        <v>-3.337670944256853</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.221713552529763</v>
+        <v>1.284671032396319</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.876276929471143</v>
+        <v>1.013368506177412</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.145861992095494</v>
+        <v>3.228116938119256</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917044</v>
+        <v>3.817932354917051</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.514563100165252</v>
+        <v>-3.357169400498861</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.218075109664038</v>
+        <v>1.281032589530594</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8281922881912387</v>
+        <v>0.9652838648975079</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.12117214695863</v>
+        <v>3.203427092982391</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405961</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.470360263079351</v>
+        <v>-3.312966563412961</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.241635847026235</v>
+        <v>1.304593326892791</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8723951252771391</v>
+        <v>1.009486701983408</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.153573451738007</v>
+        <v>3.235828397761769</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265646</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.477919928916398</v>
+        <v>-3.320526229250008</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.237021981160664</v>
+        <v>1.29997946102722</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9271985292869585</v>
+        <v>1.064290105993228</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.184865494613146</v>
+        <v>3.267120440636908</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284881</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.319628511377126</v>
+        <v>-3.162234811710735</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.351586313359412</v>
+        <v>1.414543793225969</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9271985292869585</v>
+        <v>1.064290105993228</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.236113259796186</v>
+        <v>3.318368205819947</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321025</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.11198650774265</v>
+        <v>-2.954592808076259</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.433083819407456</v>
+        <v>1.496041299274012</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.134840532921435</v>
+        <v>1.271932109627704</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.359139166571125</v>
+        <v>3.441394112594886</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475142</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.060954415020122</v>
+        <v>-2.903560715353731</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.448444884734737</v>
+        <v>1.511402364601293</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.185872625643963</v>
+        <v>1.322964202350232</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.384706650442912</v>
+        <v>3.466961596466673</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404856</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.995730233892916</v>
+        <v>-2.838336534226525</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.491721961278324</v>
+        <v>1.554679441144881</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.251096806771168</v>
+        <v>1.388188383477438</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.44102856321194</v>
+        <v>3.523283509235701</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688255</v>
+        <v>3.84006118688256</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.958303213821782</v>
+        <v>-2.800909514155391</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.502653741606058</v>
+        <v>1.565611221472615</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.25634834480035</v>
+        <v>1.393439921506619</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.440140458328729</v>
+        <v>3.522395404352491</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992653</v>
+        <v>3.845169808992665</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.97841486985649</v>
+        <v>-2.8210211701901</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.495865871523415</v>
+        <v>1.558823351389971</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.267375689797769</v>
+        <v>1.404467266504039</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.448013657658421</v>
+        <v>3.530268603682183</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636279</v>
+        <v>3.828661445636292</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.950001606756607</v>
+        <v>-2.792607907090216</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.66778894778458</v>
+        <v>1.730746427651136</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.20840012705134</v>
+        <v>1.34549170375761</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.573186091031775</v>
+        <v>3.655441037055536</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957618</v>
+        <v>3.81322282095763</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.875219345731594</v>
+        <v>-2.717825646065203</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.817814761412402</v>
+        <v>1.880772241278958</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.283182388076353</v>
+        <v>1.420273964782622</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.7381683568646</v>
+        <v>3.820423302888361</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998749</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.849135261467786</v>
+        <v>-2.691741561801396</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.819956371131784</v>
+        <v>1.88291385099834</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.283182388076353</v>
+        <v>1.420273964782622</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.729876332878459</v>
+        <v>3.81213127890222</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.80339781889693</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.761257348358666</v>
+        <v>-2.603863648692275</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.853300731959212</v>
+        <v>1.916258211825768</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.399108030499704</v>
+        <v>1.536199607205973</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.797624913916248</v>
+        <v>3.87987985994001</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959853</v>
+        <v>3.796264143959859</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.752364886965382</v>
+        <v>-2.594971187298992</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.874412122243316</v>
+        <v>1.937369602109873</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.399108030499704</v>
+        <v>1.536199607205973</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.81517931964304</v>
+        <v>3.897434265666802</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945362</v>
+        <v>3.794424941945368</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.92084100393526</v>
+        <v>-2.763447304268869</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.798876722859949</v>
+        <v>1.861834202726505</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.371160194783123</v>
+        <v>1.508251771489393</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.790265665617675</v>
+        <v>3.872520611641437</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782711</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.47458481130582</v>
+        <v>-2.317191111639429</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.958648897099587</v>
+        <v>2.021606376966143</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.276441525113491</v>
+        <v>1.41353310181976</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.714704161003758</v>
+        <v>3.796959107027519</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632632</v>
+        <v>3.784671345632639</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.451863707622667</v>
+        <v>-2.294470007956277</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.958401361069753</v>
+        <v>2.021358840936309</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.276441525113491</v>
+        <v>1.41353310181976</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.705368183500662</v>
+        <v>3.787623129524424</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777677</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.58106552091671</v>
+        <v>-2.423671821250319</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.065626761603305</v>
+        <v>2.128584241469861</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.147239711819448</v>
+        <v>1.284331288525718</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.786753221375406</v>
+        <v>3.869008167399167</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644417</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.606939919390736</v>
+        <v>-2.449546219724345</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.092354824707341</v>
+        <v>2.155312304573897</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.19215132053119</v>
+        <v>1.329242897237459</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.850778009096097</v>
+        <v>3.933032955119859</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799959</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.599885229175562</v>
+        <v>-2.442491529509172</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.091852056782955</v>
+        <v>2.154809536649512</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.199206010746363</v>
+        <v>1.336297587452633</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.851686179214747</v>
+        <v>3.933941125238508</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.572934004849074</v>
+        <v>-2.415540305182684</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.112638700158292</v>
+        <v>2.175596180024848</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.214086356774082</v>
+        <v>1.351177933480352</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.87062054047612</v>
+        <v>3.952875486499881</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784103</v>
+        <v>3.768052067784112</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.191495693610232</v>
+        <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.594478232679861</v>
+        <v>-2.437084533013471</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.15334797622454</v>
+        <v>2.351081621037493</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.214086356774082</v>
+        <v>1.351177933480352</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.919947507674681</v>
+        <v>4.136978618644841</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.183612388513225</v>
+        <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.616886350484733</v>
+        <v>-2.459492650818343</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.136501424005584</v>
+        <v>2.334235068818538</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.214086356774082</v>
+        <v>1.351177933480352</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.912064202577675</v>
+        <v>4.129095313547834</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155037</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.185666388062863</v>
+        <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.645110586062334</v>
+        <v>-2.487716886395943</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.127265729324181</v>
+        <v>2.324999374137135</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.232063109225391</v>
+        <v>1.36915468593166</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.924904253598098</v>
+        <v>4.141935364568257</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516197</v>
+        <v>3.729452285161983</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.24192010578471</v>
+        <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.654551511950864</v>
+        <v>-2.497157812284473</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.179743076690617</v>
+        <v>2.37747672150357</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.354490226768783</v>
+        <v>1.491581803475052</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.05461424184598</v>
+        <v>4.271645352816138</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321627</v>
+        <v>3.71494119332164</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.244811200330011</v>
+        <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.743428143119337</v>
+        <v>-2.586034443452947</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.147083518768528</v>
+        <v>2.344817163581482</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.265613595600309</v>
+        <v>1.402705172306578</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.004179357690196</v>
+        <v>4.221210468660355</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347696</v>
+        <v>3.727898186347709</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.242923013223786</v>
+        <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.819758120720243</v>
+        <v>-2.662364421053853</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.114663340621941</v>
+        <v>2.312396985434894</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.265613595600309</v>
+        <v>1.402705172306578</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.002291170583971</v>
+        <v>4.21932228155413</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887741</v>
+        <v>3.710654104887755</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.237743242826648</v>
+        <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.913422065397785</v>
+        <v>-2.756028365731394</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.072017992353786</v>
+        <v>2.26975163716674</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.171949650922767</v>
+        <v>1.309041227629037</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.940913033380308</v>
+        <v>4.157944144350468</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343059</v>
+        <v>3.712897612343073</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.2361772530368</v>
+        <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.07499049092504</v>
+        <v>-2.917596791258649</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.005824632353037</v>
+        <v>2.20355827716599</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.045166727124888</v>
+        <v>1.182258303831157</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.863277289311733</v>
+        <v>4.080308400281893</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389342</v>
+        <v>3.754596135389356</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.249250659902719</v>
+        <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.183291152795159</v>
+        <v>-3.025897453128769</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.975577774470907</v>
+        <v>2.173311419283861</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.045166727124888</v>
+        <v>1.182258303831157</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.876350696177652</v>
+        <v>4.093381807147811</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378385</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.241255856685659</v>
+        <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.201095124515903</v>
+        <v>-3.043701424849513</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.960461382565549</v>
+        <v>2.158195027378503</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9746321042196868</v>
+        <v>1.111723680925956</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.826035119217472</v>
+        <v>4.04306623018763</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006969</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.239779897812661</v>
+        <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.228995911625376</v>
+        <v>-3.071602211958986</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.947825108848763</v>
+        <v>2.145558753661716</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.940035180076752</v>
+        <v>1.077126756783021</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.803801005858713</v>
+        <v>4.020832116828871</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787382</v>
+        <v>3.68489577878739</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.23654434178986</v>
+        <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.35152201432827</v>
+        <v>-3.19412831466188</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.895579111744804</v>
+        <v>2.093312756557757</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8175090773738581</v>
+        <v>0.9546006540801275</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.727049788214175</v>
+        <v>3.944080899184334</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585931</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.303250301380364</v>
+        <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.582036510513859</v>
+        <v>-3.424642810847469</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.870079272861072</v>
+        <v>2.067812917674026</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5869945811882694</v>
+        <v>0.7240861578945388</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.655447050093326</v>
+        <v>3.872478161063484</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64075008781466</v>
+        <v>3.640750087814668</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.443562020382211</v>
+        <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.930781595738303</v>
+        <v>-3.773387896071912</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.870892957773141</v>
+        <v>2.068626602586095</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4782466272693716</v>
+        <v>0.615338203975641</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.730509996743834</v>
+        <v>3.947541107713993</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66828900423709</v>
+        <v>3.668289004237098</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.51254228952785</v>
+        <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.084768013514443</v>
+        <v>-3.927374313848053</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.878278659808325</v>
+        <v>2.076012304621279</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4782466272693716</v>
+        <v>0.615338203975641</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.799490265889474</v>
+        <v>4.016521376859632</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423383</v>
+        <v>3.619923016423392</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.498593491647971</v>
+        <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.289367448377452</v>
+        <v>-4.131973748711061</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.782490087983243</v>
+        <v>1.980223732796196</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4782466272693716</v>
+        <v>0.615338203975641</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.785541468009594</v>
+        <v>4.002572578979754</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609749</v>
+        <v>3.656332733609758</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.510463980703385</v>
+        <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.541842602385176</v>
+        <v>-4.384448902718786</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.693370515435567</v>
+        <v>1.89110416024852</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4782466272693716</v>
+        <v>0.615338203975641</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.797411957065008</v>
+        <v>4.014443068035168</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973152</v>
+        <v>3.674028535973163</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.511674515222329</v>
+        <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.834738358864588</v>
+        <v>-4.677344659198198</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.577422747362746</v>
+        <v>1.775156392175699</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4782466272693716</v>
+        <v>0.615338203975641</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.798622491583952</v>
+        <v>4.015653602554111</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725194</v>
+        <v>3.663509457251951</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.51579625744965</v>
+        <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.021402486999397</v>
+        <v>-4.864008787333006</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.506878838336144</v>
+        <v>1.704612483149097</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4515076564448117</v>
+        <v>0.5885992331510811</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.786700851316538</v>
+        <v>4.003731962286697</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916195</v>
+        <v>3.652149152916207</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.51087411018584</v>
+        <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.167423173913359</v>
+        <v>-5.010029474246968</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.443548416306748</v>
+        <v>1.641282061119702</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4424245646509548</v>
+        <v>0.5795161413572241</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.776328848976413</v>
+        <v>3.993359959946572</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830321</v>
+        <v>3.667962306830335</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.673078166884884</v>
+        <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.259137183022943</v>
+        <v>-5.101743483356554</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.569066869361959</v>
+        <v>1.766800514174912</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4424245646509548</v>
+        <v>0.5795161413572241</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.938532905675457</v>
+        <v>4.155564016645616</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071544</v>
+        <v>3.696539468071557</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.667924804848698</v>
+        <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.290788842082913</v>
+        <v>-5.133395142416523</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.551252843701785</v>
+        <v>1.748986488514738</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4372561074065145</v>
+        <v>0.5743476841127839</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.930278469292607</v>
+        <v>4.147309580262766</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868138</v>
+        <v>3.750044015868153</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.678154222417189</v>
+        <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.372723660351796</v>
+        <v>-5.215329960685406</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.528708333962723</v>
+        <v>1.726441978775676</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4273213618194344</v>
+        <v>0.5644129385257037</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.93454703950885</v>
+        <v>4.151578150479009</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332683</v>
+        <v>3.783632867332697</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.687079860873092</v>
+        <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.474699782600204</v>
+        <v>-5.317306082933814</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.496843523519262</v>
+        <v>1.694577168332215</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3253452395710268</v>
+        <v>0.4624368162772962</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.882287004615708</v>
+        <v>4.099318115585867</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231799</v>
+        <v>3.798296784231814</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.679232748117267</v>
+        <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.364693499122982</v>
+        <v>-5.207299799456592</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.532998924154326</v>
+        <v>1.73073256896728</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.348549811488302</v>
+        <v>0.4856413881945714</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.888362635010249</v>
+        <v>4.105393745980408</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818514</v>
+        <v>3.785563924818523</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.683482758839241</v>
+        <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.221633923382056</v>
+        <v>-5.064240223715666</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.594472765172671</v>
+        <v>1.792206409985624</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3565632380782813</v>
+        <v>0.4936548147845506</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.89742070168621</v>
+        <v>4.11445181265637</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051781</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.690743641721777</v>
+        <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.920187197910218</v>
+        <v>-4.762793498243829</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.722312338243942</v>
+        <v>1.920045983056895</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6580099635501185</v>
+        <v>0.7951015402563879</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.085549619851848</v>
+        <v>4.302580730822008</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679618</v>
+        <v>3.812635940679627</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.691714819474488</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.944777442145402</v>
+        <v>-4.787383742479013</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.713447418302579</v>
+        <v>1.911181063115532</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6580099635501185</v>
+        <v>0.7951015402563879</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.086520797604559</v>
+        <v>4.303551908574718</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474154</v>
+        <v>3.821184182474163</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.692557723854244</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.893739066138882</v>
+        <v>-4.736345366472492</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.734705673084943</v>
+        <v>1.932439317897896</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6580099635501185</v>
+        <v>0.7951015402563879</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.087363701984315</v>
+        <v>4.304394812954474</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969536</v>
+        <v>3.831734516969547</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.711595822728389</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.852599771272251</v>
+        <v>-4.695206071605861</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.77019948990574</v>
+        <v>1.967933134718694</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6991492584167494</v>
+        <v>0.8362408351230187</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.131085377778438</v>
+        <v>4.348116488748598</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270047</v>
+        <v>3.825752932700484</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.527779818852324</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.755964859253611</v>
+        <v>-4.598571159587221</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.625037450837131</v>
+        <v>1.822771095650084</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7957841704353893</v>
+        <v>0.9328757471416587</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.005250321113557</v>
+        <v>4.222281432083716</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077632</v>
+        <v>3.804688961077645</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.531281862926288</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.886545593784454</v>
+        <v>-4.729151894118064</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.576307201098758</v>
+        <v>1.774040845911712</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6652034359045468</v>
+        <v>0.8022950126108161</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.930403924469016</v>
+        <v>4.147435035439175</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.77502886083345</v>
+        <v>3.775028860833463</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.51570868200237</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.722049259593492</v>
+        <v>-4.564655559927102</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.626532553851225</v>
+        <v>1.824266198664179</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8296997700955087</v>
+        <v>0.966791346801778</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.013528544059676</v>
+        <v>4.230559655029834</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077621</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.5148963924388</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.644950658051619</v>
+        <v>-4.487556958385229</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.656559704904404</v>
+        <v>1.854293349717357</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8296997700955087</v>
+        <v>0.966791346801778</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.012716254496105</v>
+        <v>4.229747365466264</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147913</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.524765171563872</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.655335852941509</v>
+        <v>-4.497942153275119</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.662274406073521</v>
+        <v>1.860008050886474</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8193145752056193</v>
+        <v>0.9564061519118887</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.016353916687244</v>
+        <v>4.233385027657404</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735273</v>
+        <v>3.834415493735286</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.595602177340298</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.673924011663734</v>
+        <v>-4.516530311997344</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.725676148361056</v>
+        <v>1.92340979317401</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.800726416483394</v>
+        <v>0.9378179931896633</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.076038027230334</v>
+        <v>4.293069138200493</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496548</v>
+        <v>3.855120535496557</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.592471188158596</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.674222558359769</v>
+        <v>-4.51682885869338</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.72242574050094</v>
+        <v>1.920159385313894</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8004278697873581</v>
+        <v>0.9375194464936274</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.072727910031011</v>
+        <v>4.28975902100117</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108848</v>
+        <v>3.815643212108862</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.597002083097987</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.573399424669342</v>
+        <v>-4.416005725002952</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.767285888916503</v>
+        <v>1.965019533729456</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.812892085271712</v>
+        <v>0.9499836619779812</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.084737334261015</v>
+        <v>4.301768445231174</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121458</v>
+        <v>3.807356168121473</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.597131336576531</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.382618063916935</v>
+        <v>-4.225224364250545</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.843727686696009</v>
+        <v>2.041461331508962</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.003673446024119</v>
+        <v>1.140765022730389</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.199335404191003</v>
+        <v>4.416366515161162</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906071</v>
+        <v>3.775233033906086</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.576968182314127</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.275654706067513</v>
+        <v>-4.118261006401124</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.866349875573374</v>
+        <v>2.064083520386327</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.062138053983921</v>
+        <v>1.19922963069019</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.21425101470448</v>
+        <v>4.431282125674639</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912976</v>
+        <v>3.78576168591299</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.611935118926186</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.220324118165751</v>
+        <v>-4.062930418499361</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.923449047346137</v>
+        <v>2.121182692159091</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.117468641885683</v>
+        <v>1.254560218591952</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.282416304057596</v>
+        <v>4.499447415027754</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539886</v>
+        <v>3.7437679565399</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.605621686827623</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.208269991252788</v>
+        <v>-4.050876291586398</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.92195726601276</v>
+        <v>2.119690910825714</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.129522768798646</v>
+        <v>1.266614345504915</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.283335348106811</v>
+        <v>4.50036645907697</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811</v>
+        <v>3.725010844811015</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.607502317011759</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.249425110821009</v>
+        <v>-4.092031411154619</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.907375848369608</v>
+        <v>2.105109493182561</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.088367649230425</v>
+        <v>1.225459225936694</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.260522906550015</v>
+        <v>4.477554017520173</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382911</v>
+        <v>3.612322444382926</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.620353342889642</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.181376548129479</v>
+        <v>-4.023982848463089</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.947446299324102</v>
+        <v>2.145179944137055</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.156416211921955</v>
+        <v>1.293507788628224</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.314203070042815</v>
+        <v>4.531234181012974</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013418</v>
+        <v>3.645256780013433</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.640556013063236</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.41297694129898</v>
+        <v>-4.25558324163259</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.875008812229896</v>
+        <v>2.07274245704285</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.156416211921955</v>
+        <v>1.293507788628224</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.334405740216409</v>
+        <v>4.551436851186568</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498963</v>
+        <v>3.666747201498971</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.624162249130118</v>
+        <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.463028486828199</v>
+        <v>-4.305634787161809</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.83859443008509</v>
+        <v>2.036328074898044</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.156416211921955</v>
+        <v>1.293507788628224</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.318011976283291</v>
+        <v>4.53504308725345</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800092</v>
+        <v>3.6700487028001</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.584414162723585</v>
+        <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.638135319404643</v>
+        <v>-4.480741619738254</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.728803610647979</v>
+        <v>1.926537255460933</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.156416211921955</v>
+        <v>1.293507788628224</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.278263889876758</v>
+        <v>4.495295000846917</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660845</v>
+        <v>3.745573148660853</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.591436781720525</v>
+        <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.44203516597412</v>
+        <v>-4.284641466307731</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.814266291017129</v>
+        <v>2.011999935830082</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.352516365352478</v>
+        <v>1.489607942058747</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.402946600932012</v>
+        <v>4.619977711902171</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395082</v>
+        <v>3.73057047339509</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.690607781293429</v>
+        <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.289009773860836</v>
+        <v>-4.131616074194446</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.974647447435347</v>
+        <v>2.1723810922483</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.505541757465762</v>
+        <v>1.642633334172031</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.593932835772886</v>
+        <v>4.810963946743045</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791143</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.878074006201722</v>
+        <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.317317087734106</v>
+        <v>-4.159923388067717</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.150790746794331</v>
+        <v>2.348524391607285</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.505541757465762</v>
+        <v>1.642633334172031</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.781399060681179</v>
+        <v>4.998430171651338</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620429</v>
+        <v>3.699115615620437</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.847476957555804</v>
+        <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.483910312847629</v>
+        <v>-4.326516613181239</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.053556408103005</v>
+        <v>2.251290052915958</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.338948532352239</v>
+        <v>1.476040109058508</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.650846076967148</v>
+        <v>4.867877187937307</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285643</v>
+        <v>3.708182519285651</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.851153360217522</v>
+        <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.460874519486063</v>
+        <v>-4.347232760187851</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.066447128109349</v>
+        <v>2.246679996775031</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.338948532352239</v>
+        <v>1.476040109058508</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.654522479628866</v>
+        <v>4.871553590599024</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399464</v>
+        <v>3.740581401399473</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.848771415341017</v>
+        <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.431628539030366</v>
+        <v>-4.317986779732155</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.075763575415123</v>
+        <v>2.255996444080805</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.338948532352239</v>
+        <v>1.476040109058508</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.652140534752361</v>
+        <v>4.86917164572252</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256366</v>
+        <v>3.699404642256376</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.846064654498652</v>
+        <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.538554086908217</v>
+        <v>-4.424912327610006</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.030286595421618</v>
+        <v>2.210519464087299</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.232022984474388</v>
+        <v>1.369114561180657</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.585278445183286</v>
+        <v>4.802309556153444</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700995</v>
+        <v>3.689942600701007</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.847493456641887</v>
+        <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.683572645415466</v>
+        <v>-4.569930886117255</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.973707974161952</v>
+        <v>2.153940842827634</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.087004425967139</v>
+        <v>1.224096002673409</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.49969611222217</v>
+        <v>4.716727223192329</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687006</v>
+        <v>3.711852429687019</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.947424695899639</v>
+        <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.801914411200183</v>
+        <v>-4.688272651901972</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.026302507105818</v>
+        <v>2.2065353757715</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.09769046453003</v>
+        <v>1.234782041236299</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.606038974617658</v>
+        <v>4.823070085587816</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790796</v>
+        <v>3.714879051790809</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.945210393025578</v>
+        <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.853324833520891</v>
+        <v>-4.73968307422268</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.003524035303474</v>
+        <v>2.183756903969155</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.09769046453003</v>
+        <v>1.234782041236299</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.603824671743595</v>
+        <v>4.820855782713755</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437324</v>
+        <v>3.704757949437337</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.945113521099867</v>
+        <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.932744284728643</v>
+        <v>-4.819102525430432</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.971659382894662</v>
+        <v>2.151892251560344</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.09769046453003</v>
+        <v>1.234782041236299</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.603727799817886</v>
+        <v>4.820758910788045</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298391</v>
+        <v>3.736804952298404</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.945107414657911</v>
+        <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.028207282645861</v>
+        <v>-4.914565523347649</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.933468077285819</v>
+        <v>2.113700945951501</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.09769046453003</v>
+        <v>1.234782041236299</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.603721693375929</v>
+        <v>4.820752804346088</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217993</v>
+        <v>3.715372960218007</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.943203811220521</v>
+        <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.963831371795146</v>
+        <v>-4.850189612496934</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.957314838188715</v>
+        <v>2.137547706854397</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.162066375380745</v>
+        <v>1.299157952087014</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.640443636448969</v>
+        <v>4.857474747419127</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353528</v>
+        <v>3.736089413353542</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.948937628968248</v>
+        <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.019200533927339</v>
+        <v>-4.905558774629128</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.940900991083564</v>
+        <v>2.121133859749246</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.162066375380745</v>
+        <v>1.299157952087014</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.646177454196695</v>
+        <v>4.863208565166854</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113271</v>
+        <v>3.736822870113286</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.948475992311181</v>
+        <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.064638313758167</v>
+        <v>-4.950996554459955</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.922264242494166</v>
+        <v>2.102497111159847</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.119221384702585</v>
+        <v>1.256312961408854</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.620008823132732</v>
+        <v>4.83703993410289</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79027250011368</v>
+        <v>3.790272500113694</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.9683503851615</v>
+        <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.976431479610588</v>
+        <v>-4.862789720312377</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.977421369003517</v>
+        <v>2.157654237669198</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.119221384702585</v>
+        <v>1.256312961408854</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.639883215983051</v>
+        <v>4.856914326953209</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016434</v>
+        <v>3.794486844016442</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.952051085686228</v>
+        <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.870396484405279</v>
+        <v>-4.756754725107068</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.003536067610368</v>
+        <v>2.183768936276049</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.119221384702585</v>
+        <v>1.256312961408854</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.623583916507779</v>
+        <v>4.840615027477937</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307665</v>
+        <v>3.794705093307673</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.954482035150273</v>
+        <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.687184821272184</v>
+        <v>-4.573543061973973</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.079251682327652</v>
+        <v>2.259484550993333</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.119221384702585</v>
+        <v>1.256312961408854</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.626014865971825</v>
+        <v>4.843045976941982</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863546</v>
+        <v>3.776846557863554</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.920273220998163</v>
+        <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.615463374258333</v>
+        <v>-4.501821614960122</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.073731446981082</v>
+        <v>2.253964315646763</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.190942831716436</v>
+        <v>1.328034408422705</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.634838920028025</v>
+        <v>4.851870030998183</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394107</v>
+        <v>3.723789705394117</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.867188966919334</v>
+        <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.593090348650627</v>
+        <v>-4.526176630140482</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.029596403145336</v>
+        <v>2.19113805549579</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.202198582829337</v>
+        <v>1.314267922057878</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.588508116616937</v>
+        <v>4.790525885100458</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456723</v>
+        <v>3.715607446456736</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.05238717180469</v>
+        <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.626106644561371</v>
+        <v>-4.559192926051227</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.201588089666394</v>
+        <v>2.363129742016848</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.132761206162586</v>
+        <v>1.244830545391126</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.732043895502242</v>
+        <v>4.934061663985762</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883669</v>
+        <v>3.713762536883682</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.044308397632939</v>
+        <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.614579008911763</v>
+        <v>-4.547665290401619</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.198120369754486</v>
+        <v>2.35966202210494</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.191761864363948</v>
+        <v>1.303831203592489</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.759365516251308</v>
+        <v>4.961383284734829</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236289</v>
+        <v>3.717150699236305</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.047976510154728</v>
+        <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.711920510254132</v>
+        <v>-4.645006791743987</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.162851881739327</v>
+        <v>2.324393534089781</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.14734168219846</v>
+        <v>1.259411021427</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.736381519473804</v>
+        <v>4.938399287957324</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427676</v>
+        <v>3.705201079427691</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.049227592347566</v>
+        <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.797776539594098</v>
+        <v>-4.730862821083954</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.129760552196179</v>
+        <v>2.291302204546633</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.104965612972325</v>
+        <v>1.217034952200865</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.712206960130961</v>
+        <v>4.914224728614482</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610375</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.031646794168068</v>
+        <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.806613337010218</v>
+        <v>-4.739699618500073</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.108645035050233</v>
+        <v>2.270186687400687</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.097523440330974</v>
+        <v>1.209592779559514</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.690160858366652</v>
+        <v>4.892178626850173</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667447</v>
+        <v>3.715544411667461</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.041811305213117</v>
+        <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.897995899575676</v>
+        <v>-4.831082181065532</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.082256521069099</v>
+        <v>2.243798173419553</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.060958555611629</v>
+        <v>1.17302789484017</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.678386438580095</v>
+        <v>4.880404207063616</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889183</v>
+        <v>3.673978374889198</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.143939563037385</v>
+        <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.88628918158867</v>
+        <v>-4.819375463078526</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.189067466088169</v>
+        <v>2.350609118438624</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.072665273598636</v>
+        <v>1.184734612827176</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.787538727196567</v>
+        <v>4.989556495680088</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409559</v>
+        <v>3.682476099409573</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.14697190176879</v>
+        <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.786625677505008</v>
+        <v>-4.719711958994863</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.231965206453039</v>
+        <v>2.393506858803494</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.135852356802322</v>
+        <v>1.247921696030863</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.828483315850184</v>
+        <v>5.030501084333705</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452566</v>
+        <v>3.672895177452576</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.359876735046848</v>
+        <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.796941775671359</v>
+        <v>-4.730028057161215</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.440743600464557</v>
+        <v>2.602285252815011</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.135852356802322</v>
+        <v>1.247921696030863</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.041388149128242</v>
+        <v>5.243405917611763</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762279</v>
+        <v>3.623960959762294</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.359055401958938</v>
+        <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.796847807653987</v>
+        <v>-4.729934089143843</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.439959854583595</v>
+        <v>2.601501506934049</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.13622221814964</v>
+        <v>1.248291557378181</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.040788732848722</v>
+        <v>5.242806501332243</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.63321346798801</v>
+        <v>3.633213467988026</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.353287387903292</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.804066631853831</v>
+        <v>-4.737152913343687</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.431304310848011</v>
+        <v>2.592845963198465</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.13622221814964</v>
+        <v>1.248291557378181</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.035020718793076</v>
+        <v>5.237038487276597</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740916</v>
+        <v>3.647907242740924</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.353287387903292</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.803118208735793</v>
+        <v>-4.736204490225648</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.431683680095227</v>
+        <v>2.593225332445681</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.13622221814964</v>
+        <v>1.248291557378181</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.035020718793076</v>
+        <v>5.237038487276597</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.88106536666362</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.366014995884384</v>
+        <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.960186666991417</v>
+        <v>-4.893272948481272</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.381583904774069</v>
+        <v>2.543125557124523</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.13622221814964</v>
+        <v>1.248291557378181</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.047748326774168</v>
+        <v>5.249766095257689</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424764</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.367960994308771</v>
+        <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.954194420202605</v>
+        <v>-4.88728070169246</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.385926801913981</v>
+        <v>2.547468454264436</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.13622221814964</v>
+        <v>1.248291557378181</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.049694325198556</v>
+        <v>5.251712093682077</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149212</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.36161513032654</v>
+        <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.865636459071838</v>
+        <v>-4.798722740561693</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.415004122384057</v>
+        <v>2.576545774734512</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.13622221814964</v>
+        <v>1.248291557378181</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.043348461216325</v>
+        <v>5.245366229699846</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383085</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.360923807765536</v>
+        <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.847877381568764</v>
+        <v>-4.780963663058619</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.421416430824283</v>
+        <v>2.582958083174737</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.13622221814964</v>
+        <v>1.248291557378181</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.04265713865532</v>
+        <v>5.244674907138841</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720996</v>
+        <v>3.778232147721001</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.373705993674123</v>
+        <v>4.508482158620519</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.711699005129952</v>
+        <v>-4.644785286619807</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.488669967308394</v>
+        <v>2.650211619658848</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.272400594588452</v>
+        <v>1.384469933816992</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.137146350427194</v>
+        <v>5.339164118910715</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.471484921079516</v>
+        <v>3.843965128898662</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.406306053828998</v>
+        <v>4.627659897563494</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.711699005129952</v>
+        <v>-4.644785286619807</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.488669967308394</v>
+        <v>2.650211619658848</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.272400594588452</v>
+        <v>1.384469933816992</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.399369850815366</v>
+        <v>4.620723694549862</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>106.2%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>151.1%</t>
+          <t>158.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.8%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.8%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-626.1%</t>
+          <t>-611.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-111.2%</t>
+          <t>-105.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-324.0%</t>
+          <t>-322.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-85.5%</t>
+          <t>-81.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-22.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>23.2%</t>
         </is>
       </c>
     </row>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.66165290190634</v>
+        <v>-8.685717243089963</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2825004762433405</v>
+        <v>-0.2921262127167896</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.447973044473831</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.313733282148645</v>
+        <v>2.307950273995118</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.589519726618459</v>
+        <v>-8.613584067802082</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2479135018895517</v>
+        <v>-0.2575392383630009</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.447973044473831</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.319466986387281</v>
+        <v>2.313683978233754</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.728577929955328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.518153334008812</v>
+        <v>-8.542217675192434</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2291042072395579</v>
+        <v>-0.238729943713007</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.376606651864184</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.352549559559205</v>
+        <v>2.346766551405678</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.424694300023587</v>
+        <v>-8.44875864120721</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2016040749583756</v>
+        <v>-0.2112298114318247</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.376606651864184</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.342666078246297</v>
+        <v>2.33688307009277</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.414041118470156</v>
+        <v>-8.438105459653778</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1991773628363771</v>
+        <v>-0.2088030993098262</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.376606651864184</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.340831517746924</v>
+        <v>2.335048509593396</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.316134079793665</v>
+        <v>-8.340198420977288</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1603148623392414</v>
+        <v>-0.1699405988126905</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.308620902003627</v>
+        <v>-1.318259248926172</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.381322652689796</v>
+        <v>2.37553964453627</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.292180538817707</v>
+        <v>-8.31624488000133</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1500649398033649</v>
+        <v>-0.159690676276814</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.28466736102767</v>
+        <v>-1.294305707950215</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.396363283420865</v>
+        <v>2.390580275267338</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.02812060049491</v>
+        <v>-8.052184941678533</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05770128063599822</v>
+        <v>-0.06732701710944733</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.020607422704873</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.54153893025279</v>
+        <v>2.535755922099263</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.321040976990072</v>
+        <v>-7.345105318173695</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2223435351056362</v>
+        <v>0.2127177986321871</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.020607422704873</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.53875189659249</v>
+        <v>2.532968888438962</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.280856678623882</v>
+        <v>-7.304921019807504</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2387608783399537</v>
+        <v>0.2291351418665046</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9804231243386826</v>
+        <v>-0.9900614712612278</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.563206099500045</v>
+        <v>2.557423091346518</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.117456807684519</v>
+        <v>-7.141521148868142</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3034876479364557</v>
+        <v>0.2938619114630066</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8170232533993201</v>
+        <v>-0.8266616003218653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.66061284328442</v>
+        <v>2.654829835130893</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88397558545492</v>
+        <v>-6.908039926638543</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4048045656661476</v>
+        <v>0.3951788291926985</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5835420311697216</v>
+        <v>-0.5931803780922668</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.808626005460031</v>
+        <v>2.802842997306504</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.734309194447405</v>
+        <v>-6.758373535631028</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4617789117561943</v>
+        <v>0.4521531752827452</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.4906385399271856</v>
+        <v>-0.5002768868497308</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.861475889892593</v>
+        <v>2.855692881739067</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.602033720816519</v>
+        <v>-6.626098062000142</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4159498872157035</v>
+        <v>0.4063241507422544</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.358363066296299</v>
+        <v>-0.3680014132188442</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.84210196007828</v>
+        <v>2.836318951924753</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.430172505251616</v>
+        <v>-6.454236846435239</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4875094341293016</v>
+        <v>0.4778836976558525</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1865018507313961</v>
+        <v>-0.1961401976539413</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.948033750104859</v>
+        <v>2.942250741951332</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.345207838522297</v>
+        <v>-6.36927217970592</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.534401642044688</v>
+        <v>0.5247759055712389</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1015371840020766</v>
+        <v>-0.1111755309246217</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.011918891366109</v>
+        <v>3.006135883212582</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.450797828295402</v>
+        <v>-6.474862169479024</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3641897165362273</v>
+        <v>0.3545639800627782</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2071271737751809</v>
+        <v>-0.2167655206977261</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.820588967903028</v>
+        <v>2.814805959749501</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.382563243669974</v>
+        <v>-6.406627584853597</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4400278922634846</v>
+        <v>0.4304021557900355</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1887118509026449</v>
+        <v>-0.1983501978251901</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.880182503503636</v>
+        <v>2.874399495350109</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.234623202262375</v>
+        <v>-6.258687543445998</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3825831001881173</v>
+        <v>0.3729573637146681</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1683909349940874</v>
+        <v>-0.1780292819166325</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.775754244410363</v>
+        <v>2.769971236256836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.181653680008386</v>
+        <v>-6.205718021192009</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3950569228362344</v>
+        <v>0.3854311863627853</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1154214127400985</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.798821971509278</v>
+        <v>2.793038963355751</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.015865484048096</v>
+        <v>-6.039929825231718</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4544115891252578</v>
+        <v>0.4447858526518087</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1154214127400985</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.791861359414185</v>
+        <v>2.786078351260658</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.982502277569327</v>
+        <v>-6.00656661875295</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4822192260979086</v>
+        <v>0.4725934896244595</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1154214127400985</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.806323713795328</v>
+        <v>2.800540705641801</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.874243140446805</v>
+        <v>-5.898307481630428</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5200550014061123</v>
+        <v>0.5104292649326632</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1154214127400985</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.800855834254523</v>
+        <v>2.795072826100996</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.750952005629674</v>
+        <v>-5.775016346813297</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5668695493435414</v>
+        <v>0.5572438128700923</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.007869722077032015</v>
+        <v>-0.001768624845513156</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.872328609155379</v>
+        <v>2.866545601001851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.698255138498383</v>
+        <v>-5.722319479682006</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.595649274433383</v>
+        <v>0.5860235379599339</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.0605665892083232</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.911647707671478</v>
+        <v>2.905864699517951</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.454489696514939</v>
+        <v>-5.478554037698562</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6889361595738115</v>
+        <v>0.6793104231003624</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.0605665892083232</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.907428416018529</v>
+        <v>2.901645407865002</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.364714024138467</v>
+        <v>-5.388778365322089</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7269707424444163</v>
+        <v>0.7173450059709672</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.1221660341226332</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.946512396887131</v>
+        <v>2.940729388733604</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.114863630189392</v>
+        <v>-5.138927971373015</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8196529750077484</v>
+        <v>0.8100272385342993</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.1221660341226332</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.939254471870833</v>
+        <v>2.933471463717306</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.93897153772196</v>
+        <v>-4.963035878905583</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8936089355153698</v>
+        <v>0.8839831990419207</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.1221660341226332</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.942853595391482</v>
+        <v>2.937070587237955</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.767525074699496</v>
+        <v>-4.791589415883119</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.975515026778909</v>
+        <v>0.9658892903054599</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2936124971450964</v>
+        <v>0.2839741502225512</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.059048979259514</v>
+        <v>3.053265971105986</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.687502787590375</v>
+        <v>-4.711567128773998</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.006544419238854</v>
+        <v>0.9969186827654051</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3736347842542173</v>
+        <v>0.3639964373316721</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.106082829141283</v>
+        <v>3.100299820987756</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.623867045356441</v>
+        <v>-4.647931386540064</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.036693517186745</v>
+        <v>1.027067780713296</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4372705264881518</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.148959075535961</v>
+        <v>3.143176067382434</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.530169727140046</v>
+        <v>-4.554234068323669</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.055366703257099</v>
+        <v>1.04574096678365</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4372705264881518</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.130153334319757</v>
+        <v>3.124370326166229</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.540672350205335</v>
+        <v>-4.564736691388958</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.052908730655861</v>
+        <v>1.043282994182412</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.426767903422863</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.125594837105461</v>
+        <v>3.119811828951934</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.42818608953646</v>
+        <v>-4.452250430720083</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.101832548758231</v>
+        <v>1.092206812284782</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.426767903422863</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.129524150940281</v>
+        <v>3.123741142786754</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.410472402658595</v>
+        <v>-4.434536743842218</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.109596607426717</v>
+        <v>1.099970870953268</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4299492323197798</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.132111532195771</v>
+        <v>3.126328524042244</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.286998131345577</v>
+        <v>-4.311062472529199</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.155984387171918</v>
+        <v>1.146358650698469</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4299492323197798</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.129109603415765</v>
+        <v>3.123326595262237</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.066977333308566</v>
+        <v>-4.091041674492189</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.245571743397336</v>
+        <v>1.235946006923887</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.57116907738776</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.215420547467167</v>
+        <v>3.20963753931364</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.934109644245288</v>
+        <v>-3.958173985428911</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.314613001824471</v>
+        <v>1.304987265351021</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.57116907738776</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.23131473026899</v>
+        <v>3.225531722115463</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.813936560880789</v>
+        <v>-3.838000902064412</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.363828079610572</v>
+        <v>1.354202343137123</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.691342160752259</v>
+        <v>0.6817038138297138</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.304564424727992</v>
+        <v>3.298781416574464</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.678683199550812</v>
+        <v>-3.702747540734435</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.428017526704003</v>
+        <v>1.418391790230554</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8265955220822361</v>
+        <v>0.8169571751596909</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.395804544087417</v>
+        <v>3.390021535933891</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.738558026908504</v>
+        <v>-3.762622368092127</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.390105087162352</v>
+        <v>1.380479350688903</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.766720694724544</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.345917139074228</v>
+        <v>3.340134130920701</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.618737795997667</v>
+        <v>-3.64280213718129</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.453322348760895</v>
+        <v>1.443696612287446</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.766720694724544</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.361206308308437</v>
+        <v>3.355423300154909</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.621207502459473</v>
+        <v>-3.645271843643096</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.359978665498614</v>
+        <v>1.350352929025165</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7642509882627377</v>
+        <v>0.7546126413401926</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.267368683753794</v>
+        <v>3.261585675600267</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.689577688783483</v>
+        <v>-3.713642029967105</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.251892452454312</v>
+        <v>1.242266715980863</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7735266872989527</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.192195964660825</v>
+        <v>3.186412956507298</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.801449968409633</v>
+        <v>-3.825514309593256</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.197580249235743</v>
+        <v>1.187954512762294</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7735266872989527</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.182632673292716</v>
+        <v>3.176849665139189</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.856970044302223</v>
+        <v>-3.881034385485846</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.312403055570909</v>
+        <v>1.30277731909746</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7735266872989527</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.319663509984919</v>
+        <v>3.313880501831391</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.681495784509754</v>
+        <v>-3.705560125693376</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.387159991479685</v>
+        <v>1.377534255006236</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7735266872989527</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.324230741976706</v>
+        <v>3.318447733823179</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.673571409924839</v>
+        <v>-3.697635751108462</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.366071770074858</v>
+        <v>1.356446033601409</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7735266872989527</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.299972770737913</v>
+        <v>3.294189762584386</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.66729320735499</v>
+        <v>-3.691357548538613</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.297121364504247</v>
+        <v>1.287495628030798</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7798048898688017</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.232278005681272</v>
+        <v>3.226494997527745</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.607440588151267</v>
+        <v>-3.63150492933489</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.331234798617869</v>
+        <v>1.32160906214442</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7798048898688017</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.242450392113405</v>
+        <v>3.236667383959878</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.52119712512489</v>
+        <v>-3.545261466308513</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.36067845440228</v>
+        <v>1.351052717928831</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7798048898688017</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.237396662687265</v>
+        <v>3.231613654533738</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.56650394452387</v>
+        <v>-3.590568285707493</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.334331502087214</v>
+        <v>1.324705765613764</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7389947268595709</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.204686340326252</v>
+        <v>3.198903332172725</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.595537049226171</v>
+        <v>-3.619601390409794</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.323270133239395</v>
+        <v>1.313644396765945</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7389947268595709</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.205238213359354</v>
+        <v>3.199455205205827</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.502726567775312</v>
+        <v>-3.526790908958935</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.289667017711104</v>
+        <v>1.280041281237655</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8318052083104303</v>
+        <v>0.8221668613878851</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.190197194121235</v>
+        <v>3.184414185967708</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.54711603710474</v>
+        <v>-3.571180378288362</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.273784705903934</v>
+        <v>1.264158969430484</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7874157389810026</v>
+        <v>0.7777773920584574</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.165436988448179</v>
+        <v>3.159653980294652</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.526612343219242</v>
+        <v>-3.550676684402865</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.277061891969856</v>
+        <v>1.267436155496406</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.8079194328664999</v>
+        <v>0.7982810859439547</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.172814913291201</v>
+        <v>3.167031905137673</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.566536437801815</v>
+        <v>-3.590600778985437</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.266583549967494</v>
+        <v>1.256957813494045</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.8079194328664999</v>
+        <v>0.7982810859439547</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.178306209121868</v>
+        <v>3.172523200968341</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.594316835703168</v>
+        <v>-3.61838117688679</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.266968592575492</v>
+        <v>1.257342856102043</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7801390349651469</v>
+        <v>0.7705006880426017</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.173135172149595</v>
+        <v>3.167352163996068</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.712697508433306</v>
+        <v>-3.736761849616929</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.05797204348409</v>
+        <v>1.04834630701064</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7129211828141707</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.971160180859663</v>
+        <v>2.965377172706136</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.821311586876637</v>
+        <v>-3.84537592806026</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.134676072825963</v>
+        <v>1.125050336352514</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7129211828141707</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.091309841578868</v>
+        <v>3.085526833425341</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.836083859358026</v>
+        <v>-3.809966889812117</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.14328018993573</v>
+        <v>1.153726977754094</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7129211828141707</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.105822867681191</v>
+        <v>3.100039859527664</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913427</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.797700196799875</v>
+        <v>-3.771583227253966</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.156053096301359</v>
+        <v>1.166499884119723</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7513048453723219</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.126272506558451</v>
+        <v>3.120489498404924</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.620583866764709</v>
+        <v>-3.5944668972188</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.223628657160728</v>
+        <v>1.234075444979091</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7513048453723219</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.123001535403753</v>
+        <v>3.117218527250226</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.665676111598255</v>
+        <v>-3.639559142052345</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.206275150989223</v>
+        <v>1.216721938807586</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6894088022029321</v>
+        <v>0.6797704552803869</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.086547301264032</v>
+        <v>3.080764293110505</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.486300690359487</v>
+        <v>-3.460183720813578</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.271812294791144</v>
+        <v>1.282259082609508</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8461855603736508</v>
+        <v>0.8365472134511056</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.174400331472877</v>
+        <v>3.16861732331935</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.531314903880093</v>
+        <v>-3.505197934334184</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.234614064714491</v>
+        <v>1.245060852532855</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8158366650590462</v>
+        <v>0.806198318136501</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.136998449615704</v>
+        <v>3.131215441462177</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509541</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.798319414152528</v>
+        <v>-3.772202444606619</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.133503822944463</v>
+        <v>1.143950610762827</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6214736270160977</v>
+        <v>0.6118352800935525</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.026072189128881</v>
+        <v>3.020289180975354</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.899517195589701</v>
+        <v>-3.873400226043792</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.092228632266095</v>
+        <v>1.102675420084459</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5530648134707785</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.984230822898191</v>
+        <v>2.978447814744664</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.893006228975389</v>
+        <v>-3.866889259429479</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.092432980466137</v>
+        <v>1.102879768284501</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5530648134707785</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.981830784452508</v>
+        <v>2.976047776298981</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.873968101268091</v>
+        <v>-3.847851131722182</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.096572950757301</v>
+        <v>1.107019738575665</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.494881202139584</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.943445336862036</v>
+        <v>2.937662328708509</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.926483903542911</v>
+        <v>-3.900366933997002</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.194861031481563</v>
+        <v>1.205307819299927</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.494881202139584</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.062739738496226</v>
+        <v>3.056956730342699</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.929892214977491</v>
+        <v>-3.903775245431582</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.194331035893865</v>
+        <v>1.204777823712229</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5273977711489614</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.083083008887986</v>
+        <v>3.077300000734459</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.910536079083644</v>
+        <v>-3.884419109537735</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.20808202064833</v>
+        <v>1.218528808466693</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5273977711489614</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.089091539284912</v>
+        <v>3.083308531131385</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.762793108848642</v>
+        <v>-3.736676139302733</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.16512943001953</v>
+        <v>1.175576217837894</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6952051283838445</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.087726174903042</v>
+        <v>3.081943166749515</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.84661433012334</v>
+        <v>-3.820497360577431</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.134394563041132</v>
+        <v>1.144841350859495</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6952051283838445</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.090519796434523</v>
+        <v>3.084736788280996</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394734</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.840461624070556</v>
+        <v>-3.814344654524646</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.137517993853904</v>
+        <v>1.147964781672268</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.7013578344366288</v>
+        <v>0.6917194875140836</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.094873768457851</v>
+        <v>3.089090760304325</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.857270922221057</v>
+        <v>-3.831153952675148</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.129874751333813</v>
+        <v>1.140321539152177</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6845485362861272</v>
+        <v>0.674910189363582</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.083868666307661</v>
+        <v>3.078085658154134</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.794972923444935</v>
+        <v>-3.768855953899026</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.221129504641083</v>
+        <v>1.231576292459447</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7298428005605693</v>
+        <v>0.7202044536380241</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.177380778669147</v>
+        <v>3.17159777051562</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.593182725779777</v>
+        <v>-3.567065756233868</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.104137585421273</v>
+        <v>1.114584373239637</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9278609927297237</v>
+        <v>0.9182226458071785</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.098483695684767</v>
+        <v>3.09270068753124</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.644069438465972</v>
+        <v>-3.617952468920063</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.154073132668971</v>
+        <v>1.164519920487334</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8769742800435292</v>
+        <v>0.867335933120984</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.138241900395225</v>
+        <v>3.132458892241698</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.557458695816165</v>
+        <v>-3.531341726270255</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.203345165844937</v>
+        <v>1.213791953663301</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9556000112486874</v>
+        <v>0.9459616643261423</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.200045075234364</v>
+        <v>3.194262067080837</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489388</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.617667993821449</v>
+        <v>-3.59155102427554</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.177797427467495</v>
+        <v>1.188244215285859</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8953907132434029</v>
+        <v>0.8857523663208577</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.162455477255865</v>
+        <v>3.156672469102338</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397798</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.568481345137098</v>
+        <v>-3.542364375591188</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.195963704981164</v>
+        <v>1.206410492799528</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8953907132434029</v>
+        <v>0.8857523663208577</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.160947095295793</v>
+        <v>3.155164087142266</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316253</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.524108213498529</v>
+        <v>-3.49799124395262</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.213575825072028</v>
+        <v>1.224022612890391</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9397638448819715</v>
+        <v>0.9301254979594263</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.187433841714371</v>
+        <v>3.181650833560844</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.546588564357414</v>
+        <v>-3.520471594811505</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.198977478867064</v>
+        <v>1.209424266685428</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9397638448819715</v>
+        <v>0.9301254979594263</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.181827635852961</v>
+        <v>3.176044627699434</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190325</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.498932833796358</v>
+        <v>-3.472815864250449</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.224421528119291</v>
+        <v>1.234868315937655</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9874195754430272</v>
+        <v>0.977781228520482</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.216802831217399</v>
+        <v>3.211019823063872</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.398414675297603</v>
+        <v>-3.372297705751694</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.269521164893518</v>
+        <v>1.279967952711882</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.087937733941782</v>
+        <v>1.078299387019237</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.282006099691377</v>
+        <v>3.27622309153785</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557295</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.382509345865251</v>
+        <v>-3.356392376319342</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.262637969142331</v>
+        <v>1.273084756960695</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.008825073232543</v>
+        <v>0.9991867263099976</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.221293175741706</v>
+        <v>3.215510167588179</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932769</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.337670944256853</v>
+        <v>-3.311553974710943</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.284671032396319</v>
+        <v>1.295117820214683</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.013368506177412</v>
+        <v>1.003730159254867</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.228116938119256</v>
+        <v>3.222333929965729</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917051</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.357169400498861</v>
+        <v>-3.331052430952952</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.281032589530594</v>
+        <v>1.291479377348958</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9652838648975079</v>
+        <v>0.9556455179749628</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.203427092982391</v>
+        <v>3.197644084828864</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405961</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.312966563412961</v>
+        <v>-3.286849593867051</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.304593326892791</v>
+        <v>1.315040114711155</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.009486701983408</v>
+        <v>0.9998483550608632</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.235828397761769</v>
+        <v>3.230045389608242</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265646</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.320526229250008</v>
+        <v>-3.294409259704098</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.29997946102722</v>
+        <v>1.310426248845584</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.064290105993228</v>
+        <v>1.054651759070683</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.267120440636908</v>
+        <v>3.261337432483381</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284881</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.162234811710735</v>
+        <v>-3.136117842164826</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.414543793225969</v>
+        <v>1.424990581044332</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.064290105993228</v>
+        <v>1.054651759070683</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.318368205819947</v>
+        <v>3.31258519766642</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321025</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.954592808076259</v>
+        <v>-2.92847583853035</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.496041299274012</v>
+        <v>1.506488087092376</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.271932109627704</v>
+        <v>1.262293762705159</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.441394112594886</v>
+        <v>3.435611104441359</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475142</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.903560715353731</v>
+        <v>-2.877443745807822</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.511402364601293</v>
+        <v>1.521849152419657</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.322964202350232</v>
+        <v>1.313325855427687</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.466961596466673</v>
+        <v>3.461178588313146</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404856</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.838336534226525</v>
+        <v>-2.812219564680616</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.554679441144881</v>
+        <v>1.565126228963244</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.388188383477438</v>
+        <v>1.378550036554892</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.523283509235701</v>
+        <v>3.517500501082174</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.84006118688256</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.800909514155391</v>
+        <v>-2.774792544609482</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.565611221472615</v>
+        <v>1.576058009290978</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.393439921506619</v>
+        <v>1.383801574584074</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.522395404352491</v>
+        <v>3.516612396198964</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992665</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.8210211701901</v>
+        <v>-2.79490420064419</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.558823351389971</v>
+        <v>1.569270139208335</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.404467266504039</v>
+        <v>1.394828919581493</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.530268603682183</v>
+        <v>3.524485595528656</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636292</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.792607907090216</v>
+        <v>-2.766490937544307</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.730746427651136</v>
+        <v>1.741193215469499</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.34549170375761</v>
+        <v>1.335853356835065</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.655441037055536</v>
+        <v>3.649658028902009</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095763</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.717825646065203</v>
+        <v>-2.691708676519294</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.880772241278958</v>
+        <v>1.891219029097322</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.420273964782622</v>
+        <v>1.410635617860077</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.820423302888361</v>
+        <v>3.814640294734834</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.691741561801396</v>
+        <v>-2.665624592255486</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.88291385099834</v>
+        <v>1.893360638816704</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.420273964782622</v>
+        <v>1.410635617860077</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.81213127890222</v>
+        <v>3.806348270748693</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889693</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.603863648692275</v>
+        <v>-2.577746679146366</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.916258211825768</v>
+        <v>1.926704999644132</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.536199607205973</v>
+        <v>1.526561260283428</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.87987985994001</v>
+        <v>3.874096851786483</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959859</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.594971187298992</v>
+        <v>-2.568854217753082</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.937369602109873</v>
+        <v>1.947816389928236</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.536199607205973</v>
+        <v>1.526561260283428</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.897434265666802</v>
+        <v>3.891651257513274</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945368</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.763447304268869</v>
+        <v>-2.73733033472296</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.861834202726505</v>
+        <v>1.872280990544869</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.508251771489393</v>
+        <v>1.498613424566847</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.872520611641437</v>
+        <v>3.86673760348791</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782711</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.317191111639429</v>
+        <v>-2.29107414209352</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.021606376966143</v>
+        <v>2.032053164784507</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.41353310181976</v>
+        <v>1.403894754897215</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.796959107027519</v>
+        <v>3.791176098873992</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632639</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.294470007956277</v>
+        <v>-2.268353038410368</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.021358840936309</v>
+        <v>2.031805628754673</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.41353310181976</v>
+        <v>1.403894754897215</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.787623129524424</v>
+        <v>3.781840121370896</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777677</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.423671821250319</v>
+        <v>-2.39755485170441</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.128584241469861</v>
+        <v>2.139031029288224</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.284331288525718</v>
+        <v>1.274692941603172</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.869008167399167</v>
+        <v>3.86322515924564</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644417</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.449546219724345</v>
+        <v>-2.423429250178436</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.155312304573897</v>
+        <v>2.165759092392261</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.329242897237459</v>
+        <v>1.319604550314914</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933032955119859</v>
+        <v>3.927249946966332</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.442491529509172</v>
+        <v>-2.416374559963262</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.154809536649512</v>
+        <v>2.165256324467876</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.336297587452633</v>
+        <v>1.326659240530087</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933941125238508</v>
+        <v>3.928158117084981</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.415540305182684</v>
+        <v>-2.389423335636774</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.175596180024848</v>
+        <v>2.186042967843212</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.351177933480352</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952875486499881</v>
+        <v>3.947092478346354</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784112</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.437084533013471</v>
+        <v>-2.4493305673114</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.351081621037493</v>
+        <v>2.346183207318322</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.351177933480352</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136978618644841</v>
+        <v>4.131195610491313</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.459492650818343</v>
+        <v>-2.471738685116272</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.334235068818538</v>
+        <v>2.329336655099366</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.351177933480352</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.129095313547834</v>
+        <v>4.123312305394307</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155037</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.487716886395943</v>
+        <v>-2.499962920693873</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.324999374137135</v>
+        <v>2.320100960417963</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.36915468593166</v>
+        <v>1.359516339009115</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141935364568257</v>
+        <v>4.13615235641473</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161983</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.497157812284473</v>
+        <v>-2.509403846582403</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.37747672150357</v>
+        <v>2.372578307784398</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.491581803475052</v>
+        <v>1.481943456552507</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271645352816138</v>
+        <v>4.265862344662612</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332164</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.586034443452947</v>
+        <v>-2.598280477750877</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.344817163581482</v>
+        <v>2.33991874986231</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.402705172306578</v>
+        <v>1.393066825384033</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.221210468660355</v>
+        <v>4.215427460506828</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347709</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.662364421053853</v>
+        <v>-2.674610455351782</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.312396985434894</v>
+        <v>2.307498571715723</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.402705172306578</v>
+        <v>1.393066825384033</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.21932228155413</v>
+        <v>4.213539273400603</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887755</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.756028365731394</v>
+        <v>-2.768274400029324</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.26975163716674</v>
+        <v>2.264853223447568</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.309041227629037</v>
+        <v>1.299402880706491</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.157944144350468</v>
+        <v>4.15216113619694</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343073</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.917596791258649</v>
+        <v>-2.929842825556579</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.20355827716599</v>
+        <v>2.198659863446818</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.182258303831157</v>
+        <v>1.172619956908612</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.080308400281893</v>
+        <v>4.074525392128366</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389356</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.025897453128769</v>
+        <v>-3.038143487426698</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.173311419283861</v>
+        <v>2.168413005564689</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.182258303831157</v>
+        <v>1.172619956908612</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.093381807147811</v>
+        <v>4.087598798994284</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.043701424849513</v>
+        <v>-3.055947459147442</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.158195027378503</v>
+        <v>2.153296613659331</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.111723680925956</v>
+        <v>1.102085334003411</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.04306623018763</v>
+        <v>4.037283222034104</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.071602211958986</v>
+        <v>-3.083848246256915</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.145558753661716</v>
+        <v>2.140660339942544</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.077126756783021</v>
+        <v>1.067488409860476</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.020832116828871</v>
+        <v>4.015049108675345</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.68489577878739</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.19412831466188</v>
+        <v>-3.206374348959809</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.093312756557757</v>
+        <v>2.088414342838585</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9546006540801275</v>
+        <v>0.9449623071575823</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.944080899184334</v>
+        <v>3.938297891030807</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.424642810847469</v>
+        <v>-3.436888845145398</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.067812917674026</v>
+        <v>2.062914503954854</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7240861578945388</v>
+        <v>0.7144478109719936</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.872478161063484</v>
+        <v>3.866695152909958</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814668</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.773387896071912</v>
+        <v>-3.785633930369841</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.068626602586095</v>
+        <v>2.063728188866923</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.615338203975641</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.947541107713993</v>
+        <v>3.941758099560466</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237098</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.927374313848053</v>
+        <v>-3.939620348145982</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.076012304621279</v>
+        <v>2.071113890902107</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.615338203975641</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.016521376859632</v>
+        <v>4.010738368706106</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423392</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.131973748711061</v>
+        <v>-4.144219783008991</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.980223732796196</v>
+        <v>1.975325319077025</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.615338203975641</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.002572578979754</v>
+        <v>3.996789570826227</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609758</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.384448902718786</v>
+        <v>-4.396694937016715</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.89110416024852</v>
+        <v>1.886205746529349</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.615338203975641</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.014443068035168</v>
+        <v>4.008660059881641</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973163</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.677344659198198</v>
+        <v>-4.689590693496127</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.775156392175699</v>
+        <v>1.770257978456528</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.615338203975641</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.015653602554111</v>
+        <v>4.009870594400584</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251951</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.864008787333006</v>
+        <v>-4.876254821630935</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.704612483149097</v>
+        <v>1.699714069429926</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5885992331510811</v>
+        <v>0.5789608862285359</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.003731962286697</v>
+        <v>3.99794895413317</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916207</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.010029474246968</v>
+        <v>-5.022275508544897</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.641282061119702</v>
+        <v>1.63638364740053</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5795161413572241</v>
+        <v>0.5698777944346789</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.993359959946572</v>
+        <v>3.987576951793045</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830335</v>
+        <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.101743483356554</v>
+        <v>-5.113989517654483</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.766800514174912</v>
+        <v>1.76190210045574</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5795161413572241</v>
+        <v>0.5698777944346789</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.155564016645616</v>
+        <v>4.149781008492089</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071557</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.133395142416523</v>
+        <v>-5.145641176714452</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.748986488514738</v>
+        <v>1.744088074795567</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5743476841127839</v>
+        <v>0.5647093371902387</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.147309580262766</v>
+        <v>4.141526572109239</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868153</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.215329960685406</v>
+        <v>-5.227575994983336</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.726441978775676</v>
+        <v>1.721543565056504</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5644129385257037</v>
+        <v>0.5547745916031586</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.151578150479009</v>
+        <v>4.145795142325482</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332697</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.317306082933814</v>
+        <v>-5.329552117231743</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.694577168332215</v>
+        <v>1.689678754613044</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4624368162772962</v>
+        <v>0.452798469354751</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.099318115585867</v>
+        <v>4.09353510743234</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231814</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.207299799456592</v>
+        <v>-5.219545833754522</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.73073256896728</v>
+        <v>1.725834155248108</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4856413881945714</v>
+        <v>0.4760030412720262</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.105393745980408</v>
+        <v>4.099610737826881</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818523</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.064240223715666</v>
+        <v>-5.076486258013595</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.792206409985624</v>
+        <v>1.787307996266453</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4936548147845506</v>
+        <v>0.4840164678620055</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.11445181265637</v>
+        <v>4.108668804502843</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.762793498243829</v>
+        <v>-4.775039532541758</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.920045983056895</v>
+        <v>1.915147569337724</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7951015402563879</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.302580730822008</v>
+        <v>4.29679772266848</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679627</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.787383742479013</v>
+        <v>-4.799629776776942</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.911181063115532</v>
+        <v>1.906282649396361</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7951015402563879</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.303551908574718</v>
+        <v>4.297768900421191</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.736345366472492</v>
+        <v>-4.748591400770422</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.932439317897896</v>
+        <v>1.927540904178724</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7951015402563879</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.304394812954474</v>
+        <v>4.298611804800947</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969547</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.695206071605861</v>
+        <v>-4.707452105903791</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.967933134718694</v>
+        <v>1.963034720999522</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8362408351230187</v>
+        <v>0.8266024882004736</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.348116488748598</v>
+        <v>4.34233348059507</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700484</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.598571159587221</v>
+        <v>-4.610817193885151</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.822771095650084</v>
+        <v>1.817872681930913</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9328757471416587</v>
+        <v>0.9232374002191135</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.222281432083716</v>
+        <v>4.216498423930189</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077645</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.729151894118064</v>
+        <v>-4.741397928415993</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.774040845911712</v>
+        <v>1.76914243219254</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8022950126108161</v>
+        <v>0.792656665688271</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.147435035439175</v>
+        <v>4.141652027285648</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833463</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.564655559927102</v>
+        <v>-4.576901594225031</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.824266198664179</v>
+        <v>1.819367784945007</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.966791346801778</v>
+        <v>0.9571529998792329</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.230559655029834</v>
+        <v>4.224776646876307</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.487556958385229</v>
+        <v>-4.499802992683159</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.854293349717357</v>
+        <v>1.849394935998186</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.966791346801778</v>
+        <v>0.9571529998792329</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.229747365466264</v>
+        <v>4.223964357312737</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147913</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.497942153275119</v>
+        <v>-4.510188187573048</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.860008050886474</v>
+        <v>1.855109637167303</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9564061519118887</v>
+        <v>0.9467678049893435</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.233385027657404</v>
+        <v>4.227602019503876</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735286</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.516530311997344</v>
+        <v>-4.528776346295273</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.92340979317401</v>
+        <v>1.918511379454838</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9378179931896633</v>
+        <v>0.9281796462671181</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.293069138200493</v>
+        <v>4.287286130046966</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496557</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.51682885869338</v>
+        <v>-4.529074892991309</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.920159385313894</v>
+        <v>1.915260971594722</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9375194464936274</v>
+        <v>0.9278810995710822</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.28975902100117</v>
+        <v>4.283976012847643</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108862</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.416005725002952</v>
+        <v>-4.428251759300881</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.965019533729456</v>
+        <v>1.960121120010284</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9499836619779812</v>
+        <v>0.9403453150554361</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.301768445231174</v>
+        <v>4.295985437077647</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121473</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.225224364250545</v>
+        <v>-4.237470398548474</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.041461331508962</v>
+        <v>2.03656291778979</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.140765022730389</v>
+        <v>1.131126675807844</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.416366515161162</v>
+        <v>4.410583507007635</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906086</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.118261006401124</v>
+        <v>-4.130507040699053</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.064083520386327</v>
+        <v>2.059185106667155</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.19922963069019</v>
+        <v>1.189591283767645</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.431282125674639</v>
+        <v>4.425499117521112</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.78576168591299</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.062930418499361</v>
+        <v>-4.07517645279729</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.121182692159091</v>
+        <v>2.116284278439919</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.254560218591952</v>
+        <v>1.244921871669407</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.499447415027754</v>
+        <v>4.493664406874228</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.7437679565399</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.050876291586398</v>
+        <v>-4.063122325884327</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.119690910825714</v>
+        <v>2.114792497106542</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.266614345504915</v>
+        <v>1.25697599858237</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.50036645907697</v>
+        <v>4.494583450923443</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811015</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.092031411154619</v>
+        <v>-4.104277445452548</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.105109493182561</v>
+        <v>2.100211079463389</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.225459225936694</v>
+        <v>1.215820879014149</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.477554017520173</v>
+        <v>4.471771009366647</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382926</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.023982848463089</v>
+        <v>-4.036228882761018</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.145179944137055</v>
+        <v>2.140281530417884</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.293507788628224</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.531234181012974</v>
+        <v>4.525451172859447</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013433</v>
+        <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.25558324163259</v>
+        <v>-4.267829275930519</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.07274245704285</v>
+        <v>2.067844043323678</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.293507788628224</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.551436851186568</v>
+        <v>4.545653843033041</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498971</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.305634787161809</v>
+        <v>-4.317880821459738</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.036328074898044</v>
+        <v>2.031429661178872</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.293507788628224</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.53504308725345</v>
+        <v>4.529260079099923</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.6700487028001</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.480741619738254</v>
+        <v>-4.492987654036183</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.926537255460933</v>
+        <v>1.921638841741761</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.293507788628224</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.495295000846917</v>
+        <v>4.48951199269339</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660853</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.284641466307731</v>
+        <v>-4.29688750060566</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.011999935830082</v>
+        <v>2.00710152211091</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.489607942058747</v>
+        <v>1.479969595136202</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.619977711902171</v>
+        <v>4.614194703748644</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73057047339509</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.131616074194446</v>
+        <v>-4.143862108492375</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.1723810922483</v>
+        <v>2.167482678529129</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.642633334172031</v>
+        <v>1.632994987249486</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.810963946743045</v>
+        <v>4.805180938589518</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.159923388067717</v>
+        <v>-4.172169422365646</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.348524391607285</v>
+        <v>2.343625977888113</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.642633334172031</v>
+        <v>1.632994987249486</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.998430171651338</v>
+        <v>4.992647163497811</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620437</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.326516613181239</v>
+        <v>-4.338762647479168</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.251290052915958</v>
+        <v>2.246391639196786</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.476040109058508</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.867877187937307</v>
+        <v>4.86209417978378</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285651</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.347232760187851</v>
+        <v>-4.315726854117602</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.246679996775031</v>
+        <v>2.25928235920313</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.476040109058508</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.871553590599024</v>
+        <v>4.865770582445498</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399473</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.317986779732155</v>
+        <v>-4.286480873661906</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.255996444080805</v>
+        <v>2.268598806508904</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.476040109058508</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.86917164572252</v>
+        <v>4.863388637568993</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256376</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.424912327610006</v>
+        <v>-4.393406421539757</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.210519464087299</v>
+        <v>2.223121826515399</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.369114561180657</v>
+        <v>1.359476214258112</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.802309556153444</v>
+        <v>4.796526547999917</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701007</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.569930886117255</v>
+        <v>-4.538424980047005</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.153940842827634</v>
+        <v>2.166543205255733</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.224096002673409</v>
+        <v>1.214457655750864</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.716727223192329</v>
+        <v>4.710944215038802</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687019</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.688272651901972</v>
+        <v>-4.656766745831723</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.2065353757715</v>
+        <v>2.219137738199599</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.234782041236299</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.823070085587816</v>
+        <v>4.817287077434289</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790809</v>
+        <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.73968307422268</v>
+        <v>-4.708177168152431</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.183756903969155</v>
+        <v>2.196359266397255</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.234782041236299</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.820855782713755</v>
+        <v>4.815072774560227</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437337</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.819102525430432</v>
+        <v>-4.787596619360182</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.151892251560344</v>
+        <v>2.164494613988444</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.234782041236299</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.820758910788045</v>
+        <v>4.814975902634517</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298404</v>
+        <v>3.7368049522984</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.914565523347649</v>
+        <v>-4.8830596172774</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.113700945951501</v>
+        <v>2.1263033083796</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.234782041236299</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.820752804346088</v>
+        <v>4.81496979619256</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218007</v>
+        <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.850189612496934</v>
+        <v>-4.818683706426685</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.137547706854397</v>
+        <v>2.150150069282497</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.299157952087014</v>
+        <v>1.289519605164469</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.857474747419127</v>
+        <v>4.8516917392656</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353542</v>
+        <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.905558774629128</v>
+        <v>-4.874052868558879</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.121133859749246</v>
+        <v>2.133736222177346</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.299157952087014</v>
+        <v>1.289519605164469</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.863208565166854</v>
+        <v>4.857425557013327</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113286</v>
+        <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.950996554459955</v>
+        <v>-4.919490648389706</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.102497111159847</v>
+        <v>2.115099473587947</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.256312961408854</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.83703993410289</v>
+        <v>4.831256925949363</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113694</v>
+        <v>3.790272500113691</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.862789720312377</v>
+        <v>-4.831283814242128</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.157654237669198</v>
+        <v>2.170256600097297</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.256312961408854</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.856914326953209</v>
+        <v>4.851131318799682</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016442</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.756754725107068</v>
+        <v>-4.725248819036818</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.183768936276049</v>
+        <v>2.196371298704149</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.256312961408854</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.840615027477937</v>
+        <v>4.83483201932441</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307673</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.573543061973973</v>
+        <v>-4.542037155903723</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.259484550993333</v>
+        <v>2.272086913421433</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.256312961408854</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.843045976941982</v>
+        <v>4.837262968788456</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863554</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.501821614960122</v>
+        <v>-4.470315708889872</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.253964315646763</v>
+        <v>2.266566678074862</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.328034408422705</v>
+        <v>1.31839606150016</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.851870030998183</v>
+        <v>4.846087022844656</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394117</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.526176630140482</v>
+        <v>-4.447942683282166</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.19113805549579</v>
+        <v>2.222431634239117</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.314267922057878</v>
+        <v>1.329651812613061</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.790525885100458</v>
+        <v>4.799756219433569</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456736</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.559192926051227</v>
+        <v>-4.480958979192911</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.363129742016848</v>
+        <v>2.394423320760174</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.244830545391126</v>
+        <v>1.26021443594631</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.934061663985762</v>
+        <v>4.943291998318872</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883682</v>
+        <v>3.713762536883679</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.547665290401619</v>
+        <v>-4.469431343543302</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.35966202210494</v>
+        <v>2.390955600848267</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.303831203592489</v>
+        <v>1.319215094147672</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.961383284734829</v>
+        <v>4.970613619067939</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236305</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.645006791743987</v>
+        <v>-4.566772844885671</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.324393534089781</v>
+        <v>2.355687112833108</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.259411021427</v>
+        <v>1.274794911982184</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.938399287957324</v>
+        <v>4.947629622290435</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427691</v>
+        <v>3.705201079427687</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.730862821083954</v>
+        <v>-4.652628874225638</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.291302204546633</v>
+        <v>2.322595783289959</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.217034952200865</v>
+        <v>1.232418842756049</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.914224728614482</v>
+        <v>4.923455062947592</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.739699618500073</v>
+        <v>-4.661465671641757</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.270186687400687</v>
+        <v>2.301480266144013</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.209592779559514</v>
+        <v>1.224976670114698</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.892178626850173</v>
+        <v>4.901408961183283</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667461</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.831082181065532</v>
+        <v>-4.685713444045787</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.243798173419553</v>
+        <v>2.301945668227451</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.17302789484017</v>
+        <v>1.213457248270222</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.880404207063616</v>
+        <v>4.904661819121647</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889198</v>
+        <v>3.673978374889194</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.819375463078526</v>
+        <v>-4.674006726058781</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.350609118438624</v>
+        <v>2.408756613246521</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.184734612827176</v>
+        <v>1.225163966257228</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.989556495680088</v>
+        <v>5.013814107738119</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409573</v>
+        <v>3.68247609940957</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.719711958994863</v>
+        <v>-4.574343221975118</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.393506858803494</v>
+        <v>2.451654353611391</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.247921696030863</v>
+        <v>1.288351049460915</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.030501084333705</v>
+        <v>5.054758696391736</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452576</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.730028057161215</v>
+        <v>-4.58465932014147</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.602285252815011</v>
+        <v>2.660432747622909</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.247921696030863</v>
+        <v>1.288351049460915</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.243405917611763</v>
+        <v>5.267663529669794</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762294</v>
+        <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.729934089143843</v>
+        <v>-4.584565352124097</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.601501506934049</v>
+        <v>2.659649001741947</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.248291557378181</v>
+        <v>1.288720910808233</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.242806501332243</v>
+        <v>5.267064113390274</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988026</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.737152913343687</v>
+        <v>-4.591784176323942</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.592845963198465</v>
+        <v>2.650993458006363</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.248291557378181</v>
+        <v>1.288720910808233</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.237038487276597</v>
+        <v>5.261296099334628</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740924</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.736204490225648</v>
+        <v>-4.590835753205903</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.593225332445681</v>
+        <v>2.651372827253579</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.248291557378181</v>
+        <v>1.288720910808233</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.237038487276597</v>
+        <v>5.261296099334628</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.893272948481272</v>
+        <v>-4.747904211461528</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.543125557124523</v>
+        <v>2.601273051932421</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.248291557378181</v>
+        <v>1.288720910808233</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.249766095257689</v>
+        <v>5.27402370731572</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.88728070169246</v>
+        <v>-4.741911964672716</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.547468454264436</v>
+        <v>2.605615949072334</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.248291557378181</v>
+        <v>1.288720910808233</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.251712093682077</v>
+        <v>5.275969705740108</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149219</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.798722740561693</v>
+        <v>-4.653354003541948</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.576545774734512</v>
+        <v>2.634693269542409</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.248291557378181</v>
+        <v>1.288720910808233</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.245366229699846</v>
+        <v>5.269623841757877</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.780963663058619</v>
+        <v>-4.635594926038874</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.582958083174737</v>
+        <v>2.641105577982635</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.248291557378181</v>
+        <v>1.288720910808233</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.244674907138841</v>
+        <v>5.268932519196873</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147721001</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.508482158620519</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.644785286619807</v>
+        <v>-4.499416549600062</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.650211619658848</v>
+        <v>2.708359114466746</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.384469933816992</v>
+        <v>1.424899287247044</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.339164118910715</v>
+        <v>5.363421730968746</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.843965128898662</v>
+        <v>3.82438859753036</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.627659897563494</v>
+        <v>4.699003337426498</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.644785286619807</v>
+        <v>-4.499416549600062</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.650211619658848</v>
+        <v>2.708359114466746</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.384469933816992</v>
+        <v>1.424899287247044</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.620723694549862</v>
+        <v>4.692067134412865</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>21.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>102.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>158.3%</t>
+          <t>139.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>420.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.4%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-611.5%</t>
+          <t>-609.8%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-31.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-105.4%</t>
+          <t>-104.2%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.7%</t>
+          <t>-324.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-81.5%</t>
+          <t>-93.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>115.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>83.4%</t>
         </is>
       </c>
     </row>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646217</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611569</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955328</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.647931386540064</v>
+        <v>-4.669517892066827</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.027067780713296</v>
+        <v>1.018433178502591</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4060456740388441</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.143176067382434</v>
+        <v>3.130224164066377</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.554234068323669</v>
+        <v>-4.575820573850431</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.04574096678365</v>
+        <v>1.037106364572945</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.4060456740388441</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124370326166229</v>
+        <v>3.111418422850172</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.564736691388958</v>
+        <v>-4.58632319691572</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.043282994182412</v>
+        <v>1.034648391971707</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.3955430509735552</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119811828951934</v>
+        <v>3.106859925635876</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.452250430720083</v>
+        <v>-4.473836936246846</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.092206812284782</v>
+        <v>1.083572210074077</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.3955430509735552</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123741142786754</v>
+        <v>3.110789239470696</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.434536743842218</v>
+        <v>-4.45612324936898</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.099970870953268</v>
+        <v>1.091336268742563</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.398724379870472</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126328524042244</v>
+        <v>3.113376620726187</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.311062472529199</v>
+        <v>-4.332648978055962</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.146358650698469</v>
+        <v>1.137724048487764</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.398724379870472</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123326595262237</v>
+        <v>3.11037469194618</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.091041674492189</v>
+        <v>-4.112628180018952</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.235946006923887</v>
+        <v>1.227311404713182</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5399442249384523</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.20963753931364</v>
+        <v>3.196685635997582</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.958173985428911</v>
+        <v>-3.979760490955674</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.304987265351021</v>
+        <v>1.296352663140316</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5399442249384523</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225531722115463</v>
+        <v>3.212579818799405</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.838000902064412</v>
+        <v>-3.859587407591174</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.354202343137123</v>
+        <v>1.345567740926418</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6817038138297138</v>
+        <v>0.6601173083029512</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298781416574464</v>
+        <v>3.285829513258407</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.702747540734435</v>
+        <v>-3.724334046261197</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.418391790230554</v>
+        <v>1.409757188019849</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8169571751596909</v>
+        <v>0.7953706696329284</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.390021535933891</v>
+        <v>3.377069632617833</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.762622368092127</v>
+        <v>-3.78420887361889</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.380479350688903</v>
+        <v>1.371844748478197</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7354958422752362</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.340134130920701</v>
+        <v>3.327182227604643</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.64280213718129</v>
+        <v>-3.664388642708052</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.443696612287446</v>
+        <v>1.435062010076741</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7354958422752362</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355423300154909</v>
+        <v>3.342471396838852</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.645271843643096</v>
+        <v>-3.666858349169858</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.350352929025165</v>
+        <v>1.34171832681446</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7546126413401926</v>
+        <v>0.73302613581343</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261585675600267</v>
+        <v>3.24863377228421</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.713642029967105</v>
+        <v>-3.735228535493868</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.242266715980863</v>
+        <v>1.233632113770158</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.742301834849645</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186412956507298</v>
+        <v>3.17346105319124</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.825514309593256</v>
+        <v>-3.847100815120019</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.187954512762294</v>
+        <v>1.179319910551589</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.742301834849645</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176849665139189</v>
+        <v>3.163897761823131</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.881034385485846</v>
+        <v>-3.902620891012608</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.30277731909746</v>
+        <v>1.294142716886755</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.742301834849645</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313880501831391</v>
+        <v>3.300928598515334</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.705560125693376</v>
+        <v>-3.727146631220139</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.377534255006236</v>
+        <v>1.368899652795531</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.742301834849645</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.318447733823179</v>
+        <v>3.305495830507121</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.697635751108462</v>
+        <v>-3.719222256635225</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.356446033601409</v>
+        <v>1.347811431390703</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.742301834849645</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.294189762584386</v>
+        <v>3.281237859268328</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.691357548538613</v>
+        <v>-3.712944054065376</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.287495628030798</v>
+        <v>1.278861025820093</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.748580037419494</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.226494997527745</v>
+        <v>3.213543094211688</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.63150492933489</v>
+        <v>-3.653091434861653</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.32160906214442</v>
+        <v>1.312974459933715</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.748580037419494</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.236667383959878</v>
+        <v>3.22371548064382</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.545261466308513</v>
+        <v>-3.566847971835275</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.351052717928831</v>
+        <v>1.342418115718126</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.748580037419494</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.231613654533738</v>
+        <v>3.218661751217681</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.590568285707493</v>
+        <v>-3.612154791234255</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.324705765613764</v>
+        <v>1.316071163403059</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7077698744102632</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.198903332172725</v>
+        <v>3.185951428856668</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.619601390409794</v>
+        <v>-3.641187895936557</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.313644396765945</v>
+        <v>1.30500979455524</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.7077698744102632</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.199455205205827</v>
+        <v>3.186503301889769</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.526790908958935</v>
+        <v>-3.548377414485698</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.280041281237655</v>
+        <v>1.27140667902695</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8221668613878851</v>
+        <v>0.8005803558611225</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.184414185967708</v>
+        <v>3.171462282651651</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.571180378288362</v>
+        <v>-3.592766883815125</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.264158969430484</v>
+        <v>1.255524367219779</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7777773920584574</v>
+        <v>0.7561908865316949</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159653980294652</v>
+        <v>3.146702076978594</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.550676684402865</v>
+        <v>-3.572263189929628</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.267436155496406</v>
+        <v>1.258801553285701</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.7766945804171922</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.167031905137673</v>
+        <v>3.154080001821616</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.590600778985437</v>
+        <v>-3.6121872845122</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.256957813494045</v>
+        <v>1.24832321128334</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.7766945804171922</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.172523200968341</v>
+        <v>3.159571297652283</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.61838117688679</v>
+        <v>-3.639967682413553</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.257342856102043</v>
+        <v>1.248708253891337</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7705006880426017</v>
+        <v>0.7489141825158392</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.167352163996068</v>
+        <v>3.154400260680011</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.736761849616929</v>
+        <v>-3.758348355143692</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.04834630701064</v>
+        <v>1.039711704799935</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.681696330364863</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.965377172706136</v>
+        <v>2.952425269390078</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.84537592806026</v>
+        <v>-3.866962433587023</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.125050336352514</v>
+        <v>1.116415734141809</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.681696330364863</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.085526833425341</v>
+        <v>3.072574930109284</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.809966889812117</v>
+        <v>-3.83155339533888</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.153726977754094</v>
+        <v>1.145092375543389</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.681696330364863</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.100039859527664</v>
+        <v>3.087087956211607</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.771583227253966</v>
+        <v>-3.793169732780729</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.166499884119723</v>
+        <v>1.157865281909018</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7200799929230142</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.120489498404924</v>
+        <v>3.107537595088866</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.5944668972188</v>
+        <v>-3.616053402745563</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.234075444979091</v>
+        <v>1.225440842768386</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7200799929230142</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.117218527250226</v>
+        <v>3.104266623934168</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.639559142052345</v>
+        <v>-3.661145647579108</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.216721938807586</v>
+        <v>1.208087336596881</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6797704552803869</v>
+        <v>0.6581839497536244</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.080764293110505</v>
+        <v>3.067812389794447</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.460183720813578</v>
+        <v>-3.48177022634034</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.282259082609508</v>
+        <v>1.273624480398803</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8365472134511056</v>
+        <v>0.8149607079243431</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.16861732331935</v>
+        <v>3.155665420003293</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.505197934334184</v>
+        <v>-3.526784439860946</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.245060852532855</v>
+        <v>1.23642625032215</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.806198318136501</v>
+        <v>0.7846118126097384</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.131215441462177</v>
+        <v>3.11826353814612</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.772202444606619</v>
+        <v>-3.793788950133382</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.143950610762827</v>
+        <v>1.135316008552121</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6118352800935525</v>
+        <v>0.5902487745667899</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.020289180975354</v>
+        <v>3.007337277659297</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.873400226043792</v>
+        <v>-3.894986731570555</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.102675420084459</v>
+        <v>1.094040817873754</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5218399610214708</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.978447814744664</v>
+        <v>2.965495911428607</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.866889259429479</v>
+        <v>-3.888475764956242</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.102879768284501</v>
+        <v>1.094245166073796</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5218399610214708</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.976047776298981</v>
+        <v>2.963095872982923</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.847851131722182</v>
+        <v>-3.869437637248945</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.107019738575665</v>
+        <v>1.098385136364959</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.4636563496902762</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.937662328708509</v>
+        <v>2.924710425392451</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.900366933997002</v>
+        <v>-3.921953439523765</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.205307819299927</v>
+        <v>1.196673217089222</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.4636563496902762</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.056956730342699</v>
+        <v>3.044004827026642</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.903775245431582</v>
+        <v>-3.925361750958344</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.204777823712229</v>
+        <v>1.196143221501524</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.4961729186996536</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.077300000734459</v>
+        <v>3.064348097418402</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.884419109537735</v>
+        <v>-3.906005615064498</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.218528808466693</v>
+        <v>1.209894206255988</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.4961729186996536</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.083308531131385</v>
+        <v>3.070356627815328</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.736676139302733</v>
+        <v>-3.938624709473244</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.175576217837894</v>
+        <v>1.094796789769689</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.5363094269259173</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.081943166749515</v>
+        <v>2.992388754028285</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.820497360577431</v>
+        <v>-4.022445930747942</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.144841350859495</v>
+        <v>1.064061922791291</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.5363094269259173</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.084736788280996</v>
+        <v>2.995182375559766</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.814344654524646</v>
+        <v>-4.016293224695158</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.147964781672268</v>
+        <v>1.067185353604063</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6917194875140836</v>
+        <v>0.5424621329787016</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.089090760304325</v>
+        <v>2.999536347583095</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.831153952675148</v>
+        <v>-4.03310252284566</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.140321539152177</v>
+        <v>1.059542111083972</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.674910189363582</v>
+        <v>0.5256528348281999</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.078085658154134</v>
+        <v>2.988531245432904</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.768855953899026</v>
+        <v>-3.970804524069538</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.231576292459447</v>
+        <v>1.150796864391242</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7202044536380241</v>
+        <v>0.570947099102642</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.17159777051562</v>
+        <v>3.082043357794391</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.567065756233868</v>
+        <v>-3.76901432640438</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.114584373239637</v>
+        <v>1.033804945171432</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9182226458071785</v>
+        <v>0.7689652912717964</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.09270068753124</v>
+        <v>3.00314627481001</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.617952468920063</v>
+        <v>-3.819901039090575</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.164519920487334</v>
+        <v>1.08374049241913</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.867335933120984</v>
+        <v>0.7180785785856019</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.132458892241698</v>
+        <v>3.042904479520469</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.531341726270255</v>
+        <v>-3.733290296440767</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.213791953663301</v>
+        <v>1.133012525595096</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9459616643261423</v>
+        <v>0.7967043097907601</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.194262067080837</v>
+        <v>3.104707654359607</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.59155102427554</v>
+        <v>-3.793499594446052</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.188244215285859</v>
+        <v>1.107464787217654</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.7364950117854756</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.156672469102338</v>
+        <v>3.067118056381108</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.542364375591188</v>
+        <v>-3.7443129457617</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.206410492799528</v>
+        <v>1.125631064731323</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.7364950117854756</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.155164087142266</v>
+        <v>3.065609674421037</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.49799124395262</v>
+        <v>-3.699939814123132</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.224022612890391</v>
+        <v>1.143243184822187</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9301254979594263</v>
+        <v>0.7808681434240442</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.181650833560844</v>
+        <v>3.092096420839614</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.520471594811505</v>
+        <v>-3.722420164982017</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.209424266685428</v>
+        <v>1.128644838617223</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9301254979594263</v>
+        <v>0.7808681434240442</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.176044627699434</v>
+        <v>3.086490214978205</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.472815864250449</v>
+        <v>-3.674764434420961</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.234868315937655</v>
+        <v>1.15408888786945</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.977781228520482</v>
+        <v>0.8285238739850999</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.211019823063872</v>
+        <v>3.121465410342643</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.372297705751694</v>
+        <v>-3.574246275922206</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.279967952711882</v>
+        <v>1.199188524643677</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.078299387019237</v>
+        <v>0.9290420324838544</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.27622309153785</v>
+        <v>3.18666867881662</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.356392376319342</v>
+        <v>-3.558340946489854</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.273084756960695</v>
+        <v>1.19230532889249</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9991867263099976</v>
+        <v>0.8499293717746155</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.215510167588179</v>
+        <v>3.125955754866949</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.311553974710943</v>
+        <v>-3.513502544881456</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.295117820214683</v>
+        <v>1.214338392146478</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.003730159254867</v>
+        <v>0.8544728047194849</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.222333929965729</v>
+        <v>3.132779517244499</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.331052430952952</v>
+        <v>-3.533001001123464</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.291479377348958</v>
+        <v>1.210699949280753</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9556455179749628</v>
+        <v>0.8063881634395806</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.197644084828864</v>
+        <v>3.108089672107635</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.286849593867051</v>
+        <v>-3.488798164037564</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.315040114711155</v>
+        <v>1.23426068664295</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9998483550608632</v>
+        <v>0.8505910005254811</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.230045389608242</v>
+        <v>3.140490976887012</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.294409259704098</v>
+        <v>-3.496357829874611</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.310426248845584</v>
+        <v>1.229646820777379</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.054651759070683</v>
+        <v>0.9053944045353004</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.261337432483381</v>
+        <v>3.171783019762151</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.136117842164826</v>
+        <v>-3.338066412335338</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.424990581044332</v>
+        <v>1.344211152976127</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.054651759070683</v>
+        <v>0.9053944045353004</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.31258519766642</v>
+        <v>3.223030784945191</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.92847583853035</v>
+        <v>-3.130424408700862</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.506488087092376</v>
+        <v>1.425708659024171</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.262293762705159</v>
+        <v>1.113036408169777</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.435611104441359</v>
+        <v>3.34605669172013</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.86448984247514</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.877443745807822</v>
+        <v>-3.079392315978334</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.521849152419657</v>
+        <v>1.441069724351452</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.313325855427687</v>
+        <v>1.164068500892304</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.461178588313146</v>
+        <v>3.371624175591917</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.812219564680616</v>
+        <v>-3.014168134851128</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.565126228963244</v>
+        <v>1.484346800895039</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.378550036554892</v>
+        <v>1.22929268201951</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.517500501082174</v>
+        <v>3.427946088360945</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.774792544609482</v>
+        <v>-2.976741114779994</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.576058009290978</v>
+        <v>1.495278581222773</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.383801574584074</v>
+        <v>1.234544220048692</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.516612396198964</v>
+        <v>3.427057983477734</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.79490420064419</v>
+        <v>-2.996852770814703</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.569270139208335</v>
+        <v>1.48849071114013</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.394828919581493</v>
+        <v>1.245571565046111</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.524485595528656</v>
+        <v>3.434931182807426</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.82866144563629</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.766490937544307</v>
+        <v>-2.968439507714819</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.741193215469499</v>
+        <v>1.660413787401295</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.335853356835065</v>
+        <v>1.186596002299682</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.649658028902009</v>
+        <v>3.56010361618078</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.691708676519294</v>
+        <v>-2.893657246689807</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.891219029097322</v>
+        <v>1.810439601029117</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.410635617860077</v>
+        <v>1.261378263324695</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.814640294734834</v>
+        <v>3.725085882013604</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.665624592255486</v>
+        <v>-2.867573162425999</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.893360638816704</v>
+        <v>1.812581210748499</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.410635617860077</v>
+        <v>1.261378263324695</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.806348270748693</v>
+        <v>3.716793858027463</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.577746679146366</v>
+        <v>-2.779695249316878</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.926704999644132</v>
+        <v>1.845925571575927</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.526561260283428</v>
+        <v>1.377303905748046</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.874096851786483</v>
+        <v>3.784542439065254</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.568854217753082</v>
+        <v>-2.770802787923595</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.947816389928236</v>
+        <v>1.867036961860031</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.526561260283428</v>
+        <v>1.377303905748046</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.891651257513274</v>
+        <v>3.802096844792045</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.73733033472296</v>
+        <v>-2.939278904893472</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.872280990544869</v>
+        <v>1.791501562476664</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.498613424566847</v>
+        <v>1.349356070031465</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.86673760348791</v>
+        <v>3.777183190766681</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.29107414209352</v>
+        <v>-2.493022712264032</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.032053164784507</v>
+        <v>1.951273736716302</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.403894754897215</v>
+        <v>1.254637400361832</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.791176098873992</v>
+        <v>3.701621686152762</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.268353038410368</v>
+        <v>-2.47030160858088</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.031805628754673</v>
+        <v>1.951026200686468</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.403894754897215</v>
+        <v>1.254637400361832</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.781840121370896</v>
+        <v>3.692285708649667</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.39755485170441</v>
+        <v>-2.599503421874922</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.139031029288224</v>
+        <v>2.05825160122002</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.274692941603172</v>
+        <v>1.12543558706779</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.86322515924564</v>
+        <v>3.773670746524411</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.423429250178436</v>
+        <v>-2.625377820348948</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.165759092392261</v>
+        <v>2.084979664324056</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.319604550314914</v>
+        <v>1.170347195779531</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.927249946966332</v>
+        <v>3.837695534245102</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.416374559963262</v>
+        <v>-2.618323130133775</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.165256324467876</v>
+        <v>2.08447689639967</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.326659240530087</v>
+        <v>1.177401885994705</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.928158117084981</v>
+        <v>3.838603704363751</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.389423335636774</v>
+        <v>-2.591371905807287</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.186042967843212</v>
+        <v>2.105263539775007</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.341539586557807</v>
+        <v>1.192282232022424</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.947092478346354</v>
+        <v>3.857538065625125</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.4493305673114</v>
+        <v>-2.612916133638074</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.346183207318322</v>
+        <v>2.280748980787652</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.341539586557807</v>
+        <v>1.192282232022424</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.131195610491313</v>
+        <v>4.041641197770084</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.471738685116272</v>
+        <v>-2.635324251442946</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.329336655099366</v>
+        <v>2.263902428568696</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.341539586557807</v>
+        <v>1.192282232022424</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.123312305394307</v>
+        <v>4.033757892673077</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.499962920693873</v>
+        <v>-2.663548487020546</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.320100960417963</v>
+        <v>2.254666733887293</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.359516339009115</v>
+        <v>1.210258984473733</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.13615235641473</v>
+        <v>4.0465979436935</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.509403846582403</v>
+        <v>-2.672989412909076</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.372578307784398</v>
+        <v>2.307144081253729</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.481943456552507</v>
+        <v>1.332686102017124</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.265862344662612</v>
+        <v>4.176307931941382</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.598280477750877</v>
+        <v>-2.76186604407755</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33991874986231</v>
+        <v>2.27448452333164</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.393066825384033</v>
+        <v>1.24380947084865</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.215427460506828</v>
+        <v>4.125873047785599</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.674610455351782</v>
+        <v>-2.838196021678456</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.307498571715723</v>
+        <v>2.242064345185053</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.393066825384033</v>
+        <v>1.24380947084865</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.213539273400603</v>
+        <v>4.123984860679374</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.768274400029324</v>
+        <v>-2.931859966355997</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.264853223447568</v>
+        <v>2.199418996916899</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.299402880706491</v>
+        <v>1.150145526171109</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.15216113619694</v>
+        <v>4.062606723475711</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.929842825556579</v>
+        <v>-3.093428391883252</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.198659863446818</v>
+        <v>2.133225636916149</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.172619956908612</v>
+        <v>1.02336260237323</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.074525392128366</v>
+        <v>3.984970979407136</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.038143487426698</v>
+        <v>-3.201729053753372</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.168413005564689</v>
+        <v>2.10297877903402</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.172619956908612</v>
+        <v>1.02336260237323</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.087598798994284</v>
+        <v>3.998044386273055</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.055947459147442</v>
+        <v>-3.219533025474116</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.153296613659331</v>
+        <v>2.087862387128662</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.102085334003411</v>
+        <v>0.9528279794680286</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.037283222034104</v>
+        <v>3.947728809312874</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.083848246256915</v>
+        <v>-3.247433812583589</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.140660339942544</v>
+        <v>2.075226113411875</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.067488409860476</v>
+        <v>0.9182310553250937</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.015049108675345</v>
+        <v>3.925494695954115</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.206374348959809</v>
+        <v>-3.369959915286483</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.088414342838585</v>
+        <v>2.022980116307916</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9449623071575823</v>
+        <v>0.7957049526221999</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.938297891030807</v>
+        <v>3.848743478309578</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.436888845145398</v>
+        <v>-3.600474411472072</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.062914503954854</v>
+        <v>1.997480277424184</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7144478109719936</v>
+        <v>0.5651904564366111</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.866695152909958</v>
+        <v>3.777140740188728</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.785633930369841</v>
+        <v>-3.949219496696515</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.063728188866923</v>
+        <v>1.998293962336254</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.4564425025177133</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.941758099560466</v>
+        <v>3.852203686839236</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.939620348145982</v>
+        <v>-4.103205914472656</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.071113890902107</v>
+        <v>2.005679664371438</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.4564425025177133</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.010738368706106</v>
+        <v>3.921183955984876</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.144219783008991</v>
+        <v>-4.307805349335665</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.975325319077025</v>
+        <v>1.909891092546355</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.4564425025177133</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.996789570826227</v>
+        <v>3.907235158104997</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.396694937016715</v>
+        <v>-4.501597014514519</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.886205746529349</v>
+        <v>1.844244915530227</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.4564425025177133</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.008660059881641</v>
+        <v>3.919105647160411</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973161</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.689590693496127</v>
+        <v>-4.794492770993931</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.770257978456528</v>
+        <v>1.728297147457406</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.4564425025177133</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.009870594400584</v>
+        <v>3.920316181679355</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.876254821630935</v>
+        <v>-4.981156899128739</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.699714069429926</v>
+        <v>1.657753238430804</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5789608862285359</v>
+        <v>0.4297035316931535</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.99794895413317</v>
+        <v>3.90839454141194</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.022275508544897</v>
+        <v>-5.127177586042701</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.63638364740053</v>
+        <v>1.594422816401409</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5698777944346789</v>
+        <v>0.4206204398992965</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.987576951793045</v>
+        <v>3.898022539071815</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830331</v>
+        <v>3.667962306830333</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.113989517654483</v>
+        <v>-5.218891595152286</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.76190210045574</v>
+        <v>1.719941269456619</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5698777944346789</v>
+        <v>0.4206204398992965</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.149781008492089</v>
+        <v>4.060226595770859</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071555</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.145641176714452</v>
+        <v>-5.250543254212255</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.744088074795567</v>
+        <v>1.702127243796446</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5647093371902387</v>
+        <v>0.4154519826548563</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.141526572109239</v>
+        <v>4.05197215938801</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868151</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.227575994983336</v>
+        <v>-5.332478072481138</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.721543565056504</v>
+        <v>1.679582734057383</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5547745916031586</v>
+        <v>0.4055172370677761</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.145795142325482</v>
+        <v>4.056240729604252</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.329552117231743</v>
+        <v>-5.434454194729546</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.689678754613044</v>
+        <v>1.647717923613923</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.452798469354751</v>
+        <v>0.3035411148193685</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.09353510743234</v>
+        <v>4.00398069471111</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.219545833754522</v>
+        <v>-5.324447911252324</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.725834155248108</v>
+        <v>1.683873324248987</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4760030412720262</v>
+        <v>0.3267456867366437</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.099610737826881</v>
+        <v>4.010056325105651</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.076486258013595</v>
+        <v>-5.181388335511398</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.787307996266453</v>
+        <v>1.745347165267332</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4840164678620055</v>
+        <v>0.334759113326623</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.108668804502843</v>
+        <v>4.019114391781613</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.775039532541758</v>
+        <v>-4.879941610039561</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.915147569337724</v>
+        <v>1.873186738338602</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.6362058387984603</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.29679772266848</v>
+        <v>4.207243309947251</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.799629776776942</v>
+        <v>-4.904531854274745</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.906282649396361</v>
+        <v>1.86432181839724</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.6362058387984603</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.297768900421191</v>
+        <v>4.208214487699962</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.748591400770422</v>
+        <v>-4.853493478268224</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.927540904178724</v>
+        <v>1.885580073179603</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.6362058387984603</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.298611804800947</v>
+        <v>4.209057392079718</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.707452105903791</v>
+        <v>-4.812354183401593</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.963034720999522</v>
+        <v>1.921073890000401</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8266024882004736</v>
+        <v>0.6773451336650911</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.34233348059507</v>
+        <v>4.252779067873841</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.610817193885151</v>
+        <v>-4.715719271382953</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.817872681930913</v>
+        <v>1.775911850931791</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9232374002191135</v>
+        <v>0.773980045683731</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.216498423930189</v>
+        <v>4.12694401120896</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.741397928415993</v>
+        <v>-4.846300005913796</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.76914243219254</v>
+        <v>1.727181601193419</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.792656665688271</v>
+        <v>0.6433993111528885</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.141652027285648</v>
+        <v>4.052097614564419</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833461</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.576901594225031</v>
+        <v>-4.681803671722834</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.819367784945007</v>
+        <v>1.777406953945886</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9571529998792329</v>
+        <v>0.8078956453438504</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.224776646876307</v>
+        <v>4.135222234155078</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.499802992683159</v>
+        <v>-4.604705070180962</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.849394935998186</v>
+        <v>1.807434104999065</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9571529998792329</v>
+        <v>0.8078956453438504</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.223964357312737</v>
+        <v>4.134409944591508</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147911</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.510188187573048</v>
+        <v>-4.615090265070851</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.855109637167303</v>
+        <v>1.813148806168182</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9467678049893435</v>
+        <v>0.7975104504539611</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.227602019503876</v>
+        <v>4.138047606782647</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.528776346295273</v>
+        <v>-4.633678423793076</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.918511379454838</v>
+        <v>1.876550548455717</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9281796462671181</v>
+        <v>0.7789222917317358</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.287286130046966</v>
+        <v>4.197731717325737</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.529074892991309</v>
+        <v>-4.633976970489112</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.915260971594722</v>
+        <v>1.873300140595601</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9278810995710822</v>
+        <v>0.7786237450356999</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.283976012847643</v>
+        <v>4.194421600126414</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.428251759300881</v>
+        <v>-4.533153836798684</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.960121120010284</v>
+        <v>1.918160289011163</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9403453150554361</v>
+        <v>0.7910879605200537</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.295985437077647</v>
+        <v>4.206431024356418</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.237470398548474</v>
+        <v>-4.342372476046277</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.03656291778979</v>
+        <v>1.994602086790669</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.131126675807844</v>
+        <v>0.9818693212724611</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.410583507007635</v>
+        <v>4.321029094286405</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.130507040699053</v>
+        <v>-4.235409118196856</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.059185106667155</v>
+        <v>2.017224275668035</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.189591283767645</v>
+        <v>1.040333929232263</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.425499117521112</v>
+        <v>4.335944704799883</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.07517645279729</v>
+        <v>-4.180078530295093</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.116284278439919</v>
+        <v>2.074323447440798</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.244921871669407</v>
+        <v>1.095664517134025</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.493664406874228</v>
+        <v>4.404109994152998</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.063122325884327</v>
+        <v>-4.16802440338213</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.114792497106542</v>
+        <v>2.072831666107421</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.25697599858237</v>
+        <v>1.107718644046987</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.494583450923443</v>
+        <v>4.405029038202214</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.104277445452548</v>
+        <v>-4.209179522950351</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.100211079463389</v>
+        <v>2.058250248464268</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.215820879014149</v>
+        <v>1.066563524478767</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.471771009366647</v>
+        <v>4.382216596645417</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.036228882761018</v>
+        <v>-4.141130960258821</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.140281530417884</v>
+        <v>2.098320699418763</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.283869441705679</v>
+        <v>1.134612087170296</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.525451172859447</v>
+        <v>4.435896760138217</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001343</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.267829275930519</v>
+        <v>-4.372731353428322</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.067844043323678</v>
+        <v>2.025883212324556</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.283869441705679</v>
+        <v>1.134612087170296</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.545653843033041</v>
+        <v>4.456099430311811</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.317880821459738</v>
+        <v>-4.422782898957541</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.031429661178872</v>
+        <v>1.989468830179751</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.283869441705679</v>
+        <v>1.134612087170296</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.529260079099923</v>
+        <v>4.439705666378694</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.492987654036183</v>
+        <v>-4.597889731533986</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.921638841741761</v>
+        <v>1.87967801074264</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.283869441705679</v>
+        <v>1.134612087170296</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.48951199269339</v>
+        <v>4.39995757997216</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.29688750060566</v>
+        <v>-4.401789578103463</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.00710152211091</v>
+        <v>1.965140691111789</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.479969595136202</v>
+        <v>1.330712240600819</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.614194703748644</v>
+        <v>4.524640291027413</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.143862108492375</v>
+        <v>-4.248764185990178</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.167482678529129</v>
+        <v>2.125521847530007</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.632994987249486</v>
+        <v>1.483737632714103</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.805180938589518</v>
+        <v>4.715626525868289</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.172169422365646</v>
+        <v>-4.277071499863449</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.343625977888113</v>
+        <v>2.301665146888991</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.632994987249486</v>
+        <v>1.483737632714103</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.992647163497811</v>
+        <v>4.903092750776581</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.338762647479168</v>
+        <v>-4.443664724976971</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.246391639196786</v>
+        <v>2.204430808197665</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.466401762135963</v>
+        <v>1.317144407600581</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.86209417978378</v>
+        <v>4.77253976706255</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.315726854117602</v>
+        <v>-4.420628931615405</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.25928235920313</v>
+        <v>2.217321528204009</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.466401762135963</v>
+        <v>1.317144407600581</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.865770582445498</v>
+        <v>4.776216169724268</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.286480873661906</v>
+        <v>-4.391382951159708</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.268598806508904</v>
+        <v>2.226637975509783</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.466401762135963</v>
+        <v>1.317144407600581</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.863388637568993</v>
+        <v>4.773834224847763</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.393406421539757</v>
+        <v>-4.498308499037559</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.223121826515399</v>
+        <v>2.181160995516278</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.359476214258112</v>
+        <v>1.21021885972273</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.796526547999917</v>
+        <v>4.706972135278687</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.538424980047005</v>
+        <v>-4.643327057544808</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.166543205255733</v>
+        <v>2.124582374256613</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.214457655750864</v>
+        <v>1.065200301215481</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.710944215038802</v>
+        <v>4.621389802317572</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687017</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.656766745831723</v>
+        <v>-4.761668823329526</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.219137738199599</v>
+        <v>2.177176907200479</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.225143694313754</v>
+        <v>1.075886339778371</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.817287077434289</v>
+        <v>4.727732664713059</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790805</v>
+        <v>3.714879051790807</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.708177168152431</v>
+        <v>-4.813079245650234</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.196359266397255</v>
+        <v>2.154398435398134</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.225143694313754</v>
+        <v>1.075886339778371</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.815072774560227</v>
+        <v>4.725518361838998</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.787596619360182</v>
+        <v>-4.892498696857985</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.164494613988444</v>
+        <v>2.122533782989323</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.225143694313754</v>
+        <v>1.075886339778371</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.814975902634517</v>
+        <v>4.725421489913288</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.7368049522984</v>
+        <v>3.736804952298402</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.8830596172774</v>
+        <v>-4.987961694775203</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.1263033083796</v>
+        <v>2.084342477380479</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.225143694313754</v>
+        <v>1.075886339778371</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.81496979619256</v>
+        <v>4.725415383471331</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218003</v>
+        <v>3.715372960218005</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.818683706426685</v>
+        <v>-4.923585783924488</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.150150069282497</v>
+        <v>2.108189238283376</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.289519605164469</v>
+        <v>1.140262250629086</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.8516917392656</v>
+        <v>4.762137326544371</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353539</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.874052868558879</v>
+        <v>-4.978954946056682</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.133736222177346</v>
+        <v>2.091775391178225</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.289519605164469</v>
+        <v>1.140262250629086</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.857425557013327</v>
+        <v>4.767871144292098</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113282</v>
+        <v>3.736822870113284</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.919490648389706</v>
+        <v>-5.024392725887509</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.115099473587947</v>
+        <v>2.073138642588826</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.246674614486309</v>
+        <v>1.097417259950927</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.831256925949363</v>
+        <v>4.741702513228134</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113691</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.831283814242128</v>
+        <v>-4.936185891739931</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.170256600097297</v>
+        <v>2.128295769098176</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.246674614486309</v>
+        <v>1.097417259950927</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.851131318799682</v>
+        <v>4.761576906078453</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.725248819036818</v>
+        <v>-4.830150896534621</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.196371298704149</v>
+        <v>2.154410467705028</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.246674614486309</v>
+        <v>1.097417259950927</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.83483201932441</v>
+        <v>4.745277606603181</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.542037155903723</v>
+        <v>-4.646939233401526</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.272086913421433</v>
+        <v>2.230126082422311</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.246674614486309</v>
+        <v>1.097417259950927</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.837262968788456</v>
+        <v>4.747708556067226</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.470315708889872</v>
+        <v>-4.575217786387675</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.266566678074862</v>
+        <v>2.224605847075741</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.31839606150016</v>
+        <v>1.169138706964778</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.846087022844656</v>
+        <v>4.756532610123426</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.447942683282166</v>
+        <v>-4.552844760779969</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.222431634239117</v>
+        <v>2.180470803239995</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.329651812613061</v>
+        <v>1.180394458077679</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.799756219433569</v>
+        <v>4.710201806712338</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456734</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.480958979192911</v>
+        <v>-4.585861056690714</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.394423320760174</v>
+        <v>2.352462489761053</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.26021443594631</v>
+        <v>1.110957081410928</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.943291998318872</v>
+        <v>4.853737585597643</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883679</v>
+        <v>3.713762536883681</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.469431343543302</v>
+        <v>-4.574333421041105</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.390955600848267</v>
+        <v>2.348994769849146</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.319215094147672</v>
+        <v>1.16995773961229</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.970613619067939</v>
+        <v>4.88105920634671</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.566772844885671</v>
+        <v>-4.671674922383474</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.355687112833108</v>
+        <v>2.313726281833986</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.274794911982184</v>
+        <v>1.125537557446802</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.947629622290435</v>
+        <v>4.858075209569205</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427687</v>
+        <v>3.705201079427689</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.652628874225638</v>
+        <v>-4.757530951723441</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.322595783289959</v>
+        <v>2.280634952290838</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.232418842756049</v>
+        <v>1.083161488220667</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.923455062947592</v>
+        <v>4.833900650226362</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.661465671641757</v>
+        <v>-4.76636774913956</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.301480266144013</v>
+        <v>2.259519435144892</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.224976670114698</v>
+        <v>1.075719315579316</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.901408961183283</v>
+        <v>4.811854548462054</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.685713444045787</v>
+        <v>-4.857750311705018</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.301945668227451</v>
+        <v>2.233130921163758</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.213457248270222</v>
+        <v>1.039154430859971</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.904661819121647</v>
+        <v>4.800080128675496</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889194</v>
+        <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.674006726058781</v>
+        <v>-4.846043593718012</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.408756613246521</v>
+        <v>2.339941866182829</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.225163966257228</v>
+        <v>1.050861148846978</v>
       </c>
       <c r="G2076" t="n">
-        <v>5.013814107738119</v>
+        <v>4.909232417291968</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940957</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.574343221975118</v>
+        <v>-4.74638008963435</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.451654353611391</v>
+        <v>2.382839606547699</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.288351049460915</v>
+        <v>1.114048232050664</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.054758696391736</v>
+        <v>4.950177005945585</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.58465932014147</v>
+        <v>-4.756696187800702</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.660432747622909</v>
+        <v>2.591618000559216</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.288351049460915</v>
+        <v>1.114048232050664</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.267663529669794</v>
+        <v>5.163081839223643</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.584565352124097</v>
+        <v>-4.756602219783329</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.659649001741947</v>
+        <v>2.590834254678255</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.288720910808233</v>
+        <v>1.114418093397982</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.267064113390274</v>
+        <v>5.162482422944124</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988022</v>
+        <v>3.633213467988024</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.591784176323942</v>
+        <v>-4.763821043983174</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.650993458006363</v>
+        <v>2.582178710942671</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.288720910808233</v>
+        <v>1.114418093397982</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.261296099334628</v>
+        <v>5.156714408888478</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.590835753205903</v>
+        <v>-4.762872620865135</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.651372827253579</v>
+        <v>2.582558080189886</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.288720910808233</v>
+        <v>1.114418093397982</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.261296099334628</v>
+        <v>5.156714408888478</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.747904211461528</v>
+        <v>-4.919941079120759</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.601273051932421</v>
+        <v>2.532458304868729</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.288720910808233</v>
+        <v>1.114418093397982</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.27402370731572</v>
+        <v>5.16944201686957</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.741911964672716</v>
+        <v>-4.913948832331948</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.605615949072334</v>
+        <v>2.536801202008641</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.288720910808233</v>
+        <v>1.114418093397982</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.275969705740108</v>
+        <v>5.171388015293958</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.653354003541948</v>
+        <v>-4.82539087120118</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.634693269542409</v>
+        <v>2.565878522478717</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.288720910808233</v>
+        <v>1.114418093397982</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.269623841757877</v>
+        <v>5.165042151311726</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.635594926038874</v>
+        <v>-4.807631793698106</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.641105577982635</v>
+        <v>2.572290830918942</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.288720910808233</v>
+        <v>1.114418093397982</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.268932519196873</v>
+        <v>5.164350828750722</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720998</v>
       </c>
       <c r="C2086" t="n">
         <v>4.508482158620519</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.499416549600062</v>
+        <v>-4.671453417259294</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.708359114466746</v>
+        <v>2.639544367403054</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.424899287247044</v>
+        <v>1.250596469836794</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.363421730968746</v>
+        <v>5.258840040522596</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.82438859753036</v>
+        <v>3.496003654737977</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.699003337426498</v>
+        <v>4.513789695718962</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.499416549600062</v>
+        <v>-4.482571499866944</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.708359114466746</v>
+        <v>2.720404671458436</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.424899287247044</v>
+        <v>1.300478704022527</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.692067134412865</v>
+        <v>5.294076918132478</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240914.xlsx
+++ b/tame_output/ON/bt/strategyON_20240914.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>121.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-604.1%</t>
+          <t>-592.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.9%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-609.8%</t>
+          <t>-602.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-242.0%</t>
+          <t>-237.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-31.5%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>126.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-104.2%</t>
+          <t>-101.1%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-225.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-324.0%</t>
+          <t>-317.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-93.9%</t>
+          <t>-83.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>115.3%</t>
+          <t>117.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-136.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-21.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>106.8%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>89.6%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.190379852557369</v>
+        <v>-4.072007669735402</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.447563168694089</v>
+        <v>1.494912041822876</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.05393984927578033</v>
+        <v>-0.02590386077084567</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>3.108529217568277</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.425073846689921</v>
+        <v>-4.306701663867955</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.341970346043158</v>
+        <v>1.389319219171945</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.04760358204652515</v>
+        <v>-0.01956759354159049</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.08379415980496</v>
+        <v>3.10061575290792</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.760736493920374</v>
+        <v>-4.642364311098407</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.206285878806943</v>
+        <v>1.25363475193573</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.11553456753543</v>
+        <v>-0.08749857903049529</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.041616160167582</v>
+        <v>3.058437753270543</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.837180824123245</v>
+        <v>-4.718808641301279</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.182195706960036</v>
+        <v>1.229544580088823</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.03508905844176807</v>
+        <v>-0.007053069936833412</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.096371025858021</v>
+        <v>3.113192618960981</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.202308206761992</v>
+        <v>-5.083936023940026</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.035399268910368</v>
+        <v>1.082748142039155</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.3033638542358459</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.934660663387405</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.610896983942671</v>
+        <v>-5.492524801120704</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8707253020528558</v>
+        <v>0.9180741751816428</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7119526314165243</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.688268941093757</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.724657395965536</v>
+        <v>-5.606285213143568</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8204065697151703</v>
+        <v>0.8677554428439578</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7119526314165243</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.683454373565218</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.141049270252533</v>
+        <v>-6.022677087430566</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6518438706092486</v>
+        <v>0.6991927437380361</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7119526314165243</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.681448424174095</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.502222900069521</v>
+        <v>-6.383850717247554</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5176331093511326</v>
+        <v>0.56498198247992</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7119526314165243</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.691707114842774</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.84548141971254</v>
+        <v>-6.727109236890572</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3764292666396201</v>
+        <v>0.4237781397684075</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7119526314165243</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.68780667998847</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.893684236954884</v>
+        <v>-6.775312054132916</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3555530597976837</v>
+        <v>0.4029019329264707</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.7119526314165243</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.686211600043471</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.060492896929246</v>
+        <v>-6.942120714107278</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2926085717371469</v>
+        <v>0.3399574448659344</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.7542359551296609</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.647798988641836</v>
+        <v>2.664620581744797</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.247212605238548</v>
+        <v>-7.128840422416581</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2138943838790226</v>
+        <v>0.26124325700781</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.7542359551296609</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.643772684107433</v>
+        <v>2.660594277210393</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.630213993981179</v>
+        <v>-7.511841811159212</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.06059172706038618</v>
+        <v>0.1079406001891736</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.7542359551296609</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.643670582785849</v>
+        <v>2.660492175888809</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.634700439182568</v>
+        <v>-7.516328256360601</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.06136866495126103</v>
+        <v>0.108717538080048</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.7867583888359841</v>
+        <v>-0.7587224003310495</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.643550231636446</v>
+        <v>2.660371824739407</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.99423076168657</v>
+        <v>-7.875858578864602</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.07709316075228934</v>
+        <v>-0.02974428762350234</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.7867583888359841</v>
+        <v>-0.7587224003310495</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.648900534934496</v>
+        <v>2.665722128037457</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.04457982514079</v>
+        <v>-7.926207642318825</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.0893167661768004</v>
+        <v>-0.0419678930480134</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8371074522902062</v>
+        <v>-0.8090714637852716</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.62660711681914</v>
+        <v>2.643428709922101</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.142199102562186</v>
+        <v>-8.023826919740221</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1253227265235899</v>
+        <v>-0.07797385339480334</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9347267297116029</v>
+        <v>-0.9066907412066683</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.571077300988071</v>
+        <v>2.587898894091032</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.196270602070545</v>
+        <v>-8.07789841924858</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1440577700053614</v>
+        <v>-0.0967088968765748</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9887982292199623</v>
+        <v>-0.9607622407150277</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.541527957604627</v>
+        <v>2.558349550707588</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.199846388162292</v>
+        <v>-8.081474205340328</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1399748873234179</v>
+        <v>-0.09262601419463135</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.014327151136455</v>
+        <v>-0.9862911626315203</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.531723801573374</v>
+        <v>2.548545394676335</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.233499226670766</v>
+        <v>-8.115127043848801</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1489534682423712</v>
+        <v>-0.1016045951135847</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.114740519053492</v>
+        <v>-1.086704530548558</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.475958335307588</v>
+        <v>2.492779928410549</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.372585341289623</v>
+        <v>-8.254213158467659</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1892162125964933</v>
+        <v>-0.1418673394677068</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.253826633672349</v>
+        <v>-1.225790645167415</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.407878368029695</v>
+        <v>2.424699961132656</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.547709758676167</v>
+        <v>-8.429337575854202</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2447107588035937</v>
+        <v>-0.1973618856748072</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.428951051058893</v>
+        <v>-1.400915062553958</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.317358938345286</v>
+        <v>2.334180531448246</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.782161852690656</v>
+        <v>-8.663789669868692</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3457107613109858</v>
+        <v>-0.2983618881821992</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.428951051058893</v>
+        <v>-1.400915062553958</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.310139773443689</v>
+        <v>2.32696136654665</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.886536583717103</v>
+        <v>-8.768164400895138</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3941328444955405</v>
+        <v>-0.346783971366754</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.533325782085339</v>
+        <v>-1.505289793580404</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.240842744053846</v>
+        <v>2.257664337156807</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.049050049415687</v>
+        <v>-8.930677866593722</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4580224409364178</v>
+        <v>-0.4106735678076312</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.630959212504025</v>
+        <v>-1.602923223999091</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.18337847564119</v>
+        <v>2.200200068744151</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.175086842783976</v>
+        <v>-9.056714659962012</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5057434296546188</v>
+        <v>-0.4583945565258323</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.577671601189349</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.20122317795615</v>
+        <v>2.218044771059111</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.118015070888045</v>
+        <v>-8.999642888066081</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4789243852098455</v>
+        <v>-0.4315755120810589</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.577671601189349</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.205213513642551</v>
+        <v>2.222035106745512</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.259686912612166</v>
+        <v>-9.141314729790201</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5370683487982353</v>
+        <v>-0.4897194756694487</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.577671601189349</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.20373828674381</v>
+        <v>2.22055987984677</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.210096068187331</v>
+        <v>-9.091723885365367</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5021786008634295</v>
+        <v>-0.4548297277346429</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.556116745269449</v>
+        <v>-1.528080756764515</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.248546203563582</v>
+        <v>2.265367796666543</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.061177733715475</v>
+        <v>-8.94280555089351</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4556624007213697</v>
+        <v>-0.4083135275925831</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.524867154534276</v>
+        <v>-1.496831166029342</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.254244824358003</v>
+        <v>2.271066417460963</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.835332580996065</v>
+        <v>-8.716960398174098</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3557452665973972</v>
+        <v>-0.3083963934686098</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.454904490442178</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.28897990274651</v>
+        <v>2.305801495849471</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.710753924658473</v>
+        <v>-8.592381741836506</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3047746595063017</v>
+        <v>-0.2574257863775142</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.454904490442178</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.290119047302569</v>
+        <v>2.306940640405529</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.685717243089963</v>
+        <v>-8.567345060267996</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2921262127167896</v>
+        <v>-0.2447773395880026</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.429575402891442</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.307950273995118</v>
+        <v>2.324771867098078</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.613584067802082</v>
+        <v>-8.495211884980115</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2575392383630009</v>
+        <v>-0.2101903652342134</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.429575402891442</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.313683978233754</v>
+        <v>2.330505571336715</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.542217675192434</v>
+        <v>-8.447508310933992</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.238729943713007</v>
+        <v>-0.2008461980096294</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.381871828845319</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.346766551405678</v>
+        <v>2.349390453370524</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.44875864120721</v>
+        <v>-8.354049276948768</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2112298114318247</v>
+        <v>-0.1733460657284476</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.381871828845319</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.33688307009277</v>
+        <v>2.339506972057616</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.438105459653778</v>
+        <v>-8.343396095395336</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2088030993098262</v>
+        <v>-0.1709193536064486</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.381871828845319</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.335048509593396</v>
+        <v>2.337672411558242</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.340198420977288</v>
+        <v>-8.245489056718846</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1699405988126905</v>
+        <v>-0.1320568531093129</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.318259248926172</v>
+        <v>-1.313886078984762</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37553964453627</v>
+        <v>2.378163546501115</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.31624488000133</v>
+        <v>-8.221535515742888</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.159690676276814</v>
+        <v>-0.1218069305734364</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.294305707950215</v>
+        <v>-1.289932538008805</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.390580275267338</v>
+        <v>2.393204177232183</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.052184941678533</v>
+        <v>-7.957475577420092</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.06732701710944733</v>
+        <v>-0.02944327140607017</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.025872599686009</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.535755922099263</v>
+        <v>2.538379824064109</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.345105318173695</v>
+        <v>-7.250395953915254</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2127177986321871</v>
+        <v>0.2506015443355643</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.025872599686009</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.532968888438962</v>
+        <v>2.535592790403808</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.304921019807504</v>
+        <v>-7.210211655549063</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2291351418665046</v>
+        <v>0.2670188875698818</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9900614712612278</v>
+        <v>-0.9856883013198178</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.557423091346518</v>
+        <v>2.560046993311364</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.141521148868142</v>
+        <v>-7.046811784609701</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2938619114630066</v>
+        <v>0.3317456571663837</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8266616003218653</v>
+        <v>-0.8222884303804553</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.654829835130893</v>
+        <v>2.657453737095739</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.908039926638543</v>
+        <v>-6.813330562380102</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3951788291926985</v>
+        <v>0.4330625748960757</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5931803780922668</v>
+        <v>-0.5888072081508567</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.802842997306504</v>
+        <v>2.80546689927135</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.758373535631028</v>
+        <v>-6.663664171372587</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4521531752827452</v>
+        <v>0.4900369209861224</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5002768868497308</v>
+        <v>-0.4959037169083208</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855692881739067</v>
+        <v>2.858316783703912</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.626098062000142</v>
+        <v>-6.531388697741701</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4063241507422544</v>
+        <v>0.4442078964456315</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3680014132188442</v>
+        <v>-0.3636282432774341</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.836318951924753</v>
+        <v>2.838942853889599</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.454236846435239</v>
+        <v>-6.359527482176798</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4778836976558525</v>
+        <v>0.5157674433592296</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1961401976539413</v>
+        <v>-0.1917670277125313</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.942250741951332</v>
+        <v>2.944874643916178</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.36927217970592</v>
+        <v>-6.274562815447478</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.5247759055712389</v>
+        <v>0.562659651274616</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1111755309246217</v>
+        <v>-0.1068023609832117</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.006135883212582</v>
+        <v>3.008759785177428</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.474862169479024</v>
+        <v>-6.380152805220582</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3545639800627782</v>
+        <v>0.3924477257661558</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2167655206977261</v>
+        <v>-0.2123923507563161</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.814805959749501</v>
+        <v>2.817429861714347</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.406627584853597</v>
+        <v>-6.311918220595155</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4304021557900355</v>
+        <v>0.4682859014934131</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1983501978251901</v>
+        <v>-0.1939770278837801</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.874399495350109</v>
+        <v>2.877023397314955</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.258687543445998</v>
+        <v>-6.163978179187556</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3729573637146681</v>
+        <v>0.4108411094180457</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1780292819166325</v>
+        <v>-0.1736561119752225</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769971236256836</v>
+        <v>2.772595138221682</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.205718021192009</v>
+        <v>-6.111008656933567</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3854311863627853</v>
+        <v>0.4233149320661629</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1206865897212336</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793038963355751</v>
+        <v>2.795662865320597</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.039929825231718</v>
+        <v>-5.945220460973276</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4447858526518087</v>
+        <v>0.4826695983551863</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1206865897212336</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786078351260658</v>
+        <v>2.788702253225504</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.00656661875295</v>
+        <v>-5.911857254494508</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4725934896244595</v>
+        <v>0.5104772353278366</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1206865897212336</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800540705641801</v>
+        <v>2.803164607606647</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.898307481630428</v>
+        <v>-5.803598117371986</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5104292649326632</v>
+        <v>0.5483130106360403</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1206865897212336</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795072826100996</v>
+        <v>2.797696728065842</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.775016346813297</v>
+        <v>-5.680306982554855</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5572438128700923</v>
+        <v>0.5951275585734699</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.001768624845513156</v>
+        <v>0.00260454509589686</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866545601001851</v>
+        <v>2.869169502966697</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.722319479682006</v>
+        <v>-5.627610115423564</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5860235379599339</v>
+        <v>0.6239072836633115</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.05530141222718804</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.905864699517951</v>
+        <v>2.908488601482797</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.478554037698562</v>
+        <v>-5.38384467344012</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6793104231003624</v>
+        <v>0.71719416880374</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.05530141222718804</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.901645407865002</v>
+        <v>2.904269309829848</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.388778365322089</v>
+        <v>-5.294069001063647</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7173450059709672</v>
+        <v>0.7552287516743448</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1169008571414981</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.940729388733604</v>
+        <v>2.94335329069845</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.138927971373015</v>
+        <v>-5.044218607114573</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8100272385342993</v>
+        <v>0.8479109842376769</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1169008571414981</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.933471463717306</v>
+        <v>2.936095365682152</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.963035878905583</v>
+        <v>-4.868326514647141</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8839831990419207</v>
+        <v>0.9218669447452983</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.112527687200088</v>
+        <v>0.1169008571414981</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.937070587237955</v>
+        <v>2.939694489202801</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.791589415883119</v>
+        <v>-4.696880051624677</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9658892903054599</v>
+        <v>1.003773036008837</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2839741502225512</v>
+        <v>0.2883473201639612</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053265971105986</v>
+        <v>3.055889873070833</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.711567128773998</v>
+        <v>-4.616857764515556</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9969186827654051</v>
+        <v>1.034802428468783</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3639964373316721</v>
+        <v>0.3683696072730822</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100299820987756</v>
+        <v>3.102923722952602</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.669517892066827</v>
+        <v>-4.553222022281622</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.018433178502591</v>
+        <v>1.064951526416674</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4060456740388441</v>
+        <v>0.4320053495070167</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.130224164066377</v>
+        <v>3.14579996934728</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074784</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.575820573850431</v>
+        <v>-4.459524704065227</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.037106364572945</v>
+        <v>1.083624712487028</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4060456740388441</v>
+        <v>0.4320053495070167</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.111418422850172</v>
+        <v>3.126994228131076</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.58632319691572</v>
+        <v>-4.470027327130516</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.034648391971707</v>
+        <v>1.081166739885789</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3955430509735552</v>
+        <v>0.4215027264417278</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.106859925635876</v>
+        <v>3.12243573091678</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.473836936246846</v>
+        <v>-4.357541066461641</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.083572210074077</v>
+        <v>1.130090557988159</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3955430509735552</v>
+        <v>0.4215027264417278</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.110789239470696</v>
+        <v>3.1263650447516</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.45612324936898</v>
+        <v>-4.339827379583776</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.091336268742563</v>
+        <v>1.137854616656645</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.398724379870472</v>
+        <v>0.4246840553386446</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.113376620726187</v>
+        <v>3.12895242600709</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.332648978055962</v>
+        <v>-4.216353108270757</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.137724048487764</v>
+        <v>1.184242396401846</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.398724379870472</v>
+        <v>0.4246840553386446</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.11037469194618</v>
+        <v>3.125950497227084</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.112628180018952</v>
+        <v>-3.996332310233746</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.227311404713182</v>
+        <v>1.273829752627265</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5399442249384523</v>
+        <v>0.5659039004066249</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.196685635997582</v>
+        <v>3.212261441278486</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.979760490955674</v>
+        <v>-3.863464621170468</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.296352663140316</v>
+        <v>1.342871011054399</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5399442249384523</v>
+        <v>0.5659039004066249</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.212579818799405</v>
+        <v>3.228155624080309</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.859587407591174</v>
+        <v>-3.74329153780597</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.345567740926418</v>
+        <v>1.392086088840501</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6601173083029512</v>
+        <v>0.6860769837711238</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.285829513258407</v>
+        <v>3.30140531853931</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.724334046261197</v>
+        <v>-3.608038176475993</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.409757188019849</v>
+        <v>1.456275535933931</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7953706696329284</v>
+        <v>0.8213303451011009</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.377069632617833</v>
+        <v>3.392645437898736</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.78420887361889</v>
+        <v>-3.667913003833685</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.371844748478197</v>
+        <v>1.41836309639228</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7354958422752362</v>
+        <v>0.7614555177434088</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.327182227604643</v>
+        <v>3.342758032885547</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.664388642708052</v>
+        <v>-3.548092772922848</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.435062010076741</v>
+        <v>1.481580357990824</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7354958422752362</v>
+        <v>0.7614555177434088</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.342471396838852</v>
+        <v>3.358047202119756</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.666858349169858</v>
+        <v>-3.550562479384654</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.34171832681446</v>
+        <v>1.388236674728543</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.73302613581343</v>
+        <v>0.7589858112816026</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.24863377228421</v>
+        <v>3.264209577565113</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.735228535493868</v>
+        <v>-3.618932665708663</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.233632113770158</v>
+        <v>1.28015046168424</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.742301834849645</v>
+        <v>0.7682615103178175</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.17346105319124</v>
+        <v>3.189036858472144</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.847100815120019</v>
+        <v>-3.730804945334814</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.179319910551589</v>
+        <v>1.225838258465671</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.742301834849645</v>
+        <v>0.7682615103178175</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.163897761823131</v>
+        <v>3.179473567104035</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.902620891012608</v>
+        <v>-3.786325021227404</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.294142716886755</v>
+        <v>1.340661064800838</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.742301834849645</v>
+        <v>0.7682615103178175</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.300928598515334</v>
+        <v>3.316504403796237</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.727146631220139</v>
+        <v>-3.610850761434934</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.368899652795531</v>
+        <v>1.415418000709613</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.742301834849645</v>
+        <v>0.7682615103178175</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.305495830507121</v>
+        <v>3.321071635788025</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.719222256635225</v>
+        <v>-3.60292638685002</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.347811431390703</v>
+        <v>1.394329779304786</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.742301834849645</v>
+        <v>0.7682615103178175</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.281237859268328</v>
+        <v>3.296813664549232</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.712944054065376</v>
+        <v>-3.596648184280171</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.278861025820093</v>
+        <v>1.325379373734175</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.748580037419494</v>
+        <v>0.7745397128876665</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.213543094211688</v>
+        <v>3.229118899492591</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.653091434861653</v>
+        <v>-3.536795565076448</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.312974459933715</v>
+        <v>1.359492807847797</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.748580037419494</v>
+        <v>0.7745397128876665</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.22371548064382</v>
+        <v>3.239291285924724</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.566847971835275</v>
+        <v>-3.450552102050071</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.342418115718126</v>
+        <v>1.388936463632208</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.748580037419494</v>
+        <v>0.7745397128876665</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.218661751217681</v>
+        <v>3.234237556498584</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.612154791234255</v>
+        <v>-3.495858921449051</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.316071163403059</v>
+        <v>1.362589511317142</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7077698744102632</v>
+        <v>0.7337295498784357</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.185951428856668</v>
+        <v>3.201527234137571</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.641187895936557</v>
+        <v>-3.524892026151352</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.30500979455524</v>
+        <v>1.351528142469323</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7077698744102632</v>
+        <v>0.7337295498784357</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.186503301889769</v>
+        <v>3.202079107170673</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.548377414485698</v>
+        <v>-3.432081544700493</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.27140667902695</v>
+        <v>1.317925026941032</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8005803558611225</v>
+        <v>0.8265400313292951</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.171462282651651</v>
+        <v>3.187038087932554</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.592766883815125</v>
+        <v>-3.47647101402992</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.255524367219779</v>
+        <v>1.302042715133862</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7561908865316949</v>
+        <v>0.7821505619998674</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.146702076978594</v>
+        <v>3.162277882259498</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.572263189929628</v>
+        <v>-3.455967320144423</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.258801553285701</v>
+        <v>1.305319901199784</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7766945804171922</v>
+        <v>0.8026542558853648</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.154080001821616</v>
+        <v>3.16965580710252</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.6121872845122</v>
+        <v>-3.495891414726995</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.24832321128334</v>
+        <v>1.294841559197422</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7766945804171922</v>
+        <v>0.8026542558853648</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.159571297652283</v>
+        <v>3.175147102933187</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.639967682413553</v>
+        <v>-3.523671812628348</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.248708253891337</v>
+        <v>1.29522660180542</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7489141825158392</v>
+        <v>0.7748738579840118</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.154400260680011</v>
+        <v>3.169976065960914</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.758348355143692</v>
+        <v>-3.642052485358487</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.039711704799935</v>
+        <v>1.086230052714018</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.681696330364863</v>
+        <v>0.7076560058330356</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.952425269390078</v>
+        <v>2.968001074670982</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.866962433587023</v>
+        <v>-3.750666563801818</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.116415734141809</v>
+        <v>1.162934082055891</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.681696330364863</v>
+        <v>0.7076560058330356</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.072574930109284</v>
+        <v>3.088150735390187</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.83155339533888</v>
+        <v>-3.715257525553675</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.145092375543389</v>
+        <v>1.191610723457471</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.681696330364863</v>
+        <v>0.7076560058330356</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.087087956211607</v>
+        <v>3.10266376149251</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.793169732780729</v>
+        <v>-3.676873862995524</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.157865281909018</v>
+        <v>1.204383629823101</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7200799929230142</v>
+        <v>0.7460396683911867</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.107537595088866</v>
+        <v>3.12311340036977</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.616053402745563</v>
+        <v>-3.499757532960358</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.225440842768386</v>
+        <v>1.271959190682469</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7200799929230142</v>
+        <v>0.7460396683911867</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.104266623934168</v>
+        <v>3.119842429215072</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.661145647579108</v>
+        <v>-3.544849777793903</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.208087336596881</v>
+        <v>1.254605684510964</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6581839497536244</v>
+        <v>0.6841436252217969</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.067812389794447</v>
+        <v>3.083388195075351</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.48177022634034</v>
+        <v>-3.365474356555135</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.273624480398803</v>
+        <v>1.320142828312885</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8149607079243431</v>
+        <v>0.8409203833925156</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.155665420003293</v>
+        <v>3.171241225284196</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.526784439860946</v>
+        <v>-3.410488570075742</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.23642625032215</v>
+        <v>1.282944598236233</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7846118126097384</v>
+        <v>0.810571488077911</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.11826353814612</v>
+        <v>3.133839343427023</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.793788950133382</v>
+        <v>-3.677493080348177</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.135316008552121</v>
+        <v>1.181834356466204</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5902487745667899</v>
+        <v>0.6162084500349625</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.007337277659297</v>
+        <v>3.0229130829402</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.894986731570555</v>
+        <v>-3.77869086178535</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.094040817873754</v>
+        <v>1.140559165787836</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5218399610214708</v>
+        <v>0.5477996364896434</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.965495911428607</v>
+        <v>2.98107171670951</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.888475764956242</v>
+        <v>-3.772179895171037</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.094245166073796</v>
+        <v>1.140763513987878</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5218399610214708</v>
+        <v>0.5477996364896434</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.963095872982923</v>
+        <v>2.978671678263827</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.869437637248945</v>
+        <v>-3.75314176746374</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.098385136364959</v>
+        <v>1.144903484279042</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4636563496902762</v>
+        <v>0.4896160251584488</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.924710425392451</v>
+        <v>2.940286230673355</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.921953439523765</v>
+        <v>-3.80565756973856</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.196673217089222</v>
+        <v>1.243191565003305</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4636563496902762</v>
+        <v>0.4896160251584488</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.044004827026642</v>
+        <v>3.059580632307545</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.925361750958344</v>
+        <v>-3.80906588117314</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.196143221501524</v>
+        <v>1.242661569415606</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4961729186996536</v>
+        <v>0.5221325941678262</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.064348097418402</v>
+        <v>3.079923902699305</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.906005615064498</v>
+        <v>-3.789709745279293</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.209894206255988</v>
+        <v>1.256412554170071</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4961729186996536</v>
+        <v>0.5221325941678262</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.070356627815328</v>
+        <v>3.085932433096231</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.938624709473244</v>
+        <v>-3.641966775044291</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.094796789769689</v>
+        <v>1.213459963541271</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5363094269259173</v>
+        <v>0.6899399514027094</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.992388754028285</v>
+        <v>3.084567068714361</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.022445930747942</v>
+        <v>-3.725787996318989</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.064061922791291</v>
+        <v>1.182725096562873</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5363094269259173</v>
+        <v>0.6899399514027094</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.995182375559766</v>
+        <v>3.087360690245842</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.016293224695158</v>
+        <v>-3.719635290266204</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.067185353604063</v>
+        <v>1.185848527375645</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5424621329787016</v>
+        <v>0.6960926574554936</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.999536347583095</v>
+        <v>3.09171466226917</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.03310252284566</v>
+        <v>-3.736444588416706</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.059542111083972</v>
+        <v>1.178205284855555</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5256528348281999</v>
+        <v>0.6792833593049921</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.988531245432904</v>
+        <v>3.08070956011898</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.970804524069538</v>
+        <v>-3.674146589640584</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.150796864391242</v>
+        <v>1.269460038162824</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.570947099102642</v>
+        <v>0.7245776235794341</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.082043357794391</v>
+        <v>3.174221672480466</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.76901432640438</v>
+        <v>-3.472356391975426</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.033804945171432</v>
+        <v>1.152468118943015</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7689652912717964</v>
+        <v>0.9225958157485885</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.00314627481001</v>
+        <v>3.095324589496085</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.819901039090575</v>
+        <v>-3.523243104661621</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.08374049241913</v>
+        <v>1.202403666190712</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7180785785856019</v>
+        <v>0.871709103062394</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.042904479520469</v>
+        <v>3.135082794206544</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.733290296440767</v>
+        <v>-3.436632362011813</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.133012525595096</v>
+        <v>1.251675699366678</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7967043097907601</v>
+        <v>0.9503348342675523</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.104707654359607</v>
+        <v>3.196885969045683</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.793499594446052</v>
+        <v>-3.496841660017098</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.107464787217654</v>
+        <v>1.226127960989236</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7364950117854756</v>
+        <v>0.8901255362622678</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.067118056381108</v>
+        <v>3.159296371067184</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.7443129457617</v>
+        <v>-3.447655011332746</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.125631064731323</v>
+        <v>1.244294238502905</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7364950117854756</v>
+        <v>0.8901255362622678</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.065609674421037</v>
+        <v>3.157787989107112</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.699939814123132</v>
+        <v>-3.403281879694178</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.143243184822187</v>
+        <v>1.261906358593769</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7808681434240442</v>
+        <v>0.9344986679008364</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.092096420839614</v>
+        <v>3.18427473552569</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.722420164982017</v>
+        <v>-3.425762230553063</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.128644838617223</v>
+        <v>1.247308012388806</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7808681434240442</v>
+        <v>0.9344986679008364</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.086490214978205</v>
+        <v>3.17866852966428</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.674764434420961</v>
+        <v>-3.378106499992007</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.15408888786945</v>
+        <v>1.272752061641033</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8285238739850999</v>
+        <v>0.982154398461892</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.121465410342643</v>
+        <v>3.213643725028718</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.574246275922206</v>
+        <v>-3.277588341493252</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.199188524643677</v>
+        <v>1.317851698415259</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9290420324838544</v>
+        <v>1.082672556960647</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.18666867881662</v>
+        <v>3.278846993502696</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.558340946489854</v>
+        <v>-3.2616830120609</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.19230532889249</v>
+        <v>1.310968502664072</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8499293717746155</v>
+        <v>1.003559896251408</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.125955754866949</v>
+        <v>3.218134069553025</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.513502544881456</v>
+        <v>-3.216844610452501</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.214338392146478</v>
+        <v>1.33300156591806</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8544728047194849</v>
+        <v>1.008103329196277</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.132779517244499</v>
+        <v>3.224957831930575</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.533001001123464</v>
+        <v>-3.23634306669451</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.210699949280753</v>
+        <v>1.329363123052335</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8063881634395806</v>
+        <v>0.9600186879163728</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.108089672107635</v>
+        <v>3.20026798679371</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.488798164037564</v>
+        <v>-3.192140229608609</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.23426068664295</v>
+        <v>1.352923860414532</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8505910005254811</v>
+        <v>1.004221525002273</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.140490976887012</v>
+        <v>3.232669291573087</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.496357829874611</v>
+        <v>-3.199699895445656</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.229646820777379</v>
+        <v>1.348309994548961</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9053944045353004</v>
+        <v>1.059024929012093</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.171783019762151</v>
+        <v>3.263961334448227</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.338066412335338</v>
+        <v>-3.041408477906384</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.344211152976127</v>
+        <v>1.46287432674771</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9053944045353004</v>
+        <v>1.059024929012093</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.223030784945191</v>
+        <v>3.315209099631266</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.130424408700862</v>
+        <v>-2.833766474271908</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.425708659024171</v>
+        <v>1.544371832795753</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.113036408169777</v>
+        <v>1.266666932646569</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.34605669172013</v>
+        <v>3.438235006406205</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.86448984247514</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.079392315978334</v>
+        <v>-2.78273438154938</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.441069724351452</v>
+        <v>1.559732898123035</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.164068500892304</v>
+        <v>1.317699025369097</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.371624175591917</v>
+        <v>3.463802490277992</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.014168134851128</v>
+        <v>-2.717510200422174</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.484346800895039</v>
+        <v>1.603009974666622</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.22929268201951</v>
+        <v>1.382923206496302</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.427946088360945</v>
+        <v>3.52012440304702</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.976741114779994</v>
+        <v>-2.68008318035104</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.495278581222773</v>
+        <v>1.613941754994356</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.234544220048692</v>
+        <v>1.388174744525484</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.427057983477734</v>
+        <v>3.51923629816381</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992663</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.996852770814703</v>
+        <v>-2.700194836385748</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.48849071114013</v>
+        <v>1.607153884911713</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.245571565046111</v>
+        <v>1.399202089522903</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.434931182807426</v>
+        <v>3.527109497493502</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563629</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.968439507714819</v>
+        <v>-2.671781573285865</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.660413787401295</v>
+        <v>1.779076961172877</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.186596002299682</v>
+        <v>1.340226526776475</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.56010361618078</v>
+        <v>3.652281930866855</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957629</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.893657246689807</v>
+        <v>-2.596999312260852</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.810439601029117</v>
+        <v>1.929102774800699</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.261378263324695</v>
+        <v>1.415008787801487</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.725085882013604</v>
+        <v>3.81726419669968</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.867573162425999</v>
+        <v>-2.570915227997044</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.812581210748499</v>
+        <v>1.931244384520081</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.261378263324695</v>
+        <v>1.415008787801487</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.716793858027463</v>
+        <v>3.808972172713539</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.779695249316878</v>
+        <v>-2.483037314887924</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.845925571575927</v>
+        <v>1.964588745347509</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.377303905748046</v>
+        <v>1.530934430224838</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.784542439065254</v>
+        <v>3.876720753751329</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.770802787923595</v>
+        <v>-2.47414485349464</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.867036961860031</v>
+        <v>1.985700135631614</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.377303905748046</v>
+        <v>1.530934430224838</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.802096844792045</v>
+        <v>3.89427515947812</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.939278904893472</v>
+        <v>-2.642620970464518</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.791501562476664</v>
+        <v>1.910164736248247</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.349356070031465</v>
+        <v>1.502986594508257</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.777183190766681</v>
+        <v>3.869361505452756</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.493022712264032</v>
+        <v>-2.196364777835078</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.951273736716302</v>
+        <v>2.069936910487884</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.254637400361832</v>
+        <v>1.408267924838625</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.701621686152762</v>
+        <v>3.793800000838838</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.47030160858088</v>
+        <v>-2.173643674151926</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.951026200686468</v>
+        <v>2.06968937445805</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.254637400361832</v>
+        <v>1.408267924838625</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.692285708649667</v>
+        <v>3.784464023335742</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.599503421874922</v>
+        <v>-2.302845487445968</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.05825160122002</v>
+        <v>2.176914774991602</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.12543558706779</v>
+        <v>1.279066111544582</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.773670746524411</v>
+        <v>3.865849061210486</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.625377820348948</v>
+        <v>-2.328719885919994</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.084979664324056</v>
+        <v>2.203642838095639</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.170347195779531</v>
+        <v>1.323977720256324</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.837695534245102</v>
+        <v>3.929873848931178</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.618323130133775</v>
+        <v>-2.32166519570482</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.08447689639967</v>
+        <v>2.203140070171253</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.177401885994705</v>
+        <v>1.331032410471497</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.838603704363751</v>
+        <v>3.930782019049827</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.591371905807287</v>
+        <v>-2.294713971378332</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.105263539775007</v>
+        <v>2.223926713546589</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.192282232022424</v>
+        <v>1.345912756499217</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.857538065625125</v>
+        <v>3.9497163803112</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.612916133638074</v>
+        <v>-2.316258199209119</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.280748980787652</v>
+        <v>2.399412154559235</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.192282232022424</v>
+        <v>1.345912756499217</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.041641197770084</v>
+        <v>4.13381951245616</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.635324251442946</v>
+        <v>-2.338666317013991</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.263902428568696</v>
+        <v>2.382565602340279</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.192282232022424</v>
+        <v>1.345912756499217</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.033757892673077</v>
+        <v>4.125936207359153</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.663548487020546</v>
+        <v>-2.366890552591592</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.254666733887293</v>
+        <v>2.373329907658876</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.210258984473733</v>
+        <v>1.363889508950525</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.0465979436935</v>
+        <v>4.138776258379576</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.672989412909076</v>
+        <v>-2.376331478480122</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.307144081253729</v>
+        <v>2.425807255025311</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.332686102017124</v>
+        <v>1.486316626493917</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.176307931941382</v>
+        <v>4.268486246627457</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.76186604407755</v>
+        <v>-2.465208109648596</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.27448452333164</v>
+        <v>2.393147697103223</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.24380947084865</v>
+        <v>1.397439995325443</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.125873047785599</v>
+        <v>4.218051362471674</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.838196021678456</v>
+        <v>-2.541538087249501</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.242064345185053</v>
+        <v>2.360727518956636</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.24380947084865</v>
+        <v>1.397439995325443</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.123984860679374</v>
+        <v>4.216163175365449</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.931859966355997</v>
+        <v>-2.635202031927043</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.199418996916899</v>
+        <v>2.318082170688482</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.150145526171109</v>
+        <v>1.303776050647901</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.062606723475711</v>
+        <v>4.154785038161787</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.093428391883252</v>
+        <v>-2.796770457454298</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.133225636916149</v>
+        <v>2.251888810687731</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.02336260237323</v>
+        <v>1.176993126850022</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.984970979407136</v>
+        <v>4.077149294093211</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.201729053753372</v>
+        <v>-2.905071119324417</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.10297877903402</v>
+        <v>2.221641952805602</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.02336260237323</v>
+        <v>1.176993126850022</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.998044386273055</v>
+        <v>4.09022270095913</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.219533025474116</v>
+        <v>-2.922875091045162</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.087862387128662</v>
+        <v>2.206525560900245</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9528279794680286</v>
+        <v>1.106458503944821</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.947728809312874</v>
+        <v>4.039907123998949</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.247433812583589</v>
+        <v>-2.950775878154634</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.075226113411875</v>
+        <v>2.193889287183457</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9182310553250937</v>
+        <v>1.071861579801886</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.925494695954115</v>
+        <v>4.01767301064019</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.369959915286483</v>
+        <v>-3.073301980857528</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.022980116307916</v>
+        <v>2.141643290079498</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7957049526221999</v>
+        <v>0.9493354770989924</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.848743478309578</v>
+        <v>3.940921792995653</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.600474411472072</v>
+        <v>-3.303816477043117</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.997480277424184</v>
+        <v>2.116143451195767</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5651904564366111</v>
+        <v>0.7188209809134036</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.777140740188728</v>
+        <v>3.869319054874803</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.949219496696515</v>
+        <v>-3.652561562267561</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.998293962336254</v>
+        <v>2.116957136107836</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4564425025177133</v>
+        <v>0.6100730269945058</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.852203686839236</v>
+        <v>3.944382001525311</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.103205914472656</v>
+        <v>-3.806547980043701</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.005679664371438</v>
+        <v>2.12434283814302</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4564425025177133</v>
+        <v>0.6100730269945058</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.921183955984876</v>
+        <v>4.013362270670951</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.307805349335665</v>
+        <v>-4.01114741490671</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.909891092546355</v>
+        <v>2.028554266317937</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4564425025177133</v>
+        <v>0.6100730269945058</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.907235158104997</v>
+        <v>3.999413472791073</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.501597014514519</v>
+        <v>-4.263622568914434</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.844244915530227</v>
+        <v>1.939434693770262</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4564425025177133</v>
+        <v>0.6100730269945058</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.919105647160411</v>
+        <v>4.011283961846487</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973161</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.794492770993931</v>
+        <v>-4.556518325393847</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.728297147457406</v>
+        <v>1.82348692569744</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4564425025177133</v>
+        <v>0.6100730269945058</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.920316181679355</v>
+        <v>4.01249449636543</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.981156899128739</v>
+        <v>-4.743182453528655</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.657753238430804</v>
+        <v>1.752943016670839</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4297035316931535</v>
+        <v>0.5833340561699459</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.90839454141194</v>
+        <v>4.000572856098016</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.127177586042701</v>
+        <v>-4.889203140442617</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.594422816401409</v>
+        <v>1.689612594641443</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4206204398992965</v>
+        <v>0.5742509643760889</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.898022539071815</v>
+        <v>3.990200853757891</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830333</v>
+        <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.218891595152286</v>
+        <v>-4.980917149552202</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.719941269456619</v>
+        <v>1.815131047696654</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4206204398992965</v>
+        <v>0.5742509643760889</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.060226595770859</v>
+        <v>4.152404910456935</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071555</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.250543254212255</v>
+        <v>-5.012568808612171</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.702127243796446</v>
+        <v>1.79731702203648</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4154519826548563</v>
+        <v>0.5690825071316488</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.05197215938801</v>
+        <v>4.144150474074085</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868151</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.332478072481138</v>
+        <v>-5.094503626881054</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.679582734057383</v>
+        <v>1.774772512297418</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4055172370677761</v>
+        <v>0.5591477615445686</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.056240729604252</v>
+        <v>4.148419044290328</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.434454194729546</v>
+        <v>-5.196479749129462</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.647717923613923</v>
+        <v>1.742907701853957</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3035411148193685</v>
+        <v>0.457171639296161</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.00398069471111</v>
+        <v>4.096159009397186</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.324447911252324</v>
+        <v>-5.08647346565224</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.683873324248987</v>
+        <v>1.779063102489021</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.3267456867366437</v>
+        <v>0.4803762112134362</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.010056325105651</v>
+        <v>4.102234639791726</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.181388335511398</v>
+        <v>-4.943413889911314</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.745347165267332</v>
+        <v>1.840536943507366</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.334759113326623</v>
+        <v>0.4883896378034155</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.019114391781613</v>
+        <v>4.111292706467689</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.879941610039561</v>
+        <v>-4.641967164439476</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.873186738338602</v>
+        <v>1.968376516578637</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6362058387984603</v>
+        <v>0.7898363632752528</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.207243309947251</v>
+        <v>4.299421624633327</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.904531854274745</v>
+        <v>-4.66655740867466</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.86432181839724</v>
+        <v>1.959511596637274</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6362058387984603</v>
+        <v>0.7898363632752528</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.208214487699962</v>
+        <v>4.300392802386037</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.853493478268224</v>
+        <v>-4.61551903266814</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.885580073179603</v>
+        <v>1.980769851419637</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6362058387984603</v>
+        <v>0.7898363632752528</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.209057392079718</v>
+        <v>4.301235706765793</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.812354183401593</v>
+        <v>-4.574379737801509</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.921073890000401</v>
+        <v>2.016263668240435</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6773451336650911</v>
+        <v>0.8309756581418836</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.252779067873841</v>
+        <v>4.344957382559917</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700482</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.715719271382953</v>
+        <v>-4.477744825782869</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.775911850931791</v>
+        <v>1.871101629171826</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.773980045683731</v>
+        <v>0.9276105701605235</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.12694401120896</v>
+        <v>4.219122325895035</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.846300005913796</v>
+        <v>-4.608325560313712</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.727181601193419</v>
+        <v>1.822371379433453</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6433993111528885</v>
+        <v>0.797029835629681</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.052097614564419</v>
+        <v>4.144275929250494</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833461</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.681803671722834</v>
+        <v>-4.44382922612275</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.777406953945886</v>
+        <v>1.87259673218592</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8078956453438504</v>
+        <v>0.9615261698206429</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.135222234155078</v>
+        <v>4.227400548841153</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.604705070180962</v>
+        <v>-4.366730624580877</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.807434104999065</v>
+        <v>1.902623883239099</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8078956453438504</v>
+        <v>0.9615261698206429</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.134409944591508</v>
+        <v>4.226588259277583</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147911</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.615090265070851</v>
+        <v>-4.377115819470767</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.813148806168182</v>
+        <v>1.908338584408216</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.7975104504539611</v>
+        <v>0.9511409749307536</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.138047606782647</v>
+        <v>4.230225921468723</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.633678423793076</v>
+        <v>-4.395703978192992</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.876550548455717</v>
+        <v>1.971740326695751</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7789222917317358</v>
+        <v>0.9325528162085281</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.197731717325737</v>
+        <v>4.289910032011812</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.633976970489112</v>
+        <v>-4.396002524889028</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.873300140595601</v>
+        <v>1.968489918835635</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7786237450356999</v>
+        <v>0.9322542695124922</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.194421600126414</v>
+        <v>4.286599914812489</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.533153836798684</v>
+        <v>-4.2951793911986</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.918160289011163</v>
+        <v>2.013350067251197</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.7910879605200537</v>
+        <v>0.9447184849968461</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.206431024356418</v>
+        <v>4.298609339042493</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.342372476046277</v>
+        <v>-4.104398030446193</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.994602086790669</v>
+        <v>2.089791865030704</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9818693212724611</v>
+        <v>1.135499845749254</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.321029094286405</v>
+        <v>4.413207408972481</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.235409118196856</v>
+        <v>-3.997434672596771</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.017224275668035</v>
+        <v>2.112414053908069</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.040333929232263</v>
+        <v>1.193964453709055</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.335944704799883</v>
+        <v>4.428123019485958</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.180078530295093</v>
+        <v>-3.942104084695009</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.074323447440798</v>
+        <v>2.169513225680832</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.095664517134025</v>
+        <v>1.249295041610817</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.404109994152998</v>
+        <v>4.496288308839073</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.16802440338213</v>
+        <v>-3.930049957782046</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.072831666107421</v>
+        <v>2.168021444347455</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.107718644046987</v>
+        <v>1.26134916852378</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.405029038202214</v>
+        <v>4.497207352888289</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.209179522950351</v>
+        <v>-3.971205077350267</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.058250248464268</v>
+        <v>2.153440026704303</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.066563524478767</v>
+        <v>1.220194048955559</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.382216596645417</v>
+        <v>4.474394911331492</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.141130960258821</v>
+        <v>-3.903156514658737</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.098320699418763</v>
+        <v>2.193510477658797</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.134612087170296</v>
+        <v>1.288242611647089</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.435896760138217</v>
+        <v>4.528075074824293</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.372731353428322</v>
+        <v>-4.134756907828239</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.025883212324556</v>
+        <v>2.121072990564591</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.134612087170296</v>
+        <v>1.288242611647089</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.456099430311811</v>
+        <v>4.548277744997887</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.422782898957541</v>
+        <v>-4.184808453357459</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.989468830179751</v>
+        <v>2.084658608419785</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.134612087170296</v>
+        <v>1.288242611647089</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.439705666378694</v>
+        <v>4.531883981064769</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.597889731533986</v>
+        <v>-4.359915285933903</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.87967801074264</v>
+        <v>1.974867788982674</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.134612087170296</v>
+        <v>1.288242611647089</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.39995757997216</v>
+        <v>4.492135894658236</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.401789578103463</v>
+        <v>-4.16381513250338</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.965140691111789</v>
+        <v>2.060330469351823</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.330712240600819</v>
+        <v>1.484342765077612</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.524640291027413</v>
+        <v>4.616818605713489</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.248764185990178</v>
+        <v>-4.010789740390096</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.125521847530007</v>
+        <v>2.220711625770041</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.483737632714103</v>
+        <v>1.637368157190896</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.715626525868289</v>
+        <v>4.807804840554364</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.277071499863449</v>
+        <v>-4.039097054263366</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.301665146888991</v>
+        <v>2.396854925129025</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.483737632714103</v>
+        <v>1.637368157190896</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.903092750776581</v>
+        <v>4.995271065462656</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.443664724976971</v>
+        <v>-4.205690279376888</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.204430808197665</v>
+        <v>2.299620586437698</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.317144407600581</v>
+        <v>1.470774932077373</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.77253976706255</v>
+        <v>4.864718081748626</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.420628931615405</v>
+        <v>-4.182654486015323</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.217321528204009</v>
+        <v>2.312511306444043</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.317144407600581</v>
+        <v>1.470774932077373</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.776216169724268</v>
+        <v>4.868394484410343</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.391382951159708</v>
+        <v>-4.153408505559626</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.226637975509783</v>
+        <v>2.321827753749817</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.317144407600581</v>
+        <v>1.470774932077373</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.773834224847763</v>
+        <v>4.866012539533838</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.498308499037559</v>
+        <v>-4.260334053437477</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.181160995516278</v>
+        <v>2.276350773756311</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.21021885972273</v>
+        <v>1.363849384199522</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.706972135278687</v>
+        <v>4.799150449964763</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.643327057544808</v>
+        <v>-4.405352611944726</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.124582374256613</v>
+        <v>2.219772152496646</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.065200301215481</v>
+        <v>1.218830825692274</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.621389802317572</v>
+        <v>4.713568117003648</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687017</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.761668823329526</v>
+        <v>-4.523694377729443</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.177176907200479</v>
+        <v>2.272366685440512</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.075886339778371</v>
+        <v>1.229516864255164</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.727732664713059</v>
+        <v>4.819910979399135</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790807</v>
+        <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.813079245650234</v>
+        <v>-4.575104800050151</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.154398435398134</v>
+        <v>2.249588213638168</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.075886339778371</v>
+        <v>1.229516864255164</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.725518361838998</v>
+        <v>4.817696676525074</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.892498696857985</v>
+        <v>-4.654524251257903</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.122533782989323</v>
+        <v>2.217723561229357</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.075886339778371</v>
+        <v>1.229516864255164</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.725421489913288</v>
+        <v>4.817599804599364</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298402</v>
+        <v>3.7368049522984</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.987961694775203</v>
+        <v>-4.74998724917512</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.084342477380479</v>
+        <v>2.179532255620513</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.075886339778371</v>
+        <v>1.229516864255164</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.725415383471331</v>
+        <v>4.817593698157407</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218005</v>
+        <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.923585783924488</v>
+        <v>-4.685611338324406</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.108189238283376</v>
+        <v>2.203379016523409</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.140262250629086</v>
+        <v>1.293892775105879</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.762137326544371</v>
+        <v>4.854315641230446</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.978954946056682</v>
+        <v>-4.740980500456599</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.091775391178225</v>
+        <v>2.186965169418259</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.140262250629086</v>
+        <v>1.293892775105879</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.767871144292098</v>
+        <v>4.860049458978173</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113284</v>
+        <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.024392725887509</v>
+        <v>-4.786418280287426</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.073138642588826</v>
+        <v>2.16832842082886</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.097417259950927</v>
+        <v>1.251047784427719</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.741702513228134</v>
+        <v>4.833880827914209</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113691</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.936185891739931</v>
+        <v>-4.698211446139848</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.128295769098176</v>
+        <v>2.22348554733821</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.097417259950927</v>
+        <v>1.251047784427719</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.761576906078453</v>
+        <v>4.853755220764528</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79448684401644</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.830150896534621</v>
+        <v>-4.592176450934539</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.154410467705028</v>
+        <v>2.249600245945062</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.097417259950927</v>
+        <v>1.251047784427719</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.745277606603181</v>
+        <v>4.837455921289256</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.646939233401526</v>
+        <v>-4.408964787801444</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.230126082422311</v>
+        <v>2.325315860662345</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.097417259950927</v>
+        <v>1.251047784427719</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.747708556067226</v>
+        <v>4.839886870753301</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.575217786387675</v>
+        <v>-4.337243340787593</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.224605847075741</v>
+        <v>2.319795625315775</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.169138706964778</v>
+        <v>1.32276923144157</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.756532610123426</v>
+        <v>4.848710924809501</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394116</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.552844760779969</v>
+        <v>-4.314870315179887</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.180470803239995</v>
+        <v>2.275660581480029</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.180394458077679</v>
+        <v>1.334024982554471</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.710201806712338</v>
+        <v>4.802380121398414</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456734</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.585861056690714</v>
+        <v>-4.347886611090631</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.352462489761053</v>
+        <v>2.447652268001087</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.110957081410928</v>
+        <v>1.26458760588772</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.853737585597643</v>
+        <v>4.945915900283719</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883681</v>
+        <v>3.713762536883679</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.574333421041105</v>
+        <v>-4.336358975441023</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.348994769849146</v>
+        <v>2.444184548089179</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.16995773961229</v>
+        <v>1.323588264089082</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.88105920634671</v>
+        <v>4.973237521032785</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.671674922383474</v>
+        <v>-4.433700476783391</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.313726281833986</v>
+        <v>2.40891606007402</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.125537557446802</v>
+        <v>1.279168081923594</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.858075209569205</v>
+        <v>4.950253524255281</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427689</v>
+        <v>3.705201079427687</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.757530951723441</v>
+        <v>-4.519556506123358</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.280634952290838</v>
+        <v>2.375824730530872</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.083161488220667</v>
+        <v>1.236792012697459</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.833900650226362</v>
+        <v>4.926078964912438</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610382</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.76636774913956</v>
+        <v>-4.528393303539477</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.259519435144892</v>
+        <v>2.354709213384926</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.075719315579316</v>
+        <v>1.229349840056108</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.811854548462054</v>
+        <v>4.90403286314813</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166746</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.857750311705018</v>
+        <v>-4.619775866104936</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.233130921163758</v>
+        <v>2.328320699403792</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.039154430859971</v>
+        <v>1.192784955336764</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.800080128675496</v>
+        <v>4.892258443361572</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889196</v>
+        <v>3.673978374889194</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.846043593718012</v>
+        <v>-4.60806914811793</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.339941866182829</v>
+        <v>2.435131644422863</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.050861148846978</v>
+        <v>1.20449167332377</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.909232417291968</v>
+        <v>5.001410731978044</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.68247609940957</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.74638008963435</v>
+        <v>-4.508405644034267</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.382839606547699</v>
+        <v>2.478029384787733</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.114048232050664</v>
+        <v>1.267678756527457</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.950177005945585</v>
+        <v>5.04235532063166</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452574</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.756696187800702</v>
+        <v>-4.518721742200619</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.591618000559216</v>
+        <v>2.68680777879925</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.114048232050664</v>
+        <v>1.267678756527457</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.163081839223643</v>
+        <v>5.255260153909719</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762293</v>
+        <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.756602219783329</v>
+        <v>-4.518627774183247</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.590834254678255</v>
+        <v>2.686024032918288</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.114418093397982</v>
+        <v>1.268048617874775</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.162482422944124</v>
+        <v>5.254660737630199</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988024</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.763821043983174</v>
+        <v>-4.525846598383091</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.582178710942671</v>
+        <v>2.677368489182705</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.114418093397982</v>
+        <v>1.268048617874775</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.156714408888478</v>
+        <v>5.248892723574553</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.762872620865135</v>
+        <v>-4.524898175265053</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.582558080189886</v>
+        <v>2.67774785842992</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.114418093397982</v>
+        <v>1.268048617874775</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.156714408888478</v>
+        <v>5.248892723574553</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.919941079120759</v>
+        <v>-4.681966633520677</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.532458304868729</v>
+        <v>2.627648083108762</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.114418093397982</v>
+        <v>1.268048617874775</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.16944201686957</v>
+        <v>5.261620331555645</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.913948832331948</v>
+        <v>-4.675974386731865</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.536801202008641</v>
+        <v>2.631990980248674</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.114418093397982</v>
+        <v>1.268048617874775</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.171388015293958</v>
+        <v>5.263566329980033</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.82539087120118</v>
+        <v>-4.587416425601098</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.565878522478717</v>
+        <v>2.661068300718751</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.114418093397982</v>
+        <v>1.268048617874775</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.165042151311726</v>
+        <v>5.257220465997801</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.807631793698106</v>
+        <v>-4.569657348098024</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.572290830918942</v>
+        <v>2.667480609158976</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.114418093397982</v>
+        <v>1.268048617874775</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.164350828750722</v>
+        <v>5.256529143436797</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720998</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.508482158620519</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.671453417259294</v>
+        <v>-4.433478971659212</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.639544367403054</v>
+        <v>2.734734145643087</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.250596469836794</v>
+        <v>1.404226994313586</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.258840040522596</v>
+        <v>5.351018355208671</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.496003654737977</v>
+        <v>3.820543704710309</v>
       </c>
       <c r="C2087" t="n">
         <v>4.513789695718962</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.482571499866944</v>
+        <v>-4.405690969875141</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.720404671458436</v>
+        <v>2.751156883455158</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.300478704022527</v>
+        <v>1.404226994313586</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.294076918132478</v>
+        <v>5.356325892307114</v>
       </c>
     </row>
   </sheetData>
